--- a/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
+++ b/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
@@ -16,7 +16,7 @@
     <t>DATA RADAR ANOMALI KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 23 Agu 2026, 12.53</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 23 Agu 2026, 20.23</t>
   </si>
   <si>
     <t>Kode</t>

--- a/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
+++ b/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="309">
   <si>
     <t>DATA RADAR ANOMALI KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 23 Agu 2026, 20.23</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 24 Agu 2026, 07.47</t>
   </si>
   <si>
     <t>Kode</t>
@@ -295,628 +295,625 @@
     <t>LAMPUNG</t>
   </si>
   <si>
+    <t>0,01</t>
+  </si>
+  <si>
+    <t>4,03</t>
+  </si>
+  <si>
+    <t>0,74</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>18,81</t>
+  </si>
+  <si>
+    <t>0,6</t>
+  </si>
+  <si>
+    <t>0,7</t>
+  </si>
+  <si>
+    <t>2,5</t>
+  </si>
+  <si>
+    <t>0,4</t>
+  </si>
+  <si>
+    <t>2,89</t>
+  </si>
+  <si>
+    <t>0,51</t>
+  </si>
+  <si>
+    <t>0,45</t>
+  </si>
+  <si>
+    <t>42,86</t>
+  </si>
+  <si>
+    <t>1,12</t>
+  </si>
+  <si>
+    <t>0,04</t>
+  </si>
+  <si>
+    <t>16,67</t>
+  </si>
+  <si>
+    <t>7,61</t>
+  </si>
+  <si>
+    <t>0,05</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>LAMPUNG BARAT</t>
+  </si>
+  <si>
+    <t>3,62</t>
+  </si>
+  <si>
+    <t>1,03</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>24,68</t>
+  </si>
+  <si>
+    <t>0,71</t>
+  </si>
+  <si>
+    <t>0,13</t>
+  </si>
+  <si>
+    <t>1,65</t>
+  </si>
+  <si>
+    <t>4,2</t>
+  </si>
+  <si>
+    <t>0,1</t>
+  </si>
+  <si>
+    <t>38,42</t>
+  </si>
+  <si>
+    <t>0,55</t>
+  </si>
+  <si>
+    <t>12,25</t>
+  </si>
+  <si>
+    <t>12,28</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>TANGGAMUS</t>
+  </si>
+  <si>
+    <t>4,71</t>
+  </si>
+  <si>
+    <t>18,08</t>
+  </si>
+  <si>
+    <t>0,76</t>
+  </si>
+  <si>
+    <t>1,09</t>
+  </si>
+  <si>
+    <t>4,29</t>
+  </si>
+  <si>
+    <t>3,87</t>
+  </si>
+  <si>
+    <t>0,42</t>
+  </si>
+  <si>
+    <t>0,84</t>
+  </si>
+  <si>
+    <t>41,38</t>
+  </si>
+  <si>
+    <t>0,17</t>
+  </si>
+  <si>
+    <t>0,08</t>
+  </si>
+  <si>
+    <t>22,79</t>
+  </si>
+  <si>
+    <t>0,59</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>LAMPUNG SELATAN</t>
+  </si>
+  <si>
     <t>0,02</t>
   </si>
   <si>
-    <t>4,02</t>
-  </si>
-  <si>
-    <t>0,75</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>18,62</t>
-  </si>
-  <si>
-    <t>0,62</t>
-  </si>
-  <si>
-    <t>0,71</t>
-  </si>
-  <si>
-    <t>2,51</t>
-  </si>
-  <si>
-    <t>0,41</t>
-  </si>
-  <si>
-    <t>2,9</t>
-  </si>
-  <si>
-    <t>0,51</t>
-  </si>
-  <si>
-    <t>0,45</t>
-  </si>
-  <si>
-    <t>42,86</t>
-  </si>
-  <si>
-    <t>1,13</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>16,7</t>
-  </si>
-  <si>
-    <t>7,69</t>
-  </si>
-  <si>
-    <t>0,01</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>LAMPUNG BARAT</t>
-  </si>
-  <si>
-    <t>3,51</t>
-  </si>
-  <si>
-    <t>1,08</t>
-  </si>
-  <si>
-    <t>0,03</t>
-  </si>
-  <si>
-    <t>23,68</t>
-  </si>
-  <si>
-    <t>0,74</t>
-  </si>
-  <si>
-    <t>0,14</t>
-  </si>
-  <si>
-    <t>1,72</t>
-  </si>
-  <si>
-    <t>4,22</t>
-  </si>
-  <si>
-    <t>0,1</t>
-  </si>
-  <si>
-    <t>38,92</t>
+    <t>5,93</t>
+  </si>
+  <si>
+    <t>0,39</t>
+  </si>
+  <si>
+    <t>18,7</t>
+  </si>
+  <si>
+    <t>0,56</t>
+  </si>
+  <si>
+    <t>3,4</t>
+  </si>
+  <si>
+    <t>0,77</t>
+  </si>
+  <si>
+    <t>43,71</t>
+  </si>
+  <si>
+    <t>4,13</t>
+  </si>
+  <si>
+    <t>17,63</t>
+  </si>
+  <si>
+    <t>1,19</t>
+  </si>
+  <si>
+    <t>0,07</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>LAMPUNG TIMUR</t>
+  </si>
+  <si>
+    <t>0,06</t>
+  </si>
+  <si>
+    <t>4,04</t>
+  </si>
+  <si>
+    <t>0,49</t>
+  </si>
+  <si>
+    <t>23,53</t>
+  </si>
+  <si>
+    <t>0,37</t>
+  </si>
+  <si>
+    <t>1,49</t>
+  </si>
+  <si>
+    <t>3,63</t>
+  </si>
+  <si>
+    <t>3,89</t>
+  </si>
+  <si>
+    <t>2,47</t>
+  </si>
+  <si>
+    <t>40,98</t>
+  </si>
+  <si>
+    <t>15,19</t>
+  </si>
+  <si>
+    <t>2,34</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>LAMPUNG TENGAH</t>
+  </si>
+  <si>
+    <t>4,24</t>
+  </si>
+  <si>
+    <t>21,94</t>
+  </si>
+  <si>
+    <t>0,58</t>
+  </si>
+  <si>
+    <t>0,46</t>
+  </si>
+  <si>
+    <t>5,96</t>
+  </si>
+  <si>
+    <t>0,48</t>
+  </si>
+  <si>
+    <t>0,15</t>
+  </si>
+  <si>
+    <t>44,71</t>
+  </si>
+  <si>
+    <t>1,21</t>
+  </si>
+  <si>
+    <t>0,65</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>2,27</t>
+  </si>
+  <si>
+    <t>2,37</t>
+  </si>
+  <si>
+    <t>14,25</t>
+  </si>
+  <si>
+    <t>2,32</t>
+  </si>
+  <si>
+    <t>2,46</t>
+  </si>
+  <si>
+    <t>44,36</t>
+  </si>
+  <si>
+    <t>0,81</t>
+  </si>
+  <si>
+    <t>16,61</t>
+  </si>
+  <si>
+    <t>13,32</t>
+  </si>
+  <si>
+    <t>0,11</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
+    <t>4,33</t>
+  </si>
+  <si>
+    <t>19,87</t>
+  </si>
+  <si>
+    <t>0,47</t>
+  </si>
+  <si>
+    <t>0,5</t>
+  </si>
+  <si>
+    <t>2,97</t>
+  </si>
+  <si>
+    <t>0,27</t>
+  </si>
+  <si>
+    <t>40,27</t>
+  </si>
+  <si>
+    <t>0,33</t>
+  </si>
+  <si>
+    <t>26,63</t>
+  </si>
+  <si>
+    <t>1,3</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG</t>
+  </si>
+  <si>
+    <t>4,39</t>
+  </si>
+  <si>
+    <t>0,79</t>
+  </si>
+  <si>
+    <t>21,18</t>
+  </si>
+  <si>
+    <t>0,94</t>
+  </si>
+  <si>
+    <t>1,22</t>
+  </si>
+  <si>
+    <t>2,2</t>
+  </si>
+  <si>
+    <t>2,01</t>
+  </si>
+  <si>
+    <t>46,24</t>
+  </si>
+  <si>
+    <t>0,09</t>
+  </si>
+  <si>
+    <t>15,61</t>
+  </si>
+  <si>
+    <t>4,63</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PESAWARAN</t>
+  </si>
+  <si>
+    <t>3,24</t>
+  </si>
+  <si>
+    <t>1,17</t>
+  </si>
+  <si>
+    <t>12,85</t>
+  </si>
+  <si>
+    <t>0,69</t>
+  </si>
+  <si>
+    <t>0,93</t>
+  </si>
+  <si>
+    <t>0,92</t>
+  </si>
+  <si>
+    <t>1,16</t>
+  </si>
+  <si>
+    <t>40,38</t>
+  </si>
+  <si>
+    <t>0,88</t>
+  </si>
+  <si>
+    <t>14,91</t>
+  </si>
+  <si>
+    <t>22,63</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>PRINGSEWU</t>
+  </si>
+  <si>
+    <t>4,19</t>
+  </si>
+  <si>
+    <t>0,36</t>
+  </si>
+  <si>
+    <t>13,6</t>
+  </si>
+  <si>
+    <t>4,25</t>
+  </si>
+  <si>
+    <t>0,96</t>
+  </si>
+  <si>
+    <t>1,14</t>
+  </si>
+  <si>
+    <t>3,77</t>
+  </si>
+  <si>
+    <t>2,4</t>
+  </si>
+  <si>
+    <t>41,82</t>
+  </si>
+  <si>
+    <t>1,8</t>
+  </si>
+  <si>
+    <t>0,66</t>
+  </si>
+  <si>
+    <t>17,74</t>
+  </si>
+  <si>
+    <t>3,36</t>
+  </si>
+  <si>
+    <t>0,12</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
+  </si>
+  <si>
+    <t>4,42</t>
+  </si>
+  <si>
+    <t>0,85</t>
+  </si>
+  <si>
+    <t>0,82</t>
+  </si>
+  <si>
+    <t>0,98</t>
+  </si>
+  <si>
+    <t>1,51</t>
+  </si>
+  <si>
+    <t>48,84</t>
+  </si>
+  <si>
+    <t>1,34</t>
+  </si>
+  <si>
+    <t>12,73</t>
+  </si>
+  <si>
+    <t>7,23</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG BARAT</t>
+  </si>
+  <si>
+    <t>4,28</t>
+  </si>
+  <si>
+    <t>0,16</t>
+  </si>
+  <si>
+    <t>18,71</t>
+  </si>
+  <si>
+    <t>1,18</t>
+  </si>
+  <si>
+    <t>0,53</t>
+  </si>
+  <si>
+    <t>0,61</t>
+  </si>
+  <si>
+    <t>1,44</t>
+  </si>
+  <si>
+    <t>45,46</t>
+  </si>
+  <si>
+    <t>0,21</t>
+  </si>
+  <si>
+    <t>24,64</t>
+  </si>
+  <si>
+    <t>1,04</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>PESISIR BARAT</t>
+  </si>
+  <si>
+    <t>4,38</t>
+  </si>
+  <si>
+    <t>26,14</t>
+  </si>
+  <si>
+    <t>3,49</t>
+  </si>
+  <si>
+    <t>42,53</t>
+  </si>
+  <si>
+    <t>16,93</t>
+  </si>
+  <si>
+    <t>4,15</t>
+  </si>
+  <si>
+    <t>1871</t>
+  </si>
+  <si>
+    <t>BANDAR LAMPUNG</t>
+  </si>
+  <si>
+    <t>6,98</t>
+  </si>
+  <si>
+    <t>0,95</t>
+  </si>
+  <si>
+    <t>9,21</t>
+  </si>
+  <si>
+    <t>0,63</t>
+  </si>
+  <si>
+    <t>6,51</t>
+  </si>
+  <si>
+    <t>2,54</t>
+  </si>
+  <si>
+    <t>7,14</t>
+  </si>
+  <si>
+    <t>13,97</t>
+  </si>
+  <si>
+    <t>0,32</t>
+  </si>
+  <si>
+    <t>36,67</t>
+  </si>
+  <si>
+    <t>1,9</t>
+  </si>
+  <si>
+    <t>9,05</t>
+  </si>
+  <si>
+    <t>3,02</t>
+  </si>
+  <si>
+    <t>1872</t>
+  </si>
+  <si>
+    <t>METRO</t>
+  </si>
+  <si>
+    <t>1,91</t>
+  </si>
+  <si>
+    <t>0,43</t>
+  </si>
+  <si>
+    <t>10,77</t>
   </si>
   <si>
     <t>0,57</t>
-  </si>
-  <si>
-    <t>12,03</t>
-  </si>
-  <si>
-    <t>12,84</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>TANGGAMUS</t>
-  </si>
-  <si>
-    <t>4,71</t>
-  </si>
-  <si>
-    <t>18,08</t>
-  </si>
-  <si>
-    <t>0,76</t>
-  </si>
-  <si>
-    <t>1,09</t>
-  </si>
-  <si>
-    <t>4,29</t>
-  </si>
-  <si>
-    <t>3,87</t>
-  </si>
-  <si>
-    <t>0,42</t>
-  </si>
-  <si>
-    <t>0,84</t>
-  </si>
-  <si>
-    <t>41,38</t>
-  </si>
-  <si>
-    <t>0,17</t>
-  </si>
-  <si>
-    <t>0,08</t>
-  </si>
-  <si>
-    <t>22,79</t>
-  </si>
-  <si>
-    <t>0,59</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>LAMPUNG SELATAN</t>
-  </si>
-  <si>
-    <t>5,92</t>
-  </si>
-  <si>
-    <t>0,39</t>
-  </si>
-  <si>
-    <t>18,7</t>
-  </si>
-  <si>
-    <t>0,56</t>
-  </si>
-  <si>
-    <t>3,4</t>
-  </si>
-  <si>
-    <t>0,77</t>
-  </si>
-  <si>
-    <t>0,04</t>
-  </si>
-  <si>
-    <t>43,72</t>
-  </si>
-  <si>
-    <t>4,14</t>
-  </si>
-  <si>
-    <t>17,62</t>
-  </si>
-  <si>
-    <t>1,19</t>
-  </si>
-  <si>
-    <t>0,07</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>LAMPUNG TIMUR</t>
-  </si>
-  <si>
-    <t>4,1</t>
-  </si>
-  <si>
-    <t>0,52</t>
-  </si>
-  <si>
-    <t>23,11</t>
-  </si>
-  <si>
-    <t>0,54</t>
-  </si>
-  <si>
-    <t>1,55</t>
-  </si>
-  <si>
-    <t>3,76</t>
-  </si>
-  <si>
-    <t>0,4</t>
-  </si>
-  <si>
-    <t>0,48</t>
-  </si>
-  <si>
-    <t>2,63</t>
-  </si>
-  <si>
-    <t>40,23</t>
-  </si>
-  <si>
-    <t>0,13</t>
-  </si>
-  <si>
-    <t>15,24</t>
-  </si>
-  <si>
-    <t>2,49</t>
-  </si>
-  <si>
-    <t>0,06</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>LAMPUNG TENGAH</t>
-  </si>
-  <si>
-    <t>4,23</t>
-  </si>
-  <si>
-    <t>21,94</t>
-  </si>
-  <si>
-    <t>0,58</t>
-  </si>
-  <si>
-    <t>0,46</t>
-  </si>
-  <si>
-    <t>5,96</t>
-  </si>
-  <si>
-    <t>4,2</t>
-  </si>
-  <si>
-    <t>0,15</t>
-  </si>
-  <si>
-    <t>44,7</t>
-  </si>
-  <si>
-    <t>1,21</t>
-  </si>
-  <si>
-    <t>15,19</t>
-  </si>
-  <si>
-    <t>0,65</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
-  </si>
-  <si>
-    <t>2,27</t>
-  </si>
-  <si>
-    <t>2,38</t>
-  </si>
-  <si>
-    <t>14,27</t>
-  </si>
-  <si>
-    <t>2,33</t>
-  </si>
-  <si>
-    <t>2,45</t>
-  </si>
-  <si>
-    <t>44,39</t>
-  </si>
-  <si>
-    <t>0,81</t>
-  </si>
-  <si>
-    <t>16,52</t>
-  </si>
-  <si>
-    <t>13,33</t>
-  </si>
-  <si>
-    <t>0,11</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>4,34</t>
-  </si>
-  <si>
-    <t>19,88</t>
-  </si>
-  <si>
-    <t>0,43</t>
-  </si>
-  <si>
-    <t>0,5</t>
-  </si>
-  <si>
-    <t>2,47</t>
-  </si>
-  <si>
-    <t>2,97</t>
-  </si>
-  <si>
-    <t>0,23</t>
-  </si>
-  <si>
-    <t>40,29</t>
-  </si>
-  <si>
-    <t>0,33</t>
-  </si>
-  <si>
-    <t>26,65</t>
-  </si>
-  <si>
-    <t>1,3</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG</t>
-  </si>
-  <si>
-    <t>4,4</t>
-  </si>
-  <si>
-    <t>0,8</t>
-  </si>
-  <si>
-    <t>21,15</t>
-  </si>
-  <si>
-    <t>0,94</t>
-  </si>
-  <si>
-    <t>1,22</t>
-  </si>
-  <si>
-    <t>2,2</t>
-  </si>
-  <si>
-    <t>0,47</t>
-  </si>
-  <si>
-    <t>2,01</t>
-  </si>
-  <si>
-    <t>46,23</t>
-  </si>
-  <si>
-    <t>0,09</t>
-  </si>
-  <si>
-    <t>15,63</t>
-  </si>
-  <si>
-    <t>4,63</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>PESAWARAN</t>
-  </si>
-  <si>
-    <t>3,24</t>
-  </si>
-  <si>
-    <t>1,17</t>
-  </si>
-  <si>
-    <t>0,93</t>
-  </si>
-  <si>
-    <t>0,91</t>
-  </si>
-  <si>
-    <t>0,12</t>
-  </si>
-  <si>
-    <t>40,39</t>
-  </si>
-  <si>
-    <t>0,88</t>
-  </si>
-  <si>
-    <t>14,9</t>
-  </si>
-  <si>
-    <t>22,64</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>PRINGSEWU</t>
-  </si>
-  <si>
-    <t>4,19</t>
-  </si>
-  <si>
-    <t>0,36</t>
-  </si>
-  <si>
-    <t>13,6</t>
-  </si>
-  <si>
-    <t>4,25</t>
-  </si>
-  <si>
-    <t>0,96</t>
-  </si>
-  <si>
-    <t>1,14</t>
-  </si>
-  <si>
-    <t>3,77</t>
-  </si>
-  <si>
-    <t>0,6</t>
-  </si>
-  <si>
-    <t>2,4</t>
-  </si>
-  <si>
-    <t>41,82</t>
-  </si>
-  <si>
-    <t>1,8</t>
-  </si>
-  <si>
-    <t>0,66</t>
-  </si>
-  <si>
-    <t>17,74</t>
-  </si>
-  <si>
-    <t>3,36</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>4,42</t>
-  </si>
-  <si>
-    <t>0,85</t>
-  </si>
-  <si>
-    <t>0,95</t>
-  </si>
-  <si>
-    <t>1,51</t>
-  </si>
-  <si>
-    <t>48,82</t>
-  </si>
-  <si>
-    <t>1,34</t>
-  </si>
-  <si>
-    <t>12,74</t>
-  </si>
-  <si>
-    <t>7,24</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG BARAT</t>
-  </si>
-  <si>
-    <t>4,28</t>
-  </si>
-  <si>
-    <t>0,16</t>
-  </si>
-  <si>
-    <t>18,71</t>
-  </si>
-  <si>
-    <t>1,18</t>
-  </si>
-  <si>
-    <t>0,53</t>
-  </si>
-  <si>
-    <t>0,61</t>
-  </si>
-  <si>
-    <t>1,44</t>
-  </si>
-  <si>
-    <t>45,46</t>
-  </si>
-  <si>
-    <t>0,21</t>
-  </si>
-  <si>
-    <t>24,64</t>
-  </si>
-  <si>
-    <t>1,04</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>PESISIR BARAT</t>
-  </si>
-  <si>
-    <t>4,3</t>
-  </si>
-  <si>
-    <t>25,49</t>
-  </si>
-  <si>
-    <t>0,38</t>
-  </si>
-  <si>
-    <t>3,54</t>
-  </si>
-  <si>
-    <t>42,74</t>
-  </si>
-  <si>
-    <t>17,25</t>
-  </si>
-  <si>
-    <t>4,24</t>
-  </si>
-  <si>
-    <t>1871</t>
-  </si>
-  <si>
-    <t>BANDAR LAMPUNG</t>
-  </si>
-  <si>
-    <t>6,97</t>
-  </si>
-  <si>
-    <t>9,19</t>
-  </si>
-  <si>
-    <t>0,79</t>
-  </si>
-  <si>
-    <t>0,63</t>
-  </si>
-  <si>
-    <t>6,5</t>
-  </si>
-  <si>
-    <t>2,54</t>
-  </si>
-  <si>
-    <t>7,13</t>
-  </si>
-  <si>
-    <t>13,95</t>
-  </si>
-  <si>
-    <t>0,32</t>
-  </si>
-  <si>
-    <t>36,61</t>
-  </si>
-  <si>
-    <t>1,9</t>
-  </si>
-  <si>
-    <t>9,03</t>
-  </si>
-  <si>
-    <t>3,01</t>
-  </si>
-  <si>
-    <t>1872</t>
-  </si>
-  <si>
-    <t>METRO</t>
-  </si>
-  <si>
-    <t>1,91</t>
-  </si>
-  <si>
-    <t>10,77</t>
   </si>
   <si>
     <t>2,48</t>
@@ -1860,16 +1857,16 @@
         <v>93</v>
       </c>
       <c r="C6" s="6">
-        <v>52936</v>
+        <v>53482</v>
       </c>
       <c r="D6" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>94</v>
       </c>
       <c r="F6" s="6">
-        <v>2130</v>
+        <v>2155</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>95</v>
@@ -1881,67 +1878,67 @@
         <v>96</v>
       </c>
       <c r="J6" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>97</v>
       </c>
       <c r="L6" s="6">
-        <v>9856</v>
+        <v>10058</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>98</v>
       </c>
       <c r="N6" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P6" s="6">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="Q6" s="7" t="s">
         <v>99</v>
       </c>
       <c r="R6" s="6">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="S6" s="7" t="s">
         <v>100</v>
       </c>
       <c r="T6" s="6">
-        <v>1329</v>
+        <v>1336</v>
       </c>
       <c r="U6" s="7" t="s">
         <v>101</v>
       </c>
       <c r="V6" s="6">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="W6" s="7" t="s">
         <v>102</v>
       </c>
       <c r="X6" s="6">
-        <v>1535</v>
+        <v>1546</v>
       </c>
       <c r="Y6" s="7" t="s">
         <v>103</v>
       </c>
       <c r="Z6" s="6">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AA6" s="7" t="s">
         <v>104</v>
       </c>
       <c r="AB6" s="6">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AC6" s="7" t="s">
         <v>105</v>
       </c>
       <c r="AD6" s="6">
-        <v>22688</v>
+        <v>22922</v>
       </c>
       <c r="AE6" s="7" t="s">
         <v>106</v>
@@ -1953,13 +1950,13 @@
         <v>107</v>
       </c>
       <c r="AH6" s="6">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI6" s="7" t="s">
         <v>108</v>
       </c>
       <c r="AJ6" s="6">
-        <v>8838</v>
+        <v>8918</v>
       </c>
       <c r="AK6" s="7" t="s">
         <v>109</v>
@@ -1974,7 +1971,7 @@
         <v>4</v>
       </c>
       <c r="AO6" s="7" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="AP6" s="6">
         <v>0</v>
@@ -1986,7 +1983,7 @@
         <v>26</v>
       </c>
       <c r="AS6" s="7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
@@ -1997,7 +1994,7 @@
         <v>113</v>
       </c>
       <c r="C7" s="9">
-        <v>2960</v>
+        <v>3095</v>
       </c>
       <c r="D7" s="9">
         <v>0</v>
@@ -2006,7 +2003,7 @@
         <v>97</v>
       </c>
       <c r="F7" s="9">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>114</v>
@@ -2024,7 +2021,7 @@
         <v>116</v>
       </c>
       <c r="L7" s="9">
-        <v>701</v>
+        <v>764</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>117</v>
@@ -2060,7 +2057,7 @@
         <v>120</v>
       </c>
       <c r="X7" s="9">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="Y7" s="10" t="s">
         <v>121</v>
@@ -2078,7 +2075,7 @@
         <v>119</v>
       </c>
       <c r="AD7" s="9">
-        <v>1152</v>
+        <v>1189</v>
       </c>
       <c r="AE7" s="10" t="s">
         <v>123</v>
@@ -2090,13 +2087,13 @@
         <v>124</v>
       </c>
       <c r="AH7" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI7" s="10" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AJ7" s="9">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="AK7" s="10" t="s">
         <v>125</v>
@@ -2271,25 +2268,25 @@
         <v>143</v>
       </c>
       <c r="C9" s="9">
-        <v>5705</v>
+        <v>5712</v>
       </c>
       <c r="D9" s="9">
         <v>1</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="F9" s="9">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H9" s="9">
         <v>22</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J9" s="9">
         <v>0</v>
@@ -2298,10 +2295,10 @@
         <v>97</v>
       </c>
       <c r="L9" s="9">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N9" s="9">
         <v>0</v>
@@ -2313,46 +2310,46 @@
         <v>1</v>
       </c>
       <c r="Q9" s="10" t="s">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="R9" s="9">
         <v>32</v>
       </c>
       <c r="S9" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="T9" s="9">
         <v>194</v>
       </c>
       <c r="U9" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="V9" s="9">
         <v>3</v>
       </c>
       <c r="W9" s="10" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="X9" s="9">
         <v>194</v>
       </c>
       <c r="Y9" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Z9" s="9">
         <v>44</v>
       </c>
       <c r="AA9" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AB9" s="9">
         <v>2</v>
       </c>
       <c r="AC9" s="10" t="s">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="AD9" s="9">
-        <v>2494</v>
+        <v>2497</v>
       </c>
       <c r="AE9" s="10" t="s">
         <v>151</v>
@@ -2370,7 +2367,7 @@
         <v>97</v>
       </c>
       <c r="AJ9" s="9">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="AK9" s="10" t="s">
         <v>153</v>
@@ -2408,79 +2405,79 @@
         <v>157</v>
       </c>
       <c r="C10" s="9">
-        <v>4782</v>
+        <v>5095</v>
       </c>
       <c r="D10" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="F10" s="9">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H10" s="9">
         <v>25</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J10" s="9">
+        <v>0</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L10" s="9">
+        <v>1199</v>
+      </c>
+      <c r="M10" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="N10" s="9">
         <v>1</v>
       </c>
-      <c r="K10" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="L10" s="9">
-        <v>1105</v>
-      </c>
-      <c r="M10" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="N10" s="9">
-        <v>0</v>
-      </c>
       <c r="O10" s="10" t="s">
-        <v>97</v>
+        <v>144</v>
       </c>
       <c r="P10" s="9">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="R10" s="9">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="T10" s="9">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="U10" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="V10" s="9">
         <v>19</v>
       </c>
       <c r="W10" s="10" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="X10" s="9">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="Z10" s="9">
         <v>23</v>
       </c>
       <c r="AA10" s="10" t="s">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="AB10" s="9">
         <v>126</v>
@@ -2489,7 +2486,7 @@
         <v>166</v>
       </c>
       <c r="AD10" s="9">
-        <v>1924</v>
+        <v>2088</v>
       </c>
       <c r="AE10" s="10" t="s">
         <v>167</v>
@@ -2498,31 +2495,31 @@
         <v>25</v>
       </c>
       <c r="AG10" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AH10" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI10" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AJ10" s="9">
+        <v>774</v>
+      </c>
+      <c r="AK10" s="10" t="s">
         <v>168</v>
-      </c>
-      <c r="AJ10" s="9">
-        <v>729</v>
-      </c>
-      <c r="AK10" s="10" t="s">
-        <v>169</v>
       </c>
       <c r="AL10" s="9">
         <v>119</v>
       </c>
       <c r="AM10" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AN10" s="9">
         <v>1</v>
       </c>
       <c r="AO10" s="10" t="s">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="AP10" s="9">
         <v>0</v>
@@ -2534,30 +2531,30 @@
         <v>3</v>
       </c>
       <c r="AS10" s="10" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C11" s="9">
-        <v>6045</v>
+        <v>6044</v>
       </c>
       <c r="D11" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="F11" s="9">
         <v>256</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H11" s="9">
         <v>6</v>
@@ -2575,7 +2572,7 @@
         <v>1326</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="N11" s="9">
         <v>0</v>
@@ -2587,19 +2584,19 @@
         <v>35</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="R11" s="9">
         <v>28</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="T11" s="9">
         <v>360</v>
       </c>
       <c r="U11" s="10" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="V11" s="9">
         <v>5</v>
@@ -2611,31 +2608,31 @@
         <v>254</v>
       </c>
       <c r="Y11" s="10" t="s">
-        <v>179</v>
+        <v>121</v>
       </c>
       <c r="Z11" s="9">
         <v>29</v>
       </c>
       <c r="AA11" s="10" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="AB11" s="9">
         <v>9</v>
       </c>
       <c r="AC11" s="10" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AD11" s="9">
         <v>2702</v>
       </c>
       <c r="AE11" s="10" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AF11" s="9">
         <v>73</v>
       </c>
       <c r="AG11" s="10" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AH11" s="9">
         <v>0</v>
@@ -2647,13 +2644,13 @@
         <v>918</v>
       </c>
       <c r="AK11" s="10" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="AL11" s="9">
         <v>39</v>
       </c>
       <c r="AM11" s="10" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="AN11" s="9">
         <v>0</v>
@@ -2676,13 +2673,13 @@
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C12" s="9">
-        <v>5677</v>
+        <v>5685</v>
       </c>
       <c r="D12" s="9">
         <v>0</v>
@@ -2694,13 +2691,13 @@
         <v>129</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H12" s="9">
         <v>135</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J12" s="9">
         <v>0</v>
@@ -2712,7 +2709,7 @@
         <v>810</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="N12" s="9">
         <v>0</v>
@@ -2721,40 +2718,40 @@
         <v>97</v>
       </c>
       <c r="P12" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q12" s="10" t="s">
-        <v>150</v>
+        <v>111</v>
       </c>
       <c r="R12" s="9">
         <v>26</v>
       </c>
       <c r="S12" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="T12" s="9">
         <v>132</v>
       </c>
       <c r="U12" s="10" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="V12" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W12" s="10" t="s">
         <v>108</v>
       </c>
       <c r="X12" s="9">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Y12" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Z12" s="9">
         <v>32</v>
       </c>
       <c r="AA12" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AB12" s="9">
         <v>0</v>
@@ -2763,40 +2760,40 @@
         <v>97</v>
       </c>
       <c r="AD12" s="9">
-        <v>2520</v>
+        <v>2522</v>
       </c>
       <c r="AE12" s="10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AF12" s="9">
         <v>46</v>
       </c>
       <c r="AG12" s="10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AH12" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="AJ12" s="9">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="AK12" s="10" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AL12" s="9">
         <v>757</v>
       </c>
       <c r="AM12" s="10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AN12" s="9">
         <v>1</v>
       </c>
       <c r="AO12" s="10" t="s">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="AP12" s="9">
         <v>0</v>
@@ -2808,18 +2805,18 @@
         <v>6</v>
       </c>
       <c r="AS12" s="10" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C13" s="9">
-        <v>2998</v>
+        <v>3000</v>
       </c>
       <c r="D13" s="9">
         <v>0</v>
@@ -2831,7 +2828,7 @@
         <v>130</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H13" s="9">
         <v>2</v>
@@ -2849,7 +2846,7 @@
         <v>596</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="N13" s="9">
         <v>1</v>
@@ -2858,22 +2855,22 @@
         <v>116</v>
       </c>
       <c r="P13" s="9">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="R13" s="9">
         <v>15</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="T13" s="9">
         <v>74</v>
       </c>
       <c r="U13" s="10" t="s">
-        <v>203</v>
+        <v>166</v>
       </c>
       <c r="V13" s="9">
         <v>3</v>
@@ -2885,31 +2882,31 @@
         <v>89</v>
       </c>
       <c r="Y13" s="10" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="Z13" s="9">
         <v>12</v>
       </c>
       <c r="AA13" s="10" t="s">
-        <v>164</v>
+        <v>102</v>
       </c>
       <c r="AB13" s="9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC13" s="10" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="AD13" s="9">
         <v>1208</v>
       </c>
       <c r="AE13" s="10" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="AF13" s="9">
         <v>10</v>
       </c>
       <c r="AG13" s="10" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AH13" s="9">
         <v>0</v>
@@ -2921,13 +2918,13 @@
         <v>799</v>
       </c>
       <c r="AK13" s="10" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="AL13" s="9">
         <v>39</v>
       </c>
       <c r="AM13" s="10" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="AN13" s="9">
         <v>0</v>
@@ -2950,31 +2947,31 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C14" s="9">
-        <v>2137</v>
+        <v>2139</v>
       </c>
       <c r="D14" s="9">
         <v>1</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F14" s="9">
         <v>94</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="H14" s="9">
         <v>17</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="J14" s="9">
         <v>0</v>
@@ -2983,52 +2980,52 @@
         <v>97</v>
       </c>
       <c r="L14" s="9">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="N14" s="9">
         <v>1</v>
       </c>
       <c r="O14" s="10" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="P14" s="9">
         <v>20</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="R14" s="9">
         <v>26</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="T14" s="9">
         <v>47</v>
       </c>
       <c r="U14" s="10" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="V14" s="9">
         <v>10</v>
       </c>
       <c r="W14" s="10" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="X14" s="9">
         <v>43</v>
       </c>
       <c r="Y14" s="10" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="Z14" s="9">
         <v>1</v>
       </c>
       <c r="AA14" s="10" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AB14" s="9">
         <v>0</v>
@@ -3037,16 +3034,16 @@
         <v>97</v>
       </c>
       <c r="AD14" s="9">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="AE14" s="10" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="AF14" s="9">
         <v>2</v>
       </c>
       <c r="AG14" s="10" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="AH14" s="9">
         <v>0</v>
@@ -3058,19 +3055,19 @@
         <v>334</v>
       </c>
       <c r="AK14" s="10" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AL14" s="9">
         <v>99</v>
       </c>
       <c r="AM14" s="10" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="AN14" s="9">
         <v>1</v>
       </c>
       <c r="AO14" s="10" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AP14" s="9">
         <v>0</v>
@@ -3082,18 +3079,18 @@
         <v>1</v>
       </c>
       <c r="AS14" s="10" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C15" s="9">
-        <v>7492</v>
+        <v>7496</v>
       </c>
       <c r="D15" s="9">
         <v>0</v>
@@ -3105,13 +3102,13 @@
         <v>243</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H15" s="9">
         <v>88</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="J15" s="9">
         <v>0</v>
@@ -3120,10 +3117,10 @@
         <v>97</v>
       </c>
       <c r="L15" s="9">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>126</v>
+        <v>223</v>
       </c>
       <c r="N15" s="9">
         <v>0</v>
@@ -3132,82 +3129,82 @@
         <v>97</v>
       </c>
       <c r="P15" s="9">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>100</v>
+        <v>224</v>
       </c>
       <c r="R15" s="9">
         <v>70</v>
       </c>
       <c r="S15" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="T15" s="9">
+        <v>69</v>
+      </c>
+      <c r="U15" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="V15" s="9">
+        <v>6</v>
+      </c>
+      <c r="W15" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="X15" s="9">
+        <v>87</v>
+      </c>
+      <c r="Y15" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="Z15" s="9">
+        <v>7</v>
+      </c>
+      <c r="AA15" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="AB15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD15" s="9">
+        <v>3027</v>
+      </c>
+      <c r="AE15" s="10" t="s">
         <v>228</v>
-      </c>
-      <c r="T15" s="9">
-        <v>68</v>
-      </c>
-      <c r="U15" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="V15" s="9">
-        <v>9</v>
-      </c>
-      <c r="W15" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="X15" s="9">
-        <v>85</v>
-      </c>
-      <c r="Y15" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="Z15" s="9">
-        <v>6</v>
-      </c>
-      <c r="AA15" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="AB15" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD15" s="9">
-        <v>3026</v>
-      </c>
-      <c r="AE15" s="10" t="s">
-        <v>231</v>
       </c>
       <c r="AF15" s="9">
         <v>66</v>
       </c>
       <c r="AG15" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AH15" s="9">
         <v>1</v>
       </c>
       <c r="AI15" s="10" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="AJ15" s="9">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="AK15" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AL15" s="9">
         <v>1696</v>
       </c>
       <c r="AM15" s="10" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="AN15" s="9">
         <v>1</v>
       </c>
       <c r="AO15" s="10" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="AP15" s="9">
         <v>0</v>
@@ -3224,10 +3221,10 @@
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C16" s="9">
         <v>1669</v>
@@ -3242,13 +3239,13 @@
         <v>70</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H16" s="9">
         <v>6</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J16" s="9">
         <v>0</v>
@@ -3260,7 +3257,7 @@
         <v>227</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="N16" s="9">
         <v>0</v>
@@ -3272,73 +3269,73 @@
         <v>71</v>
       </c>
       <c r="Q16" s="10" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="R16" s="9">
         <v>16</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="T16" s="9">
         <v>54</v>
       </c>
       <c r="U16" s="10" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="V16" s="9">
         <v>19</v>
       </c>
       <c r="W16" s="10" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="X16" s="9">
         <v>63</v>
       </c>
       <c r="Y16" s="10" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="Z16" s="9">
         <v>10</v>
       </c>
       <c r="AA16" s="10" t="s">
-        <v>244</v>
+        <v>99</v>
       </c>
       <c r="AB16" s="9">
         <v>40</v>
       </c>
       <c r="AC16" s="10" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="AD16" s="9">
         <v>698</v>
       </c>
       <c r="AE16" s="10" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="AF16" s="9">
         <v>30</v>
       </c>
       <c r="AG16" s="10" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="AH16" s="9">
         <v>11</v>
       </c>
       <c r="AI16" s="10" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="AJ16" s="9">
         <v>296</v>
       </c>
       <c r="AK16" s="10" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="AL16" s="9">
         <v>56</v>
       </c>
       <c r="AM16" s="10" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="AN16" s="9">
         <v>0</v>
@@ -3356,18 +3353,18 @@
         <v>2</v>
       </c>
       <c r="AS16" s="10" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C17" s="9">
-        <v>3054</v>
+        <v>3055</v>
       </c>
       <c r="D17" s="9">
         <v>1</v>
@@ -3379,13 +3376,13 @@
         <v>135</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H17" s="9">
         <v>26</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="J17" s="9">
         <v>0</v>
@@ -3397,7 +3394,7 @@
         <v>607</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="N17" s="9">
         <v>0</v>
@@ -3406,34 +3403,34 @@
         <v>97</v>
       </c>
       <c r="P17" s="9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="R17" s="9">
         <v>26</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="T17" s="9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="U17" s="10" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="V17" s="9">
         <v>11</v>
       </c>
       <c r="W17" s="10" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="X17" s="9">
         <v>46</v>
       </c>
       <c r="Y17" s="10" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="Z17" s="9">
         <v>2</v>
@@ -3448,16 +3445,16 @@
         <v>122</v>
       </c>
       <c r="AD17" s="9">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="AE17" s="10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AF17" s="9">
         <v>41</v>
       </c>
       <c r="AG17" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AH17" s="9">
         <v>0</v>
@@ -3469,13 +3466,13 @@
         <v>389</v>
       </c>
       <c r="AK17" s="10" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AL17" s="9">
         <v>221</v>
       </c>
       <c r="AM17" s="10" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AN17" s="9">
         <v>0</v>
@@ -3498,10 +3495,10 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C18" s="9">
         <v>3742</v>
@@ -3516,13 +3513,13 @@
         <v>160</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H18" s="9">
         <v>6</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="J18" s="9">
         <v>0</v>
@@ -3534,7 +3531,7 @@
         <v>700</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="N18" s="9">
         <v>0</v>
@@ -3546,55 +3543,55 @@
         <v>44</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="R18" s="9">
         <v>20</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="T18" s="9">
         <v>44</v>
       </c>
       <c r="U18" s="10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="V18" s="9">
         <v>23</v>
       </c>
       <c r="W18" s="10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="X18" s="9">
         <v>54</v>
       </c>
       <c r="Y18" s="10" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="Z18" s="9">
         <v>6</v>
       </c>
       <c r="AA18" s="10" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="AB18" s="9">
         <v>15</v>
       </c>
       <c r="AC18" s="10" t="s">
-        <v>164</v>
+        <v>102</v>
       </c>
       <c r="AD18" s="9">
         <v>1701</v>
       </c>
       <c r="AE18" s="10" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AF18" s="9">
         <v>8</v>
       </c>
       <c r="AG18" s="10" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AH18" s="9">
         <v>0</v>
@@ -3606,13 +3603,13 @@
         <v>922</v>
       </c>
       <c r="AK18" s="10" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AL18" s="9">
         <v>39</v>
       </c>
       <c r="AM18" s="10" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AN18" s="9">
         <v>0</v>
@@ -3635,31 +3632,31 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="C19" s="9">
+        <v>3520</v>
+      </c>
+      <c r="D19" s="9">
+        <v>0</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" s="9">
+        <v>154</v>
+      </c>
+      <c r="G19" s="10" t="s">
         <v>274</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="C19" s="9">
-        <v>3444</v>
-      </c>
-      <c r="D19" s="9">
-        <v>0</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="F19" s="9">
-        <v>148</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>276</v>
       </c>
       <c r="H19" s="9">
         <v>18</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>159</v>
+        <v>104</v>
       </c>
       <c r="J19" s="9">
         <v>0</v>
@@ -3668,10 +3665,10 @@
         <v>97</v>
       </c>
       <c r="L19" s="9">
-        <v>878</v>
+        <v>920</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="N19" s="9">
         <v>0</v>
@@ -3683,19 +3680,19 @@
         <v>2</v>
       </c>
       <c r="Q19" s="10" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="R19" s="9">
         <v>13</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>278</v>
+        <v>162</v>
       </c>
       <c r="T19" s="9">
         <v>16</v>
       </c>
       <c r="U19" s="10" t="s">
-        <v>177</v>
+        <v>105</v>
       </c>
       <c r="V19" s="9">
         <v>1</v>
@@ -3704,16 +3701,16 @@
         <v>116</v>
       </c>
       <c r="X19" s="9">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Y19" s="10" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="Z19" s="9">
         <v>4</v>
       </c>
       <c r="AA19" s="10" t="s">
-        <v>230</v>
+        <v>193</v>
       </c>
       <c r="AB19" s="9">
         <v>1</v>
@@ -3722,10 +3719,10 @@
         <v>116</v>
       </c>
       <c r="AD19" s="9">
-        <v>1472</v>
+        <v>1497</v>
       </c>
       <c r="AE19" s="10" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="AF19" s="9">
         <v>26</v>
@@ -3740,16 +3737,16 @@
         <v>116</v>
       </c>
       <c r="AJ19" s="9">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AK19" s="10" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="AL19" s="9">
         <v>146</v>
       </c>
       <c r="AM19" s="10" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="AN19" s="9">
         <v>0</v>
@@ -3767,36 +3764,36 @@
         <v>2</v>
       </c>
       <c r="AS19" s="10" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C20" s="9">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D20" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>264</v>
+        <v>97</v>
       </c>
       <c r="F20" s="9">
         <v>44</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H20" s="9">
         <v>6</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="J20" s="9">
         <v>0</v>
@@ -3808,7 +3805,7 @@
         <v>58</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="N20" s="9">
         <v>0</v>
@@ -3820,55 +3817,55 @@
         <v>5</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>287</v>
+        <v>209</v>
       </c>
       <c r="R20" s="9">
         <v>4</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="T20" s="9">
         <v>41</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="V20" s="9">
         <v>16</v>
       </c>
       <c r="W20" s="10" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="X20" s="9">
         <v>45</v>
       </c>
       <c r="Y20" s="10" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="Z20" s="9">
         <v>88</v>
       </c>
       <c r="AA20" s="10" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="AB20" s="9">
         <v>2</v>
       </c>
       <c r="AC20" s="10" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="AD20" s="9">
         <v>231</v>
       </c>
       <c r="AE20" s="10" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AF20" s="9">
         <v>12</v>
       </c>
       <c r="AG20" s="10" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AH20" s="9">
         <v>0</v>
@@ -3880,13 +3877,13 @@
         <v>57</v>
       </c>
       <c r="AK20" s="10" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AL20" s="9">
         <v>19</v>
       </c>
       <c r="AM20" s="10" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AN20" s="9">
         <v>0</v>
@@ -3904,15 +3901,15 @@
         <v>2</v>
       </c>
       <c r="AS20" s="10" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C21" s="9">
         <v>1411</v>
@@ -3927,13 +3924,13 @@
         <v>27</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="H21" s="9">
         <v>6</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>201</v>
+        <v>298</v>
       </c>
       <c r="J21" s="9">
         <v>0</v>
@@ -3945,7 +3942,7 @@
         <v>152</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="N21" s="9">
         <v>0</v>
@@ -3963,49 +3960,49 @@
         <v>8</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>124</v>
+        <v>300</v>
       </c>
       <c r="T21" s="9">
         <v>35</v>
       </c>
       <c r="U21" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="V21" s="9">
         <v>34</v>
       </c>
       <c r="W21" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="X21" s="9">
         <v>34</v>
       </c>
       <c r="Y21" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Z21" s="9">
         <v>7</v>
       </c>
       <c r="AA21" s="10" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="AB21" s="9">
         <v>18</v>
       </c>
       <c r="AC21" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AD21" s="9">
         <v>589</v>
       </c>
       <c r="AE21" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AF21" s="9">
         <v>3</v>
       </c>
       <c r="AG21" s="10" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AH21" s="9">
         <v>0</v>
@@ -4017,13 +4014,13 @@
         <v>114</v>
       </c>
       <c r="AK21" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AL21" s="9">
         <v>384</v>
       </c>
       <c r="AM21" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AN21" s="9">
         <v>0</v>
@@ -4046,22 +4043,22 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="B22" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>309</v>
-      </c>
       <c r="C22" s="12">
-        <v>52936</v>
+        <v>53482</v>
       </c>
       <c r="D22" s="12">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>94</v>
       </c>
       <c r="F22" s="12">
-        <v>2130</v>
+        <v>2155</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>95</v>
@@ -4073,67 +4070,67 @@
         <v>96</v>
       </c>
       <c r="J22" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K22" s="13" t="s">
         <v>97</v>
       </c>
       <c r="L22" s="12">
-        <v>9856</v>
+        <v>10058</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>98</v>
       </c>
       <c r="N22" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O22" s="13" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P22" s="12">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="Q22" s="13" t="s">
         <v>99</v>
       </c>
       <c r="R22" s="12">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="S22" s="13" t="s">
         <v>100</v>
       </c>
       <c r="T22" s="12">
-        <v>1329</v>
+        <v>1336</v>
       </c>
       <c r="U22" s="13" t="s">
         <v>101</v>
       </c>
       <c r="V22" s="12">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="W22" s="13" t="s">
         <v>102</v>
       </c>
       <c r="X22" s="12">
-        <v>1535</v>
+        <v>1546</v>
       </c>
       <c r="Y22" s="13" t="s">
         <v>103</v>
       </c>
       <c r="Z22" s="12">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AA22" s="13" t="s">
         <v>104</v>
       </c>
       <c r="AB22" s="12">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AC22" s="13" t="s">
         <v>105</v>
       </c>
       <c r="AD22" s="12">
-        <v>22688</v>
+        <v>22922</v>
       </c>
       <c r="AE22" s="13" t="s">
         <v>106</v>
@@ -4145,13 +4142,13 @@
         <v>107</v>
       </c>
       <c r="AH22" s="12">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI22" s="13" t="s">
         <v>108</v>
       </c>
       <c r="AJ22" s="12">
-        <v>8838</v>
+        <v>8918</v>
       </c>
       <c r="AK22" s="13" t="s">
         <v>109</v>
@@ -4166,7 +4163,7 @@
         <v>4</v>
       </c>
       <c r="AO22" s="13" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="AP22" s="12">
         <v>0</v>
@@ -4178,7 +4175,7 @@
         <v>26</v>
       </c>
       <c r="AS22" s="13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
+++ b/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
@@ -16,7 +16,7 @@
     <t>DATA RADAR ANOMALI KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 24 Agu 2026, 07.47</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 24 Agu 2026, 21.09</t>
   </si>
   <si>
     <t>Kode</t>

--- a/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
+++ b/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="305">
   <si>
     <t>DATA RADAR ANOMALI KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 24 Agu 2026, 21.09</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 25 Agu 2026, 07.59</t>
   </si>
   <si>
     <t>Kode</t>
@@ -295,562 +295,562 @@
     <t>LAMPUNG</t>
   </si>
   <si>
+    <t>0,02</t>
+  </si>
+  <si>
+    <t>4,04</t>
+  </si>
+  <si>
+    <t>0,73</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>18,98</t>
+  </si>
+  <si>
     <t>0,01</t>
   </si>
   <si>
-    <t>4,03</t>
-  </si>
-  <si>
-    <t>0,74</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>18,81</t>
+    <t>0,56</t>
+  </si>
+  <si>
+    <t>0,7</t>
+  </si>
+  <si>
+    <t>2,48</t>
+  </si>
+  <si>
+    <t>0,38</t>
+  </si>
+  <si>
+    <t>2,89</t>
+  </si>
+  <si>
+    <t>0,52</t>
+  </si>
+  <si>
+    <t>0,44</t>
+  </si>
+  <si>
+    <t>42,91</t>
+  </si>
+  <si>
+    <t>1,1</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>16,68</t>
+  </si>
+  <si>
+    <t>7,48</t>
+  </si>
+  <si>
+    <t>0,05</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>LAMPUNG BARAT</t>
+  </si>
+  <si>
+    <t>3,6</t>
+  </si>
+  <si>
+    <t>1,03</t>
+  </si>
+  <si>
+    <t>24,85</t>
+  </si>
+  <si>
+    <t>0,71</t>
+  </si>
+  <si>
+    <t>0,13</t>
+  </si>
+  <si>
+    <t>1,64</t>
+  </si>
+  <si>
+    <t>4,24</t>
+  </si>
+  <si>
+    <t>0,1</t>
+  </si>
+  <si>
+    <t>38,36</t>
+  </si>
+  <si>
+    <t>0,55</t>
+  </si>
+  <si>
+    <t>12,3</t>
+  </si>
+  <si>
+    <t>12,2</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>TANGGAMUS</t>
+  </si>
+  <si>
+    <t>4,7</t>
+  </si>
+  <si>
+    <t>18,04</t>
+  </si>
+  <si>
+    <t>0,42</t>
+  </si>
+  <si>
+    <t>1,09</t>
+  </si>
+  <si>
+    <t>4,61</t>
+  </si>
+  <si>
+    <t>0,76</t>
+  </si>
+  <si>
+    <t>3,86</t>
+  </si>
+  <si>
+    <t>0,84</t>
+  </si>
+  <si>
+    <t>41,36</t>
+  </si>
+  <si>
+    <t>0,17</t>
+  </si>
+  <si>
+    <t>0,08</t>
+  </si>
+  <si>
+    <t>22,9</t>
+  </si>
+  <si>
+    <t>0,59</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>LAMPUNG SELATAN</t>
+  </si>
+  <si>
+    <t>5,93</t>
+  </si>
+  <si>
+    <t>18,85</t>
+  </si>
+  <si>
+    <t>0,57</t>
+  </si>
+  <si>
+    <t>3,34</t>
+  </si>
+  <si>
+    <t>3,35</t>
+  </si>
+  <si>
+    <t>43,48</t>
+  </si>
+  <si>
+    <t>4,08</t>
+  </si>
+  <si>
+    <t>17,86</t>
+  </si>
+  <si>
+    <t>1,18</t>
+  </si>
+  <si>
+    <t>0,07</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>LAMPUNG TIMUR</t>
+  </si>
+  <si>
+    <t>4,19</t>
+  </si>
+  <si>
+    <t>23,95</t>
+  </si>
+  <si>
+    <t>0,34</t>
+  </si>
+  <si>
+    <t>1,35</t>
+  </si>
+  <si>
+    <t>3,28</t>
+  </si>
+  <si>
+    <t>3,8</t>
+  </si>
+  <si>
+    <t>0,41</t>
+  </si>
+  <si>
+    <t>2,2</t>
+  </si>
+  <si>
+    <t>41,61</t>
+  </si>
+  <si>
+    <t>0,46</t>
+  </si>
+  <si>
+    <t>0,09</t>
+  </si>
+  <si>
+    <t>15,28</t>
+  </si>
+  <si>
+    <t>2,11</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>LAMPUNG TENGAH</t>
+  </si>
+  <si>
+    <t>21,93</t>
+  </si>
+  <si>
+    <t>0,58</t>
+  </si>
+  <si>
+    <t>5,94</t>
+  </si>
+  <si>
+    <t>4,21</t>
+  </si>
+  <si>
+    <t>0,48</t>
+  </si>
+  <si>
+    <t>0,18</t>
+  </si>
+  <si>
+    <t>44,67</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>15,2</t>
+  </si>
+  <si>
+    <t>0,64</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>2,27</t>
+  </si>
+  <si>
+    <t>2,37</t>
+  </si>
+  <si>
+    <t>14,28</t>
+  </si>
+  <si>
+    <t>2,32</t>
+  </si>
+  <si>
+    <t>44,35</t>
+  </si>
+  <si>
+    <t>0,81</t>
+  </si>
+  <si>
+    <t>16,58</t>
+  </si>
+  <si>
+    <t>13,3</t>
+  </si>
+  <si>
+    <t>0,11</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
+    <t>4,3</t>
+  </si>
+  <si>
+    <t>19,98</t>
+  </si>
+  <si>
+    <t>0,49</t>
+  </si>
+  <si>
+    <t>2,43</t>
+  </si>
+  <si>
+    <t>2,96</t>
+  </si>
+  <si>
+    <t>0,39</t>
+  </si>
+  <si>
+    <t>0,2</t>
+  </si>
+  <si>
+    <t>40,39</t>
+  </si>
+  <si>
+    <t>0,33</t>
+  </si>
+  <si>
+    <t>26,55</t>
+  </si>
+  <si>
+    <t>1,28</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG</t>
+  </si>
+  <si>
+    <t>4,37</t>
+  </si>
+  <si>
+    <t>0,79</t>
+  </si>
+  <si>
+    <t>21,24</t>
+  </si>
+  <si>
+    <t>0,93</t>
+  </si>
+  <si>
+    <t>1,21</t>
+  </si>
+  <si>
+    <t>2,18</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>46,38</t>
+  </si>
+  <si>
+    <t>15,52</t>
+  </si>
+  <si>
+    <t>4,6</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PESAWARAN</t>
+  </si>
+  <si>
+    <t>3,24</t>
+  </si>
+  <si>
+    <t>1,17</t>
+  </si>
+  <si>
+    <t>12,84</t>
+  </si>
+  <si>
+    <t>0,96</t>
+  </si>
+  <si>
+    <t>0,95</t>
+  </si>
+  <si>
+    <t>40,37</t>
+  </si>
+  <si>
+    <t>0,88</t>
+  </si>
+  <si>
+    <t>14,92</t>
+  </si>
+  <si>
+    <t>22,62</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>PRINGSEWU</t>
+  </si>
+  <si>
+    <t>4,2</t>
+  </si>
+  <si>
+    <t>0,35</t>
+  </si>
+  <si>
+    <t>13,95</t>
+  </si>
+  <si>
+    <t>3,62</t>
+  </si>
+  <si>
+    <t>3,68</t>
+  </si>
+  <si>
+    <t>1,05</t>
+  </si>
+  <si>
+    <t>3,79</t>
+  </si>
+  <si>
+    <t>2,22</t>
+  </si>
+  <si>
+    <t>42,09</t>
+  </si>
+  <si>
+    <t>1,81</t>
+  </si>
+  <si>
+    <t>0,47</t>
+  </si>
+  <si>
+    <t>17,81</t>
+  </si>
+  <si>
+    <t>3,27</t>
+  </si>
+  <si>
+    <t>0,12</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
+  </si>
+  <si>
+    <t>4,42</t>
+  </si>
+  <si>
+    <t>0,85</t>
+  </si>
+  <si>
+    <t>19,86</t>
+  </si>
+  <si>
+    <t>0,82</t>
+  </si>
+  <si>
+    <t>0,98</t>
+  </si>
+  <si>
+    <t>0,36</t>
+  </si>
+  <si>
+    <t>1,51</t>
+  </si>
+  <si>
+    <t>48,85</t>
+  </si>
+  <si>
+    <t>1,34</t>
+  </si>
+  <si>
+    <t>12,73</t>
+  </si>
+  <si>
+    <t>7,23</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG BARAT</t>
+  </si>
+  <si>
+    <t>0,16</t>
+  </si>
+  <si>
+    <t>19,2</t>
+  </si>
+  <si>
+    <t>1,15</t>
   </si>
   <si>
     <t>0,6</t>
   </si>
   <si>
-    <t>0,7</t>
-  </si>
-  <si>
-    <t>2,5</t>
-  </si>
-  <si>
-    <t>0,4</t>
-  </si>
-  <si>
-    <t>2,89</t>
+    <t>1,42</t>
+  </si>
+  <si>
+    <t>45,51</t>
+  </si>
+  <si>
+    <t>0,21</t>
+  </si>
+  <si>
+    <t>24,29</t>
+  </si>
+  <si>
+    <t>1,02</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>PESISIR BARAT</t>
+  </si>
+  <si>
+    <t>4,34</t>
   </si>
   <si>
     <t>0,51</t>
   </si>
   <si>
+    <t>26,01</t>
+  </si>
+  <si>
+    <t>0,06</t>
+  </si>
+  <si>
+    <t>0,37</t>
+  </si>
+  <si>
     <t>0,45</t>
   </si>
   <si>
-    <t>42,86</t>
-  </si>
-  <si>
-    <t>1,12</t>
-  </si>
-  <si>
-    <t>0,04</t>
-  </si>
-  <si>
-    <t>16,67</t>
-  </si>
-  <si>
-    <t>7,61</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>LAMPUNG BARAT</t>
-  </si>
-  <si>
-    <t>3,62</t>
-  </si>
-  <si>
-    <t>1,03</t>
-  </si>
-  <si>
-    <t>0,03</t>
-  </si>
-  <si>
-    <t>24,68</t>
-  </si>
-  <si>
-    <t>0,71</t>
-  </si>
-  <si>
-    <t>0,13</t>
-  </si>
-  <si>
-    <t>1,65</t>
-  </si>
-  <si>
-    <t>4,2</t>
-  </si>
-  <si>
-    <t>0,1</t>
-  </si>
-  <si>
-    <t>38,42</t>
-  </si>
-  <si>
-    <t>0,55</t>
-  </si>
-  <si>
-    <t>12,25</t>
-  </si>
-  <si>
-    <t>12,28</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>TANGGAMUS</t>
-  </si>
-  <si>
-    <t>4,71</t>
-  </si>
-  <si>
-    <t>18,08</t>
-  </si>
-  <si>
-    <t>0,76</t>
-  </si>
-  <si>
-    <t>1,09</t>
-  </si>
-  <si>
-    <t>4,29</t>
-  </si>
-  <si>
-    <t>3,87</t>
-  </si>
-  <si>
-    <t>0,42</t>
-  </si>
-  <si>
-    <t>0,84</t>
-  </si>
-  <si>
-    <t>41,38</t>
-  </si>
-  <si>
-    <t>0,17</t>
-  </si>
-  <si>
-    <t>0,08</t>
-  </si>
-  <si>
-    <t>22,79</t>
-  </si>
-  <si>
-    <t>0,59</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>LAMPUNG SELATAN</t>
-  </si>
-  <si>
-    <t>0,02</t>
-  </si>
-  <si>
-    <t>5,93</t>
-  </si>
-  <si>
-    <t>0,39</t>
-  </si>
-  <si>
-    <t>18,7</t>
-  </si>
-  <si>
-    <t>0,56</t>
-  </si>
-  <si>
-    <t>3,4</t>
-  </si>
-  <si>
-    <t>0,77</t>
-  </si>
-  <si>
-    <t>43,71</t>
-  </si>
-  <si>
-    <t>4,13</t>
-  </si>
-  <si>
-    <t>17,63</t>
-  </si>
-  <si>
-    <t>1,19</t>
-  </si>
-  <si>
-    <t>0,07</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>LAMPUNG TIMUR</t>
-  </si>
-  <si>
-    <t>0,06</t>
-  </si>
-  <si>
-    <t>4,04</t>
-  </si>
-  <si>
-    <t>0,49</t>
-  </si>
-  <si>
-    <t>23,53</t>
-  </si>
-  <si>
-    <t>0,37</t>
-  </si>
-  <si>
-    <t>1,49</t>
-  </si>
-  <si>
-    <t>3,63</t>
-  </si>
-  <si>
-    <t>3,89</t>
-  </si>
-  <si>
-    <t>2,47</t>
-  </si>
-  <si>
-    <t>40,98</t>
-  </si>
-  <si>
-    <t>15,19</t>
-  </si>
-  <si>
-    <t>2,34</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>LAMPUNG TENGAH</t>
-  </si>
-  <si>
-    <t>4,24</t>
-  </si>
-  <si>
-    <t>21,94</t>
-  </si>
-  <si>
-    <t>0,58</t>
-  </si>
-  <si>
-    <t>0,46</t>
-  </si>
-  <si>
-    <t>5,96</t>
-  </si>
-  <si>
-    <t>0,48</t>
-  </si>
-  <si>
-    <t>0,15</t>
-  </si>
-  <si>
-    <t>44,71</t>
-  </si>
-  <si>
-    <t>1,21</t>
-  </si>
-  <si>
-    <t>0,65</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
-  </si>
-  <si>
-    <t>2,27</t>
-  </si>
-  <si>
-    <t>2,37</t>
-  </si>
-  <si>
-    <t>14,25</t>
-  </si>
-  <si>
-    <t>2,32</t>
-  </si>
-  <si>
-    <t>2,46</t>
-  </si>
-  <si>
-    <t>44,36</t>
-  </si>
-  <si>
-    <t>0,81</t>
-  </si>
-  <si>
-    <t>16,61</t>
-  </si>
-  <si>
-    <t>13,32</t>
-  </si>
-  <si>
-    <t>0,11</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>4,33</t>
-  </si>
-  <si>
-    <t>19,87</t>
-  </si>
-  <si>
-    <t>0,47</t>
-  </si>
-  <si>
-    <t>0,5</t>
-  </si>
-  <si>
-    <t>2,97</t>
-  </si>
-  <si>
-    <t>0,27</t>
-  </si>
-  <si>
-    <t>40,27</t>
-  </si>
-  <si>
-    <t>0,33</t>
-  </si>
-  <si>
-    <t>26,63</t>
-  </si>
-  <si>
-    <t>1,3</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG</t>
-  </si>
-  <si>
-    <t>4,39</t>
-  </si>
-  <si>
-    <t>0,79</t>
-  </si>
-  <si>
-    <t>21,18</t>
-  </si>
-  <si>
-    <t>0,94</t>
-  </si>
-  <si>
-    <t>1,22</t>
-  </si>
-  <si>
-    <t>2,2</t>
-  </si>
-  <si>
-    <t>2,01</t>
-  </si>
-  <si>
-    <t>46,24</t>
-  </si>
-  <si>
-    <t>0,09</t>
-  </si>
-  <si>
-    <t>15,61</t>
-  </si>
-  <si>
-    <t>4,63</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>PESAWARAN</t>
-  </si>
-  <si>
-    <t>3,24</t>
-  </si>
-  <si>
-    <t>1,17</t>
-  </si>
-  <si>
-    <t>12,85</t>
-  </si>
-  <si>
-    <t>0,69</t>
-  </si>
-  <si>
-    <t>0,93</t>
-  </si>
-  <si>
-    <t>0,92</t>
-  </si>
-  <si>
-    <t>1,16</t>
-  </si>
-  <si>
-    <t>40,38</t>
-  </si>
-  <si>
-    <t>0,88</t>
-  </si>
-  <si>
-    <t>14,91</t>
-  </si>
-  <si>
-    <t>22,63</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>PRINGSEWU</t>
-  </si>
-  <si>
-    <t>4,19</t>
-  </si>
-  <si>
-    <t>0,36</t>
-  </si>
-  <si>
-    <t>13,6</t>
-  </si>
-  <si>
-    <t>4,25</t>
-  </si>
-  <si>
-    <t>0,96</t>
-  </si>
-  <si>
-    <t>1,14</t>
-  </si>
-  <si>
-    <t>3,77</t>
-  </si>
-  <si>
-    <t>2,4</t>
-  </si>
-  <si>
-    <t>41,82</t>
-  </si>
-  <si>
-    <t>1,8</t>
-  </si>
-  <si>
-    <t>0,66</t>
-  </si>
-  <si>
-    <t>17,74</t>
-  </si>
-  <si>
-    <t>3,36</t>
-  </si>
-  <si>
-    <t>0,12</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>4,42</t>
-  </si>
-  <si>
-    <t>0,85</t>
-  </si>
-  <si>
-    <t>0,82</t>
-  </si>
-  <si>
-    <t>0,98</t>
-  </si>
-  <si>
-    <t>1,51</t>
-  </si>
-  <si>
-    <t>48,84</t>
-  </si>
-  <si>
-    <t>1,34</t>
-  </si>
-  <si>
-    <t>12,73</t>
-  </si>
-  <si>
-    <t>7,23</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG BARAT</t>
-  </si>
-  <si>
-    <t>4,28</t>
-  </si>
-  <si>
-    <t>0,16</t>
-  </si>
-  <si>
-    <t>18,71</t>
-  </si>
-  <si>
-    <t>1,18</t>
-  </si>
-  <si>
-    <t>0,53</t>
-  </si>
-  <si>
-    <t>0,61</t>
-  </si>
-  <si>
-    <t>1,44</t>
-  </si>
-  <si>
-    <t>45,46</t>
-  </si>
-  <si>
-    <t>0,21</t>
-  </si>
-  <si>
-    <t>24,64</t>
-  </si>
-  <si>
-    <t>1,04</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>PESISIR BARAT</t>
-  </si>
-  <si>
-    <t>4,38</t>
-  </si>
-  <si>
-    <t>26,14</t>
-  </si>
-  <si>
-    <t>3,49</t>
-  </si>
-  <si>
-    <t>42,53</t>
-  </si>
-  <si>
-    <t>16,93</t>
-  </si>
-  <si>
-    <t>4,15</t>
+    <t>3,5</t>
+  </si>
+  <si>
+    <t>42,76</t>
+  </si>
+  <si>
+    <t>16,87</t>
+  </si>
+  <si>
+    <t>4,12</t>
   </si>
   <si>
     <t>1871</t>
@@ -862,9 +862,6 @@
     <t>6,98</t>
   </si>
   <si>
-    <t>0,95</t>
-  </si>
-  <si>
     <t>9,21</t>
   </si>
   <si>
@@ -904,34 +901,25 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>1,91</t>
-  </si>
-  <si>
-    <t>0,43</t>
-  </si>
-  <si>
-    <t>10,77</t>
-  </si>
-  <si>
-    <t>0,57</t>
-  </si>
-  <si>
-    <t>2,48</t>
-  </si>
-  <si>
-    <t>2,41</t>
-  </si>
-  <si>
-    <t>1,28</t>
-  </si>
-  <si>
-    <t>41,74</t>
-  </si>
-  <si>
-    <t>8,08</t>
-  </si>
-  <si>
-    <t>27,21</t>
+    <t>2,08</t>
+  </si>
+  <si>
+    <t>11,23</t>
+  </si>
+  <si>
+    <t>1,66</t>
+  </si>
+  <si>
+    <t>1,32</t>
+  </si>
+  <si>
+    <t>41,79</t>
+  </si>
+  <si>
+    <t>8,11</t>
+  </si>
+  <si>
+    <t>26,61</t>
   </si>
   <si>
     <t/>
@@ -1857,16 +1845,16 @@
         <v>93</v>
       </c>
       <c r="C6" s="6">
-        <v>53482</v>
+        <v>54369</v>
       </c>
       <c r="D6" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>94</v>
       </c>
       <c r="F6" s="6">
-        <v>2155</v>
+        <v>2196</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>95</v>
@@ -1884,7 +1872,7 @@
         <v>97</v>
       </c>
       <c r="L6" s="6">
-        <v>10058</v>
+        <v>10318</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>98</v>
@@ -1893,85 +1881,85 @@
         <v>3</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="P6" s="6">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="R6" s="6">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="S6" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T6" s="6">
-        <v>1336</v>
+        <v>1350</v>
       </c>
       <c r="U6" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="V6" s="6">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="W6" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="X6" s="6">
-        <v>1546</v>
+        <v>1572</v>
       </c>
       <c r="Y6" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z6" s="6">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="AA6" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AB6" s="6">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AC6" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AD6" s="6">
-        <v>22922</v>
+        <v>23332</v>
       </c>
       <c r="AE6" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AF6" s="6">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AG6" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AH6" s="6">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AI6" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AJ6" s="6">
-        <v>8918</v>
+        <v>9068</v>
       </c>
       <c r="AK6" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AL6" s="6">
         <v>4069</v>
       </c>
       <c r="AM6" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AN6" s="6">
         <v>4</v>
       </c>
       <c r="AO6" s="7" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="AP6" s="6">
         <v>0</v>
@@ -1983,18 +1971,18 @@
         <v>26</v>
       </c>
       <c r="AS6" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C7" s="9">
-        <v>3095</v>
+        <v>3115</v>
       </c>
       <c r="D7" s="9">
         <v>0</v>
@@ -2006,22 +1994,22 @@
         <v>112</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H7" s="9">
         <v>32</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J7" s="9">
         <v>1</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="L7" s="9">
-        <v>764</v>
+        <v>774</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>117</v>
@@ -2057,7 +2045,7 @@
         <v>120</v>
       </c>
       <c r="X7" s="9">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Y7" s="10" t="s">
         <v>121</v>
@@ -2075,7 +2063,7 @@
         <v>119</v>
       </c>
       <c r="AD7" s="9">
-        <v>1189</v>
+        <v>1195</v>
       </c>
       <c r="AE7" s="10" t="s">
         <v>123</v>
@@ -2087,13 +2075,13 @@
         <v>124</v>
       </c>
       <c r="AH7" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI7" s="10" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="AJ7" s="9">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="AK7" s="10" t="s">
         <v>125</v>
@@ -2131,7 +2119,7 @@
         <v>128</v>
       </c>
       <c r="C8" s="9">
-        <v>1189</v>
+        <v>1192</v>
       </c>
       <c r="D8" s="9">
         <v>0</v>
@@ -2170,7 +2158,7 @@
         <v>97</v>
       </c>
       <c r="P8" s="9">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q8" s="10" t="s">
         <v>131</v>
@@ -2182,7 +2170,7 @@
         <v>132</v>
       </c>
       <c r="T8" s="9">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="U8" s="10" t="s">
         <v>133</v>
@@ -2191,19 +2179,19 @@
         <v>9</v>
       </c>
       <c r="W8" s="10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="X8" s="9">
         <v>46</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Z8" s="9">
         <v>5</v>
       </c>
       <c r="AA8" s="10" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AB8" s="9">
         <v>10</v>
@@ -2212,7 +2200,7 @@
         <v>136</v>
       </c>
       <c r="AD8" s="9">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AE8" s="10" t="s">
         <v>137</v>
@@ -2230,7 +2218,7 @@
         <v>139</v>
       </c>
       <c r="AJ8" s="9">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AK8" s="10" t="s">
         <v>140</v>
@@ -2268,25 +2256,25 @@
         <v>143</v>
       </c>
       <c r="C9" s="9">
-        <v>5712</v>
+        <v>5784</v>
       </c>
       <c r="D9" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="F9" s="9">
+        <v>343</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>144</v>
-      </c>
-      <c r="F9" s="9">
-        <v>339</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>145</v>
       </c>
       <c r="H9" s="9">
         <v>22</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="J9" s="9">
         <v>0</v>
@@ -2295,10 +2283,10 @@
         <v>97</v>
       </c>
       <c r="L9" s="9">
-        <v>1068</v>
+        <v>1090</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="N9" s="9">
         <v>0</v>
@@ -2310,55 +2298,55 @@
         <v>1</v>
       </c>
       <c r="Q9" s="10" t="s">
-        <v>144</v>
+        <v>94</v>
       </c>
       <c r="R9" s="9">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S9" s="10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="T9" s="9">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="U9" s="10" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="V9" s="9">
         <v>3</v>
       </c>
       <c r="W9" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="X9" s="9">
         <v>194</v>
       </c>
       <c r="Y9" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Z9" s="9">
         <v>44</v>
       </c>
       <c r="AA9" s="10" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="AB9" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC9" s="10" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AD9" s="9">
-        <v>2497</v>
+        <v>2515</v>
       </c>
       <c r="AE9" s="10" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AF9" s="9">
         <v>236</v>
       </c>
       <c r="AG9" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AH9" s="9">
         <v>0</v>
@@ -2367,16 +2355,16 @@
         <v>97</v>
       </c>
       <c r="AJ9" s="9">
-        <v>1007</v>
+        <v>1033</v>
       </c>
       <c r="AK9" s="10" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AL9" s="9">
         <v>68</v>
       </c>
       <c r="AM9" s="10" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AN9" s="9">
         <v>0</v>
@@ -2394,36 +2382,36 @@
         <v>4</v>
       </c>
       <c r="AS9" s="10" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C10" s="9">
-        <v>5095</v>
+        <v>5633</v>
       </c>
       <c r="D10" s="9">
         <v>3</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>158</v>
+        <v>112</v>
       </c>
       <c r="F10" s="9">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H10" s="9">
         <v>25</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>160</v>
+        <v>106</v>
       </c>
       <c r="J10" s="9">
         <v>0</v>
@@ -2432,94 +2420,94 @@
         <v>97</v>
       </c>
       <c r="L10" s="9">
-        <v>1199</v>
+        <v>1349</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="N10" s="9">
         <v>1</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>144</v>
+        <v>94</v>
       </c>
       <c r="P10" s="9">
         <v>19</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="R10" s="9">
         <v>76</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="T10" s="9">
         <v>185</v>
       </c>
       <c r="U10" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="V10" s="9">
         <v>19</v>
       </c>
       <c r="W10" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="X10" s="9">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="Z10" s="9">
         <v>23</v>
       </c>
       <c r="AA10" s="10" t="s">
-        <v>105</v>
+        <v>162</v>
       </c>
       <c r="AB10" s="9">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AC10" s="10" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AD10" s="9">
-        <v>2088</v>
+        <v>2344</v>
       </c>
       <c r="AE10" s="10" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="AF10" s="9">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG10" s="10" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="AH10" s="9">
         <v>5</v>
       </c>
       <c r="AI10" s="10" t="s">
-        <v>122</v>
+        <v>166</v>
       </c>
       <c r="AJ10" s="9">
-        <v>774</v>
+        <v>861</v>
       </c>
       <c r="AK10" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AL10" s="9">
         <v>119</v>
       </c>
       <c r="AM10" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AN10" s="9">
         <v>1</v>
       </c>
       <c r="AO10" s="10" t="s">
-        <v>144</v>
+        <v>94</v>
       </c>
       <c r="AP10" s="9">
         <v>0</v>
@@ -2531,30 +2519,30 @@
         <v>3</v>
       </c>
       <c r="AS10" s="10" t="s">
-        <v>158</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>171</v>
-      </c>
       <c r="C11" s="9">
-        <v>6044</v>
+        <v>6060</v>
       </c>
       <c r="D11" s="9">
         <v>2</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F11" s="9">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>172</v>
+        <v>121</v>
       </c>
       <c r="H11" s="9">
         <v>6</v>
@@ -2569,10 +2557,10 @@
         <v>97</v>
       </c>
       <c r="L11" s="9">
-        <v>1326</v>
+        <v>1329</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N11" s="9">
         <v>0</v>
@@ -2584,55 +2572,55 @@
         <v>35</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="R11" s="9">
         <v>28</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="T11" s="9">
         <v>360</v>
       </c>
       <c r="U11" s="10" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="V11" s="9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W11" s="10" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="X11" s="9">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Y11" s="10" t="s">
-        <v>121</v>
+        <v>174</v>
       </c>
       <c r="Z11" s="9">
         <v>29</v>
       </c>
       <c r="AA11" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB11" s="9">
+        <v>11</v>
+      </c>
+      <c r="AC11" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="AD11" s="9">
+        <v>2707</v>
+      </c>
+      <c r="AE11" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="AB11" s="9">
-        <v>9</v>
-      </c>
-      <c r="AC11" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="AD11" s="9">
-        <v>2702</v>
-      </c>
-      <c r="AE11" s="10" t="s">
-        <v>179</v>
       </c>
       <c r="AF11" s="9">
         <v>73</v>
       </c>
       <c r="AG11" s="10" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AH11" s="9">
         <v>0</v>
@@ -2641,16 +2629,16 @@
         <v>97</v>
       </c>
       <c r="AJ11" s="9">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="AK11" s="10" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="AL11" s="9">
         <v>39</v>
       </c>
       <c r="AM11" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AN11" s="9">
         <v>0</v>
@@ -2668,18 +2656,18 @@
         <v>2</v>
       </c>
       <c r="AS11" s="10" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>183</v>
-      </c>
       <c r="C12" s="9">
-        <v>5685</v>
+        <v>5693</v>
       </c>
       <c r="D12" s="9">
         <v>0</v>
@@ -2691,25 +2679,25 @@
         <v>129</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H12" s="9">
         <v>135</v>
       </c>
       <c r="I12" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J12" s="9">
+        <v>0</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L12" s="9">
+        <v>813</v>
+      </c>
+      <c r="M12" s="10" t="s">
         <v>185</v>
-      </c>
-      <c r="J12" s="9">
-        <v>0</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="L12" s="9">
-        <v>810</v>
-      </c>
-      <c r="M12" s="10" t="s">
-        <v>186</v>
       </c>
       <c r="N12" s="9">
         <v>0</v>
@@ -2721,37 +2709,37 @@
         <v>3</v>
       </c>
       <c r="Q12" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R12" s="9">
         <v>26</v>
       </c>
       <c r="S12" s="10" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="T12" s="9">
         <v>132</v>
       </c>
       <c r="U12" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="V12" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W12" s="10" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="X12" s="9">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Y12" s="10" t="s">
-        <v>188</v>
+        <v>102</v>
       </c>
       <c r="Z12" s="9">
         <v>32</v>
       </c>
       <c r="AA12" s="10" t="s">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="AB12" s="9">
         <v>0</v>
@@ -2760,16 +2748,16 @@
         <v>97</v>
       </c>
       <c r="AD12" s="9">
-        <v>2522</v>
+        <v>2525</v>
       </c>
       <c r="AE12" s="10" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AF12" s="9">
         <v>46</v>
       </c>
       <c r="AG12" s="10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AH12" s="9">
         <v>0</v>
@@ -2781,19 +2769,19 @@
         <v>944</v>
       </c>
       <c r="AK12" s="10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AL12" s="9">
         <v>757</v>
       </c>
       <c r="AM12" s="10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AN12" s="9">
         <v>1</v>
       </c>
       <c r="AO12" s="10" t="s">
-        <v>144</v>
+        <v>94</v>
       </c>
       <c r="AP12" s="9">
         <v>0</v>
@@ -2805,36 +2793,36 @@
         <v>6</v>
       </c>
       <c r="AS12" s="10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C13" s="9">
+        <v>3043</v>
+      </c>
+      <c r="D13" s="9">
+        <v>0</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F13" s="9">
+        <v>131</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="C13" s="9">
-        <v>3000</v>
-      </c>
-      <c r="D13" s="9">
-        <v>0</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="F13" s="9">
-        <v>130</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>196</v>
       </c>
       <c r="H13" s="9">
         <v>2</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J13" s="9">
         <v>0</v>
@@ -2843,88 +2831,88 @@
         <v>97</v>
       </c>
       <c r="L13" s="9">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N13" s="9">
         <v>1</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="P13" s="9">
         <v>14</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="R13" s="9">
         <v>15</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="T13" s="9">
         <v>74</v>
       </c>
       <c r="U13" s="10" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="V13" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W13" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="X13" s="9">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Y13" s="10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="Z13" s="9">
         <v>12</v>
       </c>
       <c r="AA13" s="10" t="s">
-        <v>102</v>
+        <v>199</v>
       </c>
       <c r="AB13" s="9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC13" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="AD13" s="9">
+        <v>1229</v>
+      </c>
+      <c r="AE13" s="10" t="s">
         <v>201</v>
-      </c>
-      <c r="AD13" s="9">
-        <v>1208</v>
-      </c>
-      <c r="AE13" s="10" t="s">
-        <v>202</v>
       </c>
       <c r="AF13" s="9">
         <v>10</v>
       </c>
       <c r="AG13" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="AH13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ13" s="9">
+        <v>808</v>
+      </c>
+      <c r="AK13" s="10" t="s">
         <v>203</v>
-      </c>
-      <c r="AH13" s="9">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ13" s="9">
-        <v>799</v>
-      </c>
-      <c r="AK13" s="10" t="s">
-        <v>204</v>
       </c>
       <c r="AL13" s="9">
         <v>39</v>
       </c>
       <c r="AM13" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AN13" s="9">
         <v>0</v>
@@ -2947,85 +2935,85 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>207</v>
-      </c>
       <c r="C14" s="9">
-        <v>2139</v>
+        <v>2152</v>
       </c>
       <c r="D14" s="9">
         <v>1</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F14" s="9">
         <v>94</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H14" s="9">
         <v>17</v>
       </c>
       <c r="I14" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="J14" s="9">
+        <v>0</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L14" s="9">
+        <v>457</v>
+      </c>
+      <c r="M14" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="J14" s="9">
-        <v>0</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="L14" s="9">
-        <v>453</v>
-      </c>
-      <c r="M14" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="N14" s="9">
         <v>1</v>
       </c>
       <c r="O14" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P14" s="9">
         <v>20</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="R14" s="9">
         <v>26</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="T14" s="9">
         <v>47</v>
       </c>
       <c r="U14" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="V14" s="9">
         <v>10</v>
       </c>
       <c r="W14" s="10" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="X14" s="9">
         <v>43</v>
       </c>
       <c r="Y14" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Z14" s="9">
         <v>1</v>
       </c>
       <c r="AA14" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AB14" s="9">
         <v>0</v>
@@ -3034,16 +3022,16 @@
         <v>97</v>
       </c>
       <c r="AD14" s="9">
-        <v>989</v>
+        <v>998</v>
       </c>
       <c r="AE14" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AF14" s="9">
         <v>2</v>
       </c>
       <c r="AG14" s="10" t="s">
-        <v>216</v>
+        <v>166</v>
       </c>
       <c r="AH14" s="9">
         <v>0</v>
@@ -3055,19 +3043,19 @@
         <v>334</v>
       </c>
       <c r="AK14" s="10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AL14" s="9">
         <v>99</v>
       </c>
       <c r="AM14" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AN14" s="9">
         <v>1</v>
       </c>
       <c r="AO14" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AP14" s="9">
         <v>0</v>
@@ -3079,18 +3067,18 @@
         <v>1</v>
       </c>
       <c r="AS14" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C15" s="9">
-        <v>7496</v>
+        <v>7498</v>
       </c>
       <c r="D15" s="9">
         <v>0</v>
@@ -3102,13 +3090,13 @@
         <v>243</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H15" s="9">
         <v>88</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J15" s="9">
         <v>0</v>
@@ -3120,31 +3108,31 @@
         <v>963</v>
       </c>
       <c r="M15" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="N15" s="9">
+        <v>0</v>
+      </c>
+      <c r="O15" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="P15" s="9">
+        <v>48</v>
+      </c>
+      <c r="Q15" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="R15" s="9">
+        <v>72</v>
+      </c>
+      <c r="S15" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="T15" s="9">
+        <v>71</v>
+      </c>
+      <c r="U15" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="N15" s="9">
-        <v>0</v>
-      </c>
-      <c r="O15" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="P15" s="9">
-        <v>52</v>
-      </c>
-      <c r="Q15" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="R15" s="9">
-        <v>70</v>
-      </c>
-      <c r="S15" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="T15" s="9">
-        <v>69</v>
-      </c>
-      <c r="U15" s="10" t="s">
-        <v>226</v>
       </c>
       <c r="V15" s="9">
         <v>6</v>
@@ -3153,16 +3141,16 @@
         <v>139</v>
       </c>
       <c r="X15" s="9">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y15" s="10" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="Z15" s="9">
         <v>7</v>
       </c>
       <c r="AA15" s="10" t="s">
-        <v>216</v>
+        <v>166</v>
       </c>
       <c r="AB15" s="9">
         <v>0</v>
@@ -3174,37 +3162,37 @@
         <v>3027</v>
       </c>
       <c r="AE15" s="10" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="AF15" s="9">
         <v>66</v>
       </c>
       <c r="AG15" s="10" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="AH15" s="9">
         <v>1</v>
       </c>
       <c r="AI15" s="10" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="AJ15" s="9">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="AK15" s="10" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="AL15" s="9">
         <v>1696</v>
       </c>
       <c r="AM15" s="10" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="AN15" s="9">
         <v>1</v>
       </c>
       <c r="AO15" s="10" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="AP15" s="9">
         <v>0</v>
@@ -3216,18 +3204,18 @@
         <v>2</v>
       </c>
       <c r="AS15" s="10" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C16" s="9">
-        <v>1669</v>
+        <v>1713</v>
       </c>
       <c r="D16" s="9">
         <v>0</v>
@@ -3236,16 +3224,16 @@
         <v>97</v>
       </c>
       <c r="F16" s="9">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="H16" s="9">
         <v>6</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="J16" s="9">
         <v>0</v>
@@ -3254,10 +3242,10 @@
         <v>97</v>
       </c>
       <c r="L16" s="9">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="N16" s="9">
         <v>0</v>
@@ -3266,76 +3254,76 @@
         <v>97</v>
       </c>
       <c r="P16" s="9">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="Q16" s="10" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="R16" s="9">
         <v>16</v>
       </c>
       <c r="S16" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="T16" s="9">
+        <v>63</v>
+      </c>
+      <c r="U16" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="V16" s="9">
+        <v>18</v>
+      </c>
+      <c r="W16" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="X16" s="9">
+        <v>65</v>
+      </c>
+      <c r="Y16" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="Z16" s="9">
+        <v>11</v>
+      </c>
+      <c r="AA16" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="AB16" s="9">
+        <v>38</v>
+      </c>
+      <c r="AC16" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="AD16" s="9">
+        <v>721</v>
+      </c>
+      <c r="AE16" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="T16" s="9">
-        <v>54</v>
-      </c>
-      <c r="U16" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="V16" s="9">
-        <v>19</v>
-      </c>
-      <c r="W16" s="10" t="s">
+      <c r="AF16" s="9">
+        <v>31</v>
+      </c>
+      <c r="AG16" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="X16" s="9">
-        <v>63</v>
-      </c>
-      <c r="Y16" s="10" t="s">
+      <c r="AH16" s="9">
+        <v>8</v>
+      </c>
+      <c r="AI16" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="Z16" s="9">
-        <v>10</v>
-      </c>
-      <c r="AA16" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="AB16" s="9">
-        <v>40</v>
-      </c>
-      <c r="AC16" s="10" t="s">
+      <c r="AJ16" s="9">
+        <v>305</v>
+      </c>
+      <c r="AK16" s="10" t="s">
         <v>241</v>
-      </c>
-      <c r="AD16" s="9">
-        <v>698</v>
-      </c>
-      <c r="AE16" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="AF16" s="9">
-        <v>30</v>
-      </c>
-      <c r="AG16" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="AH16" s="9">
-        <v>11</v>
-      </c>
-      <c r="AI16" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="AJ16" s="9">
-        <v>296</v>
-      </c>
-      <c r="AK16" s="10" t="s">
-        <v>245</v>
       </c>
       <c r="AL16" s="9">
         <v>56</v>
       </c>
       <c r="AM16" s="10" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="AN16" s="9">
         <v>0</v>
@@ -3353,36 +3341,36 @@
         <v>2</v>
       </c>
       <c r="AS16" s="10" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C17" s="9">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="D17" s="9">
         <v>1</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F17" s="9">
         <v>135</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="H17" s="9">
         <v>26</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="J17" s="9">
         <v>0</v>
@@ -3394,7 +3382,7 @@
         <v>607</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>197</v>
+        <v>248</v>
       </c>
       <c r="N17" s="9">
         <v>0</v>
@@ -3406,37 +3394,37 @@
         <v>25</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="R17" s="9">
         <v>26</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="T17" s="9">
         <v>30</v>
       </c>
       <c r="U17" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="V17" s="9">
         <v>11</v>
       </c>
       <c r="W17" s="10" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="X17" s="9">
         <v>46</v>
       </c>
       <c r="Y17" s="10" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Z17" s="9">
         <v>2</v>
       </c>
       <c r="AA17" s="10" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AB17" s="9">
         <v>3</v>
@@ -3445,16 +3433,16 @@
         <v>122</v>
       </c>
       <c r="AD17" s="9">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="AE17" s="10" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AF17" s="9">
         <v>41</v>
       </c>
       <c r="AG17" s="10" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AH17" s="9">
         <v>0</v>
@@ -3466,13 +3454,13 @@
         <v>389</v>
       </c>
       <c r="AK17" s="10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AL17" s="9">
         <v>221</v>
       </c>
       <c r="AM17" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AN17" s="9">
         <v>0</v>
@@ -3495,13 +3483,13 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C18" s="9">
-        <v>3742</v>
+        <v>3812</v>
       </c>
       <c r="D18" s="9">
         <v>0</v>
@@ -3513,13 +3501,13 @@
         <v>160</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>261</v>
+        <v>230</v>
       </c>
       <c r="H18" s="9">
         <v>6</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="J18" s="9">
         <v>0</v>
@@ -3528,10 +3516,10 @@
         <v>97</v>
       </c>
       <c r="L18" s="9">
-        <v>700</v>
+        <v>732</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="N18" s="9">
         <v>0</v>
@@ -3543,55 +3531,55 @@
         <v>44</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="R18" s="9">
         <v>20</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>265</v>
+        <v>105</v>
       </c>
       <c r="T18" s="9">
         <v>44</v>
       </c>
       <c r="U18" s="10" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="V18" s="9">
         <v>23</v>
       </c>
       <c r="W18" s="10" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="X18" s="9">
         <v>54</v>
       </c>
       <c r="Y18" s="10" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="Z18" s="9">
         <v>6</v>
       </c>
       <c r="AA18" s="10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AB18" s="9">
         <v>15</v>
       </c>
       <c r="AC18" s="10" t="s">
-        <v>102</v>
+        <v>199</v>
       </c>
       <c r="AD18" s="9">
-        <v>1701</v>
+        <v>1735</v>
       </c>
       <c r="AE18" s="10" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="AF18" s="9">
         <v>8</v>
       </c>
       <c r="AG18" s="10" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AH18" s="9">
         <v>0</v>
@@ -3600,16 +3588,16 @@
         <v>97</v>
       </c>
       <c r="AJ18" s="9">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="AK18" s="10" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AL18" s="9">
         <v>39</v>
       </c>
       <c r="AM18" s="10" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="AN18" s="9">
         <v>0</v>
@@ -3632,13 +3620,13 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C19" s="9">
-        <v>3520</v>
+        <v>3545</v>
       </c>
       <c r="D19" s="9">
         <v>0</v>
@@ -3650,13 +3638,13 @@
         <v>154</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="H19" s="9">
         <v>18</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>104</v>
+        <v>271</v>
       </c>
       <c r="J19" s="9">
         <v>0</v>
@@ -3665,10 +3653,10 @@
         <v>97</v>
       </c>
       <c r="L19" s="9">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="N19" s="9">
         <v>0</v>
@@ -3680,28 +3668,28 @@
         <v>2</v>
       </c>
       <c r="Q19" s="10" t="s">
-        <v>158</v>
+        <v>273</v>
       </c>
       <c r="R19" s="9">
         <v>13</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>162</v>
+        <v>274</v>
       </c>
       <c r="T19" s="9">
         <v>16</v>
       </c>
       <c r="U19" s="10" t="s">
-        <v>105</v>
+        <v>275</v>
       </c>
       <c r="V19" s="9">
         <v>1</v>
       </c>
       <c r="W19" s="10" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="X19" s="9">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Y19" s="10" t="s">
         <v>276</v>
@@ -3710,16 +3698,16 @@
         <v>4</v>
       </c>
       <c r="AA19" s="10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AB19" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC19" s="10" t="s">
-        <v>116</v>
+        <v>273</v>
       </c>
       <c r="AD19" s="9">
-        <v>1497</v>
+        <v>1516</v>
       </c>
       <c r="AE19" s="10" t="s">
         <v>277</v>
@@ -3734,10 +3722,10 @@
         <v>1</v>
       </c>
       <c r="AI19" s="10" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="AJ19" s="9">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AK19" s="10" t="s">
         <v>278</v>
@@ -3764,7 +3752,7 @@
         <v>2</v>
       </c>
       <c r="AS19" s="10" t="s">
-        <v>158</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
@@ -3793,7 +3781,7 @@
         <v>6</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>283</v>
+        <v>223</v>
       </c>
       <c r="J20" s="9">
         <v>0</v>
@@ -3805,7 +3793,7 @@
         <v>58</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N20" s="9">
         <v>0</v>
@@ -3817,55 +3805,55 @@
         <v>5</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="R20" s="9">
         <v>4</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T20" s="9">
         <v>41</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="V20" s="9">
         <v>16</v>
       </c>
       <c r="W20" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="X20" s="9">
         <v>45</v>
       </c>
       <c r="Y20" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Z20" s="9">
         <v>88</v>
       </c>
       <c r="AA20" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AB20" s="9">
         <v>2</v>
       </c>
       <c r="AC20" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AD20" s="9">
         <v>231</v>
       </c>
       <c r="AE20" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AF20" s="9">
         <v>12</v>
       </c>
       <c r="AG20" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AH20" s="9">
         <v>0</v>
@@ -3877,13 +3865,13 @@
         <v>57</v>
       </c>
       <c r="AK20" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AL20" s="9">
         <v>19</v>
       </c>
       <c r="AM20" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AN20" s="9">
         <v>0</v>
@@ -3901,36 +3889,36 @@
         <v>2</v>
       </c>
       <c r="AS20" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="C21" s="9">
+        <v>1443</v>
+      </c>
+      <c r="D21" s="9">
+        <v>0</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F21" s="9">
+        <v>30</v>
+      </c>
+      <c r="G21" s="10" t="s">
         <v>296</v>
-      </c>
-      <c r="C21" s="9">
-        <v>1411</v>
-      </c>
-      <c r="D21" s="9">
-        <v>0</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="F21" s="9">
-        <v>27</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>297</v>
       </c>
       <c r="H21" s="9">
         <v>6</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>298</v>
+        <v>131</v>
       </c>
       <c r="J21" s="9">
         <v>0</v>
@@ -3939,10 +3927,10 @@
         <v>97</v>
       </c>
       <c r="L21" s="9">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="N21" s="9">
         <v>0</v>
@@ -3960,49 +3948,49 @@
         <v>8</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>300</v>
+        <v>124</v>
       </c>
       <c r="T21" s="9">
         <v>35</v>
       </c>
       <c r="U21" s="10" t="s">
-        <v>301</v>
+        <v>197</v>
       </c>
       <c r="V21" s="9">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="W21" s="10" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="X21" s="9">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y21" s="10" t="s">
-        <v>302</v>
+        <v>197</v>
       </c>
       <c r="Z21" s="9">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AA21" s="10" t="s">
-        <v>199</v>
+        <v>152</v>
       </c>
       <c r="AB21" s="9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC21" s="10" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="AD21" s="9">
-        <v>589</v>
+        <v>603</v>
       </c>
       <c r="AE21" s="10" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="AF21" s="9">
         <v>3</v>
       </c>
       <c r="AG21" s="10" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AH21" s="9">
         <v>0</v>
@@ -4011,16 +3999,16 @@
         <v>97</v>
       </c>
       <c r="AJ21" s="9">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AK21" s="10" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="AL21" s="9">
         <v>384</v>
       </c>
       <c r="AM21" s="10" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="AN21" s="9">
         <v>0</v>
@@ -4043,22 +4031,22 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C22" s="12">
-        <v>53482</v>
+        <v>54369</v>
       </c>
       <c r="D22" s="12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>94</v>
       </c>
       <c r="F22" s="12">
-        <v>2155</v>
+        <v>2196</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>95</v>
@@ -4076,7 +4064,7 @@
         <v>97</v>
       </c>
       <c r="L22" s="12">
-        <v>10058</v>
+        <v>10318</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>98</v>
@@ -4085,85 +4073,85 @@
         <v>3</v>
       </c>
       <c r="O22" s="13" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="P22" s="12">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="Q22" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="R22" s="12">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="S22" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T22" s="12">
-        <v>1336</v>
+        <v>1350</v>
       </c>
       <c r="U22" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="V22" s="12">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="W22" s="13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="X22" s="12">
-        <v>1546</v>
+        <v>1572</v>
       </c>
       <c r="Y22" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z22" s="12">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="AA22" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AB22" s="12">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AC22" s="13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AD22" s="12">
-        <v>22922</v>
+        <v>23332</v>
       </c>
       <c r="AE22" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AF22" s="12">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AG22" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AH22" s="12">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AI22" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AJ22" s="12">
-        <v>8918</v>
+        <v>9068</v>
       </c>
       <c r="AK22" s="13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AL22" s="12">
         <v>4069</v>
       </c>
       <c r="AM22" s="13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AN22" s="12">
         <v>4</v>
       </c>
       <c r="AO22" s="13" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="AP22" s="12">
         <v>0</v>
@@ -4175,7 +4163,7 @@
         <v>26</v>
       </c>
       <c r="AS22" s="13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
+++ b/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="297">
   <si>
     <t>DATA RADAR ANOMALI KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 27 Agu 2026, 12.59</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 28 Agu 2026, 10.22</t>
   </si>
   <si>
     <t>Kode</t>
@@ -301,610 +301,601 @@
     <t>4,17</t>
   </si>
   <si>
-    <t>0,71</t>
+    <t>0,7</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>19,17</t>
+    <t>19,37</t>
+  </si>
+  <si>
+    <t>0,44</t>
+  </si>
+  <si>
+    <t>2,46</t>
+  </si>
+  <si>
+    <t>0,27</t>
+  </si>
+  <si>
+    <t>2,89</t>
+  </si>
+  <si>
+    <t>0,55</t>
+  </si>
+  <si>
+    <t>0,35</t>
+  </si>
+  <si>
+    <t>43,08</t>
+  </si>
+  <si>
+    <t>1,06</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>16,67</t>
+  </si>
+  <si>
+    <t>7,19</t>
+  </si>
+  <si>
+    <t>0,05</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>LAMPUNG BARAT</t>
+  </si>
+  <si>
+    <t>3,59</t>
+  </si>
+  <si>
+    <t>1,03</t>
+  </si>
+  <si>
+    <t>24,82</t>
+  </si>
+  <si>
+    <t>0,74</t>
+  </si>
+  <si>
+    <t>0,13</t>
+  </si>
+  <si>
+    <t>1,6</t>
+  </si>
+  <si>
+    <t>4,23</t>
+  </si>
+  <si>
+    <t>0,1</t>
+  </si>
+  <si>
+    <t>38,42</t>
+  </si>
+  <si>
+    <t>12,32</t>
+  </si>
+  <si>
+    <t>12,19</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>TANGGAMUS</t>
+  </si>
+  <si>
+    <t>6,57</t>
+  </si>
+  <si>
+    <t>19,6</t>
+  </si>
+  <si>
+    <t>0,3</t>
+  </si>
+  <si>
+    <t>0,91</t>
+  </si>
+  <si>
+    <t>3,35</t>
+  </si>
+  <si>
+    <t>0,24</t>
+  </si>
+  <si>
+    <t>3,23</t>
+  </si>
+  <si>
+    <t>41,75</t>
+  </si>
+  <si>
+    <t>0,12</t>
+  </si>
+  <si>
+    <t>0,06</t>
+  </si>
+  <si>
+    <t>22,7</t>
+  </si>
+  <si>
+    <t>0,43</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>LAMPUNG SELATAN</t>
+  </si>
+  <si>
+    <t>0,02</t>
+  </si>
+  <si>
+    <t>5,83</t>
+  </si>
+  <si>
+    <t>0,37</t>
+  </si>
+  <si>
+    <t>18,98</t>
+  </si>
+  <si>
+    <t>0,56</t>
+  </si>
+  <si>
+    <t>3,28</t>
+  </si>
+  <si>
+    <t>3,37</t>
+  </si>
+  <si>
+    <t>0,75</t>
+  </si>
+  <si>
+    <t>43,73</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>17,82</t>
+  </si>
+  <si>
+    <t>1,16</t>
+  </si>
+  <si>
+    <t>0,07</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>LAMPUNG TIMUR</t>
+  </si>
+  <si>
+    <t>4,28</t>
+  </si>
+  <si>
+    <t>0,4</t>
+  </si>
+  <si>
+    <t>24,63</t>
+  </si>
+  <si>
+    <t>0,31</t>
+  </si>
+  <si>
+    <t>1,23</t>
+  </si>
+  <si>
+    <t>2,99</t>
+  </si>
+  <si>
+    <t>0,32</t>
+  </si>
+  <si>
+    <t>3,6</t>
+  </si>
+  <si>
+    <t>1,97</t>
+  </si>
+  <si>
+    <t>42,12</t>
+  </si>
+  <si>
+    <t>0,45</t>
+  </si>
+  <si>
+    <t>15,18</t>
+  </si>
+  <si>
+    <t>1,92</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>LAMPUNG TENGAH</t>
+  </si>
+  <si>
+    <t>4,25</t>
+  </si>
+  <si>
+    <t>22,01</t>
+  </si>
+  <si>
+    <t>0,46</t>
+  </si>
+  <si>
+    <t>5,9</t>
+  </si>
+  <si>
+    <t>4,18</t>
+  </si>
+  <si>
+    <t>0,47</t>
+  </si>
+  <si>
+    <t>0,15</t>
+  </si>
+  <si>
+    <t>44,74</t>
+  </si>
+  <si>
+    <t>1,19</t>
+  </si>
+  <si>
+    <t>15,2</t>
+  </si>
+  <si>
+    <t>0,64</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>2,58</t>
+  </si>
+  <si>
+    <t>2,31</t>
+  </si>
+  <si>
+    <t>14,4</t>
+  </si>
+  <si>
+    <t>2,25</t>
+  </si>
+  <si>
+    <t>2,44</t>
+  </si>
+  <si>
+    <t>44,38</t>
+  </si>
+  <si>
+    <t>0,79</t>
+  </si>
+  <si>
+    <t>16,73</t>
+  </si>
+  <si>
+    <t>12,93</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
+    <t>20,1</t>
+  </si>
+  <si>
+    <t>0,61</t>
+  </si>
+  <si>
+    <t>2,53</t>
+  </si>
+  <si>
+    <t>2,95</t>
+  </si>
+  <si>
+    <t>0,38</t>
+  </si>
+  <si>
+    <t>40,93</t>
+  </si>
+  <si>
+    <t>26,35</t>
+  </si>
+  <si>
+    <t>1,25</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG</t>
+  </si>
+  <si>
+    <t>4,32</t>
+  </si>
+  <si>
+    <t>0,78</t>
+  </si>
+  <si>
+    <t>21,44</t>
+  </si>
+  <si>
+    <t>0,92</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>2,16</t>
+  </si>
+  <si>
+    <t>2,02</t>
+  </si>
+  <si>
+    <t>46,41</t>
+  </si>
+  <si>
+    <t>0,09</t>
+  </si>
+  <si>
+    <t>15,46</t>
+  </si>
+  <si>
+    <t>4,55</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PESAWARAN</t>
+  </si>
+  <si>
+    <t>3,27</t>
+  </si>
+  <si>
+    <t>1,15</t>
+  </si>
+  <si>
+    <t>13,33</t>
+  </si>
+  <si>
+    <t>0,58</t>
+  </si>
+  <si>
+    <t>0,94</t>
+  </si>
+  <si>
+    <t>0,98</t>
+  </si>
+  <si>
+    <t>1,24</t>
+  </si>
+  <si>
+    <t>40,55</t>
+  </si>
+  <si>
+    <t>0,86</t>
+  </si>
+  <si>
+    <t>14,73</t>
+  </si>
+  <si>
+    <t>22,17</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>PRINGSEWU</t>
+  </si>
+  <si>
+    <t>5,01</t>
+  </si>
+  <si>
+    <t>14,61</t>
+  </si>
+  <si>
+    <t>1,81</t>
+  </si>
+  <si>
+    <t>4,34</t>
+  </si>
+  <si>
+    <t>0,57</t>
+  </si>
+  <si>
+    <t>1,14</t>
+  </si>
+  <si>
+    <t>43,21</t>
+  </si>
+  <si>
+    <t>0,26</t>
+  </si>
+  <si>
+    <t>18,33</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
+  </si>
+  <si>
+    <t>4,44</t>
+  </si>
+  <si>
+    <t>0,85</t>
+  </si>
+  <si>
+    <t>19,85</t>
+  </si>
+  <si>
+    <t>0,33</t>
+  </si>
+  <si>
+    <t>1,53</t>
+  </si>
+  <si>
+    <t>48,91</t>
+  </si>
+  <si>
+    <t>1,34</t>
+  </si>
+  <si>
+    <t>12,7</t>
+  </si>
+  <si>
+    <t>7,22</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG BARAT</t>
+  </si>
+  <si>
+    <t>4,16</t>
+  </si>
+  <si>
+    <t>20,18</t>
+  </si>
+  <si>
+    <t>0,88</t>
   </si>
   <si>
     <t>0,5</t>
   </si>
   <si>
-    <t>0,7</t>
-  </si>
-  <si>
-    <t>2,45</t>
-  </si>
-  <si>
-    <t>0,33</t>
-  </si>
-  <si>
-    <t>2,87</t>
-  </si>
-  <si>
-    <t>0,53</t>
-  </si>
-  <si>
-    <t>0,4</t>
-  </si>
-  <si>
-    <t>42,96</t>
-  </si>
-  <si>
-    <t>1,08</t>
-  </si>
-  <si>
-    <t>0,03</t>
-  </si>
-  <si>
-    <t>16,74</t>
-  </si>
-  <si>
-    <t>7,3</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>LAMPUNG BARAT</t>
-  </si>
-  <si>
-    <t>3,59</t>
-  </si>
-  <si>
-    <t>1,03</t>
-  </si>
-  <si>
-    <t>24,84</t>
-  </si>
-  <si>
-    <t>0,74</t>
-  </si>
-  <si>
-    <t>0,13</t>
-  </si>
-  <si>
-    <t>1,6</t>
-  </si>
-  <si>
-    <t>4,24</t>
-  </si>
-  <si>
-    <t>0,1</t>
-  </si>
-  <si>
-    <t>0,06</t>
-  </si>
-  <si>
-    <t>38,41</t>
-  </si>
-  <si>
-    <t>0,55</t>
-  </si>
-  <si>
-    <t>12,32</t>
-  </si>
-  <si>
-    <t>12,2</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>TANGGAMUS</t>
-  </si>
-  <si>
-    <t>6,61</t>
-  </si>
-  <si>
-    <t>19,63</t>
-  </si>
-  <si>
-    <t>0,24</t>
-  </si>
-  <si>
-    <t>0,92</t>
-  </si>
-  <si>
-    <t>3,36</t>
-  </si>
-  <si>
-    <t>3,24</t>
-  </si>
-  <si>
-    <t>0,31</t>
-  </si>
-  <si>
-    <t>41,65</t>
-  </si>
-  <si>
-    <t>0,12</t>
-  </si>
-  <si>
-    <t>22,75</t>
-  </si>
-  <si>
-    <t>0,43</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>LAMPUNG SELATAN</t>
-  </si>
-  <si>
-    <t>0,02</t>
-  </si>
-  <si>
-    <t>5,89</t>
-  </si>
-  <si>
-    <t>0,38</t>
-  </si>
-  <si>
-    <t>18,85</t>
-  </si>
-  <si>
-    <t>0,57</t>
-  </si>
-  <si>
-    <t>3,32</t>
-  </si>
-  <si>
-    <t>3,34</t>
-  </si>
-  <si>
-    <t>0,76</t>
-  </si>
-  <si>
-    <t>43,61</t>
-  </si>
-  <si>
-    <t>4,06</t>
-  </si>
-  <si>
-    <t>17,88</t>
-  </si>
-  <si>
-    <t>1,17</t>
-  </si>
-  <si>
-    <t>0,07</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>LAMPUNG TIMUR</t>
-  </si>
-  <si>
-    <t>4,29</t>
-  </si>
-  <si>
-    <t>0,42</t>
-  </si>
-  <si>
-    <t>24,21</t>
-  </si>
-  <si>
-    <t>0,32</t>
-  </si>
-  <si>
-    <t>1,28</t>
-  </si>
-  <si>
-    <t>3,12</t>
-  </si>
-  <si>
-    <t>0,34</t>
-  </si>
-  <si>
-    <t>3,7</t>
-  </si>
-  <si>
-    <t>0,39</t>
-  </si>
-  <si>
-    <t>2,08</t>
-  </si>
-  <si>
-    <t>41,81</t>
-  </si>
-  <si>
-    <t>0,46</t>
-  </si>
-  <si>
-    <t>15,33</t>
-  </si>
-  <si>
-    <t>2,01</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>LAMPUNG TENGAH</t>
-  </si>
-  <si>
-    <t>21,92</t>
-  </si>
-  <si>
-    <t>0,56</t>
-  </si>
-  <si>
-    <t>5,93</t>
-  </si>
-  <si>
-    <t>4,21</t>
+    <t>1,51</t>
+  </si>
+  <si>
+    <t>45,49</t>
+  </si>
+  <si>
+    <t>0,2</t>
+  </si>
+  <si>
+    <t>23,55</t>
+  </si>
+  <si>
+    <t>1,01</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>PESISIR BARAT</t>
+  </si>
+  <si>
+    <t>4,46</t>
+  </si>
+  <si>
+    <t>26,59</t>
+  </si>
+  <si>
+    <t>3,44</t>
+  </si>
+  <si>
+    <t>42,56</t>
+  </si>
+  <si>
+    <t>0,68</t>
+  </si>
+  <si>
+    <t>16,94</t>
+  </si>
+  <si>
+    <t>3,83</t>
+  </si>
+  <si>
+    <t>1871</t>
+  </si>
+  <si>
+    <t>BANDAR LAMPUNG</t>
+  </si>
+  <si>
+    <t>6,97</t>
+  </si>
+  <si>
+    <t>0,95</t>
+  </si>
+  <si>
+    <t>9,19</t>
+  </si>
+  <si>
+    <t>0,63</t>
+  </si>
+  <si>
+    <t>6,5</t>
+  </si>
+  <si>
+    <t>2,54</t>
+  </si>
+  <si>
+    <t>7,13</t>
+  </si>
+  <si>
+    <t>13,95</t>
   </si>
   <si>
     <t>0,48</t>
   </si>
   <si>
-    <t>0,15</t>
-  </si>
-  <si>
-    <t>44,72</t>
-  </si>
-  <si>
-    <t>1,2</t>
-  </si>
-  <si>
-    <t>15,23</t>
-  </si>
-  <si>
-    <t>0,64</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
-  </si>
-  <si>
-    <t>2,57</t>
-  </si>
-  <si>
-    <t>2,31</t>
-  </si>
-  <si>
-    <t>14,34</t>
-  </si>
-  <si>
-    <t>0,45</t>
-  </si>
-  <si>
-    <t>2,26</t>
-  </si>
-  <si>
-    <t>44,36</t>
-  </si>
-  <si>
-    <t>0,79</t>
-  </si>
-  <si>
-    <t>16,72</t>
-  </si>
-  <si>
-    <t>12,97</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>4,26</t>
-  </si>
-  <si>
-    <t>20,01</t>
-  </si>
-  <si>
-    <t>0,2</t>
-  </si>
-  <si>
-    <t>0,62</t>
-  </si>
-  <si>
-    <t>2,5</t>
-  </si>
-  <si>
-    <t>2,93</t>
-  </si>
-  <si>
-    <t>40,66</t>
-  </si>
-  <si>
-    <t>26,45</t>
-  </si>
-  <si>
-    <t>1,27</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG</t>
-  </si>
-  <si>
-    <t>4,33</t>
-  </si>
-  <si>
-    <t>0,78</t>
-  </si>
-  <si>
-    <t>21,44</t>
-  </si>
-  <si>
-    <t>2,17</t>
-  </si>
-  <si>
-    <t>1,98</t>
-  </si>
-  <si>
-    <t>46,38</t>
-  </si>
-  <si>
-    <t>0,09</t>
-  </si>
-  <si>
-    <t>15,49</t>
-  </si>
-  <si>
-    <t>4,56</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>PESAWARAN</t>
-  </si>
-  <si>
-    <t>12,84</t>
-  </si>
-  <si>
-    <t>0,6</t>
-  </si>
-  <si>
-    <t>0,96</t>
-  </si>
-  <si>
-    <t>0,99</t>
-  </si>
-  <si>
-    <t>1,19</t>
-  </si>
-  <si>
-    <t>0,11</t>
-  </si>
-  <si>
-    <t>40,37</t>
-  </si>
-  <si>
-    <t>0,88</t>
-  </si>
-  <si>
-    <t>14,94</t>
-  </si>
-  <si>
-    <t>22,62</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>PRINGSEWU</t>
-  </si>
-  <si>
-    <t>4,94</t>
-  </si>
-  <si>
-    <t>14,39</t>
-  </si>
-  <si>
-    <t>3,13</t>
-  </si>
-  <si>
-    <t>0,93</t>
-  </si>
-  <si>
-    <t>3,73</t>
-  </si>
-  <si>
-    <t>3,68</t>
-  </si>
-  <si>
-    <t>42,45</t>
-  </si>
-  <si>
-    <t>1,7</t>
-  </si>
-  <si>
-    <t>0,27</t>
-  </si>
-  <si>
-    <t>17,68</t>
-  </si>
-  <si>
-    <t>3,08</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>4,41</t>
-  </si>
-  <si>
-    <t>0,85</t>
-  </si>
-  <si>
-    <t>19,85</t>
-  </si>
-  <si>
-    <t>0,75</t>
-  </si>
-  <si>
-    <t>0,98</t>
-  </si>
-  <si>
-    <t>1,54</t>
-  </si>
-  <si>
-    <t>48,89</t>
-  </si>
-  <si>
-    <t>1,34</t>
-  </si>
-  <si>
-    <t>12,72</t>
-  </si>
-  <si>
-    <t>7,23</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG BARAT</t>
-  </si>
-  <si>
-    <t>4,23</t>
-  </si>
-  <si>
-    <t>19,57</t>
-  </si>
-  <si>
-    <t>1,01</t>
-  </si>
-  <si>
-    <t>0,52</t>
-  </si>
-  <si>
-    <t>1,26</t>
+    <t>36,61</t>
+  </si>
+  <si>
+    <t>1,9</t>
+  </si>
+  <si>
+    <t>9,03</t>
+  </si>
+  <si>
+    <t>3,01</t>
+  </si>
+  <si>
+    <t>1872</t>
+  </si>
+  <si>
+    <t>METRO</t>
+  </si>
+  <si>
+    <t>2,32</t>
   </si>
   <si>
     <t>0,41</t>
   </si>
   <si>
-    <t>1,45</t>
-  </si>
-  <si>
-    <t>45,41</t>
-  </si>
-  <si>
-    <t>0,21</t>
-  </si>
-  <si>
-    <t>24,06</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>PESISIR BARAT</t>
-  </si>
-  <si>
-    <t>26,51</t>
-  </si>
-  <si>
-    <t>0,37</t>
-  </si>
-  <si>
-    <t>3,45</t>
-  </si>
-  <si>
-    <t>42,6</t>
-  </si>
-  <si>
-    <t>0,69</t>
-  </si>
-  <si>
-    <t>16,92</t>
-  </si>
-  <si>
-    <t>3,88</t>
-  </si>
-  <si>
-    <t>1871</t>
-  </si>
-  <si>
-    <t>BANDAR LAMPUNG</t>
-  </si>
-  <si>
-    <t>6,98</t>
-  </si>
-  <si>
-    <t>0,95</t>
-  </si>
-  <si>
-    <t>9,21</t>
-  </si>
-  <si>
-    <t>0,63</t>
-  </si>
-  <si>
-    <t>6,51</t>
-  </si>
-  <si>
-    <t>2,54</t>
-  </si>
-  <si>
-    <t>7,14</t>
-  </si>
-  <si>
-    <t>13,97</t>
-  </si>
-  <si>
-    <t>36,67</t>
-  </si>
-  <si>
-    <t>1,9</t>
-  </si>
-  <si>
-    <t>9,05</t>
-  </si>
-  <si>
-    <t>3,02</t>
-  </si>
-  <si>
-    <t>1872</t>
-  </si>
-  <si>
-    <t>METRO</t>
-  </si>
-  <si>
-    <t>2,14</t>
-  </si>
-  <si>
-    <t>11,26</t>
-  </si>
-  <si>
-    <t>2,42</t>
-  </si>
-  <si>
-    <t>1,38</t>
-  </si>
-  <si>
-    <t>1,24</t>
-  </si>
-  <si>
-    <t>41,78</t>
-  </si>
-  <si>
-    <t>8,15</t>
-  </si>
-  <si>
-    <t>26,52</t>
+    <t>11,48</t>
+  </si>
+  <si>
+    <t>2,39</t>
+  </si>
+  <si>
+    <t>2,66</t>
+  </si>
+  <si>
+    <t>41,8</t>
+  </si>
+  <si>
+    <t>8,13</t>
+  </si>
+  <si>
+    <t>26,23</t>
   </si>
   <si>
     <t/>
@@ -1830,7 +1821,7 @@
         <v>93</v>
       </c>
       <c r="C6" s="6">
-        <v>55741</v>
+        <v>56632</v>
       </c>
       <c r="D6" s="6">
         <v>7</v>
@@ -1839,7 +1830,7 @@
         <v>94</v>
       </c>
       <c r="F6" s="6">
-        <v>2322</v>
+        <v>2361</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>95</v>
@@ -1857,7 +1848,7 @@
         <v>97</v>
       </c>
       <c r="L6" s="6">
-        <v>10684</v>
+        <v>10972</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>98</v>
@@ -1869,76 +1860,76 @@
         <v>94</v>
       </c>
       <c r="P6" s="6">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="Q6" s="7" t="s">
         <v>99</v>
       </c>
       <c r="R6" s="6">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="S6" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="T6" s="6">
+        <v>1391</v>
+      </c>
+      <c r="U6" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="T6" s="6">
-        <v>1368</v>
-      </c>
-      <c r="U6" s="7" t="s">
+      <c r="V6" s="6">
+        <v>151</v>
+      </c>
+      <c r="W6" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="V6" s="6">
-        <v>183</v>
-      </c>
-      <c r="W6" s="7" t="s">
+      <c r="X6" s="6">
+        <v>1637</v>
+      </c>
+      <c r="Y6" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="X6" s="6">
-        <v>1599</v>
-      </c>
-      <c r="Y6" s="7" t="s">
+      <c r="Z6" s="6">
+        <v>313</v>
+      </c>
+      <c r="AA6" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="Z6" s="6">
-        <v>295</v>
-      </c>
-      <c r="AA6" s="7" t="s">
+      <c r="AB6" s="6">
+        <v>200</v>
+      </c>
+      <c r="AC6" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="AB6" s="6">
-        <v>222</v>
-      </c>
-      <c r="AC6" s="7" t="s">
+      <c r="AD6" s="6">
+        <v>24396</v>
+      </c>
+      <c r="AE6" s="7" t="s">
         <v>105</v>
-      </c>
-      <c r="AD6" s="6">
-        <v>23948</v>
-      </c>
-      <c r="AE6" s="7" t="s">
-        <v>106</v>
       </c>
       <c r="AF6" s="6">
         <v>600</v>
       </c>
       <c r="AG6" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>16</v>
+      </c>
+      <c r="AI6" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="AH6" s="6">
-        <v>15</v>
-      </c>
-      <c r="AI6" s="7" t="s">
+      <c r="AJ6" s="6">
+        <v>9441</v>
+      </c>
+      <c r="AK6" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="AJ6" s="6">
-        <v>9330</v>
-      </c>
-      <c r="AK6" s="7" t="s">
+      <c r="AL6" s="6">
+        <v>4070</v>
+      </c>
+      <c r="AM6" s="7" t="s">
         <v>109</v>
-      </c>
-      <c r="AL6" s="6">
-        <v>4069</v>
-      </c>
-      <c r="AM6" s="7" t="s">
-        <v>110</v>
       </c>
       <c r="AN6" s="6">
         <v>4</v>
@@ -1956,18 +1947,18 @@
         <v>26</v>
       </c>
       <c r="AS6" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>113</v>
-      </c>
       <c r="C7" s="9">
-        <v>3116</v>
+        <v>3118</v>
       </c>
       <c r="D7" s="9">
         <v>0</v>
@@ -1979,25 +1970,25 @@
         <v>112</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H7" s="9">
         <v>32</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J7" s="9">
         <v>1</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L7" s="9">
         <v>774</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N7" s="9">
         <v>0</v>
@@ -2009,73 +2000,73 @@
         <v>23</v>
       </c>
       <c r="Q7" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R7" s="9">
         <v>4</v>
       </c>
       <c r="S7" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="T7" s="9">
         <v>4</v>
       </c>
       <c r="U7" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="V7" s="9">
         <v>50</v>
       </c>
       <c r="W7" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X7" s="9">
         <v>132</v>
       </c>
       <c r="Y7" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z7" s="9">
         <v>3</v>
       </c>
       <c r="AA7" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB7" s="9">
+        <v>3</v>
+      </c>
+      <c r="AC7" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="AD7" s="9">
+        <v>1198</v>
+      </c>
+      <c r="AE7" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="AB7" s="9">
-        <v>2</v>
-      </c>
-      <c r="AC7" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="AD7" s="9">
-        <v>1197</v>
-      </c>
-      <c r="AE7" s="10" t="s">
-        <v>123</v>
       </c>
       <c r="AF7" s="9">
         <v>17</v>
       </c>
       <c r="AG7" s="10" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="AH7" s="9">
         <v>1</v>
       </c>
       <c r="AI7" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ7" s="9">
         <v>384</v>
       </c>
       <c r="AK7" s="10" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AL7" s="9">
         <v>380</v>
       </c>
       <c r="AM7" s="10" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AN7" s="9">
         <v>0</v>
@@ -2098,13 +2089,13 @@
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C8" s="9">
-        <v>1635</v>
+        <v>1643</v>
       </c>
       <c r="D8" s="9">
         <v>0</v>
@@ -2116,7 +2107,7 @@
         <v>108</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
@@ -2131,10 +2122,10 @@
         <v>97</v>
       </c>
       <c r="L8" s="9">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="N8" s="9">
         <v>0</v>
@@ -2143,22 +2134,22 @@
         <v>97</v>
       </c>
       <c r="P8" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="R8" s="9">
         <v>15</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="T8" s="9">
         <v>55</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="V8" s="9">
         <v>4</v>
@@ -2170,49 +2161,49 @@
         <v>53</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="Z8" s="9">
         <v>5</v>
       </c>
       <c r="AA8" s="10" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="AB8" s="9">
         <v>5</v>
       </c>
       <c r="AC8" s="10" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="AD8" s="9">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="AE8" s="10" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AF8" s="9">
         <v>2</v>
       </c>
       <c r="AG8" s="10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="AH8" s="9">
         <v>1</v>
       </c>
       <c r="AI8" s="10" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="AJ8" s="9">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AK8" s="10" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AL8" s="9">
         <v>7</v>
       </c>
       <c r="AM8" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AN8" s="9">
         <v>0</v>
@@ -2230,36 +2221,36 @@
         <v>2</v>
       </c>
       <c r="AS8" s="10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C9" s="9">
-        <v>5810</v>
+        <v>5881</v>
       </c>
       <c r="D9" s="9">
         <v>1</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F9" s="9">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H9" s="9">
         <v>22</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J9" s="9">
         <v>0</v>
@@ -2268,10 +2259,10 @@
         <v>97</v>
       </c>
       <c r="L9" s="9">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N9" s="9">
         <v>0</v>
@@ -2283,73 +2274,73 @@
         <v>1</v>
       </c>
       <c r="Q9" s="10" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R9" s="9">
         <v>33</v>
       </c>
       <c r="S9" s="10" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="T9" s="9">
         <v>193</v>
       </c>
       <c r="U9" s="10" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="V9" s="9">
         <v>3</v>
       </c>
       <c r="W9" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X9" s="9">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Y9" s="10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Z9" s="9">
         <v>44</v>
       </c>
       <c r="AA9" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD9" s="9">
+        <v>2572</v>
+      </c>
+      <c r="AE9" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="AF9" s="9">
+        <v>235</v>
+      </c>
+      <c r="AG9" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="AB9" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="AD9" s="9">
-        <v>2534</v>
-      </c>
-      <c r="AE9" s="10" t="s">
+      <c r="AH9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ9" s="9">
+        <v>1048</v>
+      </c>
+      <c r="AK9" s="10" t="s">
         <v>150</v>
-      </c>
-      <c r="AF9" s="9">
-        <v>236</v>
-      </c>
-      <c r="AG9" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="AH9" s="9">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ9" s="9">
-        <v>1039</v>
-      </c>
-      <c r="AK9" s="10" t="s">
-        <v>152</v>
       </c>
       <c r="AL9" s="9">
         <v>68</v>
       </c>
       <c r="AM9" s="10" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AN9" s="9">
         <v>0</v>
@@ -2367,36 +2358,36 @@
         <v>4</v>
       </c>
       <c r="AS9" s="10" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C10" s="9">
-        <v>5922</v>
+        <v>6192</v>
       </c>
       <c r="D10" s="9">
         <v>3</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F10" s="9">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H10" s="9">
         <v>25</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J10" s="9">
         <v>0</v>
@@ -2405,94 +2396,94 @@
         <v>97</v>
       </c>
       <c r="L10" s="9">
-        <v>1434</v>
+        <v>1525</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="N10" s="9">
         <v>1</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="P10" s="9">
         <v>19</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="R10" s="9">
         <v>76</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="T10" s="9">
         <v>185</v>
       </c>
       <c r="U10" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="V10" s="9">
         <v>20</v>
       </c>
       <c r="W10" s="10" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="X10" s="9">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Z10" s="9">
         <v>23</v>
       </c>
       <c r="AA10" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="AB10" s="9">
+        <v>122</v>
+      </c>
+      <c r="AC10" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="AD10" s="9">
+        <v>2608</v>
+      </c>
+      <c r="AE10" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="AF10" s="9">
+        <v>28</v>
+      </c>
+      <c r="AG10" s="10" t="s">
         <v>165</v>
-      </c>
-      <c r="AB10" s="9">
-        <v>123</v>
-      </c>
-      <c r="AC10" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="AD10" s="9">
-        <v>2476</v>
-      </c>
-      <c r="AE10" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="AF10" s="9">
-        <v>27</v>
-      </c>
-      <c r="AG10" s="10" t="s">
-        <v>168</v>
       </c>
       <c r="AH10" s="9">
         <v>6</v>
       </c>
       <c r="AI10" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AJ10" s="9">
-        <v>908</v>
+        <v>940</v>
       </c>
       <c r="AK10" s="10" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AL10" s="9">
         <v>119</v>
       </c>
       <c r="AM10" s="10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="AN10" s="9">
         <v>1</v>
       </c>
       <c r="AO10" s="10" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AP10" s="9">
         <v>0</v>
@@ -2504,36 +2495,36 @@
         <v>3</v>
       </c>
       <c r="AS10" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C11" s="9">
-        <v>6085</v>
+        <v>6120</v>
       </c>
       <c r="D11" s="9">
         <v>2</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F11" s="9">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="H11" s="9">
         <v>6</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J11" s="9">
         <v>0</v>
@@ -2542,10 +2533,10 @@
         <v>97</v>
       </c>
       <c r="L11" s="9">
-        <v>1334</v>
+        <v>1347</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N11" s="9">
         <v>0</v>
@@ -2557,55 +2548,55 @@
         <v>34</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="R11" s="9">
         <v>28</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="T11" s="9">
         <v>361</v>
       </c>
       <c r="U11" s="10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="V11" s="9">
         <v>6</v>
       </c>
       <c r="W11" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="X11" s="9">
         <v>256</v>
       </c>
       <c r="Y11" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Z11" s="9">
         <v>29</v>
       </c>
       <c r="AA11" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AB11" s="9">
         <v>9</v>
       </c>
       <c r="AC11" s="10" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AD11" s="9">
-        <v>2721</v>
+        <v>2738</v>
       </c>
       <c r="AE11" s="10" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AF11" s="9">
         <v>73</v>
       </c>
       <c r="AG11" s="10" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AH11" s="9">
         <v>0</v>
@@ -2614,16 +2605,16 @@
         <v>97</v>
       </c>
       <c r="AJ11" s="9">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="AK11" s="10" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AL11" s="9">
         <v>39</v>
       </c>
       <c r="AM11" s="10" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AN11" s="9">
         <v>0</v>
@@ -2641,36 +2632,36 @@
         <v>2</v>
       </c>
       <c r="AS11" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C12" s="9">
+        <v>5856</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" s="9">
+        <v>151</v>
+      </c>
+      <c r="G12" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="C12" s="9">
-        <v>5836</v>
-      </c>
-      <c r="D12" s="9">
-        <v>0</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="F12" s="9">
-        <v>150</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="H12" s="9">
         <v>135</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J12" s="9">
         <v>0</v>
@@ -2679,10 +2670,10 @@
         <v>97</v>
       </c>
       <c r="L12" s="9">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="N12" s="9">
         <v>0</v>
@@ -2694,37 +2685,37 @@
         <v>3</v>
       </c>
       <c r="Q12" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="R12" s="9">
         <v>26</v>
       </c>
       <c r="S12" s="10" t="s">
-        <v>188</v>
+        <v>99</v>
       </c>
       <c r="T12" s="9">
         <v>132</v>
       </c>
       <c r="U12" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="V12" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W12" s="10" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="X12" s="9">
         <v>143</v>
       </c>
       <c r="Y12" s="10" t="s">
-        <v>101</v>
+        <v>187</v>
       </c>
       <c r="Z12" s="9">
         <v>32</v>
       </c>
       <c r="AA12" s="10" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="AB12" s="9">
         <v>0</v>
@@ -2733,16 +2724,16 @@
         <v>97</v>
       </c>
       <c r="AD12" s="9">
-        <v>2589</v>
+        <v>2599</v>
       </c>
       <c r="AE12" s="10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AF12" s="9">
         <v>46</v>
       </c>
       <c r="AG12" s="10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AH12" s="9">
         <v>0</v>
@@ -2751,22 +2742,22 @@
         <v>97</v>
       </c>
       <c r="AJ12" s="9">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="AK12" s="10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AL12" s="9">
         <v>757</v>
       </c>
       <c r="AM12" s="10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AN12" s="9">
         <v>1</v>
       </c>
       <c r="AO12" s="10" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AP12" s="9">
         <v>0</v>
@@ -2778,18 +2769,18 @@
         <v>6</v>
       </c>
       <c r="AS12" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C13" s="9">
-        <v>3074</v>
+        <v>3120</v>
       </c>
       <c r="D13" s="9">
         <v>0</v>
@@ -2798,16 +2789,16 @@
         <v>97</v>
       </c>
       <c r="F13" s="9">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>196</v>
+        <v>119</v>
       </c>
       <c r="H13" s="9">
         <v>2</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="J13" s="9">
         <v>0</v>
@@ -2816,70 +2807,70 @@
         <v>97</v>
       </c>
       <c r="L13" s="9">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="N13" s="9">
         <v>1</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P13" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>198</v>
+        <v>117</v>
       </c>
       <c r="R13" s="9">
         <v>19</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="T13" s="9">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U13" s="10" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="V13" s="9">
         <v>3</v>
       </c>
       <c r="W13" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="X13" s="9">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="Y13" s="10" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="Z13" s="9">
         <v>12</v>
       </c>
       <c r="AA13" s="10" t="s">
-        <v>165</v>
+        <v>198</v>
       </c>
       <c r="AB13" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC13" s="10" t="s">
-        <v>198</v>
+        <v>107</v>
       </c>
       <c r="AD13" s="9">
-        <v>1250</v>
+        <v>1277</v>
       </c>
       <c r="AE13" s="10" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="AF13" s="9">
         <v>10</v>
       </c>
       <c r="AG13" s="10" t="s">
-        <v>102</v>
+        <v>161</v>
       </c>
       <c r="AH13" s="9">
         <v>0</v>
@@ -2888,16 +2879,16 @@
         <v>97</v>
       </c>
       <c r="AJ13" s="9">
-        <v>813</v>
+        <v>822</v>
       </c>
       <c r="AK13" s="10" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AL13" s="9">
         <v>39</v>
       </c>
       <c r="AM13" s="10" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="AN13" s="9">
         <v>0</v>
@@ -2920,13 +2911,13 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C14" s="9">
-        <v>2169</v>
+        <v>2174</v>
       </c>
       <c r="D14" s="9">
         <v>0</v>
@@ -2938,13 +2929,13 @@
         <v>94</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H14" s="9">
         <v>17</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="J14" s="9">
         <v>0</v>
@@ -2953,52 +2944,52 @@
         <v>97</v>
       </c>
       <c r="L14" s="9">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="N14" s="9">
         <v>1</v>
       </c>
       <c r="O14" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P14" s="9">
         <v>20</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>132</v>
+        <v>207</v>
       </c>
       <c r="R14" s="9">
         <v>26</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="T14" s="9">
         <v>47</v>
       </c>
       <c r="U14" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="V14" s="9">
         <v>10</v>
       </c>
       <c r="W14" s="10" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="X14" s="9">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Y14" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Z14" s="9">
         <v>1</v>
       </c>
       <c r="AA14" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AB14" s="9">
         <v>0</v>
@@ -3007,16 +2998,16 @@
         <v>97</v>
       </c>
       <c r="AD14" s="9">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="AE14" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AF14" s="9">
         <v>2</v>
       </c>
       <c r="AG14" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AH14" s="9">
         <v>0</v>
@@ -3028,19 +3019,19 @@
         <v>336</v>
       </c>
       <c r="AK14" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AL14" s="9">
         <v>99</v>
       </c>
       <c r="AM14" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AN14" s="9">
         <v>1</v>
       </c>
       <c r="AO14" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AP14" s="9">
         <v>0</v>
@@ -3052,36 +3043,36 @@
         <v>1</v>
       </c>
       <c r="AS14" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="C15" s="9">
+        <v>7650</v>
+      </c>
+      <c r="D15" s="9">
+        <v>0</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F15" s="9">
+        <v>250</v>
+      </c>
+      <c r="G15" s="10" t="s">
         <v>217</v>
-      </c>
-      <c r="C15" s="9">
-        <v>7498</v>
-      </c>
-      <c r="D15" s="9">
-        <v>0</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="F15" s="9">
-        <v>243</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>134</v>
       </c>
       <c r="H15" s="9">
         <v>88</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>153</v>
+        <v>218</v>
       </c>
       <c r="J15" s="9">
         <v>0</v>
@@ -3090,10 +3081,10 @@
         <v>97</v>
       </c>
       <c r="L15" s="9">
-        <v>963</v>
+        <v>1020</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N15" s="9">
         <v>0</v>
@@ -3102,40 +3093,40 @@
         <v>97</v>
       </c>
       <c r="P15" s="9">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="R15" s="9">
         <v>72</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="T15" s="9">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="V15" s="9">
         <v>4</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X15" s="9">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="Y15" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Z15" s="9">
         <v>8</v>
       </c>
       <c r="AA15" s="10" t="s">
-        <v>223</v>
+        <v>120</v>
       </c>
       <c r="AB15" s="9">
         <v>0</v>
@@ -3144,7 +3135,7 @@
         <v>97</v>
       </c>
       <c r="AD15" s="9">
-        <v>3027</v>
+        <v>3102</v>
       </c>
       <c r="AE15" s="10" t="s">
         <v>224</v>
@@ -3162,7 +3153,7 @@
         <v>97</v>
       </c>
       <c r="AJ15" s="9">
-        <v>1120</v>
+        <v>1127</v>
       </c>
       <c r="AK15" s="10" t="s">
         <v>226</v>
@@ -3189,7 +3180,7 @@
         <v>2</v>
       </c>
       <c r="AS15" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
@@ -3200,7 +3191,7 @@
         <v>229</v>
       </c>
       <c r="C16" s="9">
-        <v>1821</v>
+        <v>1937</v>
       </c>
       <c r="D16" s="9">
         <v>0</v>
@@ -3209,7 +3200,7 @@
         <v>97</v>
       </c>
       <c r="F16" s="9">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G16" s="10" t="s">
         <v>230</v>
@@ -3218,7 +3209,7 @@
         <v>6</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>102</v>
+        <v>158</v>
       </c>
       <c r="J16" s="9">
         <v>0</v>
@@ -3227,7 +3218,7 @@
         <v>97</v>
       </c>
       <c r="L16" s="9">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="M16" s="10" t="s">
         <v>231</v>
@@ -3239,49 +3230,49 @@
         <v>97</v>
       </c>
       <c r="P16" s="9">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="Q16" s="10" t="s">
         <v>232</v>
       </c>
       <c r="R16" s="9">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="S16" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="T16" s="9">
+        <v>84</v>
+      </c>
+      <c r="U16" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="T16" s="9">
-        <v>68</v>
-      </c>
-      <c r="U16" s="10" t="s">
-        <v>234</v>
-      </c>
       <c r="V16" s="9">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="W16" s="10" t="s">
-        <v>221</v>
+        <v>172</v>
       </c>
       <c r="X16" s="9">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="Y16" s="10" t="s">
-        <v>235</v>
+        <v>174</v>
       </c>
       <c r="Z16" s="9">
         <v>11</v>
       </c>
       <c r="AA16" s="10" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="AB16" s="9">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="AC16" s="10" t="s">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="AD16" s="9">
-        <v>773</v>
+        <v>837</v>
       </c>
       <c r="AE16" s="10" t="s">
         <v>236</v>
@@ -3290,25 +3281,25 @@
         <v>31</v>
       </c>
       <c r="AG16" s="10" t="s">
-        <v>237</v>
+        <v>118</v>
       </c>
       <c r="AH16" s="9">
         <v>5</v>
       </c>
       <c r="AI16" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="AJ16" s="9">
+        <v>355</v>
+      </c>
+      <c r="AK16" s="10" t="s">
         <v>238</v>
-      </c>
-      <c r="AJ16" s="9">
-        <v>322</v>
-      </c>
-      <c r="AK16" s="10" t="s">
-        <v>239</v>
       </c>
       <c r="AL16" s="9">
         <v>56</v>
       </c>
       <c r="AM16" s="10" t="s">
-        <v>240</v>
+        <v>102</v>
       </c>
       <c r="AN16" s="9">
         <v>0</v>
@@ -3326,36 +3317,36 @@
         <v>2</v>
       </c>
       <c r="AS16" s="10" t="s">
-        <v>223</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C17" s="9">
-        <v>3058</v>
+        <v>3063</v>
       </c>
       <c r="D17" s="9">
         <v>1</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F17" s="9">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H17" s="9">
         <v>26</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="J17" s="9">
         <v>0</v>
@@ -3364,10 +3355,10 @@
         <v>97</v>
       </c>
       <c r="L17" s="9">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="N17" s="9">
         <v>0</v>
@@ -3379,73 +3370,73 @@
         <v>23</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>246</v>
+        <v>147</v>
       </c>
       <c r="R17" s="9">
         <v>28</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="T17" s="9">
         <v>30</v>
       </c>
       <c r="U17" s="10" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="V17" s="9">
         <v>10</v>
       </c>
       <c r="W17" s="10" t="s">
-        <v>102</v>
+        <v>244</v>
       </c>
       <c r="X17" s="9">
         <v>47</v>
       </c>
       <c r="Y17" s="10" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="Z17" s="9">
         <v>2</v>
       </c>
       <c r="AA17" s="10" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AB17" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC17" s="10" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="AD17" s="9">
-        <v>1495</v>
+        <v>1498</v>
       </c>
       <c r="AE17" s="10" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="AF17" s="9">
         <v>41</v>
       </c>
       <c r="AG17" s="10" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AH17" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI17" s="10" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="AJ17" s="9">
         <v>389</v>
       </c>
       <c r="AK17" s="10" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AL17" s="9">
         <v>221</v>
       </c>
       <c r="AM17" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AN17" s="9">
         <v>0</v>
@@ -3468,13 +3459,13 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C18" s="9">
-        <v>3874</v>
+        <v>3970</v>
       </c>
       <c r="D18" s="9">
         <v>0</v>
@@ -3483,16 +3474,16 @@
         <v>97</v>
       </c>
       <c r="F18" s="9">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="H18" s="9">
         <v>6</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J18" s="9">
         <v>0</v>
@@ -3501,10 +3492,10 @@
         <v>97</v>
       </c>
       <c r="L18" s="9">
-        <v>758</v>
+        <v>801</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="N18" s="9">
         <v>0</v>
@@ -3513,76 +3504,76 @@
         <v>97</v>
       </c>
       <c r="P18" s="9">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="R18" s="9">
         <v>20</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="T18" s="9">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="U18" s="10" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="V18" s="9">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="W18" s="10" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="X18" s="9">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="Y18" s="10" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="Z18" s="9">
         <v>12</v>
       </c>
       <c r="AA18" s="10" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="AB18" s="9">
         <v>15</v>
       </c>
       <c r="AC18" s="10" t="s">
-        <v>165</v>
+        <v>198</v>
       </c>
       <c r="AD18" s="9">
-        <v>1759</v>
+        <v>1806</v>
       </c>
       <c r="AE18" s="10" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AF18" s="9">
         <v>8</v>
       </c>
       <c r="AG18" s="10" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="AH18" s="9">
         <v>1</v>
       </c>
       <c r="AI18" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ18" s="9">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="AK18" s="10" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="AL18" s="9">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AM18" s="10" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AN18" s="9">
         <v>0</v>
@@ -3605,13 +3596,13 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C19" s="9">
-        <v>3765</v>
+        <v>3813</v>
       </c>
       <c r="D19" s="9">
         <v>0</v>
@@ -3620,16 +3611,16 @@
         <v>97</v>
       </c>
       <c r="F19" s="9">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="H19" s="9">
         <v>18</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J19" s="9">
         <v>0</v>
@@ -3638,10 +3629,10 @@
         <v>97</v>
       </c>
       <c r="L19" s="9">
-        <v>998</v>
+        <v>1014</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="N19" s="9">
         <v>0</v>
@@ -3659,13 +3650,13 @@
         <v>14</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>268</v>
+        <v>142</v>
       </c>
       <c r="T19" s="9">
         <v>17</v>
       </c>
       <c r="U19" s="10" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="V19" s="9">
         <v>0</v>
@@ -3674,52 +3665,52 @@
         <v>97</v>
       </c>
       <c r="X19" s="9">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Y19" s="10" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="Z19" s="9">
         <v>4</v>
       </c>
       <c r="AA19" s="10" t="s">
-        <v>223</v>
+        <v>120</v>
       </c>
       <c r="AB19" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC19" s="10" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="AD19" s="9">
-        <v>1604</v>
+        <v>1623</v>
       </c>
       <c r="AE19" s="10" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AF19" s="9">
         <v>26</v>
       </c>
       <c r="AG19" s="10" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="AH19" s="9">
         <v>1</v>
       </c>
       <c r="AI19" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ19" s="9">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="AK19" s="10" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="AL19" s="9">
         <v>146</v>
       </c>
       <c r="AM19" s="10" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="AN19" s="9">
         <v>0</v>
@@ -3737,18 +3728,18 @@
         <v>2</v>
       </c>
       <c r="AS19" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C20" s="9">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D20" s="9">
         <v>0</v>
@@ -3760,13 +3751,13 @@
         <v>44</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="H20" s="9">
         <v>6</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="J20" s="9">
         <v>0</v>
@@ -3778,7 +3769,7 @@
         <v>58</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="N20" s="9">
         <v>0</v>
@@ -3790,55 +3781,55 @@
         <v>5</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="R20" s="9">
         <v>4</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="T20" s="9">
         <v>41</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="V20" s="9">
         <v>16</v>
       </c>
       <c r="W20" s="10" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="X20" s="9">
         <v>45</v>
       </c>
       <c r="Y20" s="10" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="Z20" s="9">
         <v>88</v>
       </c>
       <c r="AA20" s="10" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="AB20" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC20" s="10" t="s">
-        <v>160</v>
+        <v>280</v>
       </c>
       <c r="AD20" s="9">
         <v>231</v>
       </c>
       <c r="AE20" s="10" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AF20" s="9">
         <v>12</v>
       </c>
       <c r="AG20" s="10" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="AH20" s="9">
         <v>0</v>
@@ -3850,13 +3841,13 @@
         <v>57</v>
       </c>
       <c r="AK20" s="10" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="AL20" s="9">
         <v>19</v>
       </c>
       <c r="AM20" s="10" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AN20" s="9">
         <v>0</v>
@@ -3874,18 +3865,18 @@
         <v>2</v>
       </c>
       <c r="AS20" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C21" s="9">
-        <v>1448</v>
+        <v>1464</v>
       </c>
       <c r="D21" s="9">
         <v>0</v>
@@ -3894,16 +3885,16 @@
         <v>97</v>
       </c>
       <c r="F21" s="9">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H21" s="9">
         <v>6</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="J21" s="9">
         <v>0</v>
@@ -3912,10 +3903,10 @@
         <v>97</v>
       </c>
       <c r="L21" s="9">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N21" s="9">
         <v>0</v>
@@ -3933,49 +3924,49 @@
         <v>9</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="T21" s="9">
         <v>35</v>
       </c>
       <c r="U21" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="V21" s="9">
+        <v>1</v>
+      </c>
+      <c r="W21" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="X21" s="9">
+        <v>37</v>
+      </c>
+      <c r="Y21" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z21" s="9">
+        <v>39</v>
+      </c>
+      <c r="AA21" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="AB21" s="9">
+        <v>17</v>
+      </c>
+      <c r="AC21" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="AD21" s="9">
+        <v>612</v>
+      </c>
+      <c r="AE21" s="10" t="s">
         <v>292</v>
-      </c>
-      <c r="V21" s="9">
-        <v>20</v>
-      </c>
-      <c r="W21" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="X21" s="9">
-        <v>35</v>
-      </c>
-      <c r="Y21" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="Z21" s="9">
-        <v>21</v>
-      </c>
-      <c r="AA21" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="AB21" s="9">
-        <v>18</v>
-      </c>
-      <c r="AC21" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="AD21" s="9">
-        <v>605</v>
-      </c>
-      <c r="AE21" s="10" t="s">
-        <v>295</v>
       </c>
       <c r="AF21" s="9">
         <v>3</v>
       </c>
       <c r="AG21" s="10" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="AH21" s="9">
         <v>0</v>
@@ -3984,16 +3975,16 @@
         <v>97</v>
       </c>
       <c r="AJ21" s="9">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK21" s="10" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AL21" s="9">
         <v>384</v>
       </c>
       <c r="AM21" s="10" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AN21" s="9">
         <v>0</v>
@@ -4016,13 +4007,13 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C22" s="12">
-        <v>55741</v>
+        <v>56632</v>
       </c>
       <c r="D22" s="12">
         <v>7</v>
@@ -4031,7 +4022,7 @@
         <v>94</v>
       </c>
       <c r="F22" s="12">
-        <v>2322</v>
+        <v>2361</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>95</v>
@@ -4049,7 +4040,7 @@
         <v>97</v>
       </c>
       <c r="L22" s="12">
-        <v>10684</v>
+        <v>10972</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>98</v>
@@ -4061,76 +4052,76 @@
         <v>94</v>
       </c>
       <c r="P22" s="12">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="Q22" s="13" t="s">
         <v>99</v>
       </c>
       <c r="R22" s="12">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="S22" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="T22" s="12">
+        <v>1391</v>
+      </c>
+      <c r="U22" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="T22" s="12">
-        <v>1368</v>
-      </c>
-      <c r="U22" s="13" t="s">
+      <c r="V22" s="12">
+        <v>151</v>
+      </c>
+      <c r="W22" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="V22" s="12">
-        <v>183</v>
-      </c>
-      <c r="W22" s="13" t="s">
+      <c r="X22" s="12">
+        <v>1637</v>
+      </c>
+      <c r="Y22" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="X22" s="12">
-        <v>1599</v>
-      </c>
-      <c r="Y22" s="13" t="s">
+      <c r="Z22" s="12">
+        <v>313</v>
+      </c>
+      <c r="AA22" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="Z22" s="12">
-        <v>295</v>
-      </c>
-      <c r="AA22" s="13" t="s">
+      <c r="AB22" s="12">
+        <v>200</v>
+      </c>
+      <c r="AC22" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="AB22" s="12">
-        <v>222</v>
-      </c>
-      <c r="AC22" s="13" t="s">
+      <c r="AD22" s="12">
+        <v>24396</v>
+      </c>
+      <c r="AE22" s="13" t="s">
         <v>105</v>
-      </c>
-      <c r="AD22" s="12">
-        <v>23948</v>
-      </c>
-      <c r="AE22" s="13" t="s">
-        <v>106</v>
       </c>
       <c r="AF22" s="12">
         <v>600</v>
       </c>
       <c r="AG22" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="AH22" s="12">
+        <v>16</v>
+      </c>
+      <c r="AI22" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="AH22" s="12">
-        <v>15</v>
-      </c>
-      <c r="AI22" s="13" t="s">
+      <c r="AJ22" s="12">
+        <v>9441</v>
+      </c>
+      <c r="AK22" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AJ22" s="12">
-        <v>9330</v>
-      </c>
-      <c r="AK22" s="13" t="s">
+      <c r="AL22" s="12">
+        <v>4070</v>
+      </c>
+      <c r="AM22" s="13" t="s">
         <v>109</v>
-      </c>
-      <c r="AL22" s="12">
-        <v>4069</v>
-      </c>
-      <c r="AM22" s="13" t="s">
-        <v>110</v>
       </c>
       <c r="AN22" s="12">
         <v>4</v>
@@ -4148,7 +4139,7 @@
         <v>26</v>
       </c>
       <c r="AS22" s="13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
+++ b/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="306">
   <si>
     <t>DATA RADAR ANOMALI KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 28 Agu 2026, 10.22</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 29 Agu 2026, 16.20</t>
   </si>
   <si>
     <t>Kode</t>
@@ -298,604 +298,631 @@
     <t>0,01</t>
   </si>
   <si>
-    <t>4,17</t>
+    <t>4,19</t>
+  </si>
+  <si>
+    <t>0,68</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>19,66</t>
+  </si>
+  <si>
+    <t>0,36</t>
+  </si>
+  <si>
+    <t>0,69</t>
+  </si>
+  <si>
+    <t>2,44</t>
+  </si>
+  <si>
+    <t>0,23</t>
+  </si>
+  <si>
+    <t>2,87</t>
+  </si>
+  <si>
+    <t>0,55</t>
+  </si>
+  <si>
+    <t>0,33</t>
+  </si>
+  <si>
+    <t>43,28</t>
+  </si>
+  <si>
+    <t>1,04</t>
+  </si>
+  <si>
+    <t>0,02</t>
+  </si>
+  <si>
+    <t>16,58</t>
+  </si>
+  <si>
+    <t>6,99</t>
+  </si>
+  <si>
+    <t>0,04</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>LAMPUNG BARAT</t>
+  </si>
+  <si>
+    <t>3,82</t>
+  </si>
+  <si>
+    <t>0,97</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>25,85</t>
   </si>
   <si>
     <t>0,7</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>19,37</t>
+    <t>0,12</t>
+  </si>
+  <si>
+    <t>1,52</t>
+  </si>
+  <si>
+    <t>4,09</t>
+  </si>
+  <si>
+    <t>0,09</t>
+  </si>
+  <si>
+    <t>38,27</t>
+  </si>
+  <si>
+    <t>0,52</t>
+  </si>
+  <si>
+    <t>12,27</t>
+  </si>
+  <si>
+    <t>11,52</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>TANGGAMUS</t>
+  </si>
+  <si>
+    <t>6,55</t>
+  </si>
+  <si>
+    <t>19,78</t>
+  </si>
+  <si>
+    <t>0,24</t>
+  </si>
+  <si>
+    <t>0,9</t>
+  </si>
+  <si>
+    <t>3,31</t>
+  </si>
+  <si>
+    <t>0,18</t>
+  </si>
+  <si>
+    <t>3,19</t>
+  </si>
+  <si>
+    <t>0,3</t>
+  </si>
+  <si>
+    <t>41,85</t>
+  </si>
+  <si>
+    <t>0,06</t>
+  </si>
+  <si>
+    <t>22,73</t>
+  </si>
+  <si>
+    <t>0,42</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>LAMPUNG SELATAN</t>
+  </si>
+  <si>
+    <t>5,81</t>
+  </si>
+  <si>
+    <t>0,37</t>
+  </si>
+  <si>
+    <t>19,03</t>
+  </si>
+  <si>
+    <t>0,56</t>
+  </si>
+  <si>
+    <t>3,25</t>
+  </si>
+  <si>
+    <t>3,35</t>
+  </si>
+  <si>
+    <t>0,74</t>
+  </si>
+  <si>
+    <t>43,81</t>
+  </si>
+  <si>
+    <t>3,96</t>
+  </si>
+  <si>
+    <t>17,86</t>
+  </si>
+  <si>
+    <t>1,14</t>
+  </si>
+  <si>
+    <t>0,07</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>LAMPUNG TIMUR</t>
+  </si>
+  <si>
+    <t>4,36</t>
+  </si>
+  <si>
+    <t>24,87</t>
+  </si>
+  <si>
+    <t>0,28</t>
+  </si>
+  <si>
+    <t>1,11</t>
+  </si>
+  <si>
+    <t>2,7</t>
+  </si>
+  <si>
+    <t>0,29</t>
+  </si>
+  <si>
+    <t>3,38</t>
+  </si>
+  <si>
+    <t>0,34</t>
+  </si>
+  <si>
+    <t>1,76</t>
+  </si>
+  <si>
+    <t>42,99</t>
+  </si>
+  <si>
+    <t>0,41</t>
+  </si>
+  <si>
+    <t>0,1</t>
+  </si>
+  <si>
+    <t>15,19</t>
+  </si>
+  <si>
+    <t>1,73</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>LAMPUNG TENGAH</t>
+  </si>
+  <si>
+    <t>4,2</t>
+  </si>
+  <si>
+    <t>22,04</t>
+  </si>
+  <si>
+    <t>0,45</t>
+  </si>
+  <si>
+    <t>5,84</t>
+  </si>
+  <si>
+    <t>0,47</t>
+  </si>
+  <si>
+    <t>0,15</t>
+  </si>
+  <si>
+    <t>44,87</t>
+  </si>
+  <si>
+    <t>1,18</t>
+  </si>
+  <si>
+    <t>15,18</t>
+  </si>
+  <si>
+    <t>0,63</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>2,58</t>
+  </si>
+  <si>
+    <t>2,3</t>
+  </si>
+  <si>
+    <t>14,39</t>
+  </si>
+  <si>
+    <t>0,05</t>
   </si>
   <si>
     <t>0,44</t>
   </si>
   <si>
-    <t>2,46</t>
-  </si>
-  <si>
-    <t>0,27</t>
-  </si>
-  <si>
-    <t>2,89</t>
-  </si>
-  <si>
-    <t>0,55</t>
-  </si>
-  <si>
-    <t>0,35</t>
-  </si>
-  <si>
-    <t>43,08</t>
-  </si>
-  <si>
-    <t>1,06</t>
-  </si>
-  <si>
-    <t>0,03</t>
-  </si>
-  <si>
-    <t>16,67</t>
-  </si>
-  <si>
-    <t>7,19</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>LAMPUNG BARAT</t>
-  </si>
-  <si>
-    <t>3,59</t>
-  </si>
-  <si>
-    <t>1,03</t>
-  </si>
-  <si>
-    <t>24,82</t>
-  </si>
-  <si>
-    <t>0,74</t>
+    <t>2,25</t>
+  </si>
+  <si>
+    <t>44,38</t>
+  </si>
+  <si>
+    <t>0,79</t>
+  </si>
+  <si>
+    <t>16,75</t>
+  </si>
+  <si>
+    <t>12,92</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
+    <t>4,33</t>
+  </si>
+  <si>
+    <t>20,04</t>
   </si>
   <si>
     <t>0,13</t>
   </si>
   <si>
-    <t>1,6</t>
-  </si>
-  <si>
-    <t>4,23</t>
-  </si>
-  <si>
-    <t>0,1</t>
-  </si>
-  <si>
-    <t>38,42</t>
-  </si>
-  <si>
-    <t>12,32</t>
-  </si>
-  <si>
-    <t>12,19</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>TANGGAMUS</t>
-  </si>
-  <si>
-    <t>6,57</t>
-  </si>
-  <si>
-    <t>19,6</t>
-  </si>
-  <si>
-    <t>0,3</t>
+    <t>0,6</t>
+  </si>
+  <si>
+    <t>2,48</t>
+  </si>
+  <si>
+    <t>2,95</t>
+  </si>
+  <si>
+    <t>0,38</t>
+  </si>
+  <si>
+    <t>41,25</t>
+  </si>
+  <si>
+    <t>0,31</t>
+  </si>
+  <si>
+    <t>26,1</t>
+  </si>
+  <si>
+    <t>1,22</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG</t>
+  </si>
+  <si>
+    <t>0,78</t>
+  </si>
+  <si>
+    <t>21,49</t>
+  </si>
+  <si>
+    <t>0,92</t>
+  </si>
+  <si>
+    <t>1,19</t>
+  </si>
+  <si>
+    <t>2,16</t>
+  </si>
+  <si>
+    <t>0,46</t>
+  </si>
+  <si>
+    <t>2,02</t>
+  </si>
+  <si>
+    <t>46,37</t>
+  </si>
+  <si>
+    <t>15,43</t>
+  </si>
+  <si>
+    <t>4,55</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PESAWARAN</t>
+  </si>
+  <si>
+    <t>3,29</t>
+  </si>
+  <si>
+    <t>13,41</t>
+  </si>
+  <si>
+    <t>0,95</t>
+  </si>
+  <si>
+    <t>0,99</t>
+  </si>
+  <si>
+    <t>1,26</t>
+  </si>
+  <si>
+    <t>40,61</t>
+  </si>
+  <si>
+    <t>0,86</t>
+  </si>
+  <si>
+    <t>14,7</t>
+  </si>
+  <si>
+    <t>22,05</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>PRINGSEWU</t>
+  </si>
+  <si>
+    <t>4,98</t>
+  </si>
+  <si>
+    <t>15,15</t>
+  </si>
+  <si>
+    <t>0,65</t>
+  </si>
+  <si>
+    <t>1,41</t>
+  </si>
+  <si>
+    <t>5,08</t>
+  </si>
+  <si>
+    <t>4,13</t>
+  </si>
+  <si>
+    <t>1,01</t>
   </si>
   <si>
     <t>0,91</t>
   </si>
   <si>
-    <t>3,35</t>
-  </si>
-  <si>
-    <t>0,24</t>
-  </si>
-  <si>
-    <t>3,23</t>
-  </si>
-  <si>
-    <t>41,75</t>
-  </si>
-  <si>
-    <t>0,12</t>
-  </si>
-  <si>
-    <t>0,06</t>
-  </si>
-  <si>
-    <t>22,7</t>
+    <t>43,18</t>
+  </si>
+  <si>
+    <t>1,61</t>
+  </si>
+  <si>
+    <t>18,52</t>
+  </si>
+  <si>
+    <t>2,82</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
+  </si>
+  <si>
+    <t>0,82</t>
+  </si>
+  <si>
+    <t>20,42</t>
+  </si>
+  <si>
+    <t>0,73</t>
+  </si>
+  <si>
+    <t>0,89</t>
+  </si>
+  <si>
+    <t>1,55</t>
+  </si>
+  <si>
+    <t>49,04</t>
+  </si>
+  <si>
+    <t>1,33</t>
+  </si>
+  <si>
+    <t>12,46</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG BARAT</t>
+  </si>
+  <si>
+    <t>4,15</t>
+  </si>
+  <si>
+    <t>0,14</t>
+  </si>
+  <si>
+    <t>20,71</t>
+  </si>
+  <si>
+    <t>0,51</t>
+  </si>
+  <si>
+    <t>0,48</t>
+  </si>
+  <si>
+    <t>1,62</t>
+  </si>
+  <si>
+    <t>0,17</t>
+  </si>
+  <si>
+    <t>1,64</t>
+  </si>
+  <si>
+    <t>45,67</t>
+  </si>
+  <si>
+    <t>0,22</t>
+  </si>
+  <si>
+    <t>23,03</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>PESISIR BARAT</t>
+  </si>
+  <si>
+    <t>4,45</t>
+  </si>
+  <si>
+    <t>26,53</t>
   </si>
   <si>
     <t>0,43</t>
   </si>
   <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>LAMPUNG SELATAN</t>
-  </si>
-  <si>
-    <t>0,02</t>
-  </si>
-  <si>
-    <t>5,83</t>
-  </si>
-  <si>
-    <t>0,37</t>
-  </si>
-  <si>
-    <t>18,98</t>
-  </si>
-  <si>
-    <t>0,56</t>
-  </si>
-  <si>
-    <t>3,28</t>
-  </si>
-  <si>
-    <t>3,37</t>
-  </si>
-  <si>
-    <t>0,75</t>
-  </si>
-  <si>
-    <t>43,73</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>17,82</t>
-  </si>
-  <si>
-    <t>1,16</t>
-  </si>
-  <si>
-    <t>0,07</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>LAMPUNG TIMUR</t>
-  </si>
-  <si>
-    <t>4,28</t>
-  </si>
-  <si>
-    <t>0,4</t>
-  </si>
-  <si>
-    <t>24,63</t>
-  </si>
-  <si>
-    <t>0,31</t>
-  </si>
-  <si>
-    <t>1,23</t>
-  </si>
-  <si>
-    <t>2,99</t>
+    <t>3,34</t>
+  </si>
+  <si>
+    <t>43,25</t>
+  </si>
+  <si>
+    <t>0,66</t>
+  </si>
+  <si>
+    <t>16,62</t>
+  </si>
+  <si>
+    <t>3,69</t>
+  </si>
+  <si>
+    <t>1871</t>
+  </si>
+  <si>
+    <t>BANDAR LAMPUNG</t>
+  </si>
+  <si>
+    <t>6,96</t>
+  </si>
+  <si>
+    <t>9,18</t>
+  </si>
+  <si>
+    <t>6,49</t>
+  </si>
+  <si>
+    <t>2,53</t>
+  </si>
+  <si>
+    <t>7,28</t>
+  </si>
+  <si>
+    <t>13,92</t>
+  </si>
+  <si>
+    <t>36,55</t>
+  </si>
+  <si>
+    <t>1,9</t>
+  </si>
+  <si>
+    <t>9,02</t>
+  </si>
+  <si>
+    <t>3,01</t>
   </si>
   <si>
     <t>0,32</t>
   </si>
   <si>
-    <t>3,6</t>
-  </si>
-  <si>
-    <t>1,97</t>
-  </si>
-  <si>
-    <t>42,12</t>
-  </si>
-  <si>
-    <t>0,45</t>
-  </si>
-  <si>
-    <t>15,18</t>
-  </si>
-  <si>
-    <t>1,92</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>LAMPUNG TENGAH</t>
-  </si>
-  <si>
-    <t>4,25</t>
-  </si>
-  <si>
-    <t>22,01</t>
-  </si>
-  <si>
-    <t>0,46</t>
-  </si>
-  <si>
-    <t>5,9</t>
-  </si>
-  <si>
-    <t>4,18</t>
-  </si>
-  <si>
-    <t>0,47</t>
-  </si>
-  <si>
-    <t>0,15</t>
-  </si>
-  <si>
-    <t>44,74</t>
-  </si>
-  <si>
-    <t>1,19</t>
-  </si>
-  <si>
-    <t>15,2</t>
-  </si>
-  <si>
-    <t>0,64</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
-  </si>
-  <si>
-    <t>2,58</t>
-  </si>
-  <si>
-    <t>2,31</t>
-  </si>
-  <si>
-    <t>14,4</t>
-  </si>
-  <si>
-    <t>2,25</t>
-  </si>
-  <si>
-    <t>2,44</t>
-  </si>
-  <si>
-    <t>44,38</t>
-  </si>
-  <si>
-    <t>0,79</t>
-  </si>
-  <si>
-    <t>16,73</t>
-  </si>
-  <si>
-    <t>12,93</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>20,1</t>
+    <t>1872</t>
+  </si>
+  <si>
+    <t>METRO</t>
+  </si>
+  <si>
+    <t>2,45</t>
+  </si>
+  <si>
+    <t>11,56</t>
   </si>
   <si>
     <t>0,61</t>
   </si>
   <si>
-    <t>2,53</t>
-  </si>
-  <si>
-    <t>2,95</t>
-  </si>
-  <si>
-    <t>0,38</t>
-  </si>
-  <si>
-    <t>40,93</t>
-  </si>
-  <si>
-    <t>26,35</t>
-  </si>
-  <si>
-    <t>1,25</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG</t>
-  </si>
-  <si>
-    <t>4,32</t>
-  </si>
-  <si>
-    <t>0,78</t>
-  </si>
-  <si>
-    <t>21,44</t>
-  </si>
-  <si>
-    <t>0,92</t>
-  </si>
-  <si>
-    <t>1,2</t>
-  </si>
-  <si>
-    <t>2,16</t>
-  </si>
-  <si>
-    <t>2,02</t>
-  </si>
-  <si>
-    <t>46,41</t>
-  </si>
-  <si>
-    <t>0,09</t>
-  </si>
-  <si>
-    <t>15,46</t>
-  </si>
-  <si>
-    <t>4,55</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>PESAWARAN</t>
-  </si>
-  <si>
-    <t>3,27</t>
-  </si>
-  <si>
-    <t>1,15</t>
-  </si>
-  <si>
-    <t>13,33</t>
-  </si>
-  <si>
-    <t>0,58</t>
-  </si>
-  <si>
-    <t>0,94</t>
-  </si>
-  <si>
-    <t>0,98</t>
-  </si>
-  <si>
-    <t>1,24</t>
-  </si>
-  <si>
-    <t>40,55</t>
-  </si>
-  <si>
-    <t>0,86</t>
-  </si>
-  <si>
-    <t>14,73</t>
-  </si>
-  <si>
-    <t>22,17</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>PRINGSEWU</t>
-  </si>
-  <si>
-    <t>5,01</t>
-  </si>
-  <si>
-    <t>14,61</t>
-  </si>
-  <si>
-    <t>1,81</t>
-  </si>
-  <si>
-    <t>4,34</t>
-  </si>
-  <si>
-    <t>0,57</t>
-  </si>
-  <si>
-    <t>1,14</t>
-  </si>
-  <si>
-    <t>43,21</t>
-  </si>
-  <si>
-    <t>0,26</t>
-  </si>
-  <si>
-    <t>18,33</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>4,44</t>
-  </si>
-  <si>
-    <t>0,85</t>
-  </si>
-  <si>
-    <t>19,85</t>
-  </si>
-  <si>
-    <t>0,33</t>
-  </si>
-  <si>
-    <t>1,53</t>
-  </si>
-  <si>
-    <t>48,91</t>
-  </si>
-  <si>
-    <t>1,34</t>
-  </si>
-  <si>
-    <t>12,7</t>
-  </si>
-  <si>
-    <t>7,22</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG BARAT</t>
-  </si>
-  <si>
-    <t>4,16</t>
-  </si>
-  <si>
-    <t>20,18</t>
-  </si>
-  <si>
-    <t>0,88</t>
-  </si>
-  <si>
-    <t>0,5</t>
-  </si>
-  <si>
-    <t>1,51</t>
-  </si>
-  <si>
-    <t>45,49</t>
+    <t>2,38</t>
+  </si>
+  <si>
+    <t>2,52</t>
+  </si>
+  <si>
+    <t>2,65</t>
+  </si>
+  <si>
+    <t>1,09</t>
+  </si>
+  <si>
+    <t>41,84</t>
   </si>
   <si>
     <t>0,2</t>
   </si>
   <si>
-    <t>23,55</t>
-  </si>
-  <si>
-    <t>1,01</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>PESISIR BARAT</t>
-  </si>
-  <si>
-    <t>4,46</t>
-  </si>
-  <si>
-    <t>26,59</t>
-  </si>
-  <si>
-    <t>3,44</t>
-  </si>
-  <si>
-    <t>42,56</t>
-  </si>
-  <si>
-    <t>0,68</t>
-  </si>
-  <si>
-    <t>16,94</t>
-  </si>
-  <si>
-    <t>3,83</t>
-  </si>
-  <si>
-    <t>1871</t>
-  </si>
-  <si>
-    <t>BANDAR LAMPUNG</t>
-  </si>
-  <si>
-    <t>6,97</t>
-  </si>
-  <si>
-    <t>0,95</t>
-  </si>
-  <si>
-    <t>9,19</t>
-  </si>
-  <si>
-    <t>0,63</t>
-  </si>
-  <si>
-    <t>6,5</t>
-  </si>
-  <si>
-    <t>2,54</t>
-  </si>
-  <si>
-    <t>7,13</t>
-  </si>
-  <si>
-    <t>13,95</t>
-  </si>
-  <si>
-    <t>0,48</t>
-  </si>
-  <si>
-    <t>36,61</t>
-  </si>
-  <si>
-    <t>1,9</t>
-  </si>
-  <si>
-    <t>9,03</t>
-  </si>
-  <si>
-    <t>3,01</t>
-  </si>
-  <si>
-    <t>1872</t>
-  </si>
-  <si>
-    <t>METRO</t>
-  </si>
-  <si>
-    <t>2,32</t>
-  </si>
-  <si>
-    <t>0,41</t>
-  </si>
-  <si>
-    <t>11,48</t>
-  </si>
-  <si>
-    <t>2,39</t>
-  </si>
-  <si>
-    <t>2,66</t>
-  </si>
-  <si>
-    <t>41,8</t>
-  </si>
-  <si>
-    <t>8,13</t>
-  </si>
-  <si>
-    <t>26,23</t>
+    <t>8,1</t>
+  </si>
+  <si>
+    <t>26,12</t>
   </si>
   <si>
     <t/>
@@ -1821,7 +1848,7 @@
         <v>93</v>
       </c>
       <c r="C6" s="6">
-        <v>56632</v>
+        <v>58216</v>
       </c>
       <c r="D6" s="6">
         <v>7</v>
@@ -1830,7 +1857,7 @@
         <v>94</v>
       </c>
       <c r="F6" s="6">
-        <v>2361</v>
+        <v>2441</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>95</v>
@@ -1848,7 +1875,7 @@
         <v>97</v>
       </c>
       <c r="L6" s="6">
-        <v>10972</v>
+        <v>11446</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>98</v>
@@ -1860,76 +1887,76 @@
         <v>94</v>
       </c>
       <c r="P6" s="6">
-        <v>251</v>
+        <v>211</v>
       </c>
       <c r="Q6" s="7" t="s">
         <v>99</v>
       </c>
       <c r="R6" s="6">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="S6" s="7" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="T6" s="6">
-        <v>1391</v>
+        <v>1423</v>
       </c>
       <c r="U6" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="V6" s="6">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="W6" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="X6" s="6">
-        <v>1637</v>
+        <v>1670</v>
       </c>
       <c r="Y6" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Z6" s="6">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="AA6" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB6" s="6">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="AC6" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AD6" s="6">
-        <v>24396</v>
+        <v>25193</v>
       </c>
       <c r="AE6" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AF6" s="6">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="AG6" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AH6" s="6">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI6" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AJ6" s="6">
-        <v>9441</v>
+        <v>9655</v>
       </c>
       <c r="AK6" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AL6" s="6">
         <v>4070</v>
       </c>
       <c r="AM6" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN6" s="6">
         <v>4</v>
@@ -1947,18 +1974,18 @@
         <v>26</v>
       </c>
       <c r="AS6" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C7" s="9">
-        <v>3118</v>
+        <v>3300</v>
       </c>
       <c r="D7" s="9">
         <v>0</v>
@@ -1967,28 +1994,28 @@
         <v>97</v>
       </c>
       <c r="F7" s="9">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H7" s="9">
         <v>32</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J7" s="9">
         <v>1</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="L7" s="9">
-        <v>774</v>
+        <v>853</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N7" s="9">
         <v>0</v>
@@ -2000,73 +2027,73 @@
         <v>23</v>
       </c>
       <c r="Q7" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="R7" s="9">
         <v>4</v>
       </c>
       <c r="S7" s="10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="T7" s="9">
         <v>4</v>
       </c>
       <c r="U7" s="10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="V7" s="9">
         <v>50</v>
       </c>
       <c r="W7" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="X7" s="9">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="Y7" s="10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Z7" s="9">
         <v>3</v>
       </c>
       <c r="AA7" s="10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="AB7" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC7" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AD7" s="9">
-        <v>1198</v>
+        <v>1263</v>
       </c>
       <c r="AE7" s="10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AF7" s="9">
         <v>17</v>
       </c>
       <c r="AG7" s="10" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="AH7" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="10" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="AJ7" s="9">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="AK7" s="10" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AL7" s="9">
         <v>380</v>
       </c>
       <c r="AM7" s="10" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AN7" s="9">
         <v>0</v>
@@ -2089,13 +2116,13 @@
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C8" s="9">
-        <v>1643</v>
+        <v>1663</v>
       </c>
       <c r="D8" s="9">
         <v>0</v>
@@ -2104,10 +2131,10 @@
         <v>97</v>
       </c>
       <c r="F8" s="9">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
@@ -2122,10 +2149,10 @@
         <v>97</v>
       </c>
       <c r="L8" s="9">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="N8" s="9">
         <v>0</v>
@@ -2134,76 +2161,76 @@
         <v>97</v>
       </c>
       <c r="P8" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="R8" s="9">
         <v>15</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="T8" s="9">
         <v>55</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="V8" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W8" s="10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="X8" s="9">
         <v>53</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="Z8" s="9">
         <v>5</v>
       </c>
       <c r="AA8" s="10" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="AB8" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC8" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="AD8" s="9">
-        <v>686</v>
+        <v>696</v>
       </c>
       <c r="AE8" s="10" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="AF8" s="9">
         <v>2</v>
       </c>
       <c r="AG8" s="10" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="AH8" s="9">
         <v>1</v>
       </c>
       <c r="AI8" s="10" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="AJ8" s="9">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="AK8" s="10" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AL8" s="9">
         <v>7</v>
       </c>
       <c r="AM8" s="10" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AN8" s="9">
         <v>0</v>
@@ -2221,36 +2248,36 @@
         <v>2</v>
       </c>
       <c r="AS8" s="10" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C9" s="9">
-        <v>5881</v>
+        <v>5939</v>
       </c>
       <c r="D9" s="9">
         <v>1</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="F9" s="9">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H9" s="9">
         <v>22</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J9" s="9">
         <v>0</v>
@@ -2259,10 +2286,10 @@
         <v>97</v>
       </c>
       <c r="L9" s="9">
-        <v>1116</v>
+        <v>1130</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="N9" s="9">
         <v>0</v>
@@ -2271,40 +2298,40 @@
         <v>97</v>
       </c>
       <c r="P9" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="10" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="R9" s="9">
         <v>33</v>
       </c>
       <c r="S9" s="10" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="T9" s="9">
         <v>193</v>
       </c>
       <c r="U9" s="10" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="V9" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W9" s="10" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="X9" s="9">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Y9" s="10" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Z9" s="9">
         <v>44</v>
       </c>
       <c r="AA9" s="10" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AB9" s="9">
         <v>0</v>
@@ -2313,16 +2340,16 @@
         <v>97</v>
       </c>
       <c r="AD9" s="9">
-        <v>2572</v>
+        <v>2602</v>
       </c>
       <c r="AE9" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AF9" s="9">
         <v>235</v>
       </c>
       <c r="AG9" s="10" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AH9" s="9">
         <v>0</v>
@@ -2331,16 +2358,16 @@
         <v>97</v>
       </c>
       <c r="AJ9" s="9">
-        <v>1048</v>
+        <v>1061</v>
       </c>
       <c r="AK9" s="10" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AL9" s="9">
         <v>68</v>
       </c>
       <c r="AM9" s="10" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AN9" s="9">
         <v>0</v>
@@ -2358,36 +2385,36 @@
         <v>4</v>
       </c>
       <c r="AS9" s="10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C10" s="9">
-        <v>6192</v>
+        <v>6859</v>
       </c>
       <c r="D10" s="9">
         <v>3</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F10" s="9">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H10" s="9">
         <v>25</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="J10" s="9">
         <v>0</v>
@@ -2396,94 +2423,94 @@
         <v>97</v>
       </c>
       <c r="L10" s="9">
-        <v>1525</v>
+        <v>1706</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N10" s="9">
         <v>1</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>140</v>
+        <v>94</v>
       </c>
       <c r="P10" s="9">
         <v>19</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="R10" s="9">
         <v>76</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="T10" s="9">
         <v>185</v>
       </c>
       <c r="U10" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="V10" s="9">
         <v>20</v>
       </c>
       <c r="W10" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="X10" s="9">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Z10" s="9">
         <v>23</v>
       </c>
       <c r="AA10" s="10" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="AB10" s="9">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AC10" s="10" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AD10" s="9">
-        <v>2608</v>
+        <v>2949</v>
       </c>
       <c r="AE10" s="10" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AF10" s="9">
         <v>28</v>
       </c>
       <c r="AG10" s="10" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AH10" s="9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI10" s="10" t="s">
-        <v>120</v>
+        <v>168</v>
       </c>
       <c r="AJ10" s="9">
-        <v>940</v>
+        <v>1042</v>
       </c>
       <c r="AK10" s="10" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="AL10" s="9">
         <v>119</v>
       </c>
       <c r="AM10" s="10" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="AN10" s="9">
         <v>1</v>
       </c>
       <c r="AO10" s="10" t="s">
-        <v>140</v>
+        <v>94</v>
       </c>
       <c r="AP10" s="9">
         <v>0</v>
@@ -2495,36 +2522,36 @@
         <v>3</v>
       </c>
       <c r="AS10" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C11" s="9">
-        <v>6120</v>
+        <v>6185</v>
       </c>
       <c r="D11" s="9">
         <v>2</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="F11" s="9">
         <v>260</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H11" s="9">
         <v>6</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>120</v>
+        <v>168</v>
       </c>
       <c r="J11" s="9">
         <v>0</v>
@@ -2533,10 +2560,10 @@
         <v>97</v>
       </c>
       <c r="L11" s="9">
-        <v>1347</v>
+        <v>1363</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="N11" s="9">
         <v>0</v>
@@ -2548,55 +2575,55 @@
         <v>34</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="R11" s="9">
         <v>28</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="T11" s="9">
         <v>361</v>
       </c>
       <c r="U11" s="10" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="V11" s="9">
         <v>6</v>
       </c>
       <c r="W11" s="10" t="s">
-        <v>120</v>
+        <v>168</v>
       </c>
       <c r="X11" s="9">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Y11" s="10" t="s">
-        <v>174</v>
+        <v>95</v>
       </c>
       <c r="Z11" s="9">
         <v>29</v>
       </c>
       <c r="AA11" s="10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AB11" s="9">
         <v>9</v>
       </c>
       <c r="AC11" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AD11" s="9">
-        <v>2738</v>
+        <v>2775</v>
       </c>
       <c r="AE11" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AF11" s="9">
         <v>73</v>
       </c>
       <c r="AG11" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AH11" s="9">
         <v>0</v>
@@ -2605,16 +2632,16 @@
         <v>97</v>
       </c>
       <c r="AJ11" s="9">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="AK11" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AL11" s="9">
         <v>39</v>
       </c>
       <c r="AM11" s="10" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AN11" s="9">
         <v>0</v>
@@ -2632,18 +2659,18 @@
         <v>2</v>
       </c>
       <c r="AS11" s="10" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C12" s="9">
-        <v>5856</v>
+        <v>5858</v>
       </c>
       <c r="D12" s="9">
         <v>0</v>
@@ -2655,13 +2682,13 @@
         <v>151</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H12" s="9">
         <v>135</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J12" s="9">
         <v>0</v>
@@ -2673,7 +2700,7 @@
         <v>843</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N12" s="9">
         <v>0</v>
@@ -2685,37 +2712,37 @@
         <v>3</v>
       </c>
       <c r="Q12" s="10" t="s">
-        <v>110</v>
+        <v>188</v>
       </c>
       <c r="R12" s="9">
         <v>26</v>
       </c>
       <c r="S12" s="10" t="s">
-        <v>99</v>
+        <v>189</v>
       </c>
       <c r="T12" s="9">
         <v>132</v>
       </c>
       <c r="U12" s="10" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="V12" s="9">
         <v>2</v>
       </c>
       <c r="W12" s="10" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="X12" s="9">
         <v>143</v>
       </c>
       <c r="Y12" s="10" t="s">
-        <v>187</v>
+        <v>101</v>
       </c>
       <c r="Z12" s="9">
         <v>32</v>
       </c>
       <c r="AA12" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB12" s="9">
         <v>0</v>
@@ -2724,16 +2751,16 @@
         <v>97</v>
       </c>
       <c r="AD12" s="9">
-        <v>2599</v>
+        <v>2600</v>
       </c>
       <c r="AE12" s="10" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AF12" s="9">
         <v>46</v>
       </c>
       <c r="AG12" s="10" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AH12" s="9">
         <v>0</v>
@@ -2742,22 +2769,22 @@
         <v>97</v>
       </c>
       <c r="AJ12" s="9">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="AK12" s="10" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AL12" s="9">
         <v>757</v>
       </c>
       <c r="AM12" s="10" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AN12" s="9">
         <v>1</v>
       </c>
       <c r="AO12" s="10" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="AP12" s="9">
         <v>0</v>
@@ -2769,18 +2796,18 @@
         <v>6</v>
       </c>
       <c r="AS12" s="10" t="s">
-        <v>120</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C13" s="9">
-        <v>3120</v>
+        <v>3188</v>
       </c>
       <c r="D13" s="9">
         <v>0</v>
@@ -2789,16 +2816,16 @@
         <v>97</v>
       </c>
       <c r="F13" s="9">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>119</v>
+        <v>197</v>
       </c>
       <c r="H13" s="9">
         <v>2</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="J13" s="9">
         <v>0</v>
@@ -2807,70 +2834,70 @@
         <v>97</v>
       </c>
       <c r="L13" s="9">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N13" s="9">
         <v>1</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="P13" s="9">
         <v>4</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>117</v>
+        <v>199</v>
       </c>
       <c r="R13" s="9">
         <v>19</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="T13" s="9">
         <v>79</v>
       </c>
       <c r="U13" s="10" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="V13" s="9">
         <v>3</v>
       </c>
       <c r="W13" s="10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="X13" s="9">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Y13" s="10" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="Z13" s="9">
         <v>12</v>
       </c>
       <c r="AA13" s="10" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="AB13" s="9">
         <v>1</v>
       </c>
       <c r="AC13" s="10" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="AD13" s="9">
-        <v>1277</v>
+        <v>1315</v>
       </c>
       <c r="AE13" s="10" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="AF13" s="9">
         <v>10</v>
       </c>
       <c r="AG13" s="10" t="s">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="AH13" s="9">
         <v>0</v>
@@ -2879,16 +2906,16 @@
         <v>97</v>
       </c>
       <c r="AJ13" s="9">
-        <v>822</v>
+        <v>832</v>
       </c>
       <c r="AK13" s="10" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="AL13" s="9">
         <v>39</v>
       </c>
       <c r="AM13" s="10" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AN13" s="9">
         <v>0</v>
@@ -2911,13 +2938,13 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C14" s="9">
-        <v>2174</v>
+        <v>2178</v>
       </c>
       <c r="D14" s="9">
         <v>0</v>
@@ -2926,16 +2953,16 @@
         <v>97</v>
       </c>
       <c r="F14" s="9">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>204</v>
+        <v>157</v>
       </c>
       <c r="H14" s="9">
         <v>17</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J14" s="9">
         <v>0</v>
@@ -2944,52 +2971,52 @@
         <v>97</v>
       </c>
       <c r="L14" s="9">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="N14" s="9">
         <v>1</v>
       </c>
       <c r="O14" s="10" t="s">
-        <v>110</v>
+        <v>188</v>
       </c>
       <c r="P14" s="9">
         <v>20</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="R14" s="9">
         <v>26</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="T14" s="9">
         <v>47</v>
       </c>
       <c r="U14" s="10" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="V14" s="9">
         <v>10</v>
       </c>
       <c r="W14" s="10" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="X14" s="9">
         <v>44</v>
       </c>
       <c r="Y14" s="10" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="Z14" s="9">
         <v>1</v>
       </c>
       <c r="AA14" s="10" t="s">
-        <v>110</v>
+        <v>188</v>
       </c>
       <c r="AB14" s="9">
         <v>0</v>
@@ -2998,16 +3025,16 @@
         <v>97</v>
       </c>
       <c r="AD14" s="9">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="AE14" s="10" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AF14" s="9">
         <v>2</v>
       </c>
       <c r="AG14" s="10" t="s">
-        <v>212</v>
+        <v>122</v>
       </c>
       <c r="AH14" s="9">
         <v>0</v>
@@ -3019,19 +3046,19 @@
         <v>336</v>
       </c>
       <c r="AK14" s="10" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="AL14" s="9">
         <v>99</v>
       </c>
       <c r="AM14" s="10" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="AN14" s="9">
         <v>1</v>
       </c>
       <c r="AO14" s="10" t="s">
-        <v>110</v>
+        <v>188</v>
       </c>
       <c r="AP14" s="9">
         <v>0</v>
@@ -3043,18 +3070,18 @@
         <v>1</v>
       </c>
       <c r="AS14" s="10" t="s">
-        <v>110</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C15" s="9">
-        <v>7650</v>
+        <v>7693</v>
       </c>
       <c r="D15" s="9">
         <v>0</v>
@@ -3063,16 +3090,16 @@
         <v>97</v>
       </c>
       <c r="F15" s="9">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="H15" s="9">
         <v>88</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>218</v>
+        <v>153</v>
       </c>
       <c r="J15" s="9">
         <v>0</v>
@@ -3081,10 +3108,10 @@
         <v>97</v>
       </c>
       <c r="L15" s="9">
-        <v>1020</v>
+        <v>1032</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="N15" s="9">
         <v>0</v>
@@ -3093,40 +3120,40 @@
         <v>97</v>
       </c>
       <c r="P15" s="9">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>220</v>
+        <v>104</v>
       </c>
       <c r="R15" s="9">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="T15" s="9">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="V15" s="9">
         <v>4</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>110</v>
+        <v>188</v>
       </c>
       <c r="X15" s="9">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Y15" s="10" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Z15" s="9">
         <v>8</v>
       </c>
       <c r="AA15" s="10" t="s">
-        <v>120</v>
+        <v>168</v>
       </c>
       <c r="AB15" s="9">
         <v>0</v>
@@ -3135,16 +3162,16 @@
         <v>97</v>
       </c>
       <c r="AD15" s="9">
-        <v>3102</v>
+        <v>3124</v>
       </c>
       <c r="AE15" s="10" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AF15" s="9">
         <v>66</v>
       </c>
       <c r="AG15" s="10" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AH15" s="9">
         <v>0</v>
@@ -3153,16 +3180,16 @@
         <v>97</v>
       </c>
       <c r="AJ15" s="9">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="AK15" s="10" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AL15" s="9">
         <v>1696</v>
       </c>
       <c r="AM15" s="10" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN15" s="9">
         <v>1</v>
@@ -3180,18 +3207,18 @@
         <v>2</v>
       </c>
       <c r="AS15" s="10" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C16" s="9">
-        <v>1937</v>
+        <v>1987</v>
       </c>
       <c r="D16" s="9">
         <v>0</v>
@@ -3200,16 +3227,16 @@
         <v>97</v>
       </c>
       <c r="F16" s="9">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="H16" s="9">
         <v>6</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="J16" s="9">
         <v>0</v>
@@ -3218,10 +3245,10 @@
         <v>97</v>
       </c>
       <c r="L16" s="9">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="N16" s="9">
         <v>0</v>
@@ -3230,76 +3257,76 @@
         <v>97</v>
       </c>
       <c r="P16" s="9">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="Q16" s="10" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="R16" s="9">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="S16" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="T16" s="9">
+        <v>101</v>
+      </c>
+      <c r="U16" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="V16" s="9">
+        <v>0</v>
+      </c>
+      <c r="W16" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="X16" s="9">
+        <v>82</v>
+      </c>
+      <c r="Y16" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="Z16" s="9">
+        <v>20</v>
+      </c>
+      <c r="AA16" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="AB16" s="9">
+        <v>18</v>
+      </c>
+      <c r="AC16" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="AD16" s="9">
+        <v>858</v>
+      </c>
+      <c r="AE16" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="AF16" s="9">
+        <v>32</v>
+      </c>
+      <c r="AG16" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="AH16" s="9">
+        <v>3</v>
+      </c>
+      <c r="AI16" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="T16" s="9">
-        <v>84</v>
-      </c>
-      <c r="U16" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="V16" s="9">
-        <v>9</v>
-      </c>
-      <c r="W16" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="X16" s="9">
-        <v>81</v>
-      </c>
-      <c r="Y16" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="Z16" s="9">
-        <v>11</v>
-      </c>
-      <c r="AA16" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="AB16" s="9">
-        <v>22</v>
-      </c>
-      <c r="AC16" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="AD16" s="9">
-        <v>837</v>
-      </c>
-      <c r="AE16" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="AF16" s="9">
-        <v>31</v>
-      </c>
-      <c r="AG16" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="AH16" s="9">
-        <v>5</v>
-      </c>
-      <c r="AI16" s="10" t="s">
-        <v>237</v>
-      </c>
       <c r="AJ16" s="9">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="AK16" s="10" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="AL16" s="9">
         <v>56</v>
       </c>
       <c r="AM16" s="10" t="s">
-        <v>102</v>
+        <v>244</v>
       </c>
       <c r="AN16" s="9">
         <v>0</v>
@@ -3317,36 +3344,36 @@
         <v>2</v>
       </c>
       <c r="AS16" s="10" t="s">
-        <v>120</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="C17" s="9">
-        <v>3063</v>
+        <v>3163</v>
       </c>
       <c r="D17" s="9">
         <v>1</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="F17" s="9">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>241</v>
+        <v>157</v>
       </c>
       <c r="H17" s="9">
         <v>26</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="J17" s="9">
         <v>0</v>
@@ -3355,10 +3382,10 @@
         <v>97</v>
       </c>
       <c r="L17" s="9">
-        <v>608</v>
+        <v>646</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="N17" s="9">
         <v>0</v>
@@ -3370,73 +3397,73 @@
         <v>23</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>147</v>
+        <v>249</v>
       </c>
       <c r="R17" s="9">
         <v>28</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>129</v>
+        <v>250</v>
       </c>
       <c r="T17" s="9">
         <v>30</v>
       </c>
       <c r="U17" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="V17" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W17" s="10" t="s">
-        <v>244</v>
+        <v>159</v>
       </c>
       <c r="X17" s="9">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Y17" s="10" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="Z17" s="9">
         <v>2</v>
       </c>
       <c r="AA17" s="10" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="AB17" s="9">
         <v>2</v>
       </c>
       <c r="AC17" s="10" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="AD17" s="9">
-        <v>1498</v>
+        <v>1551</v>
       </c>
       <c r="AE17" s="10" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="AF17" s="9">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AG17" s="10" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="AH17" s="9">
         <v>1</v>
       </c>
       <c r="AI17" s="10" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="AJ17" s="9">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="AK17" s="10" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="AL17" s="9">
         <v>221</v>
       </c>
       <c r="AM17" s="10" t="s">
-        <v>249</v>
+        <v>110</v>
       </c>
       <c r="AN17" s="9">
         <v>0</v>
@@ -3459,13 +3486,13 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C18" s="9">
-        <v>3970</v>
+        <v>4143</v>
       </c>
       <c r="D18" s="9">
         <v>0</v>
@@ -3474,16 +3501,16 @@
         <v>97</v>
       </c>
       <c r="F18" s="9">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="H18" s="9">
         <v>6</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>176</v>
+        <v>258</v>
       </c>
       <c r="J18" s="9">
         <v>0</v>
@@ -3492,10 +3519,10 @@
         <v>97</v>
       </c>
       <c r="L18" s="9">
-        <v>801</v>
+        <v>858</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="N18" s="9">
         <v>0</v>
@@ -3504,76 +3531,76 @@
         <v>97</v>
       </c>
       <c r="P18" s="9">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="R18" s="9">
         <v>20</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="T18" s="9">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="U18" s="10" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="V18" s="9">
+        <v>7</v>
+      </c>
+      <c r="W18" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="X18" s="9">
+        <v>68</v>
+      </c>
+      <c r="Y18" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="Z18" s="9">
         <v>13</v>
       </c>
-      <c r="W18" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="X18" s="9">
-        <v>60</v>
-      </c>
-      <c r="Y18" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="Z18" s="9">
-        <v>12</v>
-      </c>
       <c r="AA18" s="10" t="s">
-        <v>128</v>
+        <v>205</v>
       </c>
       <c r="AB18" s="9">
         <v>15</v>
       </c>
       <c r="AC18" s="10" t="s">
-        <v>198</v>
+        <v>99</v>
       </c>
       <c r="AD18" s="9">
-        <v>1806</v>
+        <v>1892</v>
       </c>
       <c r="AE18" s="10" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="AF18" s="9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG18" s="10" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="AH18" s="9">
         <v>1</v>
       </c>
       <c r="AI18" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AJ18" s="9">
-        <v>935</v>
+        <v>954</v>
       </c>
       <c r="AK18" s="10" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="AL18" s="9">
         <v>40</v>
       </c>
       <c r="AM18" s="10" t="s">
-        <v>260</v>
+        <v>115</v>
       </c>
       <c r="AN18" s="9">
         <v>0</v>
@@ -3596,13 +3623,13 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="C19" s="9">
-        <v>3813</v>
+        <v>3958</v>
       </c>
       <c r="D19" s="9">
         <v>0</v>
@@ -3611,10 +3638,10 @@
         <v>97</v>
       </c>
       <c r="F19" s="9">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="H19" s="9">
         <v>18</v>
@@ -3629,10 +3656,10 @@
         <v>97</v>
       </c>
       <c r="L19" s="9">
-        <v>1014</v>
+        <v>1050</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="N19" s="9">
         <v>0</v>
@@ -3647,16 +3674,16 @@
         <v>97</v>
       </c>
       <c r="R19" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>142</v>
+        <v>203</v>
       </c>
       <c r="T19" s="9">
         <v>17</v>
       </c>
       <c r="U19" s="10" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
       <c r="V19" s="9">
         <v>0</v>
@@ -3665,52 +3692,52 @@
         <v>97</v>
       </c>
       <c r="X19" s="9">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Y19" s="10" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="Z19" s="9">
         <v>4</v>
       </c>
       <c r="AA19" s="10" t="s">
-        <v>120</v>
+        <v>168</v>
       </c>
       <c r="AB19" s="9">
         <v>1</v>
       </c>
       <c r="AC19" s="10" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="AD19" s="9">
-        <v>1623</v>
+        <v>1712</v>
       </c>
       <c r="AE19" s="10" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="AF19" s="9">
         <v>26</v>
       </c>
       <c r="AG19" s="10" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AH19" s="9">
         <v>1</v>
       </c>
       <c r="AI19" s="10" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="AJ19" s="9">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="AK19" s="10" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="AL19" s="9">
         <v>146</v>
       </c>
       <c r="AM19" s="10" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="AN19" s="9">
         <v>0</v>
@@ -3728,18 +3755,18 @@
         <v>2</v>
       </c>
       <c r="AS19" s="10" t="s">
-        <v>110</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C20" s="9">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D20" s="9">
         <v>0</v>
@@ -3751,13 +3778,13 @@
         <v>44</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="H20" s="9">
         <v>6</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>273</v>
+        <v>224</v>
       </c>
       <c r="J20" s="9">
         <v>0</v>
@@ -3769,7 +3796,7 @@
         <v>58</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="N20" s="9">
         <v>0</v>
@@ -3781,55 +3808,55 @@
         <v>5</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="R20" s="9">
         <v>4</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>275</v>
+        <v>182</v>
       </c>
       <c r="T20" s="9">
         <v>41</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="V20" s="9">
         <v>16</v>
       </c>
       <c r="W20" s="10" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="X20" s="9">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Y20" s="10" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="Z20" s="9">
         <v>88</v>
       </c>
       <c r="AA20" s="10" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="AB20" s="9">
         <v>3</v>
       </c>
       <c r="AC20" s="10" t="s">
-        <v>280</v>
+        <v>177</v>
       </c>
       <c r="AD20" s="9">
         <v>231</v>
       </c>
       <c r="AE20" s="10" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="AF20" s="9">
         <v>12</v>
       </c>
       <c r="AG20" s="10" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="AH20" s="9">
         <v>0</v>
@@ -3841,13 +3868,13 @@
         <v>57</v>
       </c>
       <c r="AK20" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="AL20" s="9">
         <v>19</v>
       </c>
       <c r="AM20" s="10" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="AN20" s="9">
         <v>0</v>
@@ -3865,18 +3892,18 @@
         <v>2</v>
       </c>
       <c r="AS20" s="10" t="s">
-        <v>161</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C21" s="9">
-        <v>1464</v>
+        <v>1470</v>
       </c>
       <c r="D21" s="9">
         <v>0</v>
@@ -3885,16 +3912,16 @@
         <v>97</v>
       </c>
       <c r="F21" s="9">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="H21" s="9">
         <v>6</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>288</v>
+        <v>167</v>
       </c>
       <c r="J21" s="9">
         <v>0</v>
@@ -3903,10 +3930,10 @@
         <v>97</v>
       </c>
       <c r="L21" s="9">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="N21" s="9">
         <v>0</v>
@@ -3924,49 +3951,49 @@
         <v>9</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>195</v>
+        <v>295</v>
       </c>
       <c r="T21" s="9">
         <v>35</v>
       </c>
       <c r="U21" s="10" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="V21" s="9">
         <v>1</v>
       </c>
       <c r="W21" s="10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="X21" s="9">
         <v>37</v>
       </c>
       <c r="Y21" s="10" t="s">
-        <v>196</v>
+        <v>297</v>
       </c>
       <c r="Z21" s="9">
         <v>39</v>
       </c>
       <c r="AA21" s="10" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="AB21" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC21" s="10" t="s">
-        <v>151</v>
+        <v>299</v>
       </c>
       <c r="AD21" s="9">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="AE21" s="10" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="AF21" s="9">
         <v>3</v>
       </c>
       <c r="AG21" s="10" t="s">
-        <v>258</v>
+        <v>301</v>
       </c>
       <c r="AH21" s="9">
         <v>0</v>
@@ -3978,13 +4005,13 @@
         <v>119</v>
       </c>
       <c r="AK21" s="10" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="AL21" s="9">
         <v>384</v>
       </c>
       <c r="AM21" s="10" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="AN21" s="9">
         <v>0</v>
@@ -4007,13 +4034,13 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="C22" s="12">
-        <v>56632</v>
+        <v>58216</v>
       </c>
       <c r="D22" s="12">
         <v>7</v>
@@ -4022,7 +4049,7 @@
         <v>94</v>
       </c>
       <c r="F22" s="12">
-        <v>2361</v>
+        <v>2441</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>95</v>
@@ -4040,7 +4067,7 @@
         <v>97</v>
       </c>
       <c r="L22" s="12">
-        <v>10972</v>
+        <v>11446</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>98</v>
@@ -4052,76 +4079,76 @@
         <v>94</v>
       </c>
       <c r="P22" s="12">
-        <v>251</v>
+        <v>211</v>
       </c>
       <c r="Q22" s="13" t="s">
         <v>99</v>
       </c>
       <c r="R22" s="12">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="S22" s="13" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="T22" s="12">
-        <v>1391</v>
+        <v>1423</v>
       </c>
       <c r="U22" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="V22" s="12">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="W22" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="X22" s="12">
-        <v>1637</v>
+        <v>1670</v>
       </c>
       <c r="Y22" s="13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Z22" s="12">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="AA22" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB22" s="12">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="AC22" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AD22" s="12">
-        <v>24396</v>
+        <v>25193</v>
       </c>
       <c r="AE22" s="13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AF22" s="12">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="AG22" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AH22" s="12">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI22" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AJ22" s="12">
-        <v>9441</v>
+        <v>9655</v>
       </c>
       <c r="AK22" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AL22" s="12">
         <v>4070</v>
       </c>
       <c r="AM22" s="13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN22" s="12">
         <v>4</v>
@@ -4139,7 +4166,7 @@
         <v>26</v>
       </c>
       <c r="AS22" s="13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
+++ b/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="303">
   <si>
     <t>DATA RADAR ANOMALI KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 29 Agu 2026, 16.20</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 31 Agu 2026, 08.57</t>
   </si>
   <si>
     <t>Kode</t>
@@ -298,631 +298,622 @@
     <t>0,01</t>
   </si>
   <si>
-    <t>4,19</t>
+    <t>4,21</t>
+  </si>
+  <si>
+    <t>0,66</t>
+  </si>
+  <si>
+    <t>20,04</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0,32</t>
   </si>
   <si>
     <t>0,68</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>19,66</t>
+    <t>2,4</t>
+  </si>
+  <si>
+    <t>0,19</t>
+  </si>
+  <si>
+    <t>2,89</t>
+  </si>
+  <si>
+    <t>0,54</t>
+  </si>
+  <si>
+    <t>43,37</t>
+  </si>
+  <si>
+    <t>1,01</t>
+  </si>
+  <si>
+    <t>0,02</t>
+  </si>
+  <si>
+    <t>16,52</t>
+  </si>
+  <si>
+    <t>6,77</t>
+  </si>
+  <si>
+    <t>0,04</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>LAMPUNG BARAT</t>
+  </si>
+  <si>
+    <t>3,76</t>
+  </si>
+  <si>
+    <t>0,82</t>
+  </si>
+  <si>
+    <t>0,1</t>
+  </si>
+  <si>
+    <t>27,88</t>
+  </si>
+  <si>
+    <t>0,59</t>
+  </si>
+  <si>
+    <t>1,11</t>
+  </si>
+  <si>
+    <t>4,07</t>
+  </si>
+  <si>
+    <t>0,08</t>
+  </si>
+  <si>
+    <t>0,13</t>
+  </si>
+  <si>
+    <t>38,2</t>
+  </si>
+  <si>
+    <t>0,44</t>
+  </si>
+  <si>
+    <t>12,84</t>
+  </si>
+  <si>
+    <t>9,78</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>TANGGAMUS</t>
+  </si>
+  <si>
+    <t>6,55</t>
+  </si>
+  <si>
+    <t>19,76</t>
+  </si>
+  <si>
+    <t>0,3</t>
+  </si>
+  <si>
+    <t>0,9</t>
+  </si>
+  <si>
+    <t>3,3</t>
+  </si>
+  <si>
+    <t>0,18</t>
+  </si>
+  <si>
+    <t>3,18</t>
+  </si>
+  <si>
+    <t>41,8</t>
+  </si>
+  <si>
+    <t>0,12</t>
+  </si>
+  <si>
+    <t>0,06</t>
+  </si>
+  <si>
+    <t>22,7</t>
+  </si>
+  <si>
+    <t>0,42</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>LAMPUNG SELATAN</t>
+  </si>
+  <si>
+    <t>5,81</t>
+  </si>
+  <si>
+    <t>0,37</t>
+  </si>
+  <si>
+    <t>19,03</t>
+  </si>
+  <si>
+    <t>0,56</t>
+  </si>
+  <si>
+    <t>3,25</t>
+  </si>
+  <si>
+    <t>3,35</t>
+  </si>
+  <si>
+    <t>0,74</t>
+  </si>
+  <si>
+    <t>43,83</t>
+  </si>
+  <si>
+    <t>3,96</t>
+  </si>
+  <si>
+    <t>17,86</t>
+  </si>
+  <si>
+    <t>1,14</t>
+  </si>
+  <si>
+    <t>0,07</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>LAMPUNG TIMUR</t>
+  </si>
+  <si>
+    <t>4,33</t>
   </si>
   <si>
     <t>0,36</t>
   </si>
   <si>
-    <t>0,69</t>
+    <t>25,02</t>
+  </si>
+  <si>
+    <t>0,27</t>
+  </si>
+  <si>
+    <t>1,1</t>
+  </si>
+  <si>
+    <t>2,64</t>
+  </si>
+  <si>
+    <t>0,26</t>
+  </si>
+  <si>
+    <t>0,33</t>
+  </si>
+  <si>
+    <t>1,7</t>
+  </si>
+  <si>
+    <t>43,14</t>
+  </si>
+  <si>
+    <t>0,4</t>
+  </si>
+  <si>
+    <t>15,23</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>LAMPUNG TENGAH</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>22,03</t>
+  </si>
+  <si>
+    <t>0,45</t>
+  </si>
+  <si>
+    <t>5,83</t>
+  </si>
+  <si>
+    <t>4,18</t>
+  </si>
+  <si>
+    <t>0,47</t>
+  </si>
+  <si>
+    <t>0,15</t>
+  </si>
+  <si>
+    <t>44,89</t>
+  </si>
+  <si>
+    <t>1,18</t>
+  </si>
+  <si>
+    <t>15,16</t>
+  </si>
+  <si>
+    <t>0,63</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>2,57</t>
+  </si>
+  <si>
+    <t>2,3</t>
+  </si>
+  <si>
+    <t>14,37</t>
+  </si>
+  <si>
+    <t>0,05</t>
+  </si>
+  <si>
+    <t>2,25</t>
   </si>
   <si>
     <t>2,44</t>
   </si>
   <si>
-    <t>0,23</t>
-  </si>
-  <si>
-    <t>2,87</t>
-  </si>
-  <si>
     <t>0,55</t>
   </si>
   <si>
-    <t>0,33</t>
-  </si>
-  <si>
-    <t>43,28</t>
-  </si>
-  <si>
-    <t>1,04</t>
-  </si>
-  <si>
-    <t>0,02</t>
-  </si>
-  <si>
-    <t>16,58</t>
-  </si>
-  <si>
-    <t>6,99</t>
-  </si>
-  <si>
-    <t>0,04</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>LAMPUNG BARAT</t>
-  </si>
-  <si>
-    <t>3,82</t>
-  </si>
-  <si>
-    <t>0,97</t>
-  </si>
-  <si>
-    <t>0,03</t>
-  </si>
-  <si>
-    <t>25,85</t>
-  </si>
-  <si>
-    <t>0,7</t>
-  </si>
-  <si>
-    <t>0,12</t>
-  </si>
-  <si>
-    <t>1,52</t>
-  </si>
-  <si>
-    <t>4,09</t>
+    <t>44,41</t>
+  </si>
+  <si>
+    <t>0,78</t>
+  </si>
+  <si>
+    <t>16,77</t>
+  </si>
+  <si>
+    <t>12,9</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
+    <t>4,36</t>
+  </si>
+  <si>
+    <t>20,1</t>
   </si>
   <si>
     <t>0,09</t>
   </si>
   <si>
-    <t>38,27</t>
-  </si>
-  <si>
-    <t>0,52</t>
-  </si>
-  <si>
-    <t>12,27</t>
-  </si>
-  <si>
-    <t>11,52</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>TANGGAMUS</t>
-  </si>
-  <si>
-    <t>6,55</t>
-  </si>
-  <si>
-    <t>19,78</t>
-  </si>
-  <si>
-    <t>0,24</t>
-  </si>
-  <si>
-    <t>0,9</t>
+    <t>2,49</t>
+  </si>
+  <si>
+    <t>2,96</t>
+  </si>
+  <si>
+    <t>41,29</t>
+  </si>
+  <si>
+    <t>0,34</t>
+  </si>
+  <si>
+    <t>26,01</t>
+  </si>
+  <si>
+    <t>1,21</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG</t>
+  </si>
+  <si>
+    <t>4,47</t>
+  </si>
+  <si>
+    <t>21,51</t>
+  </si>
+  <si>
+    <t>0,91</t>
+  </si>
+  <si>
+    <t>1,19</t>
+  </si>
+  <si>
+    <t>2,15</t>
+  </si>
+  <si>
+    <t>0,46</t>
+  </si>
+  <si>
+    <t>2,01</t>
+  </si>
+  <si>
+    <t>46,21</t>
+  </si>
+  <si>
+    <t>15,53</t>
+  </si>
+  <si>
+    <t>4,52</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PESAWARAN</t>
+  </si>
+  <si>
+    <t>13,41</t>
+  </si>
+  <si>
+    <t>0,35</t>
+  </si>
+  <si>
+    <t>0,96</t>
+  </si>
+  <si>
+    <t>1,17</t>
+  </si>
+  <si>
+    <t>1,27</t>
+  </si>
+  <si>
+    <t>40,65</t>
+  </si>
+  <si>
+    <t>0,86</t>
+  </si>
+  <si>
+    <t>14,7</t>
+  </si>
+  <si>
+    <t>22,02</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>PRINGSEWU</t>
+  </si>
+  <si>
+    <t>5,02</t>
+  </si>
+  <si>
+    <t>15,4</t>
+  </si>
+  <si>
+    <t>0,64</t>
+  </si>
+  <si>
+    <t>1,38</t>
+  </si>
+  <si>
+    <t>4,97</t>
+  </si>
+  <si>
+    <t>4,08</t>
+  </si>
+  <si>
+    <t>0,98</t>
+  </si>
+  <si>
+    <t>0,89</t>
+  </si>
+  <si>
+    <t>42,84</t>
+  </si>
+  <si>
+    <t>1,57</t>
+  </si>
+  <si>
+    <t>18,94</t>
+  </si>
+  <si>
+    <t>2,75</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
+  </si>
+  <si>
+    <t>4,46</t>
+  </si>
+  <si>
+    <t>0,75</t>
+  </si>
+  <si>
+    <t>21,26</t>
+  </si>
+  <si>
+    <t>0,84</t>
+  </si>
+  <si>
+    <t>0,87</t>
+  </si>
+  <si>
+    <t>1,65</t>
+  </si>
+  <si>
+    <t>49,54</t>
+  </si>
+  <si>
+    <t>1,22</t>
+  </si>
+  <si>
+    <t>11,94</t>
+  </si>
+  <si>
+    <t>6,37</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG BARAT</t>
+  </si>
+  <si>
+    <t>0,14</t>
+  </si>
+  <si>
+    <t>20,89</t>
+  </si>
+  <si>
+    <t>0,11</t>
+  </si>
+  <si>
+    <t>1,83</t>
+  </si>
+  <si>
+    <t>45,59</t>
+  </si>
+  <si>
+    <t>0,28</t>
+  </si>
+  <si>
+    <t>22,95</t>
+  </si>
+  <si>
+    <t>0,99</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>PESISIR BARAT</t>
+  </si>
+  <si>
+    <t>4,56</t>
+  </si>
+  <si>
+    <t>26,78</t>
+  </si>
+  <si>
+    <t>0,38</t>
   </si>
   <si>
     <t>3,31</t>
   </si>
   <si>
-    <t>0,18</t>
-  </si>
-  <si>
-    <t>3,19</t>
-  </si>
-  <si>
-    <t>0,3</t>
-  </si>
-  <si>
-    <t>41,85</t>
-  </si>
-  <si>
-    <t>0,06</t>
-  </si>
-  <si>
-    <t>22,73</t>
-  </si>
-  <si>
-    <t>0,42</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>LAMPUNG SELATAN</t>
-  </si>
-  <si>
-    <t>5,81</t>
-  </si>
-  <si>
-    <t>0,37</t>
-  </si>
-  <si>
-    <t>19,03</t>
-  </si>
-  <si>
-    <t>0,56</t>
-  </si>
-  <si>
-    <t>3,25</t>
-  </si>
-  <si>
-    <t>3,35</t>
-  </si>
-  <si>
-    <t>0,74</t>
-  </si>
-  <si>
-    <t>43,81</t>
-  </si>
-  <si>
-    <t>3,96</t>
-  </si>
-  <si>
-    <t>17,86</t>
-  </si>
-  <si>
-    <t>1,14</t>
-  </si>
-  <si>
-    <t>0,07</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>LAMPUNG TIMUR</t>
-  </si>
-  <si>
-    <t>4,36</t>
-  </si>
-  <si>
-    <t>24,87</t>
-  </si>
-  <si>
-    <t>0,28</t>
-  </si>
-  <si>
-    <t>1,11</t>
-  </si>
-  <si>
-    <t>2,7</t>
-  </si>
-  <si>
-    <t>0,29</t>
-  </si>
-  <si>
-    <t>3,38</t>
-  </si>
-  <si>
-    <t>0,34</t>
-  </si>
-  <si>
-    <t>1,76</t>
-  </si>
-  <si>
-    <t>42,99</t>
+    <t>44,24</t>
+  </si>
+  <si>
+    <t>0,58</t>
+  </si>
+  <si>
+    <t>15,97</t>
+  </si>
+  <si>
+    <t>3,26</t>
+  </si>
+  <si>
+    <t>1871</t>
+  </si>
+  <si>
+    <t>BANDAR LAMPUNG</t>
+  </si>
+  <si>
+    <t>7,14</t>
+  </si>
+  <si>
+    <t>0,93</t>
+  </si>
+  <si>
+    <t>9,47</t>
+  </si>
+  <si>
+    <t>0,62</t>
+  </si>
+  <si>
+    <t>2,02</t>
+  </si>
+  <si>
+    <t>13,66</t>
+  </si>
+  <si>
+    <t>36,96</t>
+  </si>
+  <si>
+    <t>1,86</t>
+  </si>
+  <si>
+    <t>9,32</t>
+  </si>
+  <si>
+    <t>2,95</t>
+  </si>
+  <si>
+    <t>0,31</t>
+  </si>
+  <si>
+    <t>1872</t>
+  </si>
+  <si>
+    <t>METRO</t>
+  </si>
+  <si>
+    <t>2,45</t>
   </si>
   <si>
     <t>0,41</t>
   </si>
   <si>
-    <t>0,1</t>
-  </si>
-  <si>
-    <t>15,19</t>
-  </si>
-  <si>
-    <t>1,73</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>LAMPUNG TENGAH</t>
-  </si>
-  <si>
-    <t>4,2</t>
-  </si>
-  <si>
-    <t>22,04</t>
-  </si>
-  <si>
-    <t>0,45</t>
-  </si>
-  <si>
-    <t>5,84</t>
-  </si>
-  <si>
-    <t>0,47</t>
-  </si>
-  <si>
-    <t>0,15</t>
-  </si>
-  <si>
-    <t>44,87</t>
-  </si>
-  <si>
-    <t>1,18</t>
-  </si>
-  <si>
-    <t>15,18</t>
-  </si>
-  <si>
-    <t>0,63</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
-  </si>
-  <si>
-    <t>2,58</t>
-  </si>
-  <si>
-    <t>2,3</t>
-  </si>
-  <si>
-    <t>14,39</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>0,44</t>
-  </si>
-  <si>
-    <t>2,25</t>
-  </si>
-  <si>
-    <t>44,38</t>
-  </si>
-  <si>
-    <t>0,79</t>
-  </si>
-  <si>
-    <t>16,75</t>
-  </si>
-  <si>
-    <t>12,92</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>4,33</t>
-  </si>
-  <si>
-    <t>20,04</t>
-  </si>
-  <si>
-    <t>0,13</t>
-  </si>
-  <si>
-    <t>0,6</t>
-  </si>
-  <si>
-    <t>2,48</t>
-  </si>
-  <si>
-    <t>2,95</t>
-  </si>
-  <si>
-    <t>0,38</t>
-  </si>
-  <si>
-    <t>41,25</t>
-  </si>
-  <si>
-    <t>0,31</t>
+    <t>11,56</t>
+  </si>
+  <si>
+    <t>0,61</t>
+  </si>
+  <si>
+    <t>2,38</t>
+  </si>
+  <si>
+    <t>2,52</t>
+  </si>
+  <si>
+    <t>2,65</t>
+  </si>
+  <si>
+    <t>1,02</t>
+  </si>
+  <si>
+    <t>41,88</t>
+  </si>
+  <si>
+    <t>0,2</t>
+  </si>
+  <si>
+    <t>8,09</t>
   </si>
   <si>
     <t>26,1</t>
-  </si>
-  <si>
-    <t>1,22</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG</t>
-  </si>
-  <si>
-    <t>0,78</t>
-  </si>
-  <si>
-    <t>21,49</t>
-  </si>
-  <si>
-    <t>0,92</t>
-  </si>
-  <si>
-    <t>1,19</t>
-  </si>
-  <si>
-    <t>2,16</t>
-  </si>
-  <si>
-    <t>0,46</t>
-  </si>
-  <si>
-    <t>2,02</t>
-  </si>
-  <si>
-    <t>46,37</t>
-  </si>
-  <si>
-    <t>15,43</t>
-  </si>
-  <si>
-    <t>4,55</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>PESAWARAN</t>
-  </si>
-  <si>
-    <t>3,29</t>
-  </si>
-  <si>
-    <t>13,41</t>
-  </si>
-  <si>
-    <t>0,95</t>
-  </si>
-  <si>
-    <t>0,99</t>
-  </si>
-  <si>
-    <t>1,26</t>
-  </si>
-  <si>
-    <t>40,61</t>
-  </si>
-  <si>
-    <t>0,86</t>
-  </si>
-  <si>
-    <t>14,7</t>
-  </si>
-  <si>
-    <t>22,05</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>PRINGSEWU</t>
-  </si>
-  <si>
-    <t>4,98</t>
-  </si>
-  <si>
-    <t>15,15</t>
-  </si>
-  <si>
-    <t>0,65</t>
-  </si>
-  <si>
-    <t>1,41</t>
-  </si>
-  <si>
-    <t>5,08</t>
-  </si>
-  <si>
-    <t>4,13</t>
-  </si>
-  <si>
-    <t>1,01</t>
-  </si>
-  <si>
-    <t>0,91</t>
-  </si>
-  <si>
-    <t>43,18</t>
-  </si>
-  <si>
-    <t>1,61</t>
-  </si>
-  <si>
-    <t>18,52</t>
-  </si>
-  <si>
-    <t>2,82</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>0,82</t>
-  </si>
-  <si>
-    <t>20,42</t>
-  </si>
-  <si>
-    <t>0,73</t>
-  </si>
-  <si>
-    <t>0,89</t>
-  </si>
-  <si>
-    <t>1,55</t>
-  </si>
-  <si>
-    <t>49,04</t>
-  </si>
-  <si>
-    <t>1,33</t>
-  </si>
-  <si>
-    <t>12,46</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG BARAT</t>
-  </si>
-  <si>
-    <t>4,15</t>
-  </si>
-  <si>
-    <t>0,14</t>
-  </si>
-  <si>
-    <t>20,71</t>
-  </si>
-  <si>
-    <t>0,51</t>
-  </si>
-  <si>
-    <t>0,48</t>
-  </si>
-  <si>
-    <t>1,62</t>
-  </si>
-  <si>
-    <t>0,17</t>
-  </si>
-  <si>
-    <t>1,64</t>
-  </si>
-  <si>
-    <t>45,67</t>
-  </si>
-  <si>
-    <t>0,22</t>
-  </si>
-  <si>
-    <t>23,03</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>PESISIR BARAT</t>
-  </si>
-  <si>
-    <t>4,45</t>
-  </si>
-  <si>
-    <t>26,53</t>
-  </si>
-  <si>
-    <t>0,43</t>
-  </si>
-  <si>
-    <t>3,34</t>
-  </si>
-  <si>
-    <t>43,25</t>
-  </si>
-  <si>
-    <t>0,66</t>
-  </si>
-  <si>
-    <t>16,62</t>
-  </si>
-  <si>
-    <t>3,69</t>
-  </si>
-  <si>
-    <t>1871</t>
-  </si>
-  <si>
-    <t>BANDAR LAMPUNG</t>
-  </si>
-  <si>
-    <t>6,96</t>
-  </si>
-  <si>
-    <t>9,18</t>
-  </si>
-  <si>
-    <t>6,49</t>
-  </si>
-  <si>
-    <t>2,53</t>
-  </si>
-  <si>
-    <t>7,28</t>
-  </si>
-  <si>
-    <t>13,92</t>
-  </si>
-  <si>
-    <t>36,55</t>
-  </si>
-  <si>
-    <t>1,9</t>
-  </si>
-  <si>
-    <t>9,02</t>
-  </si>
-  <si>
-    <t>3,01</t>
-  </si>
-  <si>
-    <t>0,32</t>
-  </si>
-  <si>
-    <t>1872</t>
-  </si>
-  <si>
-    <t>METRO</t>
-  </si>
-  <si>
-    <t>2,45</t>
-  </si>
-  <si>
-    <t>11,56</t>
-  </si>
-  <si>
-    <t>0,61</t>
-  </si>
-  <si>
-    <t>2,38</t>
-  </si>
-  <si>
-    <t>2,52</t>
-  </si>
-  <si>
-    <t>2,65</t>
-  </si>
-  <si>
-    <t>1,09</t>
-  </si>
-  <si>
-    <t>41,84</t>
-  </si>
-  <si>
-    <t>0,2</t>
-  </si>
-  <si>
-    <t>8,1</t>
-  </si>
-  <si>
-    <t>26,12</t>
   </si>
   <si>
     <t/>
@@ -1848,7 +1839,7 @@
         <v>93</v>
       </c>
       <c r="C6" s="6">
-        <v>58216</v>
+        <v>60113</v>
       </c>
       <c r="D6" s="6">
         <v>7</v>
@@ -1857,7 +1848,7 @@
         <v>94</v>
       </c>
       <c r="F6" s="6">
-        <v>2441</v>
+        <v>2528</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>95</v>
@@ -1869,94 +1860,94 @@
         <v>96</v>
       </c>
       <c r="J6" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K6" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="L6" s="6">
+        <v>12044</v>
+      </c>
+      <c r="M6" s="7" t="s">
         <v>97</v>
-      </c>
-      <c r="L6" s="6">
-        <v>11446</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>98</v>
       </c>
       <c r="N6" s="6">
         <v>3</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="P6" s="6">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="Q6" s="7" t="s">
         <v>99</v>
       </c>
       <c r="R6" s="6">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="S6" s="7" t="s">
         <v>100</v>
       </c>
       <c r="T6" s="6">
-        <v>1423</v>
+        <v>1443</v>
       </c>
       <c r="U6" s="7" t="s">
         <v>101</v>
       </c>
       <c r="V6" s="6">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="W6" s="7" t="s">
         <v>102</v>
       </c>
       <c r="X6" s="6">
-        <v>1670</v>
+        <v>1735</v>
       </c>
       <c r="Y6" s="7" t="s">
         <v>103</v>
       </c>
       <c r="Z6" s="6">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AA6" s="7" t="s">
         <v>104</v>
       </c>
       <c r="AB6" s="6">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AC6" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>26070</v>
+      </c>
+      <c r="AE6" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="AD6" s="6">
-        <v>25193</v>
-      </c>
-      <c r="AE6" s="7" t="s">
+      <c r="AF6" s="6">
+        <v>607</v>
+      </c>
+      <c r="AG6" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="AF6" s="6">
-        <v>603</v>
-      </c>
-      <c r="AG6" s="7" t="s">
+      <c r="AH6" s="6">
+        <v>12</v>
+      </c>
+      <c r="AI6" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="AH6" s="6">
-        <v>14</v>
-      </c>
-      <c r="AI6" s="7" t="s">
+      <c r="AJ6" s="6">
+        <v>9930</v>
+      </c>
+      <c r="AK6" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="AJ6" s="6">
-        <v>9655</v>
-      </c>
-      <c r="AK6" s="7" t="s">
+      <c r="AL6" s="6">
+        <v>4072</v>
+      </c>
+      <c r="AM6" s="7" t="s">
         <v>109</v>
-      </c>
-      <c r="AL6" s="6">
-        <v>4070</v>
-      </c>
-      <c r="AM6" s="7" t="s">
-        <v>110</v>
       </c>
       <c r="AN6" s="6">
         <v>4</v>
@@ -1968,295 +1959,295 @@
         <v>0</v>
       </c>
       <c r="AQ6" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AR6" s="6">
         <v>26</v>
       </c>
       <c r="AS6" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="C7" s="9">
+        <v>3885</v>
+      </c>
+      <c r="D7" s="9">
+        <v>0</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" s="9">
+        <v>146</v>
+      </c>
+      <c r="G7" s="10" t="s">
         <v>113</v>
-      </c>
-      <c r="C7" s="9">
-        <v>3300</v>
-      </c>
-      <c r="D7" s="9">
-        <v>0</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="F7" s="9">
-        <v>126</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>114</v>
       </c>
       <c r="H7" s="9">
         <v>32</v>
       </c>
       <c r="I7" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J7" s="9">
+        <v>4</v>
+      </c>
+      <c r="K7" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="J7" s="9">
-        <v>1</v>
-      </c>
-      <c r="K7" s="10" t="s">
+      <c r="L7" s="9">
+        <v>1083</v>
+      </c>
+      <c r="M7" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L7" s="9">
-        <v>853</v>
-      </c>
-      <c r="M7" s="10" t="s">
-        <v>117</v>
-      </c>
       <c r="N7" s="9">
         <v>0</v>
       </c>
       <c r="O7" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P7" s="9">
         <v>23</v>
       </c>
       <c r="Q7" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R7" s="9">
         <v>4</v>
       </c>
       <c r="S7" s="10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="T7" s="9">
         <v>4</v>
       </c>
       <c r="U7" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="V7" s="9">
+        <v>43</v>
+      </c>
+      <c r="W7" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="X7" s="9">
+        <v>158</v>
+      </c>
+      <c r="Y7" s="10" t="s">
         <v>119</v>
-      </c>
-      <c r="V7" s="9">
-        <v>50</v>
-      </c>
-      <c r="W7" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X7" s="9">
-        <v>135</v>
-      </c>
-      <c r="Y7" s="10" t="s">
-        <v>121</v>
       </c>
       <c r="Z7" s="9">
         <v>3</v>
       </c>
       <c r="AA7" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB7" s="9">
+        <v>5</v>
+      </c>
+      <c r="AC7" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD7" s="9">
+        <v>1484</v>
+      </c>
+      <c r="AE7" s="10" t="s">
         <v>122</v>
-      </c>
-      <c r="AB7" s="9">
-        <v>4</v>
-      </c>
-      <c r="AC7" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="AD7" s="9">
-        <v>1263</v>
-      </c>
-      <c r="AE7" s="10" t="s">
-        <v>123</v>
       </c>
       <c r="AF7" s="9">
         <v>17</v>
       </c>
       <c r="AG7" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="AH7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ7" s="9">
+        <v>499</v>
+      </c>
+      <c r="AK7" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="AH7" s="9">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ7" s="9">
-        <v>405</v>
-      </c>
-      <c r="AK7" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="AL7" s="9">
         <v>380</v>
       </c>
       <c r="AM7" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AN7" s="9">
         <v>0</v>
       </c>
       <c r="AO7" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AP7" s="9">
         <v>0</v>
       </c>
       <c r="AQ7" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AR7" s="9">
         <v>0</v>
       </c>
       <c r="AS7" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>128</v>
-      </c>
       <c r="C8" s="9">
-        <v>1663</v>
+        <v>1665</v>
       </c>
       <c r="D8" s="9">
         <v>0</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F8" s="9">
         <v>109</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J8" s="9">
         <v>0</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L8" s="9">
         <v>329</v>
       </c>
       <c r="M8" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="N8" s="9">
+        <v>0</v>
+      </c>
+      <c r="O8" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="P8" s="9">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="10" t="s">
         <v>130</v>
-      </c>
-      <c r="N8" s="9">
-        <v>0</v>
-      </c>
-      <c r="O8" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="P8" s="9">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="10" t="s">
-        <v>131</v>
       </c>
       <c r="R8" s="9">
         <v>15</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="T8" s="9">
         <v>55</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="V8" s="9">
         <v>3</v>
       </c>
       <c r="W8" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="X8" s="9">
         <v>53</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z8" s="9">
         <v>5</v>
       </c>
       <c r="AA8" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="AB8" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC8" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD8" s="9">
         <v>696</v>
       </c>
       <c r="AE8" s="10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AF8" s="9">
         <v>2</v>
       </c>
       <c r="AG8" s="10" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="AH8" s="9">
         <v>1</v>
       </c>
       <c r="AI8" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AJ8" s="9">
         <v>378</v>
       </c>
       <c r="AK8" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AL8" s="9">
         <v>7</v>
       </c>
       <c r="AM8" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AN8" s="9">
         <v>0</v>
       </c>
       <c r="AO8" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AP8" s="9">
         <v>0</v>
       </c>
       <c r="AQ8" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AR8" s="9">
         <v>2</v>
       </c>
       <c r="AS8" s="10" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>141</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>142</v>
       </c>
       <c r="C9" s="9">
         <v>5939</v>
@@ -2265,165 +2256,165 @@
         <v>1</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F9" s="9">
         <v>345</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H9" s="9">
         <v>22</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J9" s="9">
         <v>0</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L9" s="9">
         <v>1130</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N9" s="9">
         <v>0</v>
       </c>
       <c r="O9" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P9" s="9">
         <v>0</v>
       </c>
       <c r="Q9" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="R9" s="9">
         <v>33</v>
       </c>
       <c r="S9" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="T9" s="9">
         <v>193</v>
       </c>
       <c r="U9" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="V9" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W9" s="10" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="X9" s="9">
         <v>199</v>
       </c>
       <c r="Y9" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Z9" s="9">
         <v>44</v>
       </c>
       <c r="AA9" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="AB9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="AD9" s="9">
+        <v>2603</v>
+      </c>
+      <c r="AE9" s="10" t="s">
         <v>149</v>
-      </c>
-      <c r="AB9" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD9" s="9">
-        <v>2602</v>
-      </c>
-      <c r="AE9" s="10" t="s">
-        <v>150</v>
       </c>
       <c r="AF9" s="9">
         <v>235</v>
       </c>
       <c r="AG9" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AH9" s="9">
         <v>0</v>
       </c>
       <c r="AI9" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AJ9" s="9">
         <v>1061</v>
       </c>
       <c r="AK9" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AL9" s="9">
         <v>68</v>
       </c>
       <c r="AM9" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AN9" s="9">
         <v>0</v>
       </c>
       <c r="AO9" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AP9" s="9">
         <v>0</v>
       </c>
       <c r="AQ9" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AR9" s="9">
         <v>4</v>
       </c>
       <c r="AS9" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>156</v>
-      </c>
       <c r="C10" s="9">
-        <v>6859</v>
+        <v>7017</v>
       </c>
       <c r="D10" s="9">
         <v>3</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F10" s="9">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H10" s="9">
         <v>25</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>99</v>
+        <v>157</v>
       </c>
       <c r="J10" s="9">
         <v>0</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L10" s="9">
-        <v>1706</v>
+        <v>1756</v>
       </c>
       <c r="M10" s="10" t="s">
         <v>158</v>
@@ -2441,7 +2432,7 @@
         <v>159</v>
       </c>
       <c r="R10" s="9">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S10" s="10" t="s">
         <v>160</v>
@@ -2453,58 +2444,58 @@
         <v>161</v>
       </c>
       <c r="V10" s="9">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="W10" s="10" t="s">
         <v>162</v>
       </c>
       <c r="X10" s="9">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="Z10" s="9">
         <v>23</v>
       </c>
       <c r="AA10" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB10" s="9">
+        <v>119</v>
+      </c>
+      <c r="AC10" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="AB10" s="9">
-        <v>121</v>
-      </c>
-      <c r="AC10" s="10" t="s">
+      <c r="AD10" s="9">
+        <v>3027</v>
+      </c>
+      <c r="AE10" s="10" t="s">
         <v>165</v>
-      </c>
-      <c r="AD10" s="9">
-        <v>2949</v>
-      </c>
-      <c r="AE10" s="10" t="s">
-        <v>166</v>
       </c>
       <c r="AF10" s="9">
         <v>28</v>
       </c>
       <c r="AG10" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="AH10" s="9">
+        <v>5</v>
+      </c>
+      <c r="AI10" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="AJ10" s="9">
+        <v>1069</v>
+      </c>
+      <c r="AK10" s="10" t="s">
         <v>167</v>
-      </c>
-      <c r="AH10" s="9">
-        <v>7</v>
-      </c>
-      <c r="AI10" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="AJ10" s="9">
-        <v>1042</v>
-      </c>
-      <c r="AK10" s="10" t="s">
-        <v>169</v>
       </c>
       <c r="AL10" s="9">
         <v>119</v>
       </c>
       <c r="AM10" s="10" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="AN10" s="9">
         <v>1</v>
@@ -2516,680 +2507,680 @@
         <v>0</v>
       </c>
       <c r="AQ10" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AR10" s="9">
         <v>3</v>
       </c>
       <c r="AS10" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C11" s="9">
-        <v>6185</v>
+        <v>6195</v>
       </c>
       <c r="D11" s="9">
         <v>2</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="F11" s="9">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>173</v>
+        <v>95</v>
       </c>
       <c r="H11" s="9">
         <v>6</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>168</v>
+        <v>115</v>
       </c>
       <c r="J11" s="9">
         <v>0</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L11" s="9">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="N11" s="9">
         <v>0</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P11" s="9">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="R11" s="9">
         <v>28</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="T11" s="9">
         <v>361</v>
       </c>
       <c r="U11" s="10" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="V11" s="9">
         <v>6</v>
       </c>
       <c r="W11" s="10" t="s">
-        <v>168</v>
+        <v>115</v>
       </c>
       <c r="X11" s="9">
         <v>259</v>
       </c>
       <c r="Y11" s="10" t="s">
-        <v>95</v>
+        <v>174</v>
       </c>
       <c r="Z11" s="9">
         <v>29</v>
       </c>
       <c r="AA11" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AB11" s="9">
         <v>9</v>
       </c>
       <c r="AC11" s="10" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AD11" s="9">
-        <v>2775</v>
+        <v>2781</v>
       </c>
       <c r="AE11" s="10" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AF11" s="9">
         <v>73</v>
       </c>
       <c r="AG11" s="10" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AH11" s="9">
         <v>0</v>
       </c>
       <c r="AI11" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AJ11" s="9">
         <v>939</v>
       </c>
       <c r="AK11" s="10" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AL11" s="9">
         <v>39</v>
       </c>
       <c r="AM11" s="10" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AN11" s="9">
         <v>0</v>
       </c>
       <c r="AO11" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AP11" s="9">
         <v>0</v>
       </c>
       <c r="AQ11" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AR11" s="9">
         <v>2</v>
       </c>
       <c r="AS11" s="10" t="s">
-        <v>116</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C12" s="9">
-        <v>5858</v>
+        <v>5866</v>
       </c>
       <c r="D12" s="9">
         <v>0</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F12" s="9">
         <v>151</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H12" s="9">
         <v>135</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J12" s="9">
         <v>0</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L12" s="9">
         <v>843</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="N12" s="9">
         <v>0</v>
       </c>
       <c r="O12" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P12" s="9">
         <v>3</v>
       </c>
       <c r="Q12" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R12" s="9">
         <v>26</v>
       </c>
       <c r="S12" s="10" t="s">
-        <v>189</v>
+        <v>123</v>
       </c>
       <c r="T12" s="9">
         <v>132</v>
       </c>
       <c r="U12" s="10" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="V12" s="9">
         <v>2</v>
       </c>
       <c r="W12" s="10" t="s">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="X12" s="9">
         <v>143</v>
       </c>
       <c r="Y12" s="10" t="s">
-        <v>101</v>
+        <v>188</v>
       </c>
       <c r="Z12" s="9">
         <v>32</v>
       </c>
       <c r="AA12" s="10" t="s">
-        <v>104</v>
+        <v>189</v>
       </c>
       <c r="AB12" s="9">
         <v>0</v>
       </c>
       <c r="AC12" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AD12" s="9">
-        <v>2600</v>
+        <v>2605</v>
       </c>
       <c r="AE12" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AF12" s="9">
         <v>46</v>
       </c>
       <c r="AG12" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="AH12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ12" s="9">
+        <v>984</v>
+      </c>
+      <c r="AK12" s="10" t="s">
         <v>192</v>
-      </c>
-      <c r="AH12" s="9">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ12" s="9">
-        <v>981</v>
-      </c>
-      <c r="AK12" s="10" t="s">
-        <v>193</v>
       </c>
       <c r="AL12" s="9">
         <v>757</v>
       </c>
       <c r="AM12" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AN12" s="9">
         <v>1</v>
       </c>
       <c r="AO12" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AP12" s="9">
         <v>0</v>
       </c>
       <c r="AQ12" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AR12" s="9">
         <v>6</v>
       </c>
       <c r="AS12" s="10" t="s">
-        <v>168</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="C13" s="9">
+        <v>3214</v>
+      </c>
+      <c r="D13" s="9">
+        <v>0</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F13" s="9">
+        <v>140</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="C13" s="9">
-        <v>3188</v>
-      </c>
-      <c r="D13" s="9">
-        <v>0</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="F13" s="9">
-        <v>138</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="H13" s="9">
         <v>2</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J13" s="9">
         <v>0</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L13" s="9">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N13" s="9">
         <v>1</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="P13" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="R13" s="9">
         <v>19</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>200</v>
+        <v>117</v>
       </c>
       <c r="T13" s="9">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U13" s="10" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="V13" s="9">
         <v>3</v>
       </c>
       <c r="W13" s="10" t="s">
-        <v>122</v>
+        <v>198</v>
       </c>
       <c r="X13" s="9">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Y13" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="Z13" s="9">
         <v>12</v>
       </c>
       <c r="AA13" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="AD13" s="9">
+        <v>1327</v>
+      </c>
+      <c r="AE13" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="AF13" s="9">
+        <v>11</v>
+      </c>
+      <c r="AG13" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="AH13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ13" s="9">
+        <v>836</v>
+      </c>
+      <c r="AK13" s="10" t="s">
         <v>203</v>
-      </c>
-      <c r="AB13" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC13" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="AD13" s="9">
-        <v>1315</v>
-      </c>
-      <c r="AE13" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="AF13" s="9">
-        <v>10</v>
-      </c>
-      <c r="AG13" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="AH13" s="9">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ13" s="9">
-        <v>832</v>
-      </c>
-      <c r="AK13" s="10" t="s">
-        <v>206</v>
       </c>
       <c r="AL13" s="9">
         <v>39</v>
       </c>
       <c r="AM13" s="10" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AN13" s="9">
         <v>0</v>
       </c>
       <c r="AO13" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AP13" s="9">
         <v>0</v>
       </c>
       <c r="AQ13" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AR13" s="9">
         <v>0</v>
       </c>
       <c r="AS13" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C14" s="9">
-        <v>2178</v>
+        <v>2190</v>
       </c>
       <c r="D14" s="9">
         <v>0</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F14" s="9">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>157</v>
+        <v>207</v>
       </c>
       <c r="H14" s="9">
         <v>17</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="J14" s="9">
         <v>0</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L14" s="9">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="N14" s="9">
         <v>1</v>
       </c>
       <c r="O14" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="P14" s="9">
         <v>20</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="R14" s="9">
         <v>26</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="T14" s="9">
         <v>47</v>
       </c>
       <c r="U14" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="V14" s="9">
         <v>10</v>
       </c>
       <c r="W14" s="10" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X14" s="9">
         <v>44</v>
       </c>
       <c r="Y14" s="10" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Z14" s="9">
         <v>1</v>
       </c>
       <c r="AA14" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AB14" s="9">
         <v>0</v>
       </c>
       <c r="AC14" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AD14" s="9">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="AE14" s="10" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AF14" s="9">
         <v>2</v>
       </c>
       <c r="AG14" s="10" t="s">
-        <v>122</v>
+        <v>198</v>
       </c>
       <c r="AH14" s="9">
         <v>0</v>
       </c>
       <c r="AI14" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AJ14" s="9">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="AK14" s="10" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AL14" s="9">
         <v>99</v>
       </c>
       <c r="AM14" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AN14" s="9">
         <v>1</v>
       </c>
       <c r="AO14" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AP14" s="9">
         <v>0</v>
       </c>
       <c r="AQ14" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AR14" s="9">
         <v>1</v>
       </c>
       <c r="AS14" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C15" s="9">
-        <v>7693</v>
+        <v>7703</v>
       </c>
       <c r="D15" s="9">
         <v>0</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F15" s="9">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>222</v>
+        <v>132</v>
       </c>
       <c r="H15" s="9">
         <v>88</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J15" s="9">
         <v>0</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L15" s="9">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="M15" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="N15" s="9">
+        <v>0</v>
+      </c>
+      <c r="O15" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="P15" s="9">
+        <v>27</v>
+      </c>
+      <c r="Q15" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="R15" s="9">
+        <v>74</v>
+      </c>
+      <c r="S15" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="T15" s="9">
+        <v>90</v>
+      </c>
+      <c r="U15" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="V15" s="9">
+        <v>2</v>
+      </c>
+      <c r="W15" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="X15" s="9">
+        <v>98</v>
+      </c>
+      <c r="Y15" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="N15" s="9">
-        <v>0</v>
-      </c>
-      <c r="O15" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="P15" s="9">
-        <v>42</v>
-      </c>
-      <c r="Q15" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="R15" s="9">
-        <v>73</v>
-      </c>
-      <c r="S15" s="10" t="s">
+      <c r="Z15" s="9">
+        <v>9</v>
+      </c>
+      <c r="AA15" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="AB15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="AD15" s="9">
+        <v>3131</v>
+      </c>
+      <c r="AE15" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="T15" s="9">
-        <v>76</v>
-      </c>
-      <c r="U15" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="V15" s="9">
-        <v>4</v>
-      </c>
-      <c r="W15" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="X15" s="9">
-        <v>97</v>
-      </c>
-      <c r="Y15" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="Z15" s="9">
-        <v>8</v>
-      </c>
-      <c r="AA15" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="AB15" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD15" s="9">
-        <v>3124</v>
-      </c>
-      <c r="AE15" s="10" t="s">
-        <v>227</v>
       </c>
       <c r="AF15" s="9">
         <v>66</v>
       </c>
       <c r="AG15" s="10" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AH15" s="9">
         <v>0</v>
       </c>
       <c r="AI15" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AJ15" s="9">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="AK15" s="10" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="AL15" s="9">
         <v>1696</v>
       </c>
       <c r="AM15" s="10" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="AN15" s="9">
         <v>1</v>
@@ -3201,846 +3192,846 @@
         <v>0</v>
       </c>
       <c r="AQ15" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AR15" s="9">
         <v>2</v>
       </c>
       <c r="AS15" s="10" t="s">
-        <v>116</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C16" s="9">
-        <v>1987</v>
+        <v>2033</v>
       </c>
       <c r="D16" s="9">
         <v>0</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F16" s="9">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="H16" s="9">
         <v>6</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="J16" s="9">
         <v>0</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L16" s="9">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="N16" s="9">
         <v>0</v>
       </c>
       <c r="O16" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P16" s="9">
         <v>13</v>
       </c>
       <c r="Q16" s="10" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="R16" s="9">
         <v>28</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="T16" s="9">
         <v>101</v>
       </c>
       <c r="U16" s="10" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="V16" s="9">
         <v>0</v>
       </c>
       <c r="W16" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="X16" s="9">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y16" s="10" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="Z16" s="9">
         <v>20</v>
       </c>
       <c r="AA16" s="10" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AB16" s="9">
         <v>18</v>
       </c>
       <c r="AC16" s="10" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="AD16" s="9">
-        <v>858</v>
+        <v>871</v>
       </c>
       <c r="AE16" s="10" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="AF16" s="9">
         <v>32</v>
       </c>
       <c r="AG16" s="10" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="AH16" s="9">
         <v>3</v>
       </c>
       <c r="AI16" s="10" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AJ16" s="9">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="AK16" s="10" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AL16" s="9">
         <v>56</v>
       </c>
       <c r="AM16" s="10" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AN16" s="9">
         <v>0</v>
       </c>
       <c r="AO16" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AP16" s="9">
         <v>0</v>
       </c>
       <c r="AQ16" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AR16" s="9">
         <v>2</v>
       </c>
       <c r="AS16" s="10" t="s">
-        <v>168</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C17" s="9">
-        <v>3163</v>
+        <v>3452</v>
       </c>
       <c r="D17" s="9">
         <v>1</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="F17" s="9">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>157</v>
+        <v>244</v>
       </c>
       <c r="H17" s="9">
         <v>26</v>
       </c>
       <c r="I17" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="J17" s="9">
+        <v>0</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L17" s="9">
+        <v>734</v>
+      </c>
+      <c r="M17" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="N17" s="9">
+        <v>0</v>
+      </c>
+      <c r="O17" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="P17" s="9">
+        <v>22</v>
+      </c>
+      <c r="Q17" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="R17" s="9">
+        <v>29</v>
+      </c>
+      <c r="S17" s="10" t="s">
         <v>247</v>
-      </c>
-      <c r="J17" s="9">
-        <v>0</v>
-      </c>
-      <c r="K17" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="L17" s="9">
-        <v>646</v>
-      </c>
-      <c r="M17" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="N17" s="9">
-        <v>0</v>
-      </c>
-      <c r="O17" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="P17" s="9">
-        <v>23</v>
-      </c>
-      <c r="Q17" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="R17" s="9">
-        <v>28</v>
-      </c>
-      <c r="S17" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="T17" s="9">
         <v>30</v>
       </c>
       <c r="U17" s="10" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="V17" s="9">
         <v>9</v>
       </c>
       <c r="W17" s="10" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="X17" s="9">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="Y17" s="10" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="Z17" s="9">
         <v>2</v>
       </c>
       <c r="AA17" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AB17" s="9">
         <v>2</v>
       </c>
       <c r="AC17" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AD17" s="9">
-        <v>1551</v>
+        <v>1710</v>
       </c>
       <c r="AE17" s="10" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AF17" s="9">
         <v>42</v>
       </c>
       <c r="AG17" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="AH17" s="9">
+        <v>2</v>
+      </c>
+      <c r="AI17" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="AJ17" s="9">
+        <v>412</v>
+      </c>
+      <c r="AK17" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="AL17" s="9">
+        <v>220</v>
+      </c>
+      <c r="AM17" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="AH17" s="9">
-        <v>1</v>
-      </c>
-      <c r="AI17" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="AJ17" s="9">
-        <v>394</v>
-      </c>
-      <c r="AK17" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="AL17" s="9">
-        <v>221</v>
-      </c>
-      <c r="AM17" s="10" t="s">
-        <v>110</v>
-      </c>
       <c r="AN17" s="9">
         <v>0</v>
       </c>
       <c r="AO17" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AP17" s="9">
         <v>0</v>
       </c>
       <c r="AQ17" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AR17" s="9">
         <v>0</v>
       </c>
       <c r="AS17" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>256</v>
-      </c>
       <c r="C18" s="9">
-        <v>4143</v>
+        <v>4361</v>
       </c>
       <c r="D18" s="9">
         <v>0</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F18" s="9">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="H18" s="9">
         <v>6</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="J18" s="9">
         <v>0</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L18" s="9">
-        <v>858</v>
+        <v>911</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="N18" s="9">
         <v>0</v>
       </c>
       <c r="O18" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P18" s="9">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>260</v>
+        <v>143</v>
       </c>
       <c r="R18" s="9">
         <v>20</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>261</v>
+        <v>212</v>
       </c>
       <c r="T18" s="9">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="U18" s="10" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="V18" s="9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W18" s="10" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="X18" s="9">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="Y18" s="10" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="Z18" s="9">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA18" s="10" t="s">
-        <v>205</v>
+        <v>99</v>
       </c>
       <c r="AB18" s="9">
         <v>15</v>
       </c>
       <c r="AC18" s="10" t="s">
-        <v>99</v>
+        <v>202</v>
       </c>
       <c r="AD18" s="9">
-        <v>1892</v>
+        <v>1988</v>
       </c>
       <c r="AE18" s="10" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="AF18" s="9">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AG18" s="10" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="AH18" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="10" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="AJ18" s="9">
-        <v>954</v>
+        <v>1001</v>
       </c>
       <c r="AK18" s="10" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="AL18" s="9">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AM18" s="10" t="s">
-        <v>115</v>
+        <v>263</v>
       </c>
       <c r="AN18" s="9">
         <v>0</v>
       </c>
       <c r="AO18" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AP18" s="9">
         <v>0</v>
       </c>
       <c r="AQ18" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AR18" s="9">
         <v>0</v>
       </c>
       <c r="AS18" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C19" s="9">
-        <v>3958</v>
+        <v>4478</v>
       </c>
       <c r="D19" s="9">
         <v>0</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F19" s="9">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="H19" s="9">
         <v>18</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="J19" s="9">
         <v>0</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L19" s="9">
-        <v>1050</v>
+        <v>1199</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="N19" s="9">
         <v>0</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P19" s="9">
         <v>0</v>
       </c>
       <c r="Q19" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="R19" s="9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>203</v>
+        <v>157</v>
       </c>
       <c r="T19" s="9">
         <v>17</v>
       </c>
       <c r="U19" s="10" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="V19" s="9">
         <v>0</v>
       </c>
       <c r="W19" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="X19" s="9">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="Y19" s="10" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="Z19" s="9">
         <v>4</v>
       </c>
       <c r="AA19" s="10" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="AB19" s="9">
         <v>1</v>
       </c>
       <c r="AC19" s="10" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="AD19" s="9">
-        <v>1712</v>
+        <v>1981</v>
       </c>
       <c r="AE19" s="10" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="AF19" s="9">
         <v>26</v>
       </c>
       <c r="AG19" s="10" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="AH19" s="9">
         <v>1</v>
       </c>
       <c r="AI19" s="10" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="AJ19" s="9">
-        <v>658</v>
+        <v>715</v>
       </c>
       <c r="AK19" s="10" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AL19" s="9">
         <v>146</v>
       </c>
       <c r="AM19" s="10" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="AN19" s="9">
         <v>0</v>
       </c>
       <c r="AO19" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AP19" s="9">
         <v>0</v>
       </c>
       <c r="AQ19" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AR19" s="9">
         <v>2</v>
       </c>
       <c r="AS19" s="10" t="s">
-        <v>188</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C20" s="9">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="D20" s="9">
         <v>0</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F20" s="9">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="H20" s="9">
         <v>6</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="J20" s="9">
         <v>0</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L20" s="9">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="N20" s="9">
         <v>0</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P20" s="9">
         <v>5</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="R20" s="9">
         <v>4</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>182</v>
+        <v>279</v>
       </c>
       <c r="T20" s="9">
         <v>41</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>282</v>
+        <v>253</v>
       </c>
       <c r="V20" s="9">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="W20" s="10" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="X20" s="9">
         <v>46</v>
       </c>
       <c r="Y20" s="10" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="Z20" s="9">
         <v>88</v>
       </c>
       <c r="AA20" s="10" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="AB20" s="9">
         <v>3</v>
       </c>
       <c r="AC20" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AD20" s="9">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="AE20" s="10" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="AF20" s="9">
         <v>12</v>
       </c>
       <c r="AG20" s="10" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="AH20" s="9">
         <v>0</v>
       </c>
       <c r="AI20" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AJ20" s="9">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AK20" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="AL20" s="9">
         <v>19</v>
       </c>
       <c r="AM20" s="10" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="AN20" s="9">
         <v>0</v>
       </c>
       <c r="AO20" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AP20" s="9">
         <v>0</v>
       </c>
       <c r="AQ20" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AR20" s="9">
         <v>2</v>
       </c>
       <c r="AS20" s="10" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C21" s="9">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="D21" s="9">
         <v>0</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F21" s="9">
         <v>36</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="H21" s="9">
         <v>6</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>167</v>
+        <v>290</v>
       </c>
       <c r="J21" s="9">
         <v>0</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L21" s="9">
         <v>170</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="N21" s="9">
         <v>0</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P21" s="9">
         <v>0</v>
       </c>
       <c r="Q21" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="R21" s="9">
         <v>9</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="T21" s="9">
         <v>35</v>
       </c>
       <c r="U21" s="10" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="V21" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W21" s="10" t="s">
-        <v>154</v>
+        <v>256</v>
       </c>
       <c r="X21" s="9">
         <v>37</v>
       </c>
       <c r="Y21" s="10" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="Z21" s="9">
         <v>39</v>
       </c>
       <c r="AA21" s="10" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="AB21" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC21" s="10" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="AD21" s="9">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AE21" s="10" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AF21" s="9">
         <v>3</v>
       </c>
       <c r="AG21" s="10" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AH21" s="9">
         <v>0</v>
       </c>
       <c r="AI21" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AJ21" s="9">
         <v>119</v>
       </c>
       <c r="AK21" s="10" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="AL21" s="9">
         <v>384</v>
       </c>
       <c r="AM21" s="10" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="AN21" s="9">
         <v>0</v>
       </c>
       <c r="AO21" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AP21" s="9">
         <v>0</v>
       </c>
       <c r="AQ21" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AR21" s="9">
         <v>0</v>
       </c>
       <c r="AS21" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C22" s="12">
-        <v>58216</v>
+        <v>60113</v>
       </c>
       <c r="D22" s="12">
         <v>7</v>
@@ -4049,7 +4040,7 @@
         <v>94</v>
       </c>
       <c r="F22" s="12">
-        <v>2441</v>
+        <v>2528</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>95</v>
@@ -4061,94 +4052,94 @@
         <v>96</v>
       </c>
       <c r="J22" s="12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K22" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="L22" s="12">
+        <v>12044</v>
+      </c>
+      <c r="M22" s="13" t="s">
         <v>97</v>
-      </c>
-      <c r="L22" s="12">
-        <v>11446</v>
-      </c>
-      <c r="M22" s="13" t="s">
-        <v>98</v>
       </c>
       <c r="N22" s="12">
         <v>3</v>
       </c>
       <c r="O22" s="13" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="P22" s="12">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="Q22" s="13" t="s">
         <v>99</v>
       </c>
       <c r="R22" s="12">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="S22" s="13" t="s">
         <v>100</v>
       </c>
       <c r="T22" s="12">
-        <v>1423</v>
+        <v>1443</v>
       </c>
       <c r="U22" s="13" t="s">
         <v>101</v>
       </c>
       <c r="V22" s="12">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="W22" s="13" t="s">
         <v>102</v>
       </c>
       <c r="X22" s="12">
-        <v>1670</v>
+        <v>1735</v>
       </c>
       <c r="Y22" s="13" t="s">
         <v>103</v>
       </c>
       <c r="Z22" s="12">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AA22" s="13" t="s">
         <v>104</v>
       </c>
       <c r="AB22" s="12">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AC22" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="AD22" s="12">
+        <v>26070</v>
+      </c>
+      <c r="AE22" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="AD22" s="12">
-        <v>25193</v>
-      </c>
-      <c r="AE22" s="13" t="s">
+      <c r="AF22" s="12">
+        <v>607</v>
+      </c>
+      <c r="AG22" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="AF22" s="12">
-        <v>603</v>
-      </c>
-      <c r="AG22" s="13" t="s">
+      <c r="AH22" s="12">
+        <v>12</v>
+      </c>
+      <c r="AI22" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="AH22" s="12">
-        <v>14</v>
-      </c>
-      <c r="AI22" s="13" t="s">
+      <c r="AJ22" s="12">
+        <v>9930</v>
+      </c>
+      <c r="AK22" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AJ22" s="12">
-        <v>9655</v>
-      </c>
-      <c r="AK22" s="13" t="s">
+      <c r="AL22" s="12">
+        <v>4072</v>
+      </c>
+      <c r="AM22" s="13" t="s">
         <v>109</v>
-      </c>
-      <c r="AL22" s="12">
-        <v>4070</v>
-      </c>
-      <c r="AM22" s="13" t="s">
-        <v>110</v>
       </c>
       <c r="AN22" s="12">
         <v>4</v>
@@ -4160,13 +4151,13 @@
         <v>0</v>
       </c>
       <c r="AQ22" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AR22" s="12">
         <v>26</v>
       </c>
       <c r="AS22" s="13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
+++ b/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="294">
   <si>
     <t>DATA RADAR ANOMALI KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 31 Agu 2026, 08.57</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 1 Sep 2026, 13.02</t>
   </si>
   <si>
     <t>Kode</t>
@@ -298,622 +298,595 @@
     <t>0,01</t>
   </si>
   <si>
+    <t>4,24</t>
+  </si>
+  <si>
+    <t>0,64</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>20,5</t>
+  </si>
+  <si>
+    <t>0,2</t>
+  </si>
+  <si>
+    <t>0,67</t>
+  </si>
+  <si>
+    <t>2,42</t>
+  </si>
+  <si>
+    <t>0,14</t>
+  </si>
+  <si>
+    <t>2,89</t>
+  </si>
+  <si>
+    <t>0,56</t>
+  </si>
+  <si>
+    <t>0,3</t>
+  </si>
+  <si>
+    <t>43,39</t>
+  </si>
+  <si>
+    <t>0,98</t>
+  </si>
+  <si>
+    <t>0,02</t>
+  </si>
+  <si>
+    <t>16,44</t>
+  </si>
+  <si>
+    <t>6,56</t>
+  </si>
+  <si>
+    <t>0,05</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>LAMPUNG BARAT</t>
+  </si>
+  <si>
+    <t>4,06</t>
+  </si>
+  <si>
+    <t>0,74</t>
+  </si>
+  <si>
+    <t>28,07</t>
+  </si>
+  <si>
+    <t>0,21</t>
+  </si>
+  <si>
+    <t>4,02</t>
+  </si>
+  <si>
+    <t>0,46</t>
+  </si>
+  <si>
+    <t>0,09</t>
+  </si>
+  <si>
+    <t>39,17</t>
+  </si>
+  <si>
+    <t>0,42</t>
+  </si>
+  <si>
+    <t>12,86</t>
+  </si>
+  <si>
+    <t>8,85</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>TANGGAMUS</t>
+  </si>
+  <si>
+    <t>6,6</t>
+  </si>
+  <si>
+    <t>19,75</t>
+  </si>
+  <si>
+    <t>0,9</t>
+  </si>
+  <si>
+    <t>3,3</t>
+  </si>
+  <si>
+    <t>0,12</t>
+  </si>
+  <si>
+    <t>3,18</t>
+  </si>
+  <si>
+    <t>0,24</t>
+  </si>
+  <si>
+    <t>41,84</t>
+  </si>
+  <si>
+    <t>0,06</t>
+  </si>
+  <si>
+    <t>22,75</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>LAMPUNG SELATAN</t>
+  </si>
+  <si>
+    <t>5,79</t>
+  </si>
+  <si>
+    <t>0,36</t>
+  </si>
+  <si>
+    <t>19,3</t>
+  </si>
+  <si>
+    <t>0,54</t>
+  </si>
+  <si>
+    <t>3,17</t>
+  </si>
+  <si>
+    <t>3,44</t>
+  </si>
+  <si>
+    <t>0,72</t>
+  </si>
+  <si>
+    <t>43,95</t>
+  </si>
+  <si>
+    <t>3,86</t>
+  </si>
+  <si>
+    <t>17,67</t>
+  </si>
+  <si>
+    <t>1,12</t>
+  </si>
+  <si>
+    <t>0,07</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>LAMPUNG TIMUR</t>
+  </si>
+  <si>
+    <t>0,04</t>
+  </si>
+  <si>
+    <t>4,18</t>
+  </si>
+  <si>
+    <t>0,33</t>
+  </si>
+  <si>
+    <t>25,87</t>
+  </si>
+  <si>
+    <t>0,25</t>
+  </si>
+  <si>
+    <t>1,03</t>
+  </si>
+  <si>
+    <t>2,45</t>
+  </si>
+  <si>
+    <t>3,23</t>
+  </si>
+  <si>
+    <t>1,55</t>
+  </si>
+  <si>
+    <t>42,9</t>
+  </si>
+  <si>
+    <t>0,37</t>
+  </si>
+  <si>
+    <t>15,55</t>
+  </si>
+  <si>
+    <t>1,57</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>LAMPUNG TENGAH</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
     <t>4,21</t>
   </si>
   <si>
-    <t>0,66</t>
-  </si>
-  <si>
-    <t>20,04</t>
-  </si>
-  <si>
-    <t>0</t>
+    <t>0,1</t>
+  </si>
+  <si>
+    <t>22,32</t>
+  </si>
+  <si>
+    <t>0,45</t>
+  </si>
+  <si>
+    <t>6,08</t>
+  </si>
+  <si>
+    <t>44,81</t>
+  </si>
+  <si>
+    <t>1,16</t>
+  </si>
+  <si>
+    <t>15,08</t>
+  </si>
+  <si>
+    <t>0,62</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>2,57</t>
+  </si>
+  <si>
+    <t>2,3</t>
+  </si>
+  <si>
+    <t>14,4</t>
+  </si>
+  <si>
+    <t>0,44</t>
+  </si>
+  <si>
+    <t>2,28</t>
+  </si>
+  <si>
+    <t>44,39</t>
+  </si>
+  <si>
+    <t>0,78</t>
+  </si>
+  <si>
+    <t>16,77</t>
+  </si>
+  <si>
+    <t>12,9</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
+    <t>4,32</t>
+  </si>
+  <si>
+    <t>20,46</t>
+  </si>
+  <si>
+    <t>0,58</t>
+  </si>
+  <si>
+    <t>2,44</t>
+  </si>
+  <si>
+    <t>2,95</t>
+  </si>
+  <si>
+    <t>0,4</t>
+  </si>
+  <si>
+    <t>41,14</t>
+  </si>
+  <si>
+    <t>25,91</t>
+  </si>
+  <si>
+    <t>1,19</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG</t>
+  </si>
+  <si>
+    <t>4,47</t>
+  </si>
+  <si>
+    <t>21,51</t>
+  </si>
+  <si>
+    <t>0,91</t>
+  </si>
+  <si>
+    <t>2,15</t>
+  </si>
+  <si>
+    <t>2,01</t>
+  </si>
+  <si>
+    <t>46,21</t>
+  </si>
+  <si>
+    <t>15,53</t>
+  </si>
+  <si>
+    <t>4,52</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PESAWARAN</t>
+  </si>
+  <si>
+    <t>1,14</t>
+  </si>
+  <si>
+    <t>13,48</t>
+  </si>
+  <si>
+    <t>1,01</t>
+  </si>
+  <si>
+    <t>1,41</t>
+  </si>
+  <si>
+    <t>1,28</t>
+  </si>
+  <si>
+    <t>0,13</t>
+  </si>
+  <si>
+    <t>40,65</t>
+  </si>
+  <si>
+    <t>0,85</t>
+  </si>
+  <si>
+    <t>14,71</t>
+  </si>
+  <si>
+    <t>21,95</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>PRINGSEWU</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>0,29</t>
+  </si>
+  <si>
+    <t>15,54</t>
+  </si>
+  <si>
+    <t>1,35</t>
+  </si>
+  <si>
+    <t>5,19</t>
+  </si>
+  <si>
+    <t>4,09</t>
+  </si>
+  <si>
+    <t>0,96</t>
+  </si>
+  <si>
+    <t>0,63</t>
+  </si>
+  <si>
+    <t>43,29</t>
+  </si>
+  <si>
+    <t>1,54</t>
+  </si>
+  <si>
+    <t>18,9</t>
+  </si>
+  <si>
+    <t>2,69</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
+  </si>
+  <si>
+    <t>4,73</t>
+  </si>
+  <si>
+    <t>0,69</t>
+  </si>
+  <si>
+    <t>21,76</t>
+  </si>
+  <si>
+    <t>0,59</t>
+  </si>
+  <si>
+    <t>0,77</t>
+  </si>
+  <si>
+    <t>0,8</t>
+  </si>
+  <si>
+    <t>1,7</t>
+  </si>
+  <si>
+    <t>0,08</t>
+  </si>
+  <si>
+    <t>49,81</t>
+  </si>
+  <si>
+    <t>11,73</t>
+  </si>
+  <si>
+    <t>5,85</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG BARAT</t>
+  </si>
+  <si>
+    <t>22,54</t>
   </si>
   <si>
     <t>0,32</t>
   </si>
   <si>
-    <t>0,68</t>
-  </si>
-  <si>
-    <t>2,4</t>
-  </si>
-  <si>
-    <t>0,19</t>
-  </si>
-  <si>
-    <t>2,89</t>
-  </si>
-  <si>
-    <t>0,54</t>
-  </si>
-  <si>
-    <t>43,37</t>
-  </si>
-  <si>
-    <t>1,01</t>
-  </si>
-  <si>
-    <t>0,02</t>
-  </si>
-  <si>
-    <t>16,52</t>
-  </si>
-  <si>
-    <t>6,77</t>
-  </si>
-  <si>
-    <t>0,04</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>LAMPUNG BARAT</t>
-  </si>
-  <si>
-    <t>3,76</t>
-  </si>
-  <si>
-    <t>0,82</t>
-  </si>
-  <si>
-    <t>0,1</t>
-  </si>
-  <si>
-    <t>27,88</t>
-  </si>
-  <si>
-    <t>0,59</t>
-  </si>
-  <si>
-    <t>1,11</t>
-  </si>
-  <si>
-    <t>4,07</t>
-  </si>
-  <si>
-    <t>0,08</t>
-  </si>
-  <si>
-    <t>0,13</t>
-  </si>
-  <si>
-    <t>38,2</t>
-  </si>
-  <si>
-    <t>0,44</t>
-  </si>
-  <si>
-    <t>12,84</t>
-  </si>
-  <si>
-    <t>9,78</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>TANGGAMUS</t>
-  </si>
-  <si>
-    <t>6,55</t>
-  </si>
-  <si>
-    <t>19,76</t>
-  </si>
-  <si>
-    <t>0,3</t>
-  </si>
-  <si>
-    <t>0,9</t>
-  </si>
-  <si>
-    <t>3,3</t>
-  </si>
-  <si>
-    <t>0,18</t>
-  </si>
-  <si>
-    <t>3,18</t>
-  </si>
-  <si>
-    <t>41,8</t>
-  </si>
-  <si>
-    <t>0,12</t>
-  </si>
-  <si>
-    <t>0,06</t>
-  </si>
-  <si>
-    <t>22,7</t>
-  </si>
-  <si>
-    <t>0,42</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>LAMPUNG SELATAN</t>
-  </si>
-  <si>
-    <t>5,81</t>
-  </si>
-  <si>
-    <t>0,37</t>
-  </si>
-  <si>
-    <t>19,03</t>
-  </si>
-  <si>
-    <t>0,56</t>
-  </si>
-  <si>
-    <t>3,25</t>
-  </si>
-  <si>
-    <t>3,35</t>
-  </si>
-  <si>
-    <t>0,74</t>
-  </si>
-  <si>
-    <t>43,83</t>
-  </si>
-  <si>
-    <t>3,96</t>
-  </si>
-  <si>
-    <t>17,86</t>
-  </si>
-  <si>
-    <t>1,14</t>
-  </si>
-  <si>
-    <t>0,07</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>LAMPUNG TIMUR</t>
-  </si>
-  <si>
-    <t>4,33</t>
-  </si>
-  <si>
-    <t>0,36</t>
-  </si>
-  <si>
-    <t>25,02</t>
-  </si>
-  <si>
-    <t>0,27</t>
-  </si>
-  <si>
-    <t>1,1</t>
+    <t>0,43</t>
+  </si>
+  <si>
+    <t>1,58</t>
+  </si>
+  <si>
+    <t>0,11</t>
+  </si>
+  <si>
+    <t>1,77</t>
+  </si>
+  <si>
+    <t>44,84</t>
+  </si>
+  <si>
+    <t>0,26</t>
+  </si>
+  <si>
+    <t>22,22</t>
+  </si>
+  <si>
+    <t>0,93</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>PESISIR BARAT</t>
+  </si>
+  <si>
+    <t>4,51</t>
+  </si>
+  <si>
+    <t>26,77</t>
+  </si>
+  <si>
+    <t>0,35</t>
+  </si>
+  <si>
+    <t>0,38</t>
+  </si>
+  <si>
+    <t>3,31</t>
+  </si>
+  <si>
+    <t>44,36</t>
+  </si>
+  <si>
+    <t>0,57</t>
+  </si>
+  <si>
+    <t>15,95</t>
+  </si>
+  <si>
+    <t>1871</t>
+  </si>
+  <si>
+    <t>BANDAR LAMPUNG</t>
+  </si>
+  <si>
+    <t>7,15</t>
+  </si>
+  <si>
+    <t>9,74</t>
+  </si>
+  <si>
+    <t>0,61</t>
+  </si>
+  <si>
+    <t>6,24</t>
+  </si>
+  <si>
+    <t>1,52</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>13,7</t>
+  </si>
+  <si>
+    <t>37,6</t>
+  </si>
+  <si>
+    <t>1,83</t>
+  </si>
+  <si>
+    <t>9,44</t>
+  </si>
+  <si>
+    <t>1872</t>
+  </si>
+  <si>
+    <t>METRO</t>
+  </si>
+  <si>
+    <t>0,41</t>
+  </si>
+  <si>
+    <t>11,55</t>
+  </si>
+  <si>
+    <t>2,36</t>
   </si>
   <si>
     <t>2,64</t>
   </si>
   <si>
-    <t>0,26</t>
-  </si>
-  <si>
-    <t>0,33</t>
-  </si>
-  <si>
-    <t>1,7</t>
-  </si>
-  <si>
-    <t>43,14</t>
-  </si>
-  <si>
-    <t>0,4</t>
-  </si>
-  <si>
-    <t>15,23</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>LAMPUNG TENGAH</t>
-  </si>
-  <si>
-    <t>0,03</t>
-  </si>
-  <si>
-    <t>22,03</t>
-  </si>
-  <si>
-    <t>0,45</t>
-  </si>
-  <si>
-    <t>5,83</t>
-  </si>
-  <si>
-    <t>4,18</t>
-  </si>
-  <si>
-    <t>0,47</t>
-  </si>
-  <si>
-    <t>0,15</t>
-  </si>
-  <si>
-    <t>44,89</t>
-  </si>
-  <si>
-    <t>1,18</t>
-  </si>
-  <si>
-    <t>15,16</t>
-  </si>
-  <si>
-    <t>0,63</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
-  </si>
-  <si>
-    <t>2,57</t>
-  </si>
-  <si>
-    <t>2,3</t>
-  </si>
-  <si>
-    <t>14,37</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>2,25</t>
-  </si>
-  <si>
-    <t>2,44</t>
-  </si>
-  <si>
-    <t>0,55</t>
-  </si>
-  <si>
-    <t>44,41</t>
-  </si>
-  <si>
-    <t>0,78</t>
-  </si>
-  <si>
-    <t>16,77</t>
-  </si>
-  <si>
-    <t>12,9</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>4,36</t>
-  </si>
-  <si>
-    <t>20,1</t>
-  </si>
-  <si>
-    <t>0,09</t>
-  </si>
-  <si>
-    <t>2,49</t>
-  </si>
-  <si>
-    <t>2,96</t>
-  </si>
-  <si>
-    <t>41,29</t>
-  </si>
-  <si>
-    <t>0,34</t>
-  </si>
-  <si>
-    <t>26,01</t>
-  </si>
-  <si>
-    <t>1,21</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG</t>
-  </si>
-  <si>
-    <t>4,47</t>
-  </si>
-  <si>
-    <t>21,51</t>
-  </si>
-  <si>
-    <t>0,91</t>
-  </si>
-  <si>
-    <t>1,19</t>
-  </si>
-  <si>
-    <t>2,15</t>
-  </si>
-  <si>
-    <t>0,46</t>
-  </si>
-  <si>
-    <t>2,01</t>
-  </si>
-  <si>
-    <t>46,21</t>
-  </si>
-  <si>
-    <t>15,53</t>
-  </si>
-  <si>
-    <t>4,52</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>PESAWARAN</t>
-  </si>
-  <si>
-    <t>13,41</t>
-  </si>
-  <si>
-    <t>0,35</t>
-  </si>
-  <si>
-    <t>0,96</t>
-  </si>
-  <si>
-    <t>1,17</t>
-  </si>
-  <si>
-    <t>1,27</t>
-  </si>
-  <si>
-    <t>40,65</t>
-  </si>
-  <si>
-    <t>0,86</t>
-  </si>
-  <si>
-    <t>14,7</t>
-  </si>
-  <si>
-    <t>22,02</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>PRINGSEWU</t>
-  </si>
-  <si>
-    <t>5,02</t>
-  </si>
-  <si>
-    <t>15,4</t>
-  </si>
-  <si>
-    <t>0,64</t>
-  </si>
-  <si>
-    <t>1,38</t>
-  </si>
-  <si>
-    <t>4,97</t>
-  </si>
-  <si>
-    <t>4,08</t>
-  </si>
-  <si>
-    <t>0,98</t>
-  </si>
-  <si>
-    <t>0,89</t>
-  </si>
-  <si>
-    <t>42,84</t>
-  </si>
-  <si>
-    <t>1,57</t>
-  </si>
-  <si>
-    <t>18,94</t>
-  </si>
-  <si>
-    <t>2,75</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>4,46</t>
-  </si>
-  <si>
-    <t>0,75</t>
-  </si>
-  <si>
-    <t>21,26</t>
-  </si>
-  <si>
-    <t>0,84</t>
-  </si>
-  <si>
-    <t>0,87</t>
-  </si>
-  <si>
-    <t>1,65</t>
-  </si>
-  <si>
-    <t>49,54</t>
-  </si>
-  <si>
-    <t>1,22</t>
-  </si>
-  <si>
-    <t>11,94</t>
-  </si>
-  <si>
-    <t>6,37</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG BARAT</t>
-  </si>
-  <si>
-    <t>0,14</t>
-  </si>
-  <si>
-    <t>20,89</t>
-  </si>
-  <si>
-    <t>0,11</t>
-  </si>
-  <si>
-    <t>1,83</t>
-  </si>
-  <si>
-    <t>45,59</t>
-  </si>
-  <si>
-    <t>0,28</t>
-  </si>
-  <si>
-    <t>22,95</t>
-  </si>
-  <si>
-    <t>0,99</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>PESISIR BARAT</t>
-  </si>
-  <si>
-    <t>4,56</t>
-  </si>
-  <si>
-    <t>26,78</t>
-  </si>
-  <si>
-    <t>0,38</t>
-  </si>
-  <si>
-    <t>3,31</t>
-  </si>
-  <si>
-    <t>44,24</t>
-  </si>
-  <si>
-    <t>0,58</t>
-  </si>
-  <si>
-    <t>15,97</t>
-  </si>
-  <si>
-    <t>3,26</t>
-  </si>
-  <si>
-    <t>1871</t>
-  </si>
-  <si>
-    <t>BANDAR LAMPUNG</t>
-  </si>
-  <si>
-    <t>7,14</t>
-  </si>
-  <si>
-    <t>0,93</t>
-  </si>
-  <si>
-    <t>9,47</t>
-  </si>
-  <si>
-    <t>0,62</t>
-  </si>
-  <si>
-    <t>2,02</t>
-  </si>
-  <si>
-    <t>13,66</t>
-  </si>
-  <si>
-    <t>36,96</t>
-  </si>
-  <si>
-    <t>1,86</t>
-  </si>
-  <si>
-    <t>9,32</t>
-  </si>
-  <si>
-    <t>2,95</t>
-  </si>
-  <si>
-    <t>0,31</t>
-  </si>
-  <si>
-    <t>1872</t>
-  </si>
-  <si>
-    <t>METRO</t>
-  </si>
-  <si>
-    <t>2,45</t>
-  </si>
-  <si>
-    <t>0,41</t>
-  </si>
-  <si>
-    <t>11,56</t>
-  </si>
-  <si>
-    <t>0,61</t>
-  </si>
-  <si>
-    <t>2,38</t>
-  </si>
-  <si>
-    <t>2,52</t>
-  </si>
-  <si>
-    <t>2,65</t>
-  </si>
-  <si>
-    <t>1,02</t>
-  </si>
-  <si>
-    <t>41,88</t>
-  </si>
-  <si>
-    <t>0,2</t>
-  </si>
-  <si>
-    <t>8,09</t>
-  </si>
-  <si>
-    <t>26,1</t>
+    <t>41,89</t>
+  </si>
+  <si>
+    <t>8,04</t>
+  </si>
+  <si>
+    <t>25,95</t>
   </si>
   <si>
     <t/>
@@ -1839,16 +1812,16 @@
         <v>93</v>
       </c>
       <c r="C6" s="6">
-        <v>60113</v>
+        <v>62074</v>
       </c>
       <c r="D6" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>94</v>
       </c>
       <c r="F6" s="6">
-        <v>2528</v>
+        <v>2630</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>95</v>
@@ -1860,150 +1833,150 @@
         <v>96</v>
       </c>
       <c r="J6" s="6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="L6" s="6">
-        <v>12044</v>
+        <v>12725</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N6" s="6">
         <v>3</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P6" s="6">
-        <v>191</v>
+        <v>123</v>
       </c>
       <c r="Q6" s="7" t="s">
         <v>99</v>
       </c>
       <c r="R6" s="6">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="S6" s="7" t="s">
         <v>100</v>
       </c>
       <c r="T6" s="6">
-        <v>1443</v>
+        <v>1501</v>
       </c>
       <c r="U6" s="7" t="s">
         <v>101</v>
       </c>
       <c r="V6" s="6">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="W6" s="7" t="s">
         <v>102</v>
       </c>
       <c r="X6" s="6">
-        <v>1735</v>
+        <v>1795</v>
       </c>
       <c r="Y6" s="7" t="s">
         <v>103</v>
       </c>
       <c r="Z6" s="6">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="AA6" s="7" t="s">
         <v>104</v>
       </c>
       <c r="AB6" s="6">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="AC6" s="7" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="AD6" s="6">
-        <v>26070</v>
+        <v>26937</v>
       </c>
       <c r="AE6" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AF6" s="6">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG6" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AH6" s="6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AI6" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AJ6" s="6">
-        <v>9930</v>
+        <v>10203</v>
       </c>
       <c r="AK6" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AL6" s="6">
-        <v>4072</v>
+        <v>4073</v>
       </c>
       <c r="AM6" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN6" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO6" s="7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="AP6" s="6">
         <v>0</v>
       </c>
       <c r="AQ6" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AR6" s="6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AS6" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C7" s="9">
-        <v>3885</v>
+        <v>4307</v>
       </c>
       <c r="D7" s="9">
         <v>0</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F7" s="9">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H7" s="9">
         <v>32</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J7" s="9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="L7" s="9">
-        <v>1083</v>
+        <v>1209</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>116</v>
@@ -2012,412 +1985,412 @@
         <v>0</v>
       </c>
       <c r="O7" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P7" s="9">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="Q7" s="10" t="s">
         <v>117</v>
       </c>
       <c r="R7" s="9">
+        <v>6</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="T7" s="9">
+        <v>13</v>
+      </c>
+      <c r="U7" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="V7" s="9">
+        <v>24</v>
+      </c>
+      <c r="W7" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="X7" s="9">
+        <v>173</v>
+      </c>
+      <c r="Y7" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z7" s="9">
+        <v>20</v>
+      </c>
+      <c r="AA7" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB7" s="9">
         <v>4</v>
       </c>
-      <c r="S7" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="T7" s="9">
-        <v>4</v>
-      </c>
-      <c r="U7" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="V7" s="9">
-        <v>43</v>
-      </c>
-      <c r="W7" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="X7" s="9">
-        <v>158</v>
-      </c>
-      <c r="Y7" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z7" s="9">
-        <v>3</v>
-      </c>
-      <c r="AA7" s="10" t="s">
+      <c r="AC7" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="AB7" s="9">
-        <v>5</v>
-      </c>
-      <c r="AC7" s="10" t="s">
+      <c r="AD7" s="9">
+        <v>1687</v>
+      </c>
+      <c r="AE7" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="AD7" s="9">
-        <v>1484</v>
-      </c>
-      <c r="AE7" s="10" t="s">
+      <c r="AF7" s="9">
+        <v>18</v>
+      </c>
+      <c r="AG7" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="AF7" s="9">
-        <v>17</v>
-      </c>
-      <c r="AG7" s="10" t="s">
+      <c r="AH7" s="9">
+        <v>2</v>
+      </c>
+      <c r="AI7" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="AJ7" s="9">
+        <v>554</v>
+      </c>
+      <c r="AK7" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="AH7" s="9">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="AJ7" s="9">
-        <v>499</v>
-      </c>
-      <c r="AK7" s="10" t="s">
+      <c r="AL7" s="9">
+        <v>381</v>
+      </c>
+      <c r="AM7" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="AL7" s="9">
-        <v>380</v>
-      </c>
-      <c r="AM7" s="10" t="s">
-        <v>125</v>
-      </c>
       <c r="AN7" s="9">
         <v>0</v>
       </c>
       <c r="AO7" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AP7" s="9">
         <v>0</v>
       </c>
       <c r="AQ7" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AR7" s="9">
         <v>0</v>
       </c>
       <c r="AS7" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="9">
+        <v>1666</v>
+      </c>
+      <c r="D8" s="9">
+        <v>0</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F8" s="9">
+        <v>110</v>
+      </c>
+      <c r="G8" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="C8" s="9">
-        <v>1665</v>
-      </c>
-      <c r="D8" s="9">
-        <v>0</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="F8" s="9">
-        <v>109</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>128</v>
-      </c>
       <c r="H8" s="9">
         <v>0</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J8" s="9">
         <v>0</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L8" s="9">
         <v>329</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N8" s="9">
         <v>0</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P8" s="9">
         <v>5</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="R8" s="9">
         <v>15</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="T8" s="9">
         <v>55</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="V8" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W8" s="10" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="X8" s="9">
         <v>53</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="Z8" s="9">
         <v>5</v>
       </c>
       <c r="AA8" s="10" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="AB8" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC8" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AD8" s="9">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AE8" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF8" s="9">
         <v>2</v>
       </c>
       <c r="AG8" s="10" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="AH8" s="9">
         <v>1</v>
       </c>
       <c r="AI8" s="10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AJ8" s="9">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AK8" s="10" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AL8" s="9">
         <v>7</v>
       </c>
       <c r="AM8" s="10" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="AN8" s="9">
         <v>0</v>
       </c>
       <c r="AO8" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AP8" s="9">
         <v>0</v>
       </c>
       <c r="AQ8" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AR8" s="9">
         <v>2</v>
       </c>
       <c r="AS8" s="10" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C9" s="9">
-        <v>5939</v>
+        <v>6084</v>
       </c>
       <c r="D9" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F9" s="9">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H9" s="9">
         <v>22</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="J9" s="9">
         <v>0</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L9" s="9">
-        <v>1130</v>
+        <v>1174</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="N9" s="9">
         <v>0</v>
       </c>
       <c r="O9" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P9" s="9">
         <v>0</v>
       </c>
       <c r="Q9" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R9" s="9">
         <v>33</v>
       </c>
       <c r="S9" s="10" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="T9" s="9">
         <v>193</v>
       </c>
       <c r="U9" s="10" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="V9" s="9">
         <v>1</v>
       </c>
       <c r="W9" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="X9" s="9">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="Y9" s="10" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="Z9" s="9">
         <v>44</v>
       </c>
       <c r="AA9" s="10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="AB9" s="9">
         <v>0</v>
       </c>
       <c r="AC9" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AD9" s="9">
-        <v>2603</v>
+        <v>2674</v>
       </c>
       <c r="AE9" s="10" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="AF9" s="9">
         <v>235</v>
       </c>
       <c r="AG9" s="10" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="AH9" s="9">
         <v>0</v>
       </c>
       <c r="AI9" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ9" s="9">
-        <v>1061</v>
+        <v>1075</v>
       </c>
       <c r="AK9" s="10" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="AL9" s="9">
         <v>68</v>
       </c>
       <c r="AM9" s="10" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AN9" s="9">
         <v>0</v>
       </c>
       <c r="AO9" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AP9" s="9">
         <v>0</v>
       </c>
       <c r="AQ9" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AR9" s="9">
         <v>4</v>
       </c>
       <c r="AS9" s="10" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C10" s="9">
-        <v>7017</v>
+        <v>7557</v>
       </c>
       <c r="D10" s="9">
         <v>3</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="F10" s="9">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H10" s="9">
         <v>25</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="J10" s="9">
         <v>0</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L10" s="9">
-        <v>1756</v>
+        <v>1955</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="N10" s="9">
         <v>1</v>
@@ -2429,73 +2402,73 @@
         <v>19</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="R10" s="9">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="T10" s="9">
         <v>185</v>
       </c>
       <c r="U10" s="10" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="V10" s="9">
         <v>18</v>
       </c>
       <c r="W10" s="10" t="s">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="X10" s="9">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="Z10" s="9">
         <v>23</v>
       </c>
       <c r="AA10" s="10" t="s">
-        <v>163</v>
+        <v>105</v>
       </c>
       <c r="AB10" s="9">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AC10" s="10" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="AD10" s="9">
-        <v>3027</v>
+        <v>3242</v>
       </c>
       <c r="AE10" s="10" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="AF10" s="9">
         <v>28</v>
       </c>
       <c r="AG10" s="10" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AH10" s="9">
         <v>5</v>
       </c>
       <c r="AI10" s="10" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="AJ10" s="9">
-        <v>1069</v>
+        <v>1175</v>
       </c>
       <c r="AK10" s="10" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="AL10" s="9">
         <v>119</v>
       </c>
       <c r="AM10" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AN10" s="9">
         <v>1</v>
@@ -2507,51 +2480,51 @@
         <v>0</v>
       </c>
       <c r="AQ10" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AR10" s="9">
         <v>3</v>
       </c>
       <c r="AS10" s="10" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C11" s="9">
-        <v>6195</v>
+        <v>6267</v>
       </c>
       <c r="D11" s="9">
         <v>2</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F11" s="9">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="H11" s="9">
         <v>6</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="J11" s="9">
         <v>0</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L11" s="9">
-        <v>1365</v>
+        <v>1399</v>
       </c>
       <c r="M11" s="10" t="s">
         <v>171</v>
@@ -2560,13 +2533,13 @@
         <v>0</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P11" s="9">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="R11" s="9">
         <v>28</v>
@@ -2575,364 +2548,364 @@
         <v>172</v>
       </c>
       <c r="T11" s="9">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="U11" s="10" t="s">
         <v>173</v>
       </c>
       <c r="V11" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W11" s="10" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="X11" s="9">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="Y11" s="10" t="s">
-        <v>174</v>
+        <v>95</v>
       </c>
       <c r="Z11" s="9">
         <v>29</v>
       </c>
       <c r="AA11" s="10" t="s">
-        <v>175</v>
+        <v>119</v>
       </c>
       <c r="AB11" s="9">
         <v>9</v>
       </c>
       <c r="AC11" s="10" t="s">
-        <v>176</v>
+        <v>102</v>
       </c>
       <c r="AD11" s="9">
-        <v>2781</v>
+        <v>2808</v>
       </c>
       <c r="AE11" s="10" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AF11" s="9">
         <v>73</v>
       </c>
       <c r="AG11" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="AH11" s="9">
         <v>0</v>
       </c>
       <c r="AI11" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ11" s="9">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="AK11" s="10" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="AL11" s="9">
         <v>39</v>
       </c>
       <c r="AM11" s="10" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AN11" s="9">
         <v>0</v>
       </c>
       <c r="AO11" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AP11" s="9">
         <v>0</v>
       </c>
       <c r="AQ11" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AR11" s="9">
         <v>2</v>
       </c>
       <c r="AS11" s="10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C12" s="9">
-        <v>5866</v>
+        <v>5868</v>
       </c>
       <c r="D12" s="9">
         <v>0</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F12" s="9">
         <v>151</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H12" s="9">
         <v>135</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="J12" s="9">
         <v>0</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L12" s="9">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="N12" s="9">
         <v>0</v>
       </c>
       <c r="O12" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P12" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="10" t="s">
-        <v>186</v>
+        <v>108</v>
       </c>
       <c r="R12" s="9">
         <v>26</v>
       </c>
       <c r="S12" s="10" t="s">
-        <v>123</v>
+        <v>183</v>
       </c>
       <c r="T12" s="9">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="U12" s="10" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="V12" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W12" s="10" t="s">
-        <v>170</v>
+        <v>97</v>
       </c>
       <c r="X12" s="9">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Y12" s="10" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="Z12" s="9">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AA12" s="10" t="s">
-        <v>189</v>
+        <v>104</v>
       </c>
       <c r="AB12" s="9">
         <v>0</v>
       </c>
       <c r="AC12" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AD12" s="9">
         <v>2605</v>
       </c>
       <c r="AE12" s="10" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="AF12" s="9">
         <v>46</v>
       </c>
       <c r="AG12" s="10" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="AH12" s="9">
         <v>0</v>
       </c>
       <c r="AI12" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ12" s="9">
         <v>984</v>
       </c>
       <c r="AK12" s="10" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="AL12" s="9">
         <v>757</v>
       </c>
       <c r="AM12" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="AN12" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO12" s="10" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="AP12" s="9">
         <v>0</v>
       </c>
       <c r="AQ12" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AR12" s="9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS12" s="10" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C13" s="9">
-        <v>3214</v>
+        <v>3284</v>
       </c>
       <c r="D13" s="9">
         <v>0</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F13" s="9">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="H13" s="9">
         <v>2</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J13" s="9">
         <v>0</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L13" s="9">
-        <v>646</v>
+        <v>672</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="N13" s="9">
         <v>1</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="P13" s="9">
         <v>3</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>198</v>
+        <v>120</v>
       </c>
       <c r="R13" s="9">
         <v>19</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>117</v>
+        <v>193</v>
       </c>
       <c r="T13" s="9">
         <v>80</v>
       </c>
       <c r="U13" s="10" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="V13" s="9">
         <v>3</v>
       </c>
       <c r="W13" s="10" t="s">
-        <v>198</v>
+        <v>120</v>
       </c>
       <c r="X13" s="9">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Y13" s="10" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="Z13" s="9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA13" s="10" t="s">
-        <v>143</v>
+        <v>196</v>
       </c>
       <c r="AB13" s="9">
         <v>0</v>
       </c>
       <c r="AC13" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AD13" s="9">
-        <v>1327</v>
+        <v>1351</v>
       </c>
       <c r="AE13" s="10" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AF13" s="9">
         <v>11</v>
       </c>
       <c r="AG13" s="10" t="s">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="AH13" s="9">
         <v>0</v>
       </c>
       <c r="AI13" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ13" s="9">
-        <v>836</v>
+        <v>851</v>
       </c>
       <c r="AK13" s="10" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AL13" s="9">
         <v>39</v>
       </c>
       <c r="AM13" s="10" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="AN13" s="9">
         <v>0</v>
       </c>
       <c r="AO13" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AP13" s="9">
         <v>0</v>
       </c>
       <c r="AQ13" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AR13" s="9">
         <v>0</v>
       </c>
       <c r="AS13" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C14" s="9">
         <v>2190</v>
@@ -2941,1106 +2914,1106 @@
         <v>0</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F14" s="9">
         <v>98</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="H14" s="9">
         <v>17</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="J14" s="9">
         <v>0</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L14" s="9">
         <v>471</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="N14" s="9">
         <v>1</v>
       </c>
       <c r="O14" s="10" t="s">
-        <v>186</v>
+        <v>111</v>
       </c>
       <c r="P14" s="9">
         <v>20</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="R14" s="9">
         <v>26</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="T14" s="9">
         <v>47</v>
       </c>
       <c r="U14" s="10" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="V14" s="9">
         <v>10</v>
       </c>
       <c r="W14" s="10" t="s">
-        <v>212</v>
+        <v>119</v>
       </c>
       <c r="X14" s="9">
         <v>44</v>
       </c>
       <c r="Y14" s="10" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="Z14" s="9">
         <v>1</v>
       </c>
       <c r="AA14" s="10" t="s">
-        <v>186</v>
+        <v>111</v>
       </c>
       <c r="AB14" s="9">
         <v>0</v>
       </c>
       <c r="AC14" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AD14" s="9">
         <v>1012</v>
       </c>
       <c r="AE14" s="10" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="AF14" s="9">
         <v>2</v>
       </c>
       <c r="AG14" s="10" t="s">
-        <v>198</v>
+        <v>120</v>
       </c>
       <c r="AH14" s="9">
         <v>0</v>
       </c>
       <c r="AI14" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ14" s="9">
         <v>340</v>
       </c>
       <c r="AK14" s="10" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="AL14" s="9">
         <v>99</v>
       </c>
       <c r="AM14" s="10" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="AN14" s="9">
         <v>1</v>
       </c>
       <c r="AO14" s="10" t="s">
-        <v>186</v>
+        <v>111</v>
       </c>
       <c r="AP14" s="9">
         <v>0</v>
       </c>
       <c r="AQ14" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AR14" s="9">
         <v>1</v>
       </c>
       <c r="AS14" s="10" t="s">
-        <v>186</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C15" s="9">
-        <v>7703</v>
+        <v>7725</v>
       </c>
       <c r="D15" s="9">
         <v>0</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F15" s="9">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H15" s="9">
         <v>88</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>152</v>
+        <v>212</v>
       </c>
       <c r="J15" s="9">
         <v>0</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L15" s="9">
-        <v>1033</v>
+        <v>1041</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="N15" s="9">
         <v>0</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P15" s="9">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>220</v>
+        <v>111</v>
       </c>
       <c r="R15" s="9">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="T15" s="9">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="V15" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>170</v>
+        <v>97</v>
       </c>
       <c r="X15" s="9">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Y15" s="10" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="Z15" s="9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA15" s="10" t="s">
-        <v>136</v>
+        <v>217</v>
       </c>
       <c r="AB15" s="9">
         <v>0</v>
       </c>
       <c r="AC15" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AD15" s="9">
-        <v>3131</v>
+        <v>3140</v>
       </c>
       <c r="AE15" s="10" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="AF15" s="9">
         <v>66</v>
       </c>
       <c r="AG15" s="10" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="AH15" s="9">
         <v>0</v>
       </c>
       <c r="AI15" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ15" s="9">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="AK15" s="10" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="AL15" s="9">
         <v>1696</v>
       </c>
       <c r="AM15" s="10" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="AN15" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO15" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="AP15" s="9">
         <v>0</v>
       </c>
       <c r="AQ15" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AR15" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS15" s="10" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C16" s="9">
-        <v>2033</v>
+        <v>2079</v>
       </c>
       <c r="D16" s="9">
         <v>0</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F16" s="9">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="H16" s="9">
         <v>6</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>130</v>
+        <v>225</v>
       </c>
       <c r="J16" s="9">
         <v>0</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L16" s="9">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="N16" s="9">
         <v>0</v>
       </c>
       <c r="O16" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P16" s="9">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q16" s="10" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="R16" s="9">
         <v>28</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="T16" s="9">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="U16" s="10" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="V16" s="9">
         <v>0</v>
       </c>
       <c r="W16" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="X16" s="9">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Y16" s="10" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="Z16" s="9">
         <v>20</v>
       </c>
       <c r="AA16" s="10" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="AB16" s="9">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AC16" s="10" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="AD16" s="9">
-        <v>871</v>
+        <v>900</v>
       </c>
       <c r="AE16" s="10" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="AF16" s="9">
         <v>32</v>
       </c>
       <c r="AG16" s="10" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="AH16" s="9">
         <v>3</v>
       </c>
       <c r="AI16" s="10" t="s">
-        <v>176</v>
+        <v>102</v>
       </c>
       <c r="AJ16" s="9">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="AK16" s="10" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="AL16" s="9">
         <v>56</v>
       </c>
       <c r="AM16" s="10" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="AN16" s="9">
         <v>0</v>
       </c>
       <c r="AO16" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AP16" s="9">
         <v>0</v>
       </c>
       <c r="AQ16" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AR16" s="9">
         <v>2</v>
       </c>
       <c r="AS16" s="10" t="s">
-        <v>115</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C17" s="9">
-        <v>3452</v>
+        <v>3760</v>
       </c>
       <c r="D17" s="9">
         <v>1</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F17" s="9">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="H17" s="9">
         <v>26</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="J17" s="9">
         <v>0</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L17" s="9">
-        <v>734</v>
+        <v>818</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="N17" s="9">
         <v>0</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P17" s="9">
         <v>22</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="R17" s="9">
         <v>29</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="T17" s="9">
         <v>30</v>
       </c>
       <c r="U17" s="10" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="V17" s="9">
         <v>9</v>
       </c>
       <c r="W17" s="10" t="s">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="X17" s="9">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="Y17" s="10" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="Z17" s="9">
         <v>2</v>
       </c>
       <c r="AA17" s="10" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="AB17" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC17" s="10" t="s">
-        <v>137</v>
+        <v>245</v>
       </c>
       <c r="AD17" s="9">
-        <v>1710</v>
+        <v>1873</v>
       </c>
       <c r="AE17" s="10" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="AF17" s="9">
         <v>42</v>
       </c>
       <c r="AG17" s="10" t="s">
-        <v>251</v>
+        <v>149</v>
       </c>
       <c r="AH17" s="9">
         <v>2</v>
       </c>
       <c r="AI17" s="10" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="AJ17" s="9">
-        <v>412</v>
+        <v>441</v>
       </c>
       <c r="AK17" s="10" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="AL17" s="9">
         <v>220</v>
       </c>
       <c r="AM17" s="10" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="AN17" s="9">
         <v>0</v>
       </c>
       <c r="AO17" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AP17" s="9">
         <v>0</v>
       </c>
       <c r="AQ17" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AR17" s="9">
         <v>0</v>
       </c>
       <c r="AS17" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C18" s="9">
-        <v>4361</v>
+        <v>4623</v>
       </c>
       <c r="D18" s="9">
         <v>0</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F18" s="9">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>235</v>
+        <v>95</v>
       </c>
       <c r="H18" s="9">
         <v>6</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>256</v>
+        <v>217</v>
       </c>
       <c r="J18" s="9">
         <v>0</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L18" s="9">
-        <v>911</v>
+        <v>1042</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="N18" s="9">
         <v>0</v>
       </c>
       <c r="O18" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P18" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>143</v>
+        <v>252</v>
       </c>
       <c r="R18" s="9">
         <v>20</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>212</v>
+        <v>253</v>
       </c>
       <c r="T18" s="9">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="U18" s="10" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="V18" s="9">
         <v>5</v>
       </c>
       <c r="W18" s="10" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="X18" s="9">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Y18" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="Z18" s="9">
         <v>14</v>
       </c>
       <c r="AA18" s="10" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="AB18" s="9">
         <v>15</v>
       </c>
       <c r="AC18" s="10" t="s">
-        <v>202</v>
+        <v>252</v>
       </c>
       <c r="AD18" s="9">
-        <v>1988</v>
+        <v>2073</v>
       </c>
       <c r="AE18" s="10" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AF18" s="9">
         <v>12</v>
       </c>
       <c r="AG18" s="10" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AH18" s="9">
         <v>0</v>
       </c>
       <c r="AI18" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ18" s="9">
-        <v>1001</v>
+        <v>1027</v>
       </c>
       <c r="AK18" s="10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AL18" s="9">
         <v>43</v>
       </c>
       <c r="AM18" s="10" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AN18" s="9">
         <v>0</v>
       </c>
       <c r="AO18" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AP18" s="9">
         <v>0</v>
       </c>
       <c r="AQ18" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AR18" s="9">
         <v>0</v>
       </c>
       <c r="AS18" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C19" s="9">
-        <v>4478</v>
+        <v>4527</v>
       </c>
       <c r="D19" s="9">
         <v>0</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F19" s="9">
         <v>204</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="H19" s="9">
         <v>18</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
       <c r="J19" s="9">
         <v>0</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L19" s="9">
-        <v>1199</v>
+        <v>1212</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="N19" s="9">
         <v>0</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P19" s="9">
         <v>0</v>
       </c>
       <c r="Q19" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R19" s="9">
         <v>16</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>157</v>
+        <v>265</v>
       </c>
       <c r="T19" s="9">
         <v>17</v>
       </c>
       <c r="U19" s="10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="V19" s="9">
         <v>0</v>
       </c>
       <c r="W19" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="X19" s="9">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Y19" s="10" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="Z19" s="9">
         <v>4</v>
       </c>
       <c r="AA19" s="10" t="s">
-        <v>198</v>
+        <v>120</v>
       </c>
       <c r="AB19" s="9">
         <v>1</v>
       </c>
       <c r="AC19" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AD19" s="9">
-        <v>1981</v>
+        <v>2008</v>
       </c>
       <c r="AE19" s="10" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AF19" s="9">
         <v>26</v>
       </c>
       <c r="AG19" s="10" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AH19" s="9">
         <v>1</v>
       </c>
       <c r="AI19" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AJ19" s="9">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="AK19" s="10" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AL19" s="9">
         <v>146</v>
       </c>
       <c r="AM19" s="10" t="s">
-        <v>273</v>
+        <v>160</v>
       </c>
       <c r="AN19" s="9">
         <v>0</v>
       </c>
       <c r="AO19" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AP19" s="9">
         <v>0</v>
       </c>
       <c r="AQ19" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AR19" s="9">
         <v>2</v>
       </c>
       <c r="AS19" s="10" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C20" s="9">
-        <v>644</v>
+        <v>657</v>
       </c>
       <c r="D20" s="9">
         <v>0</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F20" s="9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H20" s="9">
         <v>6</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>277</v>
+        <v>204</v>
       </c>
       <c r="J20" s="9">
         <v>0</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L20" s="9">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="N20" s="9">
         <v>0</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P20" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>191</v>
+        <v>275</v>
       </c>
       <c r="R20" s="9">
         <v>4</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="T20" s="9">
         <v>41</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="V20" s="9">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="W20" s="10" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="X20" s="9">
         <v>46</v>
       </c>
       <c r="Y20" s="10" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Z20" s="9">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AA20" s="10" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AB20" s="9">
         <v>3</v>
       </c>
       <c r="AC20" s="10" t="s">
-        <v>175</v>
+        <v>119</v>
       </c>
       <c r="AD20" s="9">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="AE20" s="10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AF20" s="9">
         <v>12</v>
       </c>
       <c r="AG20" s="10" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AH20" s="9">
         <v>0</v>
       </c>
       <c r="AI20" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ20" s="9">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AK20" s="10" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AL20" s="9">
         <v>19</v>
       </c>
       <c r="AM20" s="10" t="s">
-        <v>285</v>
+        <v>103</v>
       </c>
       <c r="AN20" s="9">
         <v>0</v>
       </c>
       <c r="AO20" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AP20" s="9">
         <v>0</v>
       </c>
       <c r="AQ20" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AR20" s="9">
         <v>2</v>
       </c>
       <c r="AS20" s="10" t="s">
-        <v>286</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C21" s="9">
-        <v>1471</v>
+        <v>1480</v>
       </c>
       <c r="D21" s="9">
         <v>0</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F21" s="9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>289</v>
+        <v>180</v>
       </c>
       <c r="H21" s="9">
         <v>6</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="J21" s="9">
         <v>0</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L21" s="9">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="N21" s="9">
         <v>0</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P21" s="9">
         <v>0</v>
       </c>
       <c r="Q21" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R21" s="9">
         <v>9</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="T21" s="9">
         <v>35</v>
       </c>
       <c r="U21" s="10" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="V21" s="9">
         <v>2</v>
       </c>
       <c r="W21" s="10" t="s">
-        <v>256</v>
+        <v>102</v>
       </c>
       <c r="X21" s="9">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Y21" s="10" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="Z21" s="9">
         <v>39</v>
       </c>
       <c r="AA21" s="10" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="AB21" s="9">
         <v>15</v>
       </c>
       <c r="AC21" s="10" t="s">
-        <v>296</v>
+        <v>214</v>
       </c>
       <c r="AD21" s="9">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="AE21" s="10" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="AF21" s="9">
         <v>3</v>
       </c>
       <c r="AG21" s="10" t="s">
-        <v>298</v>
+        <v>99</v>
       </c>
       <c r="AH21" s="9">
         <v>0</v>
       </c>
       <c r="AI21" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ21" s="9">
         <v>119</v>
       </c>
       <c r="AK21" s="10" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="AL21" s="9">
         <v>384</v>
       </c>
       <c r="AM21" s="10" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="AN21" s="9">
         <v>0</v>
       </c>
       <c r="AO21" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AP21" s="9">
         <v>0</v>
       </c>
       <c r="AQ21" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AR21" s="9">
         <v>0</v>
       </c>
       <c r="AS21" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="C22" s="12">
-        <v>60113</v>
+        <v>62074</v>
       </c>
       <c r="D22" s="12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>94</v>
       </c>
       <c r="F22" s="12">
-        <v>2528</v>
+        <v>2630</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>95</v>
@@ -4052,112 +4025,112 @@
         <v>96</v>
       </c>
       <c r="J22" s="12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="L22" s="12">
-        <v>12044</v>
+        <v>12725</v>
       </c>
       <c r="M22" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N22" s="12">
         <v>3</v>
       </c>
       <c r="O22" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P22" s="12">
-        <v>191</v>
+        <v>123</v>
       </c>
       <c r="Q22" s="13" t="s">
         <v>99</v>
       </c>
       <c r="R22" s="12">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="S22" s="13" t="s">
         <v>100</v>
       </c>
       <c r="T22" s="12">
-        <v>1443</v>
+        <v>1501</v>
       </c>
       <c r="U22" s="13" t="s">
         <v>101</v>
       </c>
       <c r="V22" s="12">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="W22" s="13" t="s">
         <v>102</v>
       </c>
       <c r="X22" s="12">
-        <v>1735</v>
+        <v>1795</v>
       </c>
       <c r="Y22" s="13" t="s">
         <v>103</v>
       </c>
       <c r="Z22" s="12">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="AA22" s="13" t="s">
         <v>104</v>
       </c>
       <c r="AB22" s="12">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="AC22" s="13" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="AD22" s="12">
-        <v>26070</v>
+        <v>26937</v>
       </c>
       <c r="AE22" s="13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AF22" s="12">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG22" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AH22" s="12">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AI22" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AJ22" s="12">
-        <v>9930</v>
+        <v>10203</v>
       </c>
       <c r="AK22" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AL22" s="12">
-        <v>4072</v>
+        <v>4073</v>
       </c>
       <c r="AM22" s="13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN22" s="12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO22" s="13" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="AP22" s="12">
         <v>0</v>
       </c>
       <c r="AQ22" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AR22" s="12">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AS22" s="13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
+++ b/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="291">
   <si>
     <t>DATA RADAR ANOMALI KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 1 Sep 2026, 13.02</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 2 Sep 2026, 10.04</t>
   </si>
   <si>
     <t>Kode</t>
@@ -298,595 +298,586 @@
     <t>0,01</t>
   </si>
   <si>
-    <t>4,24</t>
-  </si>
-  <si>
-    <t>0,64</t>
+    <t>4,26</t>
+  </si>
+  <si>
+    <t>0,62</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>20,5</t>
+    <t>20,77</t>
+  </si>
+  <si>
+    <t>0,17</t>
+  </si>
+  <si>
+    <t>0,66</t>
+  </si>
+  <si>
+    <t>2,39</t>
+  </si>
+  <si>
+    <t>0,13</t>
+  </si>
+  <si>
+    <t>2,91</t>
+  </si>
+  <si>
+    <t>0,55</t>
+  </si>
+  <si>
+    <t>0,27</t>
+  </si>
+  <si>
+    <t>43,46</t>
+  </si>
+  <si>
+    <t>0,97</t>
+  </si>
+  <si>
+    <t>0,02</t>
+  </si>
+  <si>
+    <t>16,37</t>
+  </si>
+  <si>
+    <t>6,41</t>
+  </si>
+  <si>
+    <t>0,04</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>LAMPUNG BARAT</t>
+  </si>
+  <si>
+    <t>4,1</t>
+  </si>
+  <si>
+    <t>0,71</t>
+  </si>
+  <si>
+    <t>28,21</t>
+  </si>
+  <si>
+    <t>0,18</t>
+  </si>
+  <si>
+    <t>0,48</t>
+  </si>
+  <si>
+    <t>4,25</t>
+  </si>
+  <si>
+    <t>0,46</t>
+  </si>
+  <si>
+    <t>39,56</t>
+  </si>
+  <si>
+    <t>12,63</t>
+  </si>
+  <si>
+    <t>8,4</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>TANGGAMUS</t>
+  </si>
+  <si>
+    <t>6,62</t>
+  </si>
+  <si>
+    <t>19,73</t>
+  </si>
+  <si>
+    <t>0,89</t>
+  </si>
+  <si>
+    <t>3,4</t>
+  </si>
+  <si>
+    <t>3,22</t>
+  </si>
+  <si>
+    <t>0,3</t>
+  </si>
+  <si>
+    <t>41,9</t>
+  </si>
+  <si>
+    <t>0,12</t>
+  </si>
+  <si>
+    <t>0,06</t>
+  </si>
+  <si>
+    <t>22,88</t>
+  </si>
+  <si>
+    <t>0,42</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>LAMPUNG SELATAN</t>
+  </si>
+  <si>
+    <t>5,82</t>
+  </si>
+  <si>
+    <t>0,35</t>
+  </si>
+  <si>
+    <t>19,38</t>
+  </si>
+  <si>
+    <t>0,53</t>
+  </si>
+  <si>
+    <t>3,11</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>3,84</t>
+  </si>
+  <si>
+    <t>17,65</t>
+  </si>
+  <si>
+    <t>1,1</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>LAMPUNG TIMUR</t>
+  </si>
+  <si>
+    <t>4,21</t>
+  </si>
+  <si>
+    <t>0,32</t>
+  </si>
+  <si>
+    <t>25,91</t>
+  </si>
+  <si>
+    <t>0,24</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2,36</t>
+  </si>
+  <si>
+    <t>0,23</t>
+  </si>
+  <si>
+    <t>3,18</t>
+  </si>
+  <si>
+    <t>0,29</t>
+  </si>
+  <si>
+    <t>1,5</t>
+  </si>
+  <si>
+    <t>43,07</t>
+  </si>
+  <si>
+    <t>0,36</t>
+  </si>
+  <si>
+    <t>15,65</t>
+  </si>
+  <si>
+    <t>1,52</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>LAMPUNG TENGAH</t>
+  </si>
+  <si>
+    <t>4,22</t>
+  </si>
+  <si>
+    <t>0,09</t>
+  </si>
+  <si>
+    <t>22,23</t>
+  </si>
+  <si>
+    <t>0,44</t>
+  </si>
+  <si>
+    <t>6,02</t>
+  </si>
+  <si>
+    <t>0,14</t>
+  </si>
+  <si>
+    <t>44,97</t>
+  </si>
+  <si>
+    <t>1,15</t>
+  </si>
+  <si>
+    <t>15,08</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>2,59</t>
+  </si>
+  <si>
+    <t>2,3</t>
+  </si>
+  <si>
+    <t>14,46</t>
+  </si>
+  <si>
+    <t>2,47</t>
+  </si>
+  <si>
+    <t>0,56</t>
+  </si>
+  <si>
+    <t>44,37</t>
+  </si>
+  <si>
+    <t>0,78</t>
+  </si>
+  <si>
+    <t>16,75</t>
+  </si>
+  <si>
+    <t>12,87</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
+    <t>4,31</t>
+  </si>
+  <si>
+    <t>20,57</t>
+  </si>
+  <si>
+    <t>0,57</t>
+  </si>
+  <si>
+    <t>2,44</t>
+  </si>
+  <si>
+    <t>2,96</t>
+  </si>
+  <si>
+    <t>0,39</t>
+  </si>
+  <si>
+    <t>41,24</t>
+  </si>
+  <si>
+    <t>0,33</t>
+  </si>
+  <si>
+    <t>25,79</t>
+  </si>
+  <si>
+    <t>1,18</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG</t>
+  </si>
+  <si>
+    <t>4,54</t>
+  </si>
+  <si>
+    <t>0,77</t>
+  </si>
+  <si>
+    <t>21,64</t>
+  </si>
+  <si>
+    <t>0,05</t>
+  </si>
+  <si>
+    <t>0,91</t>
+  </si>
+  <si>
+    <t>2,13</t>
+  </si>
+  <si>
+    <t>0,45</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>46,19</t>
+  </si>
+  <si>
+    <t>15,43</t>
+  </si>
+  <si>
+    <t>4,49</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PESAWARAN</t>
+  </si>
+  <si>
+    <t>3,3</t>
+  </si>
+  <si>
+    <t>1,14</t>
+  </si>
+  <si>
+    <t>13,48</t>
+  </si>
+  <si>
+    <t>1,01</t>
+  </si>
+  <si>
+    <t>1,41</t>
+  </si>
+  <si>
+    <t>1,28</t>
+  </si>
+  <si>
+    <t>40,65</t>
+  </si>
+  <si>
+    <t>0,85</t>
+  </si>
+  <si>
+    <t>14,71</t>
+  </si>
+  <si>
+    <t>21,95</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>PRINGSEWU</t>
+  </si>
+  <si>
+    <t>5,01</t>
+  </si>
+  <si>
+    <t>0,28</t>
+  </si>
+  <si>
+    <t>16,1</t>
+  </si>
+  <si>
+    <t>1,33</t>
+  </si>
+  <si>
+    <t>5,15</t>
+  </si>
+  <si>
+    <t>4,05</t>
+  </si>
+  <si>
+    <t>0,92</t>
+  </si>
+  <si>
+    <t>43,33</t>
+  </si>
+  <si>
+    <t>1,61</t>
+  </si>
+  <si>
+    <t>19,18</t>
+  </si>
+  <si>
+    <t>2,62</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
+  </si>
+  <si>
+    <t>4,69</t>
+  </si>
+  <si>
+    <t>0,67</t>
+  </si>
+  <si>
+    <t>22,38</t>
+  </si>
+  <si>
+    <t>0,75</t>
+  </si>
+  <si>
+    <t>1,74</t>
+  </si>
+  <si>
+    <t>0,08</t>
+  </si>
+  <si>
+    <t>49,57</t>
+  </si>
+  <si>
+    <t>1,09</t>
+  </si>
+  <si>
+    <t>11,63</t>
+  </si>
+  <si>
+    <t>5,7</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG BARAT</t>
+  </si>
+  <si>
+    <t>22,72</t>
+  </si>
+  <si>
+    <t>1,55</t>
+  </si>
+  <si>
+    <t>1,82</t>
+  </si>
+  <si>
+    <t>44,8</t>
+  </si>
+  <si>
+    <t>0,25</t>
+  </si>
+  <si>
+    <t>22,14</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>PESISIR BARAT</t>
+  </si>
+  <si>
+    <t>4,55</t>
+  </si>
+  <si>
+    <t>27,78</t>
+  </si>
+  <si>
+    <t>0,34</t>
+  </si>
+  <si>
+    <t>3,21</t>
+  </si>
+  <si>
+    <t>15,42</t>
+  </si>
+  <si>
+    <t>2,95</t>
+  </si>
+  <si>
+    <t>1871</t>
+  </si>
+  <si>
+    <t>BANDAR LAMPUNG</t>
+  </si>
+  <si>
+    <t>7,11</t>
+  </si>
+  <si>
+    <t>9,98</t>
+  </si>
+  <si>
+    <t>0,61</t>
+  </si>
+  <si>
+    <t>6,2</t>
+  </si>
+  <si>
+    <t>1,51</t>
+  </si>
+  <si>
+    <t>6,96</t>
+  </si>
+  <si>
+    <t>13,62</t>
+  </si>
+  <si>
+    <t>37,52</t>
+  </si>
+  <si>
+    <t>9,53</t>
+  </si>
+  <si>
+    <t>2,87</t>
+  </si>
+  <si>
+    <t>1872</t>
+  </si>
+  <si>
+    <t>METRO</t>
+  </si>
+  <si>
+    <t>2,61</t>
+  </si>
+  <si>
+    <t>0,4</t>
+  </si>
+  <si>
+    <t>11,62</t>
+  </si>
+  <si>
+    <t>0,6</t>
+  </si>
+  <si>
+    <t>2,34</t>
+  </si>
+  <si>
+    <t>2,74</t>
+  </si>
+  <si>
+    <t>42,08</t>
   </si>
   <si>
     <t>0,2</t>
   </si>
   <si>
-    <t>0,67</t>
-  </si>
-  <si>
-    <t>2,42</t>
-  </si>
-  <si>
-    <t>0,14</t>
-  </si>
-  <si>
-    <t>2,89</t>
-  </si>
-  <si>
-    <t>0,56</t>
-  </si>
-  <si>
-    <t>0,3</t>
-  </si>
-  <si>
-    <t>43,39</t>
-  </si>
-  <si>
-    <t>0,98</t>
-  </si>
-  <si>
-    <t>0,02</t>
-  </si>
-  <si>
-    <t>16,44</t>
-  </si>
-  <si>
-    <t>6,56</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>LAMPUNG BARAT</t>
-  </si>
-  <si>
-    <t>4,06</t>
-  </si>
-  <si>
-    <t>0,74</t>
-  </si>
-  <si>
-    <t>28,07</t>
-  </si>
-  <si>
-    <t>0,21</t>
-  </si>
-  <si>
-    <t>4,02</t>
-  </si>
-  <si>
-    <t>0,46</t>
-  </si>
-  <si>
-    <t>0,09</t>
-  </si>
-  <si>
-    <t>39,17</t>
-  </si>
-  <si>
-    <t>0,42</t>
-  </si>
-  <si>
-    <t>12,86</t>
-  </si>
-  <si>
-    <t>8,85</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>TANGGAMUS</t>
-  </si>
-  <si>
-    <t>6,6</t>
-  </si>
-  <si>
-    <t>19,75</t>
-  </si>
-  <si>
-    <t>0,9</t>
-  </si>
-  <si>
-    <t>3,3</t>
-  </si>
-  <si>
-    <t>0,12</t>
-  </si>
-  <si>
-    <t>3,18</t>
-  </si>
-  <si>
-    <t>0,24</t>
-  </si>
-  <si>
-    <t>41,84</t>
-  </si>
-  <si>
-    <t>0,06</t>
-  </si>
-  <si>
-    <t>22,75</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>LAMPUNG SELATAN</t>
-  </si>
-  <si>
-    <t>5,79</t>
-  </si>
-  <si>
-    <t>0,36</t>
-  </si>
-  <si>
-    <t>19,3</t>
-  </si>
-  <si>
-    <t>0,54</t>
-  </si>
-  <si>
-    <t>3,17</t>
-  </si>
-  <si>
-    <t>3,44</t>
-  </si>
-  <si>
-    <t>0,72</t>
-  </si>
-  <si>
-    <t>43,95</t>
-  </si>
-  <si>
-    <t>3,86</t>
-  </si>
-  <si>
-    <t>17,67</t>
-  </si>
-  <si>
-    <t>1,12</t>
-  </si>
-  <si>
-    <t>0,07</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>LAMPUNG TIMUR</t>
-  </si>
-  <si>
-    <t>0,04</t>
-  </si>
-  <si>
-    <t>4,18</t>
-  </si>
-  <si>
-    <t>0,33</t>
-  </si>
-  <si>
-    <t>25,87</t>
-  </si>
-  <si>
-    <t>0,25</t>
-  </si>
-  <si>
-    <t>1,03</t>
-  </si>
-  <si>
-    <t>2,45</t>
-  </si>
-  <si>
-    <t>3,23</t>
-  </si>
-  <si>
-    <t>1,55</t>
-  </si>
-  <si>
-    <t>42,9</t>
-  </si>
-  <si>
-    <t>0,37</t>
-  </si>
-  <si>
-    <t>15,55</t>
-  </si>
-  <si>
-    <t>1,57</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>LAMPUNG TENGAH</t>
-  </si>
-  <si>
-    <t>0,03</t>
-  </si>
-  <si>
-    <t>4,21</t>
-  </si>
-  <si>
-    <t>0,1</t>
-  </si>
-  <si>
-    <t>22,32</t>
-  </si>
-  <si>
-    <t>0,45</t>
-  </si>
-  <si>
-    <t>6,08</t>
-  </si>
-  <si>
-    <t>44,81</t>
-  </si>
-  <si>
-    <t>1,16</t>
-  </si>
-  <si>
-    <t>15,08</t>
-  </si>
-  <si>
-    <t>0,62</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
-  </si>
-  <si>
-    <t>2,57</t>
-  </si>
-  <si>
-    <t>2,3</t>
-  </si>
-  <si>
-    <t>14,4</t>
-  </si>
-  <si>
-    <t>0,44</t>
-  </si>
-  <si>
-    <t>2,28</t>
-  </si>
-  <si>
-    <t>44,39</t>
-  </si>
-  <si>
-    <t>0,78</t>
-  </si>
-  <si>
-    <t>16,77</t>
-  </si>
-  <si>
-    <t>12,9</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>4,32</t>
-  </si>
-  <si>
-    <t>20,46</t>
-  </si>
-  <si>
-    <t>0,58</t>
-  </si>
-  <si>
-    <t>2,44</t>
-  </si>
-  <si>
-    <t>2,95</t>
-  </si>
-  <si>
-    <t>0,4</t>
-  </si>
-  <si>
-    <t>41,14</t>
-  </si>
-  <si>
-    <t>25,91</t>
-  </si>
-  <si>
-    <t>1,19</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG</t>
-  </si>
-  <si>
-    <t>4,47</t>
-  </si>
-  <si>
-    <t>21,51</t>
-  </si>
-  <si>
-    <t>0,91</t>
-  </si>
-  <si>
-    <t>2,15</t>
-  </si>
-  <si>
-    <t>2,01</t>
-  </si>
-  <si>
-    <t>46,21</t>
-  </si>
-  <si>
-    <t>15,53</t>
-  </si>
-  <si>
-    <t>4,52</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>PESAWARAN</t>
-  </si>
-  <si>
-    <t>1,14</t>
-  </si>
-  <si>
-    <t>13,48</t>
-  </si>
-  <si>
-    <t>1,01</t>
-  </si>
-  <si>
-    <t>1,41</t>
-  </si>
-  <si>
-    <t>1,28</t>
-  </si>
-  <si>
-    <t>0,13</t>
-  </si>
-  <si>
-    <t>40,65</t>
-  </si>
-  <si>
-    <t>0,85</t>
-  </si>
-  <si>
-    <t>14,71</t>
-  </si>
-  <si>
-    <t>21,95</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>PRINGSEWU</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>0,29</t>
-  </si>
-  <si>
-    <t>15,54</t>
-  </si>
-  <si>
-    <t>1,35</t>
-  </si>
-  <si>
-    <t>5,19</t>
-  </si>
-  <si>
-    <t>4,09</t>
-  </si>
-  <si>
-    <t>0,96</t>
-  </si>
-  <si>
-    <t>0,63</t>
-  </si>
-  <si>
-    <t>43,29</t>
-  </si>
-  <si>
-    <t>1,54</t>
-  </si>
-  <si>
-    <t>18,9</t>
-  </si>
-  <si>
-    <t>2,69</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>4,73</t>
-  </si>
-  <si>
-    <t>0,69</t>
-  </si>
-  <si>
-    <t>21,76</t>
-  </si>
-  <si>
-    <t>0,59</t>
-  </si>
-  <si>
-    <t>0,77</t>
-  </si>
-  <si>
-    <t>0,8</t>
-  </si>
-  <si>
-    <t>1,7</t>
-  </si>
-  <si>
-    <t>0,08</t>
-  </si>
-  <si>
-    <t>49,81</t>
-  </si>
-  <si>
-    <t>11,73</t>
-  </si>
-  <si>
-    <t>5,85</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG BARAT</t>
-  </si>
-  <si>
-    <t>22,54</t>
-  </si>
-  <si>
-    <t>0,32</t>
-  </si>
-  <si>
-    <t>0,43</t>
-  </si>
-  <si>
-    <t>1,58</t>
-  </si>
-  <si>
-    <t>0,11</t>
-  </si>
-  <si>
-    <t>1,77</t>
-  </si>
-  <si>
-    <t>44,84</t>
-  </si>
-  <si>
-    <t>0,26</t>
-  </si>
-  <si>
-    <t>22,22</t>
-  </si>
-  <si>
-    <t>0,93</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>PESISIR BARAT</t>
-  </si>
-  <si>
-    <t>4,51</t>
-  </si>
-  <si>
-    <t>26,77</t>
-  </si>
-  <si>
-    <t>0,35</t>
-  </si>
-  <si>
-    <t>0,38</t>
-  </si>
-  <si>
-    <t>3,31</t>
-  </si>
-  <si>
-    <t>44,36</t>
-  </si>
-  <si>
-    <t>0,57</t>
-  </si>
-  <si>
-    <t>15,95</t>
-  </si>
-  <si>
-    <t>1871</t>
-  </si>
-  <si>
-    <t>BANDAR LAMPUNG</t>
-  </si>
-  <si>
-    <t>7,15</t>
-  </si>
-  <si>
-    <t>9,74</t>
-  </si>
-  <si>
-    <t>0,61</t>
-  </si>
-  <si>
-    <t>6,24</t>
-  </si>
-  <si>
-    <t>1,52</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>13,7</t>
-  </si>
-  <si>
-    <t>37,6</t>
-  </si>
-  <si>
-    <t>1,83</t>
-  </si>
-  <si>
-    <t>9,44</t>
-  </si>
-  <si>
-    <t>1872</t>
-  </si>
-  <si>
-    <t>METRO</t>
-  </si>
-  <si>
-    <t>0,41</t>
-  </si>
-  <si>
-    <t>11,55</t>
-  </si>
-  <si>
-    <t>2,36</t>
-  </si>
-  <si>
-    <t>2,64</t>
-  </si>
-  <si>
-    <t>41,89</t>
-  </si>
-  <si>
-    <t>8,04</t>
-  </si>
-  <si>
-    <t>25,95</t>
+    <t>8,02</t>
+  </si>
+  <si>
+    <t>25,65</t>
   </si>
   <si>
     <t/>
@@ -1812,7 +1803,7 @@
         <v>93</v>
       </c>
       <c r="C6" s="6">
-        <v>62074</v>
+        <v>63549</v>
       </c>
       <c r="D6" s="6">
         <v>6</v>
@@ -1821,7 +1812,7 @@
         <v>94</v>
       </c>
       <c r="F6" s="6">
-        <v>2630</v>
+        <v>2706</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>95</v>
@@ -1839,7 +1830,7 @@
         <v>97</v>
       </c>
       <c r="L6" s="6">
-        <v>12725</v>
+        <v>13197</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>98</v>
@@ -1851,73 +1842,73 @@
         <v>97</v>
       </c>
       <c r="P6" s="6">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="Q6" s="7" t="s">
         <v>99</v>
       </c>
       <c r="R6" s="6">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="S6" s="7" t="s">
         <v>100</v>
       </c>
       <c r="T6" s="6">
-        <v>1501</v>
+        <v>1518</v>
       </c>
       <c r="U6" s="7" t="s">
         <v>101</v>
       </c>
       <c r="V6" s="6">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="W6" s="7" t="s">
         <v>102</v>
       </c>
       <c r="X6" s="6">
-        <v>1795</v>
+        <v>1849</v>
       </c>
       <c r="Y6" s="7" t="s">
         <v>103</v>
       </c>
       <c r="Z6" s="6">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AA6" s="7" t="s">
         <v>104</v>
       </c>
       <c r="AB6" s="6">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="AC6" s="7" t="s">
         <v>105</v>
       </c>
       <c r="AD6" s="6">
-        <v>26937</v>
+        <v>27618</v>
       </c>
       <c r="AE6" s="7" t="s">
         <v>106</v>
       </c>
       <c r="AF6" s="6">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="AG6" s="7" t="s">
         <v>107</v>
       </c>
       <c r="AH6" s="6">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AI6" s="7" t="s">
         <v>108</v>
       </c>
       <c r="AJ6" s="6">
-        <v>10203</v>
+        <v>10402</v>
       </c>
       <c r="AK6" s="7" t="s">
         <v>109</v>
       </c>
       <c r="AL6" s="6">
-        <v>4073</v>
+        <v>4074</v>
       </c>
       <c r="AM6" s="7" t="s">
         <v>110</v>
@@ -1949,7 +1940,7 @@
         <v>113</v>
       </c>
       <c r="C7" s="9">
-        <v>4307</v>
+        <v>4537</v>
       </c>
       <c r="D7" s="9">
         <v>0</v>
@@ -1958,7 +1949,7 @@
         <v>97</v>
       </c>
       <c r="F7" s="9">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>114</v>
@@ -1976,7 +1967,7 @@
         <v>97</v>
       </c>
       <c r="L7" s="9">
-        <v>1209</v>
+        <v>1280</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>116</v>
@@ -1988,58 +1979,58 @@
         <v>97</v>
       </c>
       <c r="P7" s="9">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="R7" s="9">
+        <v>8</v>
+      </c>
+      <c r="S7" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="R7" s="9">
-        <v>6</v>
-      </c>
-      <c r="S7" s="10" t="s">
-        <v>102</v>
-      </c>
       <c r="T7" s="9">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="U7" s="10" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="V7" s="9">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="W7" s="10" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="X7" s="9">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="Y7" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Z7" s="9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA7" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AB7" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC7" s="10" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="AD7" s="9">
-        <v>1687</v>
+        <v>1795</v>
       </c>
       <c r="AE7" s="10" t="s">
         <v>121</v>
       </c>
       <c r="AF7" s="9">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AG7" s="10" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AH7" s="9">
         <v>2</v>
@@ -2048,16 +2039,16 @@
         <v>111</v>
       </c>
       <c r="AJ7" s="9">
-        <v>554</v>
+        <v>573</v>
       </c>
       <c r="AK7" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AL7" s="9">
         <v>381</v>
       </c>
       <c r="AM7" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AN7" s="9">
         <v>0</v>
@@ -2080,44 +2071,44 @@
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="9">
+        <v>1678</v>
+      </c>
+      <c r="D8" s="9">
+        <v>0</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F8" s="9">
+        <v>111</v>
+      </c>
+      <c r="G8" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="C8" s="9">
-        <v>1666</v>
-      </c>
-      <c r="D8" s="9">
-        <v>0</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="F8" s="9">
-        <v>110</v>
-      </c>
-      <c r="G8" s="10" t="s">
+      <c r="H8" s="9">
+        <v>0</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="J8" s="9">
+        <v>0</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L8" s="9">
+        <v>331</v>
+      </c>
+      <c r="M8" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H8" s="9">
-        <v>0</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="J8" s="9">
-        <v>0</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="L8" s="9">
-        <v>329</v>
-      </c>
-      <c r="M8" s="10" t="s">
-        <v>128</v>
-      </c>
       <c r="N8" s="9">
         <v>0</v>
       </c>
@@ -2125,76 +2116,76 @@
         <v>97</v>
       </c>
       <c r="P8" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="R8" s="9">
         <v>15</v>
       </c>
       <c r="S8" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="T8" s="9">
+        <v>57</v>
+      </c>
+      <c r="U8" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="T8" s="9">
-        <v>55</v>
-      </c>
-      <c r="U8" s="10" t="s">
+      <c r="V8" s="9">
+        <v>0</v>
+      </c>
+      <c r="W8" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="X8" s="9">
+        <v>54</v>
+      </c>
+      <c r="Y8" s="10" t="s">
         <v>130</v>
-      </c>
-      <c r="V8" s="9">
-        <v>2</v>
-      </c>
-      <c r="W8" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="X8" s="9">
-        <v>53</v>
-      </c>
-      <c r="Y8" s="10" t="s">
-        <v>132</v>
       </c>
       <c r="Z8" s="9">
         <v>5</v>
       </c>
       <c r="AA8" s="10" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="AB8" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC8" s="10" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="AD8" s="9">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="AE8" s="10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AF8" s="9">
         <v>2</v>
       </c>
       <c r="AG8" s="10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AH8" s="9">
         <v>1</v>
       </c>
       <c r="AI8" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="AJ8" s="9">
+        <v>384</v>
+      </c>
+      <c r="AK8" s="10" t="s">
         <v>135</v>
-      </c>
-      <c r="AJ8" s="9">
-        <v>379</v>
-      </c>
-      <c r="AK8" s="10" t="s">
-        <v>136</v>
       </c>
       <c r="AL8" s="9">
         <v>7</v>
       </c>
       <c r="AM8" s="10" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="AN8" s="9">
         <v>0</v>
@@ -2212,7 +2203,7 @@
         <v>2</v>
       </c>
       <c r="AS8" s="10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
@@ -2223,7 +2214,7 @@
         <v>138</v>
       </c>
       <c r="C9" s="9">
-        <v>6084</v>
+        <v>6198</v>
       </c>
       <c r="D9" s="9">
         <v>0</v>
@@ -2232,7 +2223,7 @@
         <v>97</v>
       </c>
       <c r="F9" s="9">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>139</v>
@@ -2250,7 +2241,7 @@
         <v>97</v>
       </c>
       <c r="L9" s="9">
-        <v>1174</v>
+        <v>1201</v>
       </c>
       <c r="M9" s="10" t="s">
         <v>141</v>
@@ -2280,58 +2271,58 @@
         <v>143</v>
       </c>
       <c r="V9" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W9" s="10" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="X9" s="9">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Y9" s="10" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="Z9" s="9">
         <v>44</v>
       </c>
       <c r="AA9" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD9" s="9">
+        <v>2727</v>
+      </c>
+      <c r="AE9" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="AB9" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD9" s="9">
-        <v>2674</v>
-      </c>
-      <c r="AE9" s="10" t="s">
+      <c r="AF9" s="9">
+        <v>238</v>
+      </c>
+      <c r="AG9" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="AF9" s="9">
-        <v>235</v>
-      </c>
-      <c r="AG9" s="10" t="s">
+      <c r="AH9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ9" s="9">
+        <v>1094</v>
+      </c>
+      <c r="AK9" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="AH9" s="9">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ9" s="9">
-        <v>1075</v>
-      </c>
-      <c r="AK9" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="AL9" s="9">
         <v>68</v>
       </c>
       <c r="AM9" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AN9" s="9">
         <v>0</v>
@@ -2349,36 +2340,36 @@
         <v>4</v>
       </c>
       <c r="AS9" s="10" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C10" s="9">
-        <v>7557</v>
+        <v>7823</v>
       </c>
       <c r="D10" s="9">
         <v>3</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>153</v>
+        <v>111</v>
       </c>
       <c r="F10" s="9">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H10" s="9">
         <v>25</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J10" s="9">
         <v>0</v>
@@ -2387,10 +2378,10 @@
         <v>97</v>
       </c>
       <c r="L10" s="9">
-        <v>1955</v>
+        <v>2027</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="N10" s="9">
         <v>1</v>
@@ -2402,73 +2393,73 @@
         <v>19</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="R10" s="9">
         <v>78</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="T10" s="9">
         <v>185</v>
       </c>
       <c r="U10" s="10" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="V10" s="9">
         <v>18</v>
       </c>
       <c r="W10" s="10" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="X10" s="9">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Z10" s="9">
         <v>23</v>
       </c>
       <c r="AA10" s="10" t="s">
-        <v>105</v>
+        <v>159</v>
       </c>
       <c r="AB10" s="9">
         <v>117</v>
       </c>
       <c r="AC10" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="AD10" s="9">
+        <v>3369</v>
+      </c>
+      <c r="AE10" s="10" t="s">
         <v>161</v>
-      </c>
-      <c r="AD10" s="9">
-        <v>3242</v>
-      </c>
-      <c r="AE10" s="10" t="s">
-        <v>162</v>
       </c>
       <c r="AF10" s="9">
         <v>28</v>
       </c>
       <c r="AG10" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AH10" s="9">
         <v>5</v>
       </c>
       <c r="AI10" s="10" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="AJ10" s="9">
-        <v>1175</v>
+        <v>1224</v>
       </c>
       <c r="AK10" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL10" s="9">
         <v>119</v>
       </c>
       <c r="AM10" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AN10" s="9">
         <v>1</v>
@@ -2486,36 +2477,36 @@
         <v>3</v>
       </c>
       <c r="AS10" s="10" t="s">
-        <v>153</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>167</v>
-      </c>
       <c r="C11" s="9">
-        <v>6267</v>
+        <v>6328</v>
       </c>
       <c r="D11" s="9">
         <v>2</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="F11" s="9">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H11" s="9">
         <v>6</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J11" s="9">
         <v>0</v>
@@ -2524,10 +2515,10 @@
         <v>97</v>
       </c>
       <c r="L11" s="9">
-        <v>1399</v>
+        <v>1407</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N11" s="9">
         <v>0</v>
@@ -2539,19 +2530,19 @@
         <v>15</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="R11" s="9">
         <v>28</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="T11" s="9">
         <v>381</v>
       </c>
       <c r="U11" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="V11" s="9">
         <v>1</v>
@@ -2560,52 +2551,52 @@
         <v>108</v>
       </c>
       <c r="X11" s="9">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Y11" s="10" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="Z11" s="9">
         <v>29</v>
       </c>
       <c r="AA11" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AB11" s="9">
         <v>9</v>
       </c>
       <c r="AC11" s="10" t="s">
-        <v>102</v>
+        <v>172</v>
       </c>
       <c r="AD11" s="9">
-        <v>2808</v>
+        <v>2846</v>
       </c>
       <c r="AE11" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AF11" s="9">
         <v>73</v>
       </c>
       <c r="AG11" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="AH11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ11" s="9">
+        <v>954</v>
+      </c>
+      <c r="AK11" s="10" t="s">
         <v>175</v>
-      </c>
-      <c r="AH11" s="9">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ11" s="9">
-        <v>945</v>
-      </c>
-      <c r="AK11" s="10" t="s">
-        <v>176</v>
       </c>
       <c r="AL11" s="9">
         <v>39</v>
       </c>
       <c r="AM11" s="10" t="s">
-        <v>177</v>
+        <v>96</v>
       </c>
       <c r="AN11" s="9">
         <v>0</v>
@@ -2623,36 +2614,36 @@
         <v>2</v>
       </c>
       <c r="AS11" s="10" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C12" s="9">
+        <v>5880</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" s="9">
+        <v>152</v>
+      </c>
+      <c r="G12" s="10" t="s">
         <v>178</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="C12" s="9">
-        <v>5868</v>
-      </c>
-      <c r="D12" s="9">
-        <v>0</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="F12" s="9">
-        <v>151</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>180</v>
       </c>
       <c r="H12" s="9">
         <v>135</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="J12" s="9">
         <v>0</v>
@@ -2661,10 +2652,10 @@
         <v>97</v>
       </c>
       <c r="L12" s="9">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="N12" s="9">
         <v>0</v>
@@ -2673,22 +2664,22 @@
         <v>97</v>
       </c>
       <c r="P12" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="10" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="R12" s="9">
         <v>26</v>
       </c>
       <c r="S12" s="10" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="T12" s="9">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="U12" s="10" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="V12" s="9">
         <v>0</v>
@@ -2697,16 +2688,16 @@
         <v>97</v>
       </c>
       <c r="X12" s="9">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Y12" s="10" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="Z12" s="9">
         <v>33</v>
       </c>
       <c r="AA12" s="10" t="s">
-        <v>104</v>
+        <v>182</v>
       </c>
       <c r="AB12" s="9">
         <v>0</v>
@@ -2715,16 +2706,16 @@
         <v>97</v>
       </c>
       <c r="AD12" s="9">
-        <v>2605</v>
+        <v>2609</v>
       </c>
       <c r="AE12" s="10" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AF12" s="9">
         <v>46</v>
       </c>
       <c r="AG12" s="10" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AH12" s="9">
         <v>0</v>
@@ -2733,16 +2724,16 @@
         <v>97</v>
       </c>
       <c r="AJ12" s="9">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="AK12" s="10" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AL12" s="9">
         <v>757</v>
       </c>
       <c r="AM12" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AN12" s="9">
         <v>0</v>
@@ -2760,36 +2751,36 @@
         <v>7</v>
       </c>
       <c r="AS12" s="10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13" s="9">
+        <v>3315</v>
+      </c>
+      <c r="D13" s="9">
+        <v>0</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F13" s="9">
+        <v>143</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>189</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="C13" s="9">
-        <v>3284</v>
-      </c>
-      <c r="D13" s="9">
-        <v>0</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="F13" s="9">
-        <v>142</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="H13" s="9">
         <v>2</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J13" s="9">
         <v>0</v>
@@ -2798,52 +2789,52 @@
         <v>97</v>
       </c>
       <c r="L13" s="9">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="N13" s="9">
         <v>1</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="P13" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="R13" s="9">
         <v>19</v>
       </c>
       <c r="S13" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="T13" s="9">
+        <v>81</v>
+      </c>
+      <c r="U13" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="V13" s="9">
+        <v>2</v>
+      </c>
+      <c r="W13" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="X13" s="9">
+        <v>98</v>
+      </c>
+      <c r="Y13" s="10" t="s">
         <v>193</v>
-      </c>
-      <c r="T13" s="9">
-        <v>80</v>
-      </c>
-      <c r="U13" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="V13" s="9">
-        <v>3</v>
-      </c>
-      <c r="W13" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X13" s="9">
-        <v>97</v>
-      </c>
-      <c r="Y13" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="Z13" s="9">
         <v>13</v>
       </c>
       <c r="AA13" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AB13" s="9">
         <v>0</v>
@@ -2852,16 +2843,16 @@
         <v>97</v>
       </c>
       <c r="AD13" s="9">
-        <v>1351</v>
+        <v>1367</v>
       </c>
       <c r="AE13" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AF13" s="9">
         <v>11</v>
       </c>
       <c r="AG13" s="10" t="s">
-        <v>155</v>
+        <v>196</v>
       </c>
       <c r="AH13" s="9">
         <v>0</v>
@@ -2870,16 +2861,16 @@
         <v>97</v>
       </c>
       <c r="AJ13" s="9">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="AK13" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AL13" s="9">
         <v>39</v>
       </c>
       <c r="AM13" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AN13" s="9">
         <v>0</v>
@@ -2902,31 +2893,31 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="C14" s="9">
+        <v>2204</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F14" s="9">
+        <v>100</v>
+      </c>
+      <c r="G14" s="10" t="s">
         <v>201</v>
-      </c>
-      <c r="C14" s="9">
-        <v>2190</v>
-      </c>
-      <c r="D14" s="9">
-        <v>0</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="F14" s="9">
-        <v>98</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>202</v>
       </c>
       <c r="H14" s="9">
         <v>17</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="J14" s="9">
         <v>0</v>
@@ -2935,7 +2926,7 @@
         <v>97</v>
       </c>
       <c r="L14" s="9">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="M14" s="10" t="s">
         <v>203</v>
@@ -2944,43 +2935,43 @@
         <v>1</v>
       </c>
       <c r="O14" s="10" t="s">
-        <v>111</v>
+        <v>204</v>
       </c>
       <c r="P14" s="9">
         <v>20</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="R14" s="9">
         <v>26</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="T14" s="9">
         <v>47</v>
       </c>
       <c r="U14" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="V14" s="9">
         <v>10</v>
       </c>
       <c r="W14" s="10" t="s">
-        <v>119</v>
+        <v>207</v>
       </c>
       <c r="X14" s="9">
         <v>44</v>
       </c>
       <c r="Y14" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Z14" s="9">
         <v>1</v>
       </c>
       <c r="AA14" s="10" t="s">
-        <v>111</v>
+        <v>204</v>
       </c>
       <c r="AB14" s="9">
         <v>0</v>
@@ -2989,16 +2980,16 @@
         <v>97</v>
       </c>
       <c r="AD14" s="9">
-        <v>1012</v>
+        <v>1018</v>
       </c>
       <c r="AE14" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AF14" s="9">
         <v>2</v>
       </c>
       <c r="AG14" s="10" t="s">
-        <v>120</v>
+        <v>168</v>
       </c>
       <c r="AH14" s="9">
         <v>0</v>
@@ -3010,19 +3001,19 @@
         <v>340</v>
       </c>
       <c r="AK14" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AL14" s="9">
         <v>99</v>
       </c>
       <c r="AM14" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AN14" s="9">
         <v>1</v>
       </c>
       <c r="AO14" s="10" t="s">
-        <v>111</v>
+        <v>204</v>
       </c>
       <c r="AP14" s="9">
         <v>0</v>
@@ -3034,15 +3025,15 @@
         <v>1</v>
       </c>
       <c r="AS14" s="10" t="s">
-        <v>111</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C15" s="9">
         <v>7725</v>
@@ -3057,13 +3048,13 @@
         <v>255</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>130</v>
+        <v>214</v>
       </c>
       <c r="H15" s="9">
         <v>88</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J15" s="9">
         <v>0</v>
@@ -3075,7 +3066,7 @@
         <v>1041</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="N15" s="9">
         <v>0</v>
@@ -3087,19 +3078,19 @@
         <v>4</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>111</v>
+        <v>204</v>
       </c>
       <c r="R15" s="9">
         <v>78</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="T15" s="9">
         <v>109</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="V15" s="9">
         <v>0</v>
@@ -3111,13 +3102,13 @@
         <v>99</v>
       </c>
       <c r="Y15" s="10" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Z15" s="9">
         <v>10</v>
       </c>
       <c r="AA15" s="10" t="s">
-        <v>217</v>
+        <v>102</v>
       </c>
       <c r="AB15" s="9">
         <v>0</v>
@@ -3129,13 +3120,13 @@
         <v>3140</v>
       </c>
       <c r="AE15" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AF15" s="9">
         <v>66</v>
       </c>
       <c r="AG15" s="10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AH15" s="9">
         <v>0</v>
@@ -3147,13 +3138,13 @@
         <v>1136</v>
       </c>
       <c r="AK15" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AL15" s="9">
         <v>1696</v>
       </c>
       <c r="AM15" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AN15" s="9">
         <v>0</v>
@@ -3171,18 +3162,18 @@
         <v>3</v>
       </c>
       <c r="AS15" s="10" t="s">
-        <v>153</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C16" s="9">
-        <v>2079</v>
+        <v>2174</v>
       </c>
       <c r="D16" s="9">
         <v>0</v>
@@ -3191,16 +3182,16 @@
         <v>97</v>
       </c>
       <c r="F16" s="9">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H16" s="9">
         <v>6</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="J16" s="9">
         <v>0</v>
@@ -3209,10 +3200,10 @@
         <v>97</v>
       </c>
       <c r="L16" s="9">
-        <v>323</v>
+        <v>350</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="N16" s="9">
         <v>0</v>
@@ -3221,22 +3212,22 @@
         <v>97</v>
       </c>
       <c r="P16" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="10" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="R16" s="9">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="T16" s="9">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="U16" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="V16" s="9">
         <v>0</v>
@@ -3245,52 +3236,52 @@
         <v>97</v>
       </c>
       <c r="X16" s="9">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="Y16" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Z16" s="9">
         <v>20</v>
       </c>
       <c r="AA16" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AB16" s="9">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AC16" s="10" t="s">
-        <v>231</v>
+        <v>157</v>
       </c>
       <c r="AD16" s="9">
-        <v>900</v>
+        <v>942</v>
       </c>
       <c r="AE16" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AF16" s="9">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="AG16" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AH16" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI16" s="10" t="s">
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="AJ16" s="9">
-        <v>393</v>
+        <v>417</v>
       </c>
       <c r="AK16" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AL16" s="9">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AM16" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN16" s="9">
         <v>0</v>
@@ -3308,36 +3299,36 @@
         <v>2</v>
       </c>
       <c r="AS16" s="10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C17" s="9">
-        <v>3760</v>
+        <v>3861</v>
       </c>
       <c r="D17" s="9">
         <v>1</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="F17" s="9">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H17" s="9">
         <v>26</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J17" s="9">
         <v>0</v>
@@ -3346,10 +3337,10 @@
         <v>97</v>
       </c>
       <c r="L17" s="9">
-        <v>818</v>
+        <v>864</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N17" s="9">
         <v>0</v>
@@ -3361,7 +3352,7 @@
         <v>22</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>241</v>
+        <v>191</v>
       </c>
       <c r="R17" s="9">
         <v>29</v>
@@ -3373,52 +3364,52 @@
         <v>30</v>
       </c>
       <c r="U17" s="10" t="s">
-        <v>243</v>
+        <v>184</v>
       </c>
       <c r="V17" s="9">
         <v>9</v>
       </c>
       <c r="W17" s="10" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="X17" s="9">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="Y17" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Z17" s="9">
         <v>2</v>
       </c>
       <c r="AA17" s="10" t="s">
-        <v>111</v>
+        <v>204</v>
       </c>
       <c r="AB17" s="9">
         <v>3</v>
       </c>
       <c r="AC17" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="AD17" s="9">
+        <v>1914</v>
+      </c>
+      <c r="AE17" s="10" t="s">
         <v>245</v>
-      </c>
-      <c r="AD17" s="9">
-        <v>1873</v>
-      </c>
-      <c r="AE17" s="10" t="s">
-        <v>246</v>
       </c>
       <c r="AF17" s="9">
         <v>42</v>
       </c>
       <c r="AG17" s="10" t="s">
-        <v>149</v>
+        <v>246</v>
       </c>
       <c r="AH17" s="9">
         <v>2</v>
       </c>
       <c r="AI17" s="10" t="s">
-        <v>111</v>
+        <v>204</v>
       </c>
       <c r="AJ17" s="9">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="AK17" s="10" t="s">
         <v>247</v>
@@ -3456,7 +3447,7 @@
         <v>250</v>
       </c>
       <c r="C18" s="9">
-        <v>4623</v>
+        <v>4719</v>
       </c>
       <c r="D18" s="9">
         <v>0</v>
@@ -3465,7 +3456,7 @@
         <v>97</v>
       </c>
       <c r="F18" s="9">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>95</v>
@@ -3474,7 +3465,7 @@
         <v>6</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>217</v>
+        <v>102</v>
       </c>
       <c r="J18" s="9">
         <v>0</v>
@@ -3483,7 +3474,7 @@
         <v>97</v>
       </c>
       <c r="L18" s="9">
-        <v>1042</v>
+        <v>1072</v>
       </c>
       <c r="M18" s="10" t="s">
         <v>251</v>
@@ -3498,55 +3489,55 @@
         <v>15</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>252</v>
+        <v>152</v>
       </c>
       <c r="R18" s="9">
         <v>20</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>253</v>
+        <v>136</v>
       </c>
       <c r="T18" s="9">
         <v>73</v>
       </c>
       <c r="U18" s="10" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="V18" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W18" s="10" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="X18" s="9">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="Y18" s="10" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="Z18" s="9">
         <v>14</v>
       </c>
       <c r="AA18" s="10" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="AB18" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC18" s="10" t="s">
-        <v>252</v>
+        <v>131</v>
       </c>
       <c r="AD18" s="9">
-        <v>2073</v>
+        <v>2114</v>
       </c>
       <c r="AE18" s="10" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="AF18" s="9">
         <v>12</v>
       </c>
       <c r="AG18" s="10" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="AH18" s="9">
         <v>0</v>
@@ -3555,16 +3546,16 @@
         <v>97</v>
       </c>
       <c r="AJ18" s="9">
-        <v>1027</v>
+        <v>1045</v>
       </c>
       <c r="AK18" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="AL18" s="9">
         <v>43</v>
       </c>
       <c r="AM18" s="10" t="s">
-        <v>260</v>
+        <v>205</v>
       </c>
       <c r="AN18" s="9">
         <v>0</v>
@@ -3587,13 +3578,13 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C19" s="9">
-        <v>4527</v>
+        <v>4949</v>
       </c>
       <c r="D19" s="9">
         <v>0</v>
@@ -3602,16 +3593,16 @@
         <v>97</v>
       </c>
       <c r="F19" s="9">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="H19" s="9">
         <v>18</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>196</v>
+        <v>162</v>
       </c>
       <c r="J19" s="9">
         <v>0</v>
@@ -3620,10 +3611,10 @@
         <v>97</v>
       </c>
       <c r="L19" s="9">
-        <v>1212</v>
+        <v>1375</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="N19" s="9">
         <v>0</v>
@@ -3638,16 +3629,16 @@
         <v>97</v>
       </c>
       <c r="R19" s="9">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>265</v>
+        <v>162</v>
       </c>
       <c r="T19" s="9">
         <v>17</v>
       </c>
       <c r="U19" s="10" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="V19" s="9">
         <v>0</v>
@@ -3656,52 +3647,52 @@
         <v>97</v>
       </c>
       <c r="X19" s="9">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="Y19" s="10" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="Z19" s="9">
         <v>4</v>
       </c>
       <c r="AA19" s="10" t="s">
-        <v>120</v>
+        <v>244</v>
       </c>
       <c r="AB19" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC19" s="10" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AD19" s="9">
-        <v>2008</v>
+        <v>2196</v>
       </c>
       <c r="AE19" s="10" t="s">
-        <v>268</v>
+        <v>183</v>
       </c>
       <c r="AF19" s="9">
         <v>26</v>
       </c>
       <c r="AG19" s="10" t="s">
-        <v>269</v>
+        <v>142</v>
       </c>
       <c r="AH19" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="10" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AJ19" s="9">
-        <v>722</v>
+        <v>763</v>
       </c>
       <c r="AK19" s="10" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="AL19" s="9">
         <v>146</v>
       </c>
       <c r="AM19" s="10" t="s">
-        <v>160</v>
+        <v>264</v>
       </c>
       <c r="AN19" s="9">
         <v>0</v>
@@ -3719,18 +3710,18 @@
         <v>2</v>
       </c>
       <c r="AS19" s="10" t="s">
-        <v>153</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C20" s="9">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="D20" s="9">
         <v>0</v>
@@ -3742,13 +3733,13 @@
         <v>47</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="H20" s="9">
         <v>6</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J20" s="9">
         <v>0</v>
@@ -3757,10 +3748,10 @@
         <v>97</v>
       </c>
       <c r="L20" s="9">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="N20" s="9">
         <v>0</v>
@@ -3772,55 +3763,55 @@
         <v>4</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="R20" s="9">
         <v>4</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="T20" s="9">
         <v>41</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="V20" s="9">
         <v>10</v>
       </c>
       <c r="W20" s="10" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="X20" s="9">
         <v>46</v>
       </c>
       <c r="Y20" s="10" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="Z20" s="9">
         <v>90</v>
       </c>
       <c r="AA20" s="10" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="AB20" s="9">
         <v>3</v>
       </c>
       <c r="AC20" s="10" t="s">
-        <v>119</v>
+        <v>207</v>
       </c>
       <c r="AD20" s="9">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AE20" s="10" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="AF20" s="9">
         <v>12</v>
       </c>
       <c r="AG20" s="10" t="s">
-        <v>281</v>
+        <v>253</v>
       </c>
       <c r="AH20" s="9">
         <v>0</v>
@@ -3829,16 +3820,16 @@
         <v>97</v>
       </c>
       <c r="AJ20" s="9">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AK20" s="10" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="AL20" s="9">
         <v>19</v>
       </c>
       <c r="AM20" s="10" t="s">
-        <v>103</v>
+        <v>276</v>
       </c>
       <c r="AN20" s="9">
         <v>0</v>
@@ -3856,18 +3847,18 @@
         <v>2</v>
       </c>
       <c r="AS20" s="10" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C21" s="9">
-        <v>1480</v>
+        <v>1497</v>
       </c>
       <c r="D21" s="9">
         <v>0</v>
@@ -3876,16 +3867,16 @@
         <v>97</v>
       </c>
       <c r="F21" s="9">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>180</v>
+        <v>279</v>
       </c>
       <c r="H21" s="9">
         <v>6</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="J21" s="9">
         <v>0</v>
@@ -3894,10 +3885,10 @@
         <v>97</v>
       </c>
       <c r="L21" s="9">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="N21" s="9">
         <v>0</v>
@@ -3915,13 +3906,13 @@
         <v>9</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="T21" s="9">
         <v>35</v>
       </c>
       <c r="U21" s="10" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="V21" s="9">
         <v>2</v>
@@ -3930,34 +3921,34 @@
         <v>102</v>
       </c>
       <c r="X21" s="9">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Y21" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="Z21" s="9">
         <v>39</v>
       </c>
       <c r="AA21" s="10" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="AB21" s="9">
         <v>15</v>
       </c>
       <c r="AC21" s="10" t="s">
-        <v>214</v>
+        <v>155</v>
       </c>
       <c r="AD21" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
       <c r="AE21" s="10" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="AF21" s="9">
         <v>3</v>
       </c>
       <c r="AG21" s="10" t="s">
-        <v>99</v>
+        <v>286</v>
       </c>
       <c r="AH21" s="9">
         <v>0</v>
@@ -3966,16 +3957,16 @@
         <v>97</v>
       </c>
       <c r="AJ21" s="9">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK21" s="10" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="AL21" s="9">
         <v>384</v>
       </c>
       <c r="AM21" s="10" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="AN21" s="9">
         <v>0</v>
@@ -3998,13 +3989,13 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C22" s="12">
-        <v>62074</v>
+        <v>63549</v>
       </c>
       <c r="D22" s="12">
         <v>6</v>
@@ -4013,7 +4004,7 @@
         <v>94</v>
       </c>
       <c r="F22" s="12">
-        <v>2630</v>
+        <v>2706</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>95</v>
@@ -4031,7 +4022,7 @@
         <v>97</v>
       </c>
       <c r="L22" s="12">
-        <v>12725</v>
+        <v>13197</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>98</v>
@@ -4043,73 +4034,73 @@
         <v>97</v>
       </c>
       <c r="P22" s="12">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="Q22" s="13" t="s">
         <v>99</v>
       </c>
       <c r="R22" s="12">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="S22" s="13" t="s">
         <v>100</v>
       </c>
       <c r="T22" s="12">
-        <v>1501</v>
+        <v>1518</v>
       </c>
       <c r="U22" s="13" t="s">
         <v>101</v>
       </c>
       <c r="V22" s="12">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="W22" s="13" t="s">
         <v>102</v>
       </c>
       <c r="X22" s="12">
-        <v>1795</v>
+        <v>1849</v>
       </c>
       <c r="Y22" s="13" t="s">
         <v>103</v>
       </c>
       <c r="Z22" s="12">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AA22" s="13" t="s">
         <v>104</v>
       </c>
       <c r="AB22" s="12">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="AC22" s="13" t="s">
         <v>105</v>
       </c>
       <c r="AD22" s="12">
-        <v>26937</v>
+        <v>27618</v>
       </c>
       <c r="AE22" s="13" t="s">
         <v>106</v>
       </c>
       <c r="AF22" s="12">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="AG22" s="13" t="s">
         <v>107</v>
       </c>
       <c r="AH22" s="12">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AI22" s="13" t="s">
         <v>108</v>
       </c>
       <c r="AJ22" s="12">
-        <v>10203</v>
+        <v>10402</v>
       </c>
       <c r="AK22" s="13" t="s">
         <v>109</v>
       </c>
       <c r="AL22" s="12">
-        <v>4073</v>
+        <v>4074</v>
       </c>
       <c r="AM22" s="13" t="s">
         <v>110</v>

--- a/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
+++ b/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="297">
   <si>
     <t>DATA RADAR ANOMALI KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 2 Sep 2026, 10.04</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 3 Sep 2026, 13.27</t>
   </si>
   <si>
     <t>Kode</t>
@@ -298,583 +298,601 @@
     <t>0,01</t>
   </si>
   <si>
-    <t>4,26</t>
-  </si>
-  <si>
-    <t>0,62</t>
+    <t>4,24</t>
+  </si>
+  <si>
+    <t>0,61</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>20,77</t>
+    <t>21,03</t>
+  </si>
+  <si>
+    <t>0,15</t>
+  </si>
+  <si>
+    <t>0,65</t>
+  </si>
+  <si>
+    <t>2,35</t>
+  </si>
+  <si>
+    <t>0,11</t>
+  </si>
+  <si>
+    <t>2,9</t>
+  </si>
+  <si>
+    <t>0,54</t>
+  </si>
+  <si>
+    <t>0,24</t>
+  </si>
+  <si>
+    <t>43,58</t>
+  </si>
+  <si>
+    <t>0,95</t>
+  </si>
+  <si>
+    <t>0,02</t>
+  </si>
+  <si>
+    <t>16,31</t>
+  </si>
+  <si>
+    <t>6,26</t>
+  </si>
+  <si>
+    <t>0,04</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>LAMPUNG BARAT</t>
+  </si>
+  <si>
+    <t>4,23</t>
+  </si>
+  <si>
+    <t>0,67</t>
+  </si>
+  <si>
+    <t>28,2</t>
   </si>
   <si>
     <t>0,17</t>
   </si>
   <si>
-    <t>0,66</t>
-  </si>
-  <si>
-    <t>2,39</t>
+    <t>0,46</t>
+  </si>
+  <si>
+    <t>4,15</t>
+  </si>
+  <si>
+    <t>0,44</t>
+  </si>
+  <si>
+    <t>39,76</t>
+  </si>
+  <si>
+    <t>0,08</t>
+  </si>
+  <si>
+    <t>12,85</t>
+  </si>
+  <si>
+    <t>8,02</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>TANGGAMUS</t>
+  </si>
+  <si>
+    <t>6,65</t>
+  </si>
+  <si>
+    <t>19,7</t>
+  </si>
+  <si>
+    <t>0,18</t>
+  </si>
+  <si>
+    <t>0,89</t>
+  </si>
+  <si>
+    <t>3,38</t>
+  </si>
+  <si>
+    <t>3,2</t>
+  </si>
+  <si>
+    <t>0,3</t>
+  </si>
+  <si>
+    <t>41,84</t>
+  </si>
+  <si>
+    <t>0,12</t>
+  </si>
+  <si>
+    <t>0,06</t>
+  </si>
+  <si>
+    <t>22,97</t>
+  </si>
+  <si>
+    <t>0,42</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>LAMPUNG SELATAN</t>
+  </si>
+  <si>
+    <t>5,78</t>
+  </si>
+  <si>
+    <t>0,35</t>
+  </si>
+  <si>
+    <t>19,69</t>
+  </si>
+  <si>
+    <t>0,52</t>
+  </si>
+  <si>
+    <t>3,05</t>
+  </si>
+  <si>
+    <t>3,35</t>
+  </si>
+  <si>
+    <t>0,71</t>
+  </si>
+  <si>
+    <t>44,05</t>
+  </si>
+  <si>
+    <t>3,78</t>
+  </si>
+  <si>
+    <t>17,57</t>
+  </si>
+  <si>
+    <t>1,07</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>LAMPUNG TIMUR</t>
+  </si>
+  <si>
+    <t>0,31</t>
+  </si>
+  <si>
+    <t>26,32</t>
+  </si>
+  <si>
+    <t>0,25</t>
+  </si>
+  <si>
+    <t>0,99</t>
+  </si>
+  <si>
+    <t>2,31</t>
+  </si>
+  <si>
+    <t>0,22</t>
+  </si>
+  <si>
+    <t>3,12</t>
+  </si>
+  <si>
+    <t>0,29</t>
+  </si>
+  <si>
+    <t>1,41</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>15,64</t>
+  </si>
+  <si>
+    <t>1,48</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>LAMPUNG TENGAH</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>4,19</t>
+  </si>
+  <si>
+    <t>0,09</t>
+  </si>
+  <si>
+    <t>22,35</t>
+  </si>
+  <si>
+    <t>5,97</t>
+  </si>
+  <si>
+    <t>0,45</t>
+  </si>
+  <si>
+    <t>0,14</t>
+  </si>
+  <si>
+    <t>45,05</t>
+  </si>
+  <si>
+    <t>1,14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>2,58</t>
+  </si>
+  <si>
+    <t>2,29</t>
+  </si>
+  <si>
+    <t>14,46</t>
+  </si>
+  <si>
+    <t>2,46</t>
+  </si>
+  <si>
+    <t>0,56</t>
+  </si>
+  <si>
+    <t>44,37</t>
+  </si>
+  <si>
+    <t>0,78</t>
+  </si>
+  <si>
+    <t>16,76</t>
+  </si>
+  <si>
+    <t>12,87</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
+    <t>4,33</t>
+  </si>
+  <si>
+    <t>20,58</t>
+  </si>
+  <si>
+    <t>0,57</t>
+  </si>
+  <si>
+    <t>2,47</t>
+  </si>
+  <si>
+    <t>2,98</t>
+  </si>
+  <si>
+    <t>41,25</t>
+  </si>
+  <si>
+    <t>0,33</t>
+  </si>
+  <si>
+    <t>25,78</t>
+  </si>
+  <si>
+    <t>1,17</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG</t>
+  </si>
+  <si>
+    <t>4,51</t>
+  </si>
+  <si>
+    <t>0,75</t>
+  </si>
+  <si>
+    <t>22,09</t>
+  </si>
+  <si>
+    <t>0,84</t>
+  </si>
+  <si>
+    <t>1,19</t>
+  </si>
+  <si>
+    <t>2,12</t>
+  </si>
+  <si>
+    <t>0,4</t>
+  </si>
+  <si>
+    <t>2,08</t>
+  </si>
+  <si>
+    <t>46,18</t>
+  </si>
+  <si>
+    <t>15,2</t>
+  </si>
+  <si>
+    <t>4,37</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PESAWARAN</t>
+  </si>
+  <si>
+    <t>3,3</t>
+  </si>
+  <si>
+    <t>13,48</t>
+  </si>
+  <si>
+    <t>0,05</t>
+  </si>
+  <si>
+    <t>1,01</t>
+  </si>
+  <si>
+    <t>1,28</t>
   </si>
   <si>
     <t>0,13</t>
   </si>
   <si>
-    <t>2,91</t>
-  </si>
-  <si>
-    <t>0,55</t>
+    <t>40,65</t>
+  </si>
+  <si>
+    <t>0,85</t>
+  </si>
+  <si>
+    <t>14,71</t>
+  </si>
+  <si>
+    <t>21,95</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>PRINGSEWU</t>
+  </si>
+  <si>
+    <t>4,98</t>
   </si>
   <si>
     <t>0,27</t>
   </si>
   <si>
-    <t>43,46</t>
-  </si>
-  <si>
-    <t>0,97</t>
-  </si>
-  <si>
-    <t>0,02</t>
-  </si>
-  <si>
-    <t>16,37</t>
-  </si>
-  <si>
-    <t>6,41</t>
-  </si>
-  <si>
-    <t>0,04</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>LAMPUNG BARAT</t>
-  </si>
-  <si>
-    <t>4,1</t>
-  </si>
-  <si>
-    <t>0,71</t>
-  </si>
-  <si>
-    <t>28,21</t>
-  </si>
-  <si>
-    <t>0,18</t>
-  </si>
-  <si>
-    <t>0,48</t>
-  </si>
-  <si>
-    <t>4,25</t>
-  </si>
-  <si>
-    <t>0,46</t>
-  </si>
-  <si>
-    <t>39,56</t>
-  </si>
-  <si>
-    <t>12,63</t>
-  </si>
-  <si>
-    <t>8,4</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>TANGGAMUS</t>
-  </si>
-  <si>
-    <t>6,62</t>
-  </si>
-  <si>
-    <t>19,73</t>
-  </si>
-  <si>
-    <t>0,89</t>
-  </si>
-  <si>
-    <t>3,4</t>
-  </si>
-  <si>
-    <t>3,22</t>
-  </si>
-  <si>
-    <t>0,3</t>
-  </si>
-  <si>
-    <t>41,9</t>
-  </si>
-  <si>
-    <t>0,12</t>
-  </si>
-  <si>
-    <t>0,06</t>
-  </si>
-  <si>
-    <t>22,88</t>
-  </si>
-  <si>
-    <t>0,42</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>LAMPUNG SELATAN</t>
-  </si>
-  <si>
-    <t>5,82</t>
-  </si>
-  <si>
-    <t>0,35</t>
-  </si>
-  <si>
-    <t>19,38</t>
-  </si>
-  <si>
-    <t>0,53</t>
-  </si>
-  <si>
-    <t>3,11</t>
-  </si>
-  <si>
-    <t>0,03</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>3,84</t>
-  </si>
-  <si>
-    <t>17,65</t>
-  </si>
-  <si>
-    <t>1,1</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>LAMPUNG TIMUR</t>
-  </si>
-  <si>
-    <t>4,21</t>
+    <t>16,71</t>
+  </si>
+  <si>
+    <t>1,33</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>43,42</t>
+  </si>
+  <si>
+    <t>1,56</t>
+  </si>
+  <si>
+    <t>18,98</t>
+  </si>
+  <si>
+    <t>2,53</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
+  </si>
+  <si>
+    <t>4,58</t>
+  </si>
+  <si>
+    <t>0,64</t>
+  </si>
+  <si>
+    <t>22,91</t>
+  </si>
+  <si>
+    <t>0,72</t>
+  </si>
+  <si>
+    <t>0,74</t>
+  </si>
+  <si>
+    <t>1,73</t>
+  </si>
+  <si>
+    <t>49,53</t>
+  </si>
+  <si>
+    <t>1,04</t>
+  </si>
+  <si>
+    <t>11,71</t>
+  </si>
+  <si>
+    <t>5,45</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG BARAT</t>
+  </si>
+  <si>
+    <t>4,22</t>
+  </si>
+  <si>
+    <t>22,77</t>
+  </si>
+  <si>
+    <t>0,16</t>
+  </si>
+  <si>
+    <t>0,41</t>
+  </si>
+  <si>
+    <t>1,62</t>
+  </si>
+  <si>
+    <t>1,85</t>
+  </si>
+  <si>
+    <t>0,28</t>
+  </si>
+  <si>
+    <t>45,37</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>0,87</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>PESISIR BARAT</t>
+  </si>
+  <si>
+    <t>4,44</t>
+  </si>
+  <si>
+    <t>0,34</t>
+  </si>
+  <si>
+    <t>27,99</t>
   </si>
   <si>
     <t>0,32</t>
   </si>
   <si>
-    <t>25,91</t>
-  </si>
-  <si>
-    <t>0,24</t>
+    <t>0,07</t>
+  </si>
+  <si>
+    <t>44,86</t>
+  </si>
+  <si>
+    <t>0,49</t>
+  </si>
+  <si>
+    <t>15,07</t>
+  </si>
+  <si>
+    <t>2,74</t>
+  </si>
+  <si>
+    <t>1871</t>
+  </si>
+  <si>
+    <t>BANDAR LAMPUNG</t>
+  </si>
+  <si>
+    <t>7,11</t>
+  </si>
+  <si>
+    <t>0,91</t>
+  </si>
+  <si>
+    <t>9,98</t>
+  </si>
+  <si>
+    <t>6,2</t>
+  </si>
+  <si>
+    <t>1,21</t>
+  </si>
+  <si>
+    <t>6,96</t>
+  </si>
+  <si>
+    <t>13,62</t>
+  </si>
+  <si>
+    <t>37,67</t>
+  </si>
+  <si>
+    <t>1,82</t>
+  </si>
+  <si>
+    <t>9,53</t>
+  </si>
+  <si>
+    <t>2,87</t>
+  </si>
+  <si>
+    <t>1872</t>
+  </si>
+  <si>
+    <t>METRO</t>
+  </si>
+  <si>
+    <t>2,61</t>
+  </si>
+  <si>
+    <t>11,62</t>
+  </si>
+  <si>
+    <t>0,6</t>
+  </si>
+  <si>
+    <t>2,34</t>
+  </si>
+  <si>
+    <t>2,81</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>2,36</t>
-  </si>
-  <si>
-    <t>0,23</t>
-  </si>
-  <si>
-    <t>3,18</t>
-  </si>
-  <si>
-    <t>0,29</t>
-  </si>
-  <si>
-    <t>1,5</t>
-  </si>
-  <si>
-    <t>43,07</t>
-  </si>
-  <si>
-    <t>0,36</t>
-  </si>
-  <si>
-    <t>15,65</t>
-  </si>
-  <si>
-    <t>1,52</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>LAMPUNG TENGAH</t>
-  </si>
-  <si>
-    <t>4,22</t>
-  </si>
-  <si>
-    <t>0,09</t>
-  </si>
-  <si>
-    <t>22,23</t>
-  </si>
-  <si>
-    <t>0,44</t>
-  </si>
-  <si>
-    <t>6,02</t>
-  </si>
-  <si>
-    <t>0,14</t>
-  </si>
-  <si>
-    <t>44,97</t>
-  </si>
-  <si>
-    <t>1,15</t>
-  </si>
-  <si>
-    <t>15,08</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
-  </si>
-  <si>
-    <t>2,59</t>
-  </si>
-  <si>
-    <t>2,3</t>
-  </si>
-  <si>
-    <t>14,46</t>
-  </si>
-  <si>
-    <t>2,47</t>
-  </si>
-  <si>
-    <t>0,56</t>
-  </si>
-  <si>
-    <t>44,37</t>
-  </si>
-  <si>
-    <t>0,78</t>
-  </si>
-  <si>
-    <t>16,75</t>
-  </si>
-  <si>
-    <t>12,87</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>4,31</t>
-  </si>
-  <si>
-    <t>20,57</t>
-  </si>
-  <si>
-    <t>0,57</t>
-  </si>
-  <si>
-    <t>2,44</t>
-  </si>
-  <si>
-    <t>2,96</t>
-  </si>
-  <si>
-    <t>0,39</t>
-  </si>
-  <si>
-    <t>41,24</t>
-  </si>
-  <si>
-    <t>0,33</t>
-  </si>
-  <si>
-    <t>25,79</t>
-  </si>
-  <si>
-    <t>1,18</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG</t>
-  </si>
-  <si>
-    <t>4,54</t>
-  </si>
-  <si>
-    <t>0,77</t>
-  </si>
-  <si>
-    <t>21,64</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>0,91</t>
-  </si>
-  <si>
-    <t>2,13</t>
-  </si>
-  <si>
-    <t>0,45</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>46,19</t>
-  </si>
-  <si>
-    <t>15,43</t>
-  </si>
-  <si>
-    <t>4,49</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>PESAWARAN</t>
-  </si>
-  <si>
-    <t>3,3</t>
-  </si>
-  <si>
-    <t>1,14</t>
-  </si>
-  <si>
-    <t>13,48</t>
-  </si>
-  <si>
-    <t>1,01</t>
-  </si>
-  <si>
-    <t>1,41</t>
-  </si>
-  <si>
-    <t>1,28</t>
-  </si>
-  <si>
-    <t>40,65</t>
-  </si>
-  <si>
-    <t>0,85</t>
-  </si>
-  <si>
-    <t>14,71</t>
-  </si>
-  <si>
-    <t>21,95</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>PRINGSEWU</t>
-  </si>
-  <si>
-    <t>5,01</t>
-  </si>
-  <si>
-    <t>0,28</t>
-  </si>
-  <si>
-    <t>16,1</t>
-  </si>
-  <si>
-    <t>1,33</t>
-  </si>
-  <si>
-    <t>5,15</t>
-  </si>
-  <si>
-    <t>4,05</t>
-  </si>
-  <si>
-    <t>0,92</t>
-  </si>
-  <si>
-    <t>43,33</t>
-  </si>
-  <si>
-    <t>1,61</t>
-  </si>
-  <si>
-    <t>19,18</t>
-  </si>
-  <si>
-    <t>2,62</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>4,69</t>
-  </si>
-  <si>
-    <t>0,67</t>
-  </si>
-  <si>
-    <t>22,38</t>
-  </si>
-  <si>
-    <t>0,75</t>
-  </si>
-  <si>
-    <t>1,74</t>
-  </si>
-  <si>
-    <t>0,08</t>
-  </si>
-  <si>
-    <t>49,57</t>
-  </si>
-  <si>
-    <t>1,09</t>
-  </si>
-  <si>
-    <t>11,63</t>
-  </si>
-  <si>
-    <t>5,7</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG BARAT</t>
-  </si>
-  <si>
-    <t>22,72</t>
-  </si>
-  <si>
-    <t>1,55</t>
-  </si>
-  <si>
-    <t>1,82</t>
-  </si>
-  <si>
-    <t>44,8</t>
-  </si>
-  <si>
-    <t>0,25</t>
-  </si>
-  <si>
-    <t>22,14</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>PESISIR BARAT</t>
-  </si>
-  <si>
-    <t>4,55</t>
-  </si>
-  <si>
-    <t>27,78</t>
-  </si>
-  <si>
-    <t>0,34</t>
-  </si>
-  <si>
-    <t>3,21</t>
-  </si>
-  <si>
-    <t>15,42</t>
-  </si>
-  <si>
-    <t>2,95</t>
-  </si>
-  <si>
-    <t>1871</t>
-  </si>
-  <si>
-    <t>BANDAR LAMPUNG</t>
-  </si>
-  <si>
-    <t>7,11</t>
-  </si>
-  <si>
-    <t>9,98</t>
-  </si>
-  <si>
-    <t>0,61</t>
-  </si>
-  <si>
-    <t>6,2</t>
-  </si>
-  <si>
-    <t>1,51</t>
-  </si>
-  <si>
-    <t>6,96</t>
-  </si>
-  <si>
-    <t>13,62</t>
-  </si>
-  <si>
-    <t>37,52</t>
-  </si>
-  <si>
-    <t>9,53</t>
-  </si>
-  <si>
-    <t>2,87</t>
-  </si>
-  <si>
-    <t>1872</t>
-  </si>
-  <si>
-    <t>METRO</t>
-  </si>
-  <si>
-    <t>2,61</t>
-  </si>
-  <si>
-    <t>0,4</t>
-  </si>
-  <si>
-    <t>11,62</t>
-  </si>
-  <si>
-    <t>0,6</t>
-  </si>
-  <si>
-    <t>2,34</t>
-  </si>
-  <si>
-    <t>2,74</t>
-  </si>
-  <si>
     <t>42,08</t>
   </si>
   <si>
     <t>0,2</t>
-  </si>
-  <si>
-    <t>8,02</t>
   </si>
   <si>
     <t>25,65</t>
@@ -1803,7 +1821,7 @@
         <v>93</v>
       </c>
       <c r="C6" s="6">
-        <v>63549</v>
+        <v>65062</v>
       </c>
       <c r="D6" s="6">
         <v>6</v>
@@ -1812,7 +1830,7 @@
         <v>94</v>
       </c>
       <c r="F6" s="6">
-        <v>2706</v>
+        <v>2760</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>95</v>
@@ -1830,7 +1848,7 @@
         <v>97</v>
       </c>
       <c r="L6" s="6">
-        <v>13197</v>
+        <v>13685</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>98</v>
@@ -1842,67 +1860,67 @@
         <v>97</v>
       </c>
       <c r="P6" s="6">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="Q6" s="7" t="s">
         <v>99</v>
       </c>
       <c r="R6" s="6">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="S6" s="7" t="s">
         <v>100</v>
       </c>
       <c r="T6" s="6">
-        <v>1518</v>
+        <v>1527</v>
       </c>
       <c r="U6" s="7" t="s">
         <v>101</v>
       </c>
       <c r="V6" s="6">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="W6" s="7" t="s">
         <v>102</v>
       </c>
       <c r="X6" s="6">
-        <v>1849</v>
+        <v>1888</v>
       </c>
       <c r="Y6" s="7" t="s">
         <v>103</v>
       </c>
       <c r="Z6" s="6">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AA6" s="7" t="s">
         <v>104</v>
       </c>
       <c r="AB6" s="6">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="AC6" s="7" t="s">
         <v>105</v>
       </c>
       <c r="AD6" s="6">
-        <v>27618</v>
+        <v>28354</v>
       </c>
       <c r="AE6" s="7" t="s">
         <v>106</v>
       </c>
       <c r="AF6" s="6">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG6" s="7" t="s">
         <v>107</v>
       </c>
       <c r="AH6" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AI6" s="7" t="s">
         <v>108</v>
       </c>
       <c r="AJ6" s="6">
-        <v>10402</v>
+        <v>10614</v>
       </c>
       <c r="AK6" s="7" t="s">
         <v>109</v>
@@ -1914,7 +1932,7 @@
         <v>110</v>
       </c>
       <c r="AN6" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO6" s="7" t="s">
         <v>97</v>
@@ -1926,7 +1944,7 @@
         <v>97</v>
       </c>
       <c r="AR6" s="6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS6" s="7" t="s">
         <v>111</v>
@@ -1940,7 +1958,7 @@
         <v>113</v>
       </c>
       <c r="C7" s="9">
-        <v>4537</v>
+        <v>4748</v>
       </c>
       <c r="D7" s="9">
         <v>0</v>
@@ -1949,7 +1967,7 @@
         <v>97</v>
       </c>
       <c r="F7" s="9">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>114</v>
@@ -1967,7 +1985,7 @@
         <v>97</v>
       </c>
       <c r="L7" s="9">
-        <v>1280</v>
+        <v>1339</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>116</v>
@@ -2003,7 +2021,7 @@
         <v>118</v>
       </c>
       <c r="X7" s="9">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Y7" s="10" t="s">
         <v>119</v>
@@ -2015,13 +2033,13 @@
         <v>120</v>
       </c>
       <c r="AB7" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC7" s="10" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AD7" s="9">
-        <v>1795</v>
+        <v>1888</v>
       </c>
       <c r="AE7" s="10" t="s">
         <v>121</v>
@@ -2033,22 +2051,22 @@
         <v>120</v>
       </c>
       <c r="AH7" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI7" s="10" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="AJ7" s="9">
-        <v>573</v>
+        <v>610</v>
       </c>
       <c r="AK7" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AL7" s="9">
         <v>381</v>
       </c>
       <c r="AM7" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AN7" s="9">
         <v>0</v>
@@ -2071,13 +2089,13 @@
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C8" s="9">
-        <v>1678</v>
+        <v>1685</v>
       </c>
       <c r="D8" s="9">
         <v>0</v>
@@ -2086,10 +2104,10 @@
         <v>97</v>
       </c>
       <c r="F8" s="9">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
@@ -2104,10 +2122,10 @@
         <v>97</v>
       </c>
       <c r="L8" s="9">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N8" s="9">
         <v>0</v>
@@ -2119,19 +2137,19 @@
         <v>3</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="R8" s="9">
         <v>15</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="T8" s="9">
         <v>57</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="V8" s="9">
         <v>0</v>
@@ -2143,49 +2161,49 @@
         <v>54</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Z8" s="9">
         <v>5</v>
       </c>
       <c r="AA8" s="10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AB8" s="9">
         <v>3</v>
       </c>
       <c r="AC8" s="10" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="AD8" s="9">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="AE8" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AF8" s="9">
         <v>2</v>
       </c>
       <c r="AG8" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AH8" s="9">
         <v>1</v>
       </c>
       <c r="AI8" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AJ8" s="9">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AK8" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AL8" s="9">
         <v>7</v>
       </c>
       <c r="AM8" s="10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AN8" s="9">
         <v>0</v>
@@ -2203,18 +2221,18 @@
         <v>2</v>
       </c>
       <c r="AS8" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C9" s="9">
-        <v>6198</v>
+        <v>6329</v>
       </c>
       <c r="D9" s="9">
         <v>0</v>
@@ -2223,16 +2241,16 @@
         <v>97</v>
       </c>
       <c r="F9" s="9">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H9" s="9">
         <v>22</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J9" s="9">
         <v>0</v>
@@ -2241,10 +2259,10 @@
         <v>97</v>
       </c>
       <c r="L9" s="9">
-        <v>1201</v>
+        <v>1246</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N9" s="9">
         <v>0</v>
@@ -2262,31 +2280,31 @@
         <v>33</v>
       </c>
       <c r="S9" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="T9" s="9">
         <v>193</v>
       </c>
       <c r="U9" s="10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="V9" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W9" s="10" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="X9" s="9">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Y9" s="10" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="Z9" s="9">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AA9" s="10" t="s">
-        <v>115</v>
+        <v>147</v>
       </c>
       <c r="AB9" s="9">
         <v>0</v>
@@ -2295,16 +2313,16 @@
         <v>97</v>
       </c>
       <c r="AD9" s="9">
-        <v>2727</v>
+        <v>2788</v>
       </c>
       <c r="AE9" s="10" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="AF9" s="9">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG9" s="10" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="AH9" s="9">
         <v>0</v>
@@ -2313,16 +2331,16 @@
         <v>97</v>
       </c>
       <c r="AJ9" s="9">
-        <v>1094</v>
+        <v>1112</v>
       </c>
       <c r="AK9" s="10" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="AL9" s="9">
         <v>68</v>
       </c>
       <c r="AM9" s="10" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AN9" s="9">
         <v>0</v>
@@ -2340,18 +2358,18 @@
         <v>4</v>
       </c>
       <c r="AS9" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C10" s="9">
-        <v>7823</v>
+        <v>8017</v>
       </c>
       <c r="D10" s="9">
         <v>3</v>
@@ -2360,16 +2378,16 @@
         <v>111</v>
       </c>
       <c r="F10" s="9">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="H10" s="9">
         <v>25</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="J10" s="9">
         <v>0</v>
@@ -2378,10 +2396,10 @@
         <v>97</v>
       </c>
       <c r="L10" s="9">
-        <v>2027</v>
+        <v>2110</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N10" s="9">
         <v>1</v>
@@ -2390,76 +2408,76 @@
         <v>94</v>
       </c>
       <c r="P10" s="9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="R10" s="9">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="T10" s="9">
         <v>185</v>
       </c>
       <c r="U10" s="10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="V10" s="9">
         <v>18</v>
       </c>
       <c r="W10" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="X10" s="9">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Z10" s="9">
         <v>23</v>
       </c>
       <c r="AA10" s="10" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AB10" s="9">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AC10" s="10" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AD10" s="9">
-        <v>3369</v>
+        <v>3447</v>
       </c>
       <c r="AE10" s="10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AF10" s="9">
         <v>28</v>
       </c>
       <c r="AG10" s="10" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="AH10" s="9">
         <v>5</v>
       </c>
       <c r="AI10" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AJ10" s="9">
-        <v>1224</v>
+        <v>1254</v>
       </c>
       <c r="AK10" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AL10" s="9">
         <v>119</v>
       </c>
       <c r="AM10" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AN10" s="9">
         <v>1</v>
@@ -2482,31 +2500,31 @@
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C11" s="9">
-        <v>6328</v>
+        <v>6379</v>
       </c>
       <c r="D11" s="9">
         <v>2</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="F11" s="9">
         <v>267</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H11" s="9">
         <v>6</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J11" s="9">
         <v>0</v>
@@ -2515,10 +2533,10 @@
         <v>97</v>
       </c>
       <c r="L11" s="9">
-        <v>1407</v>
+        <v>1426</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N11" s="9">
         <v>0</v>
@@ -2530,19 +2548,19 @@
         <v>15</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>154</v>
+        <v>105</v>
       </c>
       <c r="R11" s="9">
         <v>28</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="T11" s="9">
         <v>381</v>
       </c>
       <c r="U11" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="V11" s="9">
         <v>1</v>
@@ -2551,34 +2569,34 @@
         <v>108</v>
       </c>
       <c r="X11" s="9">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Y11" s="10" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="Z11" s="9">
         <v>29</v>
       </c>
       <c r="AA11" s="10" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="AB11" s="9">
         <v>9</v>
       </c>
       <c r="AC11" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AD11" s="9">
-        <v>2846</v>
+        <v>2874</v>
       </c>
       <c r="AE11" s="10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AF11" s="9">
         <v>73</v>
       </c>
       <c r="AG11" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AH11" s="9">
         <v>0</v>
@@ -2587,10 +2605,10 @@
         <v>97</v>
       </c>
       <c r="AJ11" s="9">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="AK11" s="10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AL11" s="9">
         <v>39</v>
@@ -2614,18 +2632,18 @@
         <v>2</v>
       </c>
       <c r="AS11" s="10" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C12" s="9">
-        <v>5880</v>
+        <v>5884</v>
       </c>
       <c r="D12" s="9">
         <v>0</v>
@@ -2637,13 +2655,13 @@
         <v>152</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H12" s="9">
         <v>135</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J12" s="9">
         <v>0</v>
@@ -2652,10 +2670,10 @@
         <v>97</v>
       </c>
       <c r="L12" s="9">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N12" s="9">
         <v>0</v>
@@ -2673,13 +2691,13 @@
         <v>26</v>
       </c>
       <c r="S12" s="10" t="s">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="T12" s="9">
         <v>135</v>
       </c>
       <c r="U12" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="V12" s="9">
         <v>0</v>
@@ -2691,13 +2709,13 @@
         <v>145</v>
       </c>
       <c r="Y12" s="10" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Z12" s="9">
         <v>33</v>
       </c>
       <c r="AA12" s="10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AB12" s="9">
         <v>0</v>
@@ -2706,16 +2724,16 @@
         <v>97</v>
       </c>
       <c r="AD12" s="9">
-        <v>2609</v>
+        <v>2611</v>
       </c>
       <c r="AE12" s="10" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AF12" s="9">
         <v>46</v>
       </c>
       <c r="AG12" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AH12" s="9">
         <v>0</v>
@@ -2724,16 +2742,16 @@
         <v>97</v>
       </c>
       <c r="AJ12" s="9">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="AK12" s="10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AL12" s="9">
         <v>757</v>
       </c>
       <c r="AM12" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AN12" s="9">
         <v>0</v>
@@ -2751,18 +2769,18 @@
         <v>7</v>
       </c>
       <c r="AS12" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C13" s="9">
-        <v>3315</v>
+        <v>3324</v>
       </c>
       <c r="D13" s="9">
         <v>0</v>
@@ -2771,16 +2789,16 @@
         <v>97</v>
       </c>
       <c r="F13" s="9">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H13" s="9">
         <v>2</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J13" s="9">
         <v>0</v>
@@ -2789,52 +2807,52 @@
         <v>97</v>
       </c>
       <c r="L13" s="9">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="N13" s="9">
         <v>1</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="P13" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="R13" s="9">
         <v>19</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="T13" s="9">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U13" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="V13" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W13" s="10" t="s">
-        <v>134</v>
+        <v>97</v>
       </c>
       <c r="X13" s="9">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Y13" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Z13" s="9">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA13" s="10" t="s">
-        <v>194</v>
+        <v>138</v>
       </c>
       <c r="AB13" s="9">
         <v>0</v>
@@ -2843,16 +2861,16 @@
         <v>97</v>
       </c>
       <c r="AD13" s="9">
-        <v>1367</v>
+        <v>1371</v>
       </c>
       <c r="AE13" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AF13" s="9">
         <v>11</v>
       </c>
       <c r="AG13" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AH13" s="9">
         <v>0</v>
@@ -2861,16 +2879,16 @@
         <v>97</v>
       </c>
       <c r="AJ13" s="9">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="AK13" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AL13" s="9">
         <v>39</v>
       </c>
       <c r="AM13" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AN13" s="9">
         <v>0</v>
@@ -2893,13 +2911,13 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C14" s="9">
-        <v>2204</v>
+        <v>2263</v>
       </c>
       <c r="D14" s="9">
         <v>0</v>
@@ -2908,16 +2926,16 @@
         <v>97</v>
       </c>
       <c r="F14" s="9">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H14" s="9">
         <v>17</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J14" s="9">
         <v>0</v>
@@ -2926,52 +2944,52 @@
         <v>97</v>
       </c>
       <c r="L14" s="9">
-        <v>477</v>
+        <v>500</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N14" s="9">
         <v>1</v>
       </c>
       <c r="O14" s="10" t="s">
-        <v>204</v>
+        <v>111</v>
       </c>
       <c r="P14" s="9">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q14" s="10" t="s">
         <v>205</v>
       </c>
       <c r="R14" s="9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="T14" s="9">
+        <v>48</v>
+      </c>
+      <c r="U14" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="V14" s="9">
+        <v>9</v>
+      </c>
+      <c r="W14" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="X14" s="9">
         <v>47</v>
       </c>
-      <c r="U14" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="V14" s="9">
-        <v>10</v>
-      </c>
-      <c r="W14" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="X14" s="9">
-        <v>44</v>
-      </c>
       <c r="Y14" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Z14" s="9">
         <v>1</v>
       </c>
       <c r="AA14" s="10" t="s">
-        <v>204</v>
+        <v>111</v>
       </c>
       <c r="AB14" s="9">
         <v>0</v>
@@ -2980,16 +2998,16 @@
         <v>97</v>
       </c>
       <c r="AD14" s="9">
-        <v>1018</v>
+        <v>1045</v>
       </c>
       <c r="AE14" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AF14" s="9">
         <v>2</v>
       </c>
       <c r="AG14" s="10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AH14" s="9">
         <v>0</v>
@@ -2998,22 +3016,22 @@
         <v>97</v>
       </c>
       <c r="AJ14" s="9">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AK14" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AL14" s="9">
         <v>99</v>
       </c>
       <c r="AM14" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AN14" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO14" s="10" t="s">
-        <v>204</v>
+        <v>97</v>
       </c>
       <c r="AP14" s="9">
         <v>0</v>
@@ -3022,18 +3040,18 @@
         <v>97</v>
       </c>
       <c r="AR14" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS14" s="10" t="s">
-        <v>204</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C15" s="9">
         <v>7725</v>
@@ -3048,13 +3066,13 @@
         <v>255</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H15" s="9">
         <v>88</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>215</v>
+        <v>176</v>
       </c>
       <c r="J15" s="9">
         <v>0</v>
@@ -3078,19 +3096,19 @@
         <v>4</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="R15" s="9">
         <v>78</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="T15" s="9">
         <v>109</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>218</v>
+        <v>162</v>
       </c>
       <c r="V15" s="9">
         <v>0</v>
@@ -3108,7 +3126,7 @@
         <v>10</v>
       </c>
       <c r="AA15" s="10" t="s">
-        <v>102</v>
+        <v>220</v>
       </c>
       <c r="AB15" s="9">
         <v>0</v>
@@ -3120,13 +3138,13 @@
         <v>3140</v>
       </c>
       <c r="AE15" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AF15" s="9">
         <v>66</v>
       </c>
       <c r="AG15" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AH15" s="9">
         <v>0</v>
@@ -3138,13 +3156,13 @@
         <v>1136</v>
       </c>
       <c r="AK15" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AL15" s="9">
         <v>1696</v>
       </c>
       <c r="AM15" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AN15" s="9">
         <v>0</v>
@@ -3167,13 +3185,13 @@
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C16" s="9">
-        <v>2174</v>
+        <v>2250</v>
       </c>
       <c r="D16" s="9">
         <v>0</v>
@@ -3182,16 +3200,16 @@
         <v>97</v>
       </c>
       <c r="F16" s="9">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H16" s="9">
         <v>6</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J16" s="9">
         <v>0</v>
@@ -3200,10 +3218,10 @@
         <v>97</v>
       </c>
       <c r="L16" s="9">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N16" s="9">
         <v>0</v>
@@ -3215,19 +3233,19 @@
         <v>1</v>
       </c>
       <c r="Q16" s="10" t="s">
-        <v>204</v>
+        <v>111</v>
       </c>
       <c r="R16" s="9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="T16" s="9">
         <v>112</v>
       </c>
       <c r="U16" s="10" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="V16" s="9">
         <v>0</v>
@@ -3236,7 +3254,7 @@
         <v>97</v>
       </c>
       <c r="X16" s="9">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Y16" s="10" t="s">
         <v>231</v>
@@ -3245,43 +3263,43 @@
         <v>20</v>
       </c>
       <c r="AA16" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB16" s="9">
+        <v>4</v>
+      </c>
+      <c r="AC16" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD16" s="9">
+        <v>977</v>
+      </c>
+      <c r="AE16" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="AB16" s="9">
-        <v>5</v>
-      </c>
-      <c r="AC16" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="AD16" s="9">
-        <v>942</v>
-      </c>
-      <c r="AE16" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="AF16" s="9">
         <v>35</v>
       </c>
       <c r="AG16" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AH16" s="9">
         <v>1</v>
       </c>
       <c r="AI16" s="10" t="s">
-        <v>204</v>
+        <v>111</v>
       </c>
       <c r="AJ16" s="9">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="AK16" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL16" s="9">
         <v>57</v>
       </c>
       <c r="AM16" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AN16" s="9">
         <v>0</v>
@@ -3299,48 +3317,48 @@
         <v>2</v>
       </c>
       <c r="AS16" s="10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>238</v>
-      </c>
       <c r="C17" s="9">
-        <v>3861</v>
+        <v>4038</v>
       </c>
       <c r="D17" s="9">
         <v>1</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="F17" s="9">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H17" s="9">
         <v>26</v>
       </c>
       <c r="I17" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="J17" s="9">
+        <v>0</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L17" s="9">
+        <v>925</v>
+      </c>
+      <c r="M17" s="10" t="s">
         <v>240</v>
-      </c>
-      <c r="J17" s="9">
-        <v>0</v>
-      </c>
-      <c r="K17" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="L17" s="9">
-        <v>864</v>
-      </c>
-      <c r="M17" s="10" t="s">
-        <v>241</v>
       </c>
       <c r="N17" s="9">
         <v>0</v>
@@ -3352,28 +3370,28 @@
         <v>22</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>191</v>
+        <v>104</v>
       </c>
       <c r="R17" s="9">
         <v>29</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="T17" s="9">
         <v>30</v>
       </c>
       <c r="U17" s="10" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="V17" s="9">
         <v>9</v>
       </c>
       <c r="W17" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="X17" s="9">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="Y17" s="10" t="s">
         <v>243</v>
@@ -3382,43 +3400,43 @@
         <v>2</v>
       </c>
       <c r="AA17" s="10" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="AB17" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC17" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="AD17" s="9">
+        <v>2000</v>
+      </c>
+      <c r="AE17" s="10" t="s">
         <v>244</v>
-      </c>
-      <c r="AD17" s="9">
-        <v>1914</v>
-      </c>
-      <c r="AE17" s="10" t="s">
-        <v>245</v>
       </c>
       <c r="AF17" s="9">
         <v>42</v>
       </c>
       <c r="AG17" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AH17" s="9">
         <v>2</v>
       </c>
       <c r="AI17" s="10" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="AJ17" s="9">
-        <v>449</v>
+        <v>473</v>
       </c>
       <c r="AK17" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AL17" s="9">
         <v>220</v>
       </c>
       <c r="AM17" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AN17" s="9">
         <v>0</v>
@@ -3441,31 +3459,31 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="C18" s="9">
+        <v>4928</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F18" s="9">
+        <v>208</v>
+      </c>
+      <c r="G18" s="10" t="s">
         <v>250</v>
-      </c>
-      <c r="C18" s="9">
-        <v>4719</v>
-      </c>
-      <c r="D18" s="9">
-        <v>0</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="F18" s="9">
-        <v>201</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>95</v>
       </c>
       <c r="H18" s="9">
         <v>6</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="J18" s="9">
         <v>0</v>
@@ -3474,7 +3492,7 @@
         <v>97</v>
       </c>
       <c r="L18" s="9">
-        <v>1072</v>
+        <v>1122</v>
       </c>
       <c r="M18" s="10" t="s">
         <v>251</v>
@@ -3486,58 +3504,58 @@
         <v>97</v>
       </c>
       <c r="P18" s="9">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>152</v>
+        <v>252</v>
       </c>
       <c r="R18" s="9">
         <v>20</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>136</v>
+        <v>253</v>
       </c>
       <c r="T18" s="9">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="U18" s="10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="V18" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W18" s="10" t="s">
-        <v>244</v>
+        <v>111</v>
       </c>
       <c r="X18" s="9">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="Y18" s="10" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Z18" s="9">
         <v>14</v>
       </c>
       <c r="AA18" s="10" t="s">
-        <v>131</v>
+        <v>256</v>
       </c>
       <c r="AB18" s="9">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AC18" s="10" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="AD18" s="9">
-        <v>2114</v>
+        <v>2236</v>
       </c>
       <c r="AE18" s="10" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AF18" s="9">
         <v>12</v>
       </c>
       <c r="AG18" s="10" t="s">
-        <v>255</v>
+        <v>105</v>
       </c>
       <c r="AH18" s="9">
         <v>0</v>
@@ -3546,16 +3564,16 @@
         <v>97</v>
       </c>
       <c r="AJ18" s="9">
-        <v>1045</v>
+        <v>1084</v>
       </c>
       <c r="AK18" s="10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AL18" s="9">
         <v>43</v>
       </c>
       <c r="AM18" s="10" t="s">
-        <v>205</v>
+        <v>259</v>
       </c>
       <c r="AN18" s="9">
         <v>0</v>
@@ -3578,13 +3596,13 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C19" s="9">
-        <v>4949</v>
+        <v>5334</v>
       </c>
       <c r="D19" s="9">
         <v>0</v>
@@ -3593,16 +3611,16 @@
         <v>97</v>
       </c>
       <c r="F19" s="9">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="H19" s="9">
         <v>18</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>162</v>
+        <v>263</v>
       </c>
       <c r="J19" s="9">
         <v>0</v>
@@ -3611,10 +3629,10 @@
         <v>97</v>
       </c>
       <c r="L19" s="9">
-        <v>1375</v>
+        <v>1493</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="N19" s="9">
         <v>0</v>
@@ -3632,13 +3650,13 @@
         <v>18</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>162</v>
+        <v>263</v>
       </c>
       <c r="T19" s="9">
         <v>17</v>
       </c>
       <c r="U19" s="10" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="V19" s="9">
         <v>0</v>
@@ -3647,16 +3665,16 @@
         <v>97</v>
       </c>
       <c r="X19" s="9">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="Y19" s="10" t="s">
-        <v>262</v>
+        <v>215</v>
       </c>
       <c r="Z19" s="9">
         <v>4</v>
       </c>
       <c r="AA19" s="10" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="AB19" s="9">
         <v>0</v>
@@ -3665,16 +3683,16 @@
         <v>97</v>
       </c>
       <c r="AD19" s="9">
-        <v>2196</v>
+        <v>2393</v>
       </c>
       <c r="AE19" s="10" t="s">
-        <v>183</v>
+        <v>267</v>
       </c>
       <c r="AF19" s="9">
         <v>26</v>
       </c>
       <c r="AG19" s="10" t="s">
-        <v>142</v>
+        <v>268</v>
       </c>
       <c r="AH19" s="9">
         <v>0</v>
@@ -3683,16 +3701,16 @@
         <v>97</v>
       </c>
       <c r="AJ19" s="9">
-        <v>763</v>
+        <v>804</v>
       </c>
       <c r="AK19" s="10" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="AL19" s="9">
         <v>146</v>
       </c>
       <c r="AM19" s="10" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="AN19" s="9">
         <v>0</v>
@@ -3715,10 +3733,10 @@
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C20" s="9">
         <v>661</v>
@@ -3733,13 +3751,13 @@
         <v>47</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="H20" s="9">
         <v>6</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>205</v>
+        <v>274</v>
       </c>
       <c r="J20" s="9">
         <v>0</v>
@@ -3751,7 +3769,7 @@
         <v>66</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="N20" s="9">
         <v>0</v>
@@ -3763,55 +3781,55 @@
         <v>4</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>269</v>
+        <v>96</v>
       </c>
       <c r="R20" s="9">
         <v>4</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>269</v>
+        <v>96</v>
       </c>
       <c r="T20" s="9">
         <v>41</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="V20" s="9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W20" s="10" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="X20" s="9">
         <v>46</v>
       </c>
       <c r="Y20" s="10" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="Z20" s="9">
         <v>90</v>
       </c>
       <c r="AA20" s="10" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="AB20" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC20" s="10" t="s">
-        <v>207</v>
+        <v>96</v>
       </c>
       <c r="AD20" s="9">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AE20" s="10" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="AF20" s="9">
         <v>12</v>
       </c>
       <c r="AG20" s="10" t="s">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="AH20" s="9">
         <v>0</v>
@@ -3823,13 +3841,13 @@
         <v>63</v>
       </c>
       <c r="AK20" s="10" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="AL20" s="9">
         <v>19</v>
       </c>
       <c r="AM20" s="10" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="AN20" s="9">
         <v>0</v>
@@ -3847,15 +3865,15 @@
         <v>2</v>
       </c>
       <c r="AS20" s="10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="C21" s="9">
         <v>1497</v>
@@ -3870,13 +3888,13 @@
         <v>39</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="H21" s="9">
         <v>6</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="J21" s="9">
         <v>0</v>
@@ -3888,7 +3906,7 @@
         <v>174</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="N21" s="9">
         <v>0</v>
@@ -3906,49 +3924,49 @@
         <v>9</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="T21" s="9">
         <v>35</v>
       </c>
       <c r="U21" s="10" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="V21" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W21" s="10" t="s">
-        <v>102</v>
+        <v>266</v>
       </c>
       <c r="X21" s="9">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y21" s="10" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="Z21" s="9">
         <v>39</v>
       </c>
       <c r="AA21" s="10" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="AB21" s="9">
         <v>15</v>
       </c>
       <c r="AC21" s="10" t="s">
-        <v>155</v>
+        <v>291</v>
       </c>
       <c r="AD21" s="9">
         <v>630</v>
       </c>
       <c r="AE21" s="10" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="AF21" s="9">
         <v>3</v>
       </c>
       <c r="AG21" s="10" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="AH21" s="9">
         <v>0</v>
@@ -3960,13 +3978,13 @@
         <v>120</v>
       </c>
       <c r="AK21" s="10" t="s">
-        <v>287</v>
+        <v>124</v>
       </c>
       <c r="AL21" s="9">
         <v>384</v>
       </c>
       <c r="AM21" s="10" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="AN21" s="9">
         <v>0</v>
@@ -3989,13 +4007,13 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C22" s="12">
-        <v>63549</v>
+        <v>65062</v>
       </c>
       <c r="D22" s="12">
         <v>6</v>
@@ -4004,7 +4022,7 @@
         <v>94</v>
       </c>
       <c r="F22" s="12">
-        <v>2706</v>
+        <v>2760</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>95</v>
@@ -4022,7 +4040,7 @@
         <v>97</v>
       </c>
       <c r="L22" s="12">
-        <v>13197</v>
+        <v>13685</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>98</v>
@@ -4034,67 +4052,67 @@
         <v>97</v>
       </c>
       <c r="P22" s="12">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="Q22" s="13" t="s">
         <v>99</v>
       </c>
       <c r="R22" s="12">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="S22" s="13" t="s">
         <v>100</v>
       </c>
       <c r="T22" s="12">
-        <v>1518</v>
+        <v>1527</v>
       </c>
       <c r="U22" s="13" t="s">
         <v>101</v>
       </c>
       <c r="V22" s="12">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="W22" s="13" t="s">
         <v>102</v>
       </c>
       <c r="X22" s="12">
-        <v>1849</v>
+        <v>1888</v>
       </c>
       <c r="Y22" s="13" t="s">
         <v>103</v>
       </c>
       <c r="Z22" s="12">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AA22" s="13" t="s">
         <v>104</v>
       </c>
       <c r="AB22" s="12">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="AC22" s="13" t="s">
         <v>105</v>
       </c>
       <c r="AD22" s="12">
-        <v>27618</v>
+        <v>28354</v>
       </c>
       <c r="AE22" s="13" t="s">
         <v>106</v>
       </c>
       <c r="AF22" s="12">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG22" s="13" t="s">
         <v>107</v>
       </c>
       <c r="AH22" s="12">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AI22" s="13" t="s">
         <v>108</v>
       </c>
       <c r="AJ22" s="12">
-        <v>10402</v>
+        <v>10614</v>
       </c>
       <c r="AK22" s="13" t="s">
         <v>109</v>
@@ -4106,7 +4124,7 @@
         <v>110</v>
       </c>
       <c r="AN22" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO22" s="13" t="s">
         <v>97</v>
@@ -4118,7 +4136,7 @@
         <v>97</v>
       </c>
       <c r="AR22" s="12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS22" s="13" t="s">
         <v>111</v>

--- a/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
+++ b/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
@@ -16,7 +16,7 @@
     <t>DATA RADAR ANOMALI KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 3 Sep 2026, 13.27</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 4 Sep 2026, 08.16</t>
   </si>
   <si>
     <t>Kode</t>
@@ -301,529 +301,532 @@
     <t>4,24</t>
   </si>
   <si>
+    <t>0,6</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>21,27</t>
+  </si>
+  <si>
+    <t>0,13</t>
+  </si>
+  <si>
+    <t>0,64</t>
+  </si>
+  <si>
+    <t>2,32</t>
+  </si>
+  <si>
+    <t>0,11</t>
+  </si>
+  <si>
+    <t>2,88</t>
+  </si>
+  <si>
+    <t>0,53</t>
+  </si>
+  <si>
+    <t>0,29</t>
+  </si>
+  <si>
+    <t>43,61</t>
+  </si>
+  <si>
+    <t>0,94</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>16,22</t>
+  </si>
+  <si>
+    <t>6,14</t>
+  </si>
+  <si>
+    <t>0,04</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>LAMPUNG BARAT</t>
+  </si>
+  <si>
+    <t>4,23</t>
+  </si>
+  <si>
+    <t>0,67</t>
+  </si>
+  <si>
+    <t>28,4</t>
+  </si>
+  <si>
+    <t>0,17</t>
+  </si>
+  <si>
+    <t>0,46</t>
+  </si>
+  <si>
+    <t>4,12</t>
+  </si>
+  <si>
+    <t>0,44</t>
+  </si>
+  <si>
+    <t>0,1</t>
+  </si>
+  <si>
+    <t>39,65</t>
+  </si>
+  <si>
+    <t>0,08</t>
+  </si>
+  <si>
+    <t>12,81</t>
+  </si>
+  <si>
+    <t>7,97</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>TANGGAMUS</t>
+  </si>
+  <si>
+    <t>6,59</t>
+  </si>
+  <si>
+    <t>19,78</t>
+  </si>
+  <si>
+    <t>0,06</t>
+  </si>
+  <si>
+    <t>0,88</t>
+  </si>
+  <si>
+    <t>3,47</t>
+  </si>
+  <si>
+    <t>3,24</t>
+  </si>
+  <si>
+    <t>0,18</t>
+  </si>
+  <si>
+    <t>41,91</t>
+  </si>
+  <si>
+    <t>0,12</t>
+  </si>
+  <si>
+    <t>22,9</t>
+  </si>
+  <si>
+    <t>0,41</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>LAMPUNG SELATAN</t>
+  </si>
+  <si>
+    <t>5,75</t>
+  </si>
+  <si>
+    <t>0,34</t>
+  </si>
+  <si>
+    <t>20,24</t>
+  </si>
+  <si>
+    <t>0,52</t>
+  </si>
+  <si>
+    <t>2,94</t>
+  </si>
+  <si>
+    <t>3,31</t>
+  </si>
+  <si>
+    <t>0,69</t>
+  </si>
+  <si>
+    <t>44,15</t>
+  </si>
+  <si>
+    <t>3,65</t>
+  </si>
+  <si>
+    <t>17,32</t>
+  </si>
+  <si>
+    <t>1,04</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>LAMPUNG TIMUR</t>
+  </si>
+  <si>
+    <t>4,15</t>
+  </si>
+  <si>
+    <t>0,3</t>
+  </si>
+  <si>
+    <t>26,52</t>
+  </si>
+  <si>
+    <t>0,24</t>
+  </si>
+  <si>
+    <t>0,96</t>
+  </si>
+  <si>
+    <t>2,25</t>
+  </si>
+  <si>
+    <t>0,22</t>
+  </si>
+  <si>
+    <t>3,1</t>
+  </si>
+  <si>
+    <t>0,28</t>
+  </si>
+  <si>
+    <t>1,35</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>0,35</t>
+  </si>
+  <si>
+    <t>0,07</t>
+  </si>
+  <si>
+    <t>15,66</t>
+  </si>
+  <si>
+    <t>1,45</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>LAMPUNG TENGAH</t>
+  </si>
+  <si>
+    <t>4,18</t>
+  </si>
+  <si>
+    <t>0,09</t>
+  </si>
+  <si>
+    <t>22,38</t>
+  </si>
+  <si>
+    <t>0,23</t>
+  </si>
+  <si>
+    <t>5,96</t>
+  </si>
+  <si>
+    <t>0,45</t>
+  </si>
+  <si>
+    <t>0,14</t>
+  </si>
+  <si>
+    <t>45,05</t>
+  </si>
+  <si>
+    <t>1,14</t>
+  </si>
+  <si>
+    <t>14,99</t>
+  </si>
+  <si>
     <t>0,61</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>21,03</t>
-  </si>
-  <si>
-    <t>0,15</t>
-  </si>
-  <si>
-    <t>0,65</t>
-  </si>
-  <si>
-    <t>2,35</t>
-  </si>
-  <si>
-    <t>0,11</t>
-  </si>
-  <si>
-    <t>2,9</t>
-  </si>
-  <si>
-    <t>0,54</t>
-  </si>
-  <si>
-    <t>0,24</t>
-  </si>
-  <si>
-    <t>43,58</t>
-  </si>
-  <si>
-    <t>0,95</t>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>2,58</t>
+  </si>
+  <si>
+    <t>2,29</t>
+  </si>
+  <si>
+    <t>14,48</t>
+  </si>
+  <si>
+    <t>2,46</t>
+  </si>
+  <si>
+    <t>0,56</t>
+  </si>
+  <si>
+    <t>44,37</t>
+  </si>
+  <si>
+    <t>0,78</t>
+  </si>
+  <si>
+    <t>16,77</t>
+  </si>
+  <si>
+    <t>12,85</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
+    <t>4,25</t>
+  </si>
+  <si>
+    <t>20,37</t>
+  </si>
+  <si>
+    <t>0,59</t>
+  </si>
+  <si>
+    <t>2,42</t>
+  </si>
+  <si>
+    <t>2,92</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>40,8</t>
+  </si>
+  <si>
+    <t>25,45</t>
+  </si>
+  <si>
+    <t>1,15</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG</t>
+  </si>
+  <si>
+    <t>4,39</t>
+  </si>
+  <si>
+    <t>0,72</t>
+  </si>
+  <si>
+    <t>23,33</t>
+  </si>
+  <si>
+    <t>1,18</t>
+  </si>
+  <si>
+    <t>2,49</t>
+  </si>
+  <si>
+    <t>0,25</t>
+  </si>
+  <si>
+    <t>2,15</t>
+  </si>
+  <si>
+    <t>46,03</t>
+  </si>
+  <si>
+    <t>14,68</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PESAWARAN</t>
+  </si>
+  <si>
+    <t>3,3</t>
+  </si>
+  <si>
+    <t>13,47</t>
+  </si>
+  <si>
+    <t>0,05</t>
+  </si>
+  <si>
+    <t>1,01</t>
+  </si>
+  <si>
+    <t>1,41</t>
+  </si>
+  <si>
+    <t>1,28</t>
+  </si>
+  <si>
+    <t>40,63</t>
+  </si>
+  <si>
+    <t>0,85</t>
+  </si>
+  <si>
+    <t>14,69</t>
+  </si>
+  <si>
+    <t>21,94</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>PRINGSEWU</t>
+  </si>
+  <si>
+    <t>4,96</t>
+  </si>
+  <si>
+    <t>0,27</t>
+  </si>
+  <si>
+    <t>16,73</t>
+  </si>
+  <si>
+    <t>1,33</t>
+  </si>
+  <si>
+    <t>4,03</t>
+  </si>
+  <si>
+    <t>43,45</t>
+  </si>
+  <si>
+    <t>1,55</t>
+  </si>
+  <si>
+    <t>18,98</t>
+  </si>
+  <si>
+    <t>2,52</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
   </si>
   <si>
     <t>0,02</t>
   </si>
   <si>
-    <t>16,31</t>
-  </si>
-  <si>
-    <t>6,26</t>
-  </si>
-  <si>
-    <t>0,04</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>LAMPUNG BARAT</t>
-  </si>
-  <si>
-    <t>4,23</t>
-  </si>
-  <si>
-    <t>0,67</t>
-  </si>
-  <si>
-    <t>28,2</t>
-  </si>
-  <si>
-    <t>0,17</t>
-  </si>
-  <si>
-    <t>0,46</t>
-  </si>
-  <si>
-    <t>4,15</t>
-  </si>
-  <si>
-    <t>0,44</t>
-  </si>
-  <si>
-    <t>39,76</t>
-  </si>
-  <si>
-    <t>0,08</t>
-  </si>
-  <si>
-    <t>12,85</t>
-  </si>
-  <si>
-    <t>8,02</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>TANGGAMUS</t>
-  </si>
-  <si>
-    <t>6,65</t>
-  </si>
-  <si>
-    <t>19,7</t>
-  </si>
-  <si>
-    <t>0,18</t>
-  </si>
-  <si>
-    <t>0,89</t>
-  </si>
-  <si>
-    <t>3,38</t>
+    <t>4,63</t>
+  </si>
+  <si>
+    <t>23,26</t>
+  </si>
+  <si>
+    <t>0,51</t>
+  </si>
+  <si>
+    <t>0,68</t>
+  </si>
+  <si>
+    <t>0,7</t>
+  </si>
+  <si>
+    <t>0,21</t>
+  </si>
+  <si>
+    <t>1,73</t>
+  </si>
+  <si>
+    <t>49,7</t>
+  </si>
+  <si>
+    <t>0,98</t>
+  </si>
+  <si>
+    <t>11,62</t>
+  </si>
+  <si>
+    <t>5,14</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG BARAT</t>
+  </si>
+  <si>
+    <t>4,27</t>
+  </si>
+  <si>
+    <t>22,76</t>
+  </si>
+  <si>
+    <t>0,16</t>
+  </si>
+  <si>
+    <t>0,4</t>
+  </si>
+  <si>
+    <t>1,61</t>
+  </si>
+  <si>
+    <t>1,83</t>
+  </si>
+  <si>
+    <t>45,53</t>
+  </si>
+  <si>
+    <t>21,89</t>
+  </si>
+  <si>
+    <t>0,87</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>PESISIR BARAT</t>
+  </si>
+  <si>
+    <t>4,41</t>
+  </si>
+  <si>
+    <t>0,32</t>
+  </si>
+  <si>
+    <t>28,34</t>
   </si>
   <si>
     <t>3,2</t>
   </si>
   <si>
-    <t>0,3</t>
-  </si>
-  <si>
-    <t>41,84</t>
-  </si>
-  <si>
-    <t>0,12</t>
-  </si>
-  <si>
-    <t>0,06</t>
-  </si>
-  <si>
-    <t>22,97</t>
-  </si>
-  <si>
-    <t>0,42</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>LAMPUNG SELATAN</t>
-  </si>
-  <si>
-    <t>5,78</t>
-  </si>
-  <si>
-    <t>0,35</t>
-  </si>
-  <si>
-    <t>19,69</t>
-  </si>
-  <si>
-    <t>0,52</t>
-  </si>
-  <si>
-    <t>3,05</t>
-  </si>
-  <si>
-    <t>3,35</t>
-  </si>
-  <si>
-    <t>0,71</t>
-  </si>
-  <si>
-    <t>44,05</t>
-  </si>
-  <si>
-    <t>3,78</t>
-  </si>
-  <si>
-    <t>17,57</t>
-  </si>
-  <si>
-    <t>1,07</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>LAMPUNG TIMUR</t>
-  </si>
-  <si>
-    <t>0,31</t>
-  </si>
-  <si>
-    <t>26,32</t>
-  </si>
-  <si>
-    <t>0,25</t>
-  </si>
-  <si>
-    <t>0,99</t>
-  </si>
-  <si>
-    <t>2,31</t>
-  </si>
-  <si>
-    <t>0,22</t>
-  </si>
-  <si>
-    <t>3,12</t>
-  </si>
-  <si>
-    <t>0,29</t>
-  </si>
-  <si>
-    <t>1,41</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>15,64</t>
-  </si>
-  <si>
-    <t>1,48</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>LAMPUNG TENGAH</t>
-  </si>
-  <si>
-    <t>0,03</t>
-  </si>
-  <si>
-    <t>4,19</t>
-  </si>
-  <si>
-    <t>0,09</t>
-  </si>
-  <si>
-    <t>22,35</t>
-  </si>
-  <si>
-    <t>5,97</t>
-  </si>
-  <si>
-    <t>0,45</t>
-  </si>
-  <si>
-    <t>0,14</t>
-  </si>
-  <si>
-    <t>45,05</t>
-  </si>
-  <si>
-    <t>1,14</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
-  </si>
-  <si>
-    <t>2,58</t>
-  </si>
-  <si>
-    <t>2,29</t>
-  </si>
-  <si>
-    <t>14,46</t>
-  </si>
-  <si>
-    <t>2,46</t>
-  </si>
-  <si>
-    <t>0,56</t>
-  </si>
-  <si>
-    <t>44,37</t>
-  </si>
-  <si>
-    <t>0,78</t>
-  </si>
-  <si>
-    <t>16,76</t>
-  </si>
-  <si>
-    <t>12,87</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>4,33</t>
-  </si>
-  <si>
-    <t>20,58</t>
-  </si>
-  <si>
-    <t>0,57</t>
-  </si>
-  <si>
-    <t>2,47</t>
-  </si>
-  <si>
-    <t>2,98</t>
-  </si>
-  <si>
-    <t>41,25</t>
-  </si>
-  <si>
-    <t>0,33</t>
-  </si>
-  <si>
-    <t>25,78</t>
-  </si>
-  <si>
-    <t>1,17</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG</t>
-  </si>
-  <si>
-    <t>4,51</t>
-  </si>
-  <si>
-    <t>0,75</t>
-  </si>
-  <si>
-    <t>22,09</t>
-  </si>
-  <si>
-    <t>0,84</t>
-  </si>
-  <si>
-    <t>1,19</t>
-  </si>
-  <si>
-    <t>2,12</t>
-  </si>
-  <si>
-    <t>0,4</t>
-  </si>
-  <si>
-    <t>2,08</t>
-  </si>
-  <si>
-    <t>46,18</t>
-  </si>
-  <si>
-    <t>15,2</t>
-  </si>
-  <si>
-    <t>4,37</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>PESAWARAN</t>
-  </si>
-  <si>
-    <t>3,3</t>
-  </si>
-  <si>
-    <t>13,48</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>1,01</t>
-  </si>
-  <si>
-    <t>1,28</t>
-  </si>
-  <si>
-    <t>0,13</t>
-  </si>
-  <si>
-    <t>40,65</t>
-  </si>
-  <si>
-    <t>0,85</t>
-  </si>
-  <si>
-    <t>14,71</t>
-  </si>
-  <si>
-    <t>21,95</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>PRINGSEWU</t>
-  </si>
-  <si>
-    <t>4,98</t>
-  </si>
-  <si>
-    <t>0,27</t>
-  </si>
-  <si>
-    <t>16,71</t>
-  </si>
-  <si>
-    <t>1,33</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>43,42</t>
-  </si>
-  <si>
-    <t>1,56</t>
-  </si>
-  <si>
-    <t>18,98</t>
-  </si>
-  <si>
-    <t>2,53</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>4,58</t>
-  </si>
-  <si>
-    <t>0,64</t>
-  </si>
-  <si>
-    <t>22,91</t>
-  </si>
-  <si>
-    <t>0,72</t>
-  </si>
-  <si>
-    <t>0,74</t>
-  </si>
-  <si>
-    <t>1,73</t>
-  </si>
-  <si>
-    <t>49,53</t>
-  </si>
-  <si>
-    <t>1,04</t>
-  </si>
-  <si>
-    <t>11,71</t>
-  </si>
-  <si>
-    <t>5,45</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG BARAT</t>
-  </si>
-  <si>
-    <t>4,22</t>
-  </si>
-  <si>
-    <t>22,77</t>
-  </si>
-  <si>
-    <t>0,16</t>
-  </si>
-  <si>
-    <t>0,41</t>
-  </si>
-  <si>
-    <t>1,62</t>
-  </si>
-  <si>
-    <t>1,85</t>
-  </si>
-  <si>
-    <t>0,28</t>
-  </si>
-  <si>
-    <t>45,37</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>0,87</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>PESISIR BARAT</t>
-  </si>
-  <si>
-    <t>4,44</t>
-  </si>
-  <si>
-    <t>0,34</t>
-  </si>
-  <si>
-    <t>27,99</t>
-  </si>
-  <si>
-    <t>0,32</t>
-  </si>
-  <si>
-    <t>0,07</t>
-  </si>
-  <si>
-    <t>44,86</t>
-  </si>
-  <si>
-    <t>0,49</t>
-  </si>
-  <si>
-    <t>15,07</t>
-  </si>
-  <si>
-    <t>2,74</t>
+    <t>44,89</t>
+  </si>
+  <si>
+    <t>15,04</t>
+  </si>
+  <si>
+    <t>2,6</t>
   </si>
   <si>
     <t>1871</t>
@@ -832,34 +835,34 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>7,11</t>
+    <t>7,1</t>
   </si>
   <si>
     <t>0,91</t>
   </si>
   <si>
-    <t>9,98</t>
-  </si>
-  <si>
-    <t>6,2</t>
+    <t>9,97</t>
+  </si>
+  <si>
+    <t>6,19</t>
   </si>
   <si>
     <t>1,21</t>
   </si>
   <si>
-    <t>6,96</t>
-  </si>
-  <si>
-    <t>13,62</t>
-  </si>
-  <si>
-    <t>37,67</t>
-  </si>
-  <si>
-    <t>1,82</t>
-  </si>
-  <si>
-    <t>9,53</t>
+    <t>6,95</t>
+  </si>
+  <si>
+    <t>13,6</t>
+  </si>
+  <si>
+    <t>37,76</t>
+  </si>
+  <si>
+    <t>1,81</t>
+  </si>
+  <si>
+    <t>9,52</t>
   </si>
   <si>
     <t>2,87</t>
@@ -871,31 +874,28 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>2,61</t>
-  </si>
-  <si>
-    <t>11,62</t>
-  </si>
-  <si>
-    <t>0,6</t>
-  </si>
-  <si>
-    <t>2,34</t>
-  </si>
-  <si>
-    <t>2,81</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>42,08</t>
+    <t>2,67</t>
+  </si>
+  <si>
+    <t>11,61</t>
+  </si>
+  <si>
+    <t>2,33</t>
+  </si>
+  <si>
+    <t>2,8</t>
+  </si>
+  <si>
+    <t>42,09</t>
   </si>
   <si>
     <t>0,2</t>
   </si>
   <si>
-    <t>25,65</t>
+    <t>8,01</t>
+  </si>
+  <si>
+    <t>25,62</t>
   </si>
   <si>
     <t/>
@@ -1821,16 +1821,16 @@
         <v>93</v>
       </c>
       <c r="C6" s="6">
-        <v>65062</v>
+        <v>66310</v>
       </c>
       <c r="D6" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>94</v>
       </c>
       <c r="F6" s="6">
-        <v>2760</v>
+        <v>2811</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>95</v>
@@ -1848,7 +1848,7 @@
         <v>97</v>
       </c>
       <c r="L6" s="6">
-        <v>13685</v>
+        <v>14103</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>98</v>
@@ -1860,67 +1860,67 @@
         <v>97</v>
       </c>
       <c r="P6" s="6">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="Q6" s="7" t="s">
         <v>99</v>
       </c>
       <c r="R6" s="6">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="S6" s="7" t="s">
         <v>100</v>
       </c>
       <c r="T6" s="6">
-        <v>1527</v>
+        <v>1540</v>
       </c>
       <c r="U6" s="7" t="s">
         <v>101</v>
       </c>
       <c r="V6" s="6">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="W6" s="7" t="s">
         <v>102</v>
       </c>
       <c r="X6" s="6">
-        <v>1888</v>
+        <v>1912</v>
       </c>
       <c r="Y6" s="7" t="s">
         <v>103</v>
       </c>
       <c r="Z6" s="6">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AA6" s="7" t="s">
         <v>104</v>
       </c>
       <c r="AB6" s="6">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="AC6" s="7" t="s">
         <v>105</v>
       </c>
       <c r="AD6" s="6">
-        <v>28354</v>
+        <v>28917</v>
       </c>
       <c r="AE6" s="7" t="s">
         <v>106</v>
       </c>
       <c r="AF6" s="6">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AG6" s="7" t="s">
         <v>107</v>
       </c>
       <c r="AH6" s="6">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AI6" s="7" t="s">
         <v>108</v>
       </c>
       <c r="AJ6" s="6">
-        <v>10614</v>
+        <v>10757</v>
       </c>
       <c r="AK6" s="7" t="s">
         <v>109</v>
@@ -1958,7 +1958,7 @@
         <v>113</v>
       </c>
       <c r="C7" s="9">
-        <v>4748</v>
+        <v>4779</v>
       </c>
       <c r="D7" s="9">
         <v>0</v>
@@ -1967,7 +1967,7 @@
         <v>97</v>
       </c>
       <c r="F7" s="9">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>114</v>
@@ -1985,7 +1985,7 @@
         <v>97</v>
       </c>
       <c r="L7" s="9">
-        <v>1339</v>
+        <v>1357</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>116</v>
@@ -2033,16 +2033,16 @@
         <v>120</v>
       </c>
       <c r="AB7" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC7" s="10" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="AD7" s="9">
-        <v>1888</v>
+        <v>1895</v>
       </c>
       <c r="AE7" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AF7" s="9">
         <v>21</v>
@@ -2054,19 +2054,19 @@
         <v>4</v>
       </c>
       <c r="AI7" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AJ7" s="9">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AK7" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AL7" s="9">
         <v>381</v>
       </c>
       <c r="AM7" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AN7" s="9">
         <v>0</v>
@@ -2089,13 +2089,13 @@
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C8" s="9">
-        <v>1685</v>
+        <v>1699</v>
       </c>
       <c r="D8" s="9">
         <v>0</v>
@@ -2107,7 +2107,7 @@
         <v>112</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
@@ -2122,10 +2122,10 @@
         <v>97</v>
       </c>
       <c r="L8" s="9">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N8" s="9">
         <v>0</v>
@@ -2134,22 +2134,22 @@
         <v>97</v>
       </c>
       <c r="P8" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="R8" s="9">
         <v>15</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="T8" s="9">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="V8" s="9">
         <v>0</v>
@@ -2158,43 +2158,43 @@
         <v>97</v>
       </c>
       <c r="X8" s="9">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Z8" s="9">
         <v>5</v>
       </c>
       <c r="AA8" s="10" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="AB8" s="9">
         <v>3</v>
       </c>
       <c r="AC8" s="10" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="AD8" s="9">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="AE8" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AF8" s="9">
         <v>2</v>
       </c>
       <c r="AG8" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AH8" s="9">
         <v>1</v>
       </c>
       <c r="AI8" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="AJ8" s="9">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AK8" s="10" t="s">
         <v>137</v>
@@ -2221,7 +2221,7 @@
         <v>2</v>
       </c>
       <c r="AS8" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
@@ -2232,7 +2232,7 @@
         <v>140</v>
       </c>
       <c r="C9" s="9">
-        <v>6329</v>
+        <v>6555</v>
       </c>
       <c r="D9" s="9">
         <v>0</v>
@@ -2241,7 +2241,7 @@
         <v>97</v>
       </c>
       <c r="F9" s="9">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>141</v>
@@ -2259,7 +2259,7 @@
         <v>97</v>
       </c>
       <c r="L9" s="9">
-        <v>1246</v>
+        <v>1327</v>
       </c>
       <c r="M9" s="10" t="s">
         <v>143</v>
@@ -2277,7 +2277,7 @@
         <v>97</v>
       </c>
       <c r="R9" s="9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S9" s="10" t="s">
         <v>144</v>
@@ -2289,13 +2289,13 @@
         <v>145</v>
       </c>
       <c r="V9" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W9" s="10" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="X9" s="9">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="Y9" s="10" t="s">
         <v>146</v>
@@ -2313,7 +2313,7 @@
         <v>97</v>
       </c>
       <c r="AD9" s="9">
-        <v>2788</v>
+        <v>2894</v>
       </c>
       <c r="AE9" s="10" t="s">
         <v>148</v>
@@ -2331,7 +2331,7 @@
         <v>97</v>
       </c>
       <c r="AJ9" s="9">
-        <v>1112</v>
+        <v>1135</v>
       </c>
       <c r="AK9" s="10" t="s">
         <v>150</v>
@@ -2358,7 +2358,7 @@
         <v>4</v>
       </c>
       <c r="AS9" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
@@ -2369,7 +2369,7 @@
         <v>153</v>
       </c>
       <c r="C10" s="9">
-        <v>8017</v>
+        <v>8221</v>
       </c>
       <c r="D10" s="9">
         <v>3</v>
@@ -2378,16 +2378,16 @@
         <v>111</v>
       </c>
       <c r="F10" s="9">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="H10" s="9">
         <v>25</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J10" s="9">
         <v>0</v>
@@ -2396,10 +2396,10 @@
         <v>97</v>
       </c>
       <c r="L10" s="9">
-        <v>2110</v>
+        <v>2180</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N10" s="9">
         <v>1</v>
@@ -2411,73 +2411,73 @@
         <v>20</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="R10" s="9">
         <v>79</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="T10" s="9">
         <v>185</v>
       </c>
       <c r="U10" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V10" s="9">
         <v>18</v>
       </c>
       <c r="W10" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="X10" s="9">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Z10" s="9">
         <v>23</v>
       </c>
       <c r="AA10" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AB10" s="9">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AC10" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD10" s="9">
-        <v>3447</v>
+        <v>3535</v>
       </c>
       <c r="AE10" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AF10" s="9">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG10" s="10" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="AH10" s="9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI10" s="10" t="s">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="AJ10" s="9">
-        <v>1254</v>
+        <v>1287</v>
       </c>
       <c r="AK10" s="10" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="AL10" s="9">
         <v>119</v>
       </c>
       <c r="AM10" s="10" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AN10" s="9">
         <v>1</v>
@@ -2500,31 +2500,31 @@
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C11" s="9">
-        <v>6379</v>
+        <v>6390</v>
       </c>
       <c r="D11" s="9">
         <v>2</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>168</v>
+        <v>108</v>
       </c>
       <c r="F11" s="9">
         <v>267</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H11" s="9">
         <v>6</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="J11" s="9">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>97</v>
       </c>
       <c r="L11" s="9">
-        <v>1426</v>
+        <v>1430</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N11" s="9">
         <v>0</v>
@@ -2548,7 +2548,7 @@
         <v>15</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>105</v>
+        <v>174</v>
       </c>
       <c r="R11" s="9">
         <v>28</v>
@@ -2560,10 +2560,10 @@
         <v>381</v>
       </c>
       <c r="U11" s="10" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="V11" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W11" s="10" t="s">
         <v>108</v>
@@ -2578,25 +2578,25 @@
         <v>29</v>
       </c>
       <c r="AA11" s="10" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AB11" s="9">
         <v>9</v>
       </c>
       <c r="AC11" s="10" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AD11" s="9">
-        <v>2874</v>
+        <v>2879</v>
       </c>
       <c r="AE11" s="10" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="AF11" s="9">
         <v>73</v>
       </c>
       <c r="AG11" s="10" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AH11" s="9">
         <v>0</v>
@@ -2605,16 +2605,16 @@
         <v>97</v>
       </c>
       <c r="AJ11" s="9">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="AK11" s="10" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AL11" s="9">
         <v>39</v>
       </c>
       <c r="AM11" s="10" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="AN11" s="9">
         <v>0</v>
@@ -2632,18 +2632,18 @@
         <v>2</v>
       </c>
       <c r="AS11" s="10" t="s">
-        <v>168</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C12" s="9">
-        <v>5884</v>
+        <v>5891</v>
       </c>
       <c r="D12" s="9">
         <v>0</v>
@@ -2655,13 +2655,13 @@
         <v>152</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="H12" s="9">
         <v>135</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J12" s="9">
         <v>0</v>
@@ -2670,10 +2670,10 @@
         <v>97</v>
       </c>
       <c r="L12" s="9">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="N12" s="9">
         <v>0</v>
@@ -2697,7 +2697,7 @@
         <v>135</v>
       </c>
       <c r="U12" s="10" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="V12" s="9">
         <v>0</v>
@@ -2709,13 +2709,13 @@
         <v>145</v>
       </c>
       <c r="Y12" s="10" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Z12" s="9">
         <v>33</v>
       </c>
       <c r="AA12" s="10" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="AB12" s="9">
         <v>0</v>
@@ -2724,16 +2724,16 @@
         <v>97</v>
       </c>
       <c r="AD12" s="9">
-        <v>2611</v>
+        <v>2614</v>
       </c>
       <c r="AE12" s="10" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="AF12" s="9">
         <v>46</v>
       </c>
       <c r="AG12" s="10" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="AH12" s="9">
         <v>0</v>
@@ -2742,16 +2742,16 @@
         <v>97</v>
       </c>
       <c r="AJ12" s="9">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="AK12" s="10" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AL12" s="9">
         <v>757</v>
       </c>
       <c r="AM12" s="10" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AN12" s="9">
         <v>0</v>
@@ -2769,18 +2769,18 @@
         <v>7</v>
       </c>
       <c r="AS12" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C13" s="9">
-        <v>3324</v>
+        <v>3387</v>
       </c>
       <c r="D13" s="9">
         <v>0</v>
@@ -2792,13 +2792,13 @@
         <v>144</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H13" s="9">
         <v>2</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="J13" s="9">
         <v>0</v>
@@ -2807,46 +2807,46 @@
         <v>97</v>
       </c>
       <c r="L13" s="9">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="N13" s="9">
         <v>1</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>168</v>
+        <v>108</v>
       </c>
       <c r="P13" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="R13" s="9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="T13" s="9">
         <v>82</v>
       </c>
       <c r="U13" s="10" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="V13" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" s="10" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="X13" s="9">
         <v>99</v>
       </c>
       <c r="Y13" s="10" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Z13" s="9">
         <v>14</v>
@@ -2855,40 +2855,40 @@
         <v>138</v>
       </c>
       <c r="AB13" s="9">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AC13" s="10" t="s">
-        <v>97</v>
+        <v>200</v>
       </c>
       <c r="AD13" s="9">
-        <v>1371</v>
+        <v>1382</v>
       </c>
       <c r="AE13" s="10" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="AF13" s="9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG13" s="10" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="AH13" s="9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI13" s="10" t="s">
-        <v>97</v>
+        <v>172</v>
       </c>
       <c r="AJ13" s="9">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="AK13" s="10" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="AL13" s="9">
         <v>39</v>
       </c>
       <c r="AM13" s="10" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="AN13" s="9">
         <v>0</v>
@@ -2911,13 +2911,13 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C14" s="9">
-        <v>2263</v>
+        <v>2370</v>
       </c>
       <c r="D14" s="9">
         <v>0</v>
@@ -2926,16 +2926,16 @@
         <v>97</v>
       </c>
       <c r="F14" s="9">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="H14" s="9">
         <v>17</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="J14" s="9">
         <v>0</v>
@@ -2944,10 +2944,10 @@
         <v>97</v>
       </c>
       <c r="L14" s="9">
-        <v>500</v>
+        <v>553</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="N14" s="9">
         <v>1</v>
@@ -2956,40 +2956,40 @@
         <v>111</v>
       </c>
       <c r="P14" s="9">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>205</v>
+        <v>155</v>
       </c>
       <c r="R14" s="9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="T14" s="9">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="U14" s="10" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="V14" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W14" s="10" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="X14" s="9">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y14" s="10" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Z14" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA14" s="10" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="AB14" s="9">
         <v>0</v>
@@ -2998,16 +2998,16 @@
         <v>97</v>
       </c>
       <c r="AD14" s="9">
-        <v>1045</v>
+        <v>1091</v>
       </c>
       <c r="AE14" s="10" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="AF14" s="9">
         <v>2</v>
       </c>
       <c r="AG14" s="10" t="s">
-        <v>170</v>
+        <v>123</v>
       </c>
       <c r="AH14" s="9">
         <v>0</v>
@@ -3016,16 +3016,16 @@
         <v>97</v>
       </c>
       <c r="AJ14" s="9">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="AK14" s="10" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AL14" s="9">
         <v>99</v>
       </c>
       <c r="AM14" s="10" t="s">
-        <v>212</v>
+        <v>171</v>
       </c>
       <c r="AN14" s="9">
         <v>0</v>
@@ -3043,36 +3043,36 @@
         <v>2</v>
       </c>
       <c r="AS14" s="10" t="s">
-        <v>170</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C15" s="9">
-        <v>7725</v>
+        <v>7731</v>
       </c>
       <c r="D15" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F15" s="9">
         <v>255</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H15" s="9">
         <v>88</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J15" s="9">
         <v>0</v>
@@ -3084,7 +3084,7 @@
         <v>1041</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N15" s="9">
         <v>0</v>
@@ -3096,37 +3096,37 @@
         <v>4</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="R15" s="9">
         <v>78</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="T15" s="9">
         <v>109</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>162</v>
+        <v>221</v>
       </c>
       <c r="V15" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="X15" s="9">
         <v>99</v>
       </c>
       <c r="Y15" s="10" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Z15" s="9">
         <v>10</v>
       </c>
       <c r="AA15" s="10" t="s">
-        <v>220</v>
+        <v>99</v>
       </c>
       <c r="AB15" s="9">
         <v>0</v>
@@ -3135,34 +3135,34 @@
         <v>97</v>
       </c>
       <c r="AD15" s="9">
-        <v>3140</v>
+        <v>3141</v>
       </c>
       <c r="AE15" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AF15" s="9">
         <v>66</v>
       </c>
       <c r="AG15" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AH15" s="9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI15" s="10" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="AJ15" s="9">
         <v>1136</v>
       </c>
       <c r="AK15" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AL15" s="9">
         <v>1696</v>
       </c>
       <c r="AM15" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN15" s="9">
         <v>0</v>
@@ -3185,13 +3185,13 @@
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C16" s="9">
-        <v>2250</v>
+        <v>2260</v>
       </c>
       <c r="D16" s="9">
         <v>0</v>
@@ -3203,13 +3203,13 @@
         <v>112</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H16" s="9">
         <v>6</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J16" s="9">
         <v>0</v>
@@ -3218,10 +3218,10 @@
         <v>97</v>
       </c>
       <c r="L16" s="9">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N16" s="9">
         <v>0</v>
@@ -3239,13 +3239,13 @@
         <v>30</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="T16" s="9">
         <v>112</v>
       </c>
       <c r="U16" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="V16" s="9">
         <v>0</v>
@@ -3254,34 +3254,34 @@
         <v>97</v>
       </c>
       <c r="X16" s="9">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Y16" s="10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Z16" s="9">
         <v>20</v>
       </c>
       <c r="AA16" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AB16" s="9">
         <v>4</v>
       </c>
       <c r="AC16" s="10" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="AD16" s="9">
-        <v>977</v>
+        <v>982</v>
       </c>
       <c r="AE16" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AF16" s="9">
         <v>35</v>
       </c>
       <c r="AG16" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AH16" s="9">
         <v>1</v>
@@ -3290,16 +3290,16 @@
         <v>111</v>
       </c>
       <c r="AJ16" s="9">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AK16" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AL16" s="9">
         <v>57</v>
       </c>
       <c r="AM16" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AN16" s="9">
         <v>0</v>
@@ -3317,36 +3317,36 @@
         <v>2</v>
       </c>
       <c r="AS16" s="10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C17" s="9">
-        <v>4038</v>
+        <v>4278</v>
       </c>
       <c r="D17" s="9">
         <v>1</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>108</v>
+        <v>240</v>
       </c>
       <c r="F17" s="9">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="H17" s="9">
         <v>26</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>239</v>
+        <v>181</v>
       </c>
       <c r="J17" s="9">
         <v>0</v>
@@ -3355,10 +3355,10 @@
         <v>97</v>
       </c>
       <c r="L17" s="9">
-        <v>925</v>
+        <v>995</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N17" s="9">
         <v>0</v>
@@ -3370,73 +3370,73 @@
         <v>22</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>104</v>
+        <v>243</v>
       </c>
       <c r="R17" s="9">
         <v>29</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="T17" s="9">
         <v>30</v>
       </c>
       <c r="U17" s="10" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="V17" s="9">
         <v>9</v>
       </c>
       <c r="W17" s="10" t="s">
-        <v>159</v>
+        <v>246</v>
       </c>
       <c r="X17" s="9">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="Y17" s="10" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Z17" s="9">
         <v>2</v>
       </c>
       <c r="AA17" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AB17" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC17" s="10" t="s">
-        <v>217</v>
+        <v>172</v>
       </c>
       <c r="AD17" s="9">
-        <v>2000</v>
+        <v>2126</v>
       </c>
       <c r="AE17" s="10" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AF17" s="9">
         <v>42</v>
       </c>
       <c r="AG17" s="10" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AH17" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI17" s="10" t="s">
-        <v>217</v>
+        <v>166</v>
       </c>
       <c r="AJ17" s="9">
-        <v>473</v>
+        <v>497</v>
       </c>
       <c r="AK17" s="10" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="AL17" s="9">
         <v>220</v>
       </c>
       <c r="AM17" s="10" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="AN17" s="9">
         <v>0</v>
@@ -3459,13 +3459,13 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C18" s="9">
-        <v>4928</v>
+        <v>4970</v>
       </c>
       <c r="D18" s="9">
         <v>0</v>
@@ -3474,16 +3474,16 @@
         <v>97</v>
       </c>
       <c r="F18" s="9">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H18" s="9">
         <v>6</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J18" s="9">
         <v>0</v>
@@ -3492,10 +3492,10 @@
         <v>97</v>
       </c>
       <c r="L18" s="9">
-        <v>1122</v>
+        <v>1131</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="N18" s="9">
         <v>0</v>
@@ -3507,19 +3507,19 @@
         <v>8</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="R18" s="9">
         <v>20</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="T18" s="9">
         <v>80</v>
       </c>
       <c r="U18" s="10" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="V18" s="9">
         <v>2</v>
@@ -3531,31 +3531,31 @@
         <v>91</v>
       </c>
       <c r="Y18" s="10" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Z18" s="9">
         <v>14</v>
       </c>
       <c r="AA18" s="10" t="s">
-        <v>256</v>
+        <v>162</v>
       </c>
       <c r="AB18" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC18" s="10" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="AD18" s="9">
-        <v>2236</v>
+        <v>2263</v>
       </c>
       <c r="AE18" s="10" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AF18" s="9">
         <v>12</v>
       </c>
       <c r="AG18" s="10" t="s">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c r="AH18" s="9">
         <v>0</v>
@@ -3564,16 +3564,16 @@
         <v>97</v>
       </c>
       <c r="AJ18" s="9">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="AK18" s="10" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AL18" s="9">
         <v>43</v>
       </c>
       <c r="AM18" s="10" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AN18" s="9">
         <v>0</v>
@@ -3596,13 +3596,13 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C19" s="9">
-        <v>5334</v>
+        <v>5618</v>
       </c>
       <c r="D19" s="9">
         <v>0</v>
@@ -3611,16 +3611,16 @@
         <v>97</v>
       </c>
       <c r="F19" s="9">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="H19" s="9">
         <v>18</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="J19" s="9">
         <v>0</v>
@@ -3629,10 +3629,10 @@
         <v>97</v>
       </c>
       <c r="L19" s="9">
-        <v>1493</v>
+        <v>1592</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="N19" s="9">
         <v>0</v>
@@ -3650,13 +3650,13 @@
         <v>18</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="T19" s="9">
         <v>17</v>
       </c>
       <c r="U19" s="10" t="s">
-        <v>265</v>
+        <v>155</v>
       </c>
       <c r="V19" s="9">
         <v>0</v>
@@ -3665,16 +3665,16 @@
         <v>97</v>
       </c>
       <c r="X19" s="9">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="Y19" s="10" t="s">
-        <v>215</v>
+        <v>268</v>
       </c>
       <c r="Z19" s="9">
         <v>4</v>
       </c>
       <c r="AA19" s="10" t="s">
-        <v>266</v>
+        <v>166</v>
       </c>
       <c r="AB19" s="9">
         <v>0</v>
@@ -3683,16 +3683,16 @@
         <v>97</v>
       </c>
       <c r="AD19" s="9">
-        <v>2393</v>
+        <v>2522</v>
       </c>
       <c r="AE19" s="10" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AF19" s="9">
         <v>26</v>
       </c>
       <c r="AG19" s="10" t="s">
-        <v>268</v>
+        <v>118</v>
       </c>
       <c r="AH19" s="9">
         <v>0</v>
@@ -3701,16 +3701,16 @@
         <v>97</v>
       </c>
       <c r="AJ19" s="9">
-        <v>804</v>
+        <v>845</v>
       </c>
       <c r="AK19" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL19" s="9">
         <v>146</v>
       </c>
       <c r="AM19" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AN19" s="9">
         <v>0</v>
@@ -3733,13 +3733,13 @@
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C20" s="9">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D20" s="9">
         <v>0</v>
@@ -3751,13 +3751,13 @@
         <v>47</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H20" s="9">
         <v>6</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J20" s="9">
         <v>0</v>
@@ -3769,7 +3769,7 @@
         <v>66</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N20" s="9">
         <v>0</v>
@@ -3793,25 +3793,25 @@
         <v>41</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="V20" s="9">
         <v>8</v>
       </c>
       <c r="W20" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="X20" s="9">
         <v>46</v>
       </c>
       <c r="Y20" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Z20" s="9">
         <v>90</v>
       </c>
       <c r="AA20" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AB20" s="9">
         <v>4</v>
@@ -3820,16 +3820,16 @@
         <v>96</v>
       </c>
       <c r="AD20" s="9">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AE20" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AF20" s="9">
         <v>12</v>
       </c>
       <c r="AG20" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AH20" s="9">
         <v>0</v>
@@ -3841,13 +3841,13 @@
         <v>63</v>
       </c>
       <c r="AK20" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AL20" s="9">
         <v>19</v>
       </c>
       <c r="AM20" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN20" s="9">
         <v>0</v>
@@ -3865,18 +3865,18 @@
         <v>2</v>
       </c>
       <c r="AS20" s="10" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C21" s="9">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="D21" s="9">
         <v>0</v>
@@ -3885,16 +3885,16 @@
         <v>97</v>
       </c>
       <c r="F21" s="9">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H21" s="9">
         <v>6</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>208</v>
+        <v>257</v>
       </c>
       <c r="J21" s="9">
         <v>0</v>
@@ -3906,7 +3906,7 @@
         <v>174</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N21" s="9">
         <v>0</v>
@@ -3924,7 +3924,7 @@
         <v>9</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>288</v>
+        <v>96</v>
       </c>
       <c r="T21" s="9">
         <v>35</v>
@@ -3936,7 +3936,7 @@
         <v>1</v>
       </c>
       <c r="W21" s="10" t="s">
-        <v>266</v>
+        <v>166</v>
       </c>
       <c r="X21" s="9">
         <v>42</v>
@@ -3948,25 +3948,25 @@
         <v>39</v>
       </c>
       <c r="AA21" s="10" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="AB21" s="9">
         <v>15</v>
       </c>
       <c r="AC21" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="AD21" s="9">
+        <v>631</v>
+      </c>
+      <c r="AE21" s="10" t="s">
         <v>291</v>
-      </c>
-      <c r="AD21" s="9">
-        <v>630</v>
-      </c>
-      <c r="AE21" s="10" t="s">
-        <v>292</v>
       </c>
       <c r="AF21" s="9">
         <v>3</v>
       </c>
       <c r="AG21" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AH21" s="9">
         <v>0</v>
@@ -3978,7 +3978,7 @@
         <v>120</v>
       </c>
       <c r="AK21" s="10" t="s">
-        <v>124</v>
+        <v>293</v>
       </c>
       <c r="AL21" s="9">
         <v>384</v>
@@ -4013,16 +4013,16 @@
         <v>296</v>
       </c>
       <c r="C22" s="12">
-        <v>65062</v>
+        <v>66310</v>
       </c>
       <c r="D22" s="12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>94</v>
       </c>
       <c r="F22" s="12">
-        <v>2760</v>
+        <v>2811</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>95</v>
@@ -4040,7 +4040,7 @@
         <v>97</v>
       </c>
       <c r="L22" s="12">
-        <v>13685</v>
+        <v>14103</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>98</v>
@@ -4052,67 +4052,67 @@
         <v>97</v>
       </c>
       <c r="P22" s="12">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="Q22" s="13" t="s">
         <v>99</v>
       </c>
       <c r="R22" s="12">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="S22" s="13" t="s">
         <v>100</v>
       </c>
       <c r="T22" s="12">
-        <v>1527</v>
+        <v>1540</v>
       </c>
       <c r="U22" s="13" t="s">
         <v>101</v>
       </c>
       <c r="V22" s="12">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="W22" s="13" t="s">
         <v>102</v>
       </c>
       <c r="X22" s="12">
-        <v>1888</v>
+        <v>1912</v>
       </c>
       <c r="Y22" s="13" t="s">
         <v>103</v>
       </c>
       <c r="Z22" s="12">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AA22" s="13" t="s">
         <v>104</v>
       </c>
       <c r="AB22" s="12">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="AC22" s="13" t="s">
         <v>105</v>
       </c>
       <c r="AD22" s="12">
-        <v>28354</v>
+        <v>28917</v>
       </c>
       <c r="AE22" s="13" t="s">
         <v>106</v>
       </c>
       <c r="AF22" s="12">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AG22" s="13" t="s">
         <v>107</v>
       </c>
       <c r="AH22" s="12">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AI22" s="13" t="s">
         <v>108</v>
       </c>
       <c r="AJ22" s="12">
-        <v>10614</v>
+        <v>10757</v>
       </c>
       <c r="AK22" s="13" t="s">
         <v>109</v>

--- a/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
+++ b/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="295">
   <si>
     <t>DATA RADAR ANOMALI KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 4 Sep 2026, 08.16</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 5 Sep 2026, 06.52</t>
   </si>
   <si>
     <t>Kode</t>
@@ -298,604 +298,598 @@
     <t>0,01</t>
   </si>
   <si>
-    <t>4,24</t>
+    <t>4,21</t>
+  </si>
+  <si>
+    <t>0,59</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>21,11</t>
+  </si>
+  <si>
+    <t>0,13</t>
+  </si>
+  <si>
+    <t>0,64</t>
+  </si>
+  <si>
+    <t>2,31</t>
+  </si>
+  <si>
+    <t>0,1</t>
+  </si>
+  <si>
+    <t>2,86</t>
+  </si>
+  <si>
+    <t>0,53</t>
+  </si>
+  <si>
+    <t>0,32</t>
+  </si>
+  <si>
+    <t>43,83</t>
+  </si>
+  <si>
+    <t>0,93</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>16,26</t>
+  </si>
+  <si>
+    <t>6,1</t>
+  </si>
+  <si>
+    <t>0,04</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>LAMPUNG BARAT</t>
+  </si>
+  <si>
+    <t>4,23</t>
+  </si>
+  <si>
+    <t>0,67</t>
+  </si>
+  <si>
+    <t>28,4</t>
+  </si>
+  <si>
+    <t>0,17</t>
+  </si>
+  <si>
+    <t>0,46</t>
+  </si>
+  <si>
+    <t>4,12</t>
+  </si>
+  <si>
+    <t>0,44</t>
+  </si>
+  <si>
+    <t>39,65</t>
+  </si>
+  <si>
+    <t>0,08</t>
+  </si>
+  <si>
+    <t>12,81</t>
+  </si>
+  <si>
+    <t>7,97</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>TANGGAMUS</t>
+  </si>
+  <si>
+    <t>6,56</t>
+  </si>
+  <si>
+    <t>19,68</t>
+  </si>
+  <si>
+    <t>0,06</t>
+  </si>
+  <si>
+    <t>0,88</t>
+  </si>
+  <si>
+    <t>3,46</t>
+  </si>
+  <si>
+    <t>3,22</t>
+  </si>
+  <si>
+    <t>0,29</t>
+  </si>
+  <si>
+    <t>0,18</t>
+  </si>
+  <si>
+    <t>42,06</t>
+  </si>
+  <si>
+    <t>0,12</t>
+  </si>
+  <si>
+    <t>22,91</t>
+  </si>
+  <si>
+    <t>0,41</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>LAMPUNG SELATAN</t>
+  </si>
+  <si>
+    <t>5,7</t>
+  </si>
+  <si>
+    <t>0,33</t>
+  </si>
+  <si>
+    <t>20,06</t>
+  </si>
+  <si>
+    <t>0,51</t>
+  </si>
+  <si>
+    <t>2,92</t>
+  </si>
+  <si>
+    <t>3,28</t>
+  </si>
+  <si>
+    <t>0,68</t>
+  </si>
+  <si>
+    <t>44,39</t>
+  </si>
+  <si>
+    <t>3,61</t>
+  </si>
+  <si>
+    <t>17,43</t>
+  </si>
+  <si>
+    <t>1,03</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>LAMPUNG TIMUR</t>
+  </si>
+  <si>
+    <t>4,06</t>
+  </si>
+  <si>
+    <t>0,3</t>
+  </si>
+  <si>
+    <t>25,96</t>
+  </si>
+  <si>
+    <t>0,24</t>
+  </si>
+  <si>
+    <t>0,94</t>
+  </si>
+  <si>
+    <t>2,2</t>
+  </si>
+  <si>
+    <t>0,21</t>
+  </si>
+  <si>
+    <t>3,04</t>
+  </si>
+  <si>
+    <t>0,27</t>
+  </si>
+  <si>
+    <t>1,32</t>
+  </si>
+  <si>
+    <t>43,69</t>
+  </si>
+  <si>
+    <t>0,35</t>
+  </si>
+  <si>
+    <t>0,07</t>
+  </si>
+  <si>
+    <t>15,83</t>
+  </si>
+  <si>
+    <t>1,42</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>LAMPUNG TENGAH</t>
+  </si>
+  <si>
+    <t>4,17</t>
+  </si>
+  <si>
+    <t>0,09</t>
+  </si>
+  <si>
+    <t>22,34</t>
+  </si>
+  <si>
+    <t>0,23</t>
+  </si>
+  <si>
+    <t>5,95</t>
+  </si>
+  <si>
+    <t>4,22</t>
+  </si>
+  <si>
+    <t>0,45</t>
+  </si>
+  <si>
+    <t>0,14</t>
+  </si>
+  <si>
+    <t>45,13</t>
+  </si>
+  <si>
+    <t>1,14</t>
+  </si>
+  <si>
+    <t>14,98</t>
+  </si>
+  <si>
+    <t>0,61</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>2,58</t>
+  </si>
+  <si>
+    <t>2,29</t>
+  </si>
+  <si>
+    <t>14,46</t>
+  </si>
+  <si>
+    <t>2,46</t>
+  </si>
+  <si>
+    <t>0,56</t>
+  </si>
+  <si>
+    <t>44,45</t>
+  </si>
+  <si>
+    <t>0,78</t>
+  </si>
+  <si>
+    <t>16,75</t>
+  </si>
+  <si>
+    <t>12,83</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
+    <t>4,2</t>
+  </si>
+  <si>
+    <t>20,12</t>
+  </si>
+  <si>
+    <t>0,58</t>
+  </si>
+  <si>
+    <t>2,39</t>
+  </si>
+  <si>
+    <t>2,89</t>
+  </si>
+  <si>
+    <t>1,81</t>
+  </si>
+  <si>
+    <t>40,54</t>
+  </si>
+  <si>
+    <t>25,28</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG</t>
+  </si>
+  <si>
+    <t>4,38</t>
+  </si>
+  <si>
+    <t>0,72</t>
+  </si>
+  <si>
+    <t>23,27</t>
+  </si>
+  <si>
+    <t>1,18</t>
+  </si>
+  <si>
+    <t>2,48</t>
+  </si>
+  <si>
+    <t>0,25</t>
+  </si>
+  <si>
+    <t>2,15</t>
+  </si>
+  <si>
+    <t>46,13</t>
+  </si>
+  <si>
+    <t>14,69</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PESAWARAN</t>
+  </si>
+  <si>
+    <t>3,3</t>
+  </si>
+  <si>
+    <t>13,47</t>
+  </si>
+  <si>
+    <t>0,05</t>
+  </si>
+  <si>
+    <t>1,01</t>
+  </si>
+  <si>
+    <t>1,41</t>
+  </si>
+  <si>
+    <t>1,28</t>
+  </si>
+  <si>
+    <t>40,66</t>
+  </si>
+  <si>
+    <t>0,85</t>
+  </si>
+  <si>
+    <t>14,7</t>
+  </si>
+  <si>
+    <t>21,95</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>PRINGSEWU</t>
+  </si>
+  <si>
+    <t>4,96</t>
+  </si>
+  <si>
+    <t>16,73</t>
+  </si>
+  <si>
+    <t>1,33</t>
+  </si>
+  <si>
+    <t>4,03</t>
+  </si>
+  <si>
+    <t>43,45</t>
+  </si>
+  <si>
+    <t>1,55</t>
+  </si>
+  <si>
+    <t>18,98</t>
+  </si>
+  <si>
+    <t>2,52</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
+  </si>
+  <si>
+    <t>0,02</t>
+  </si>
+  <si>
+    <t>4,57</t>
   </si>
   <si>
     <t>0,6</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>21,27</t>
-  </si>
-  <si>
-    <t>0,13</t>
-  </si>
-  <si>
-    <t>0,64</t>
-  </si>
-  <si>
-    <t>2,32</t>
-  </si>
-  <si>
-    <t>0,11</t>
-  </si>
-  <si>
-    <t>2,88</t>
-  </si>
-  <si>
-    <t>0,53</t>
-  </si>
-  <si>
-    <t>0,29</t>
-  </si>
-  <si>
-    <t>43,61</t>
-  </si>
-  <si>
-    <t>0,94</t>
-  </si>
-  <si>
-    <t>0,03</t>
-  </si>
-  <si>
-    <t>16,22</t>
-  </si>
-  <si>
-    <t>6,14</t>
-  </si>
-  <si>
-    <t>0,04</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>LAMPUNG BARAT</t>
-  </si>
-  <si>
-    <t>4,23</t>
-  </si>
-  <si>
-    <t>0,67</t>
-  </si>
-  <si>
-    <t>28,4</t>
-  </si>
-  <si>
-    <t>0,17</t>
-  </si>
-  <si>
-    <t>0,46</t>
-  </si>
-  <si>
-    <t>4,12</t>
-  </si>
-  <si>
-    <t>0,44</t>
-  </si>
-  <si>
-    <t>0,1</t>
-  </si>
-  <si>
-    <t>39,65</t>
-  </si>
-  <si>
-    <t>0,08</t>
-  </si>
-  <si>
-    <t>12,81</t>
-  </si>
-  <si>
-    <t>7,97</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>TANGGAMUS</t>
-  </si>
-  <si>
-    <t>6,59</t>
-  </si>
-  <si>
-    <t>19,78</t>
-  </si>
-  <si>
-    <t>0,06</t>
-  </si>
-  <si>
-    <t>0,88</t>
-  </si>
-  <si>
-    <t>3,47</t>
-  </si>
-  <si>
-    <t>3,24</t>
-  </si>
-  <si>
-    <t>0,18</t>
-  </si>
-  <si>
-    <t>41,91</t>
-  </si>
-  <si>
-    <t>0,12</t>
-  </si>
-  <si>
-    <t>22,9</t>
-  </si>
-  <si>
-    <t>0,41</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>LAMPUNG SELATAN</t>
-  </si>
-  <si>
-    <t>5,75</t>
-  </si>
-  <si>
-    <t>0,34</t>
-  </si>
-  <si>
-    <t>20,24</t>
-  </si>
-  <si>
-    <t>0,52</t>
-  </si>
-  <si>
-    <t>2,94</t>
-  </si>
-  <si>
-    <t>3,31</t>
+    <t>22,96</t>
   </si>
   <si>
     <t>0,69</t>
   </si>
   <si>
-    <t>44,15</t>
-  </si>
-  <si>
-    <t>3,65</t>
-  </si>
-  <si>
-    <t>17,32</t>
-  </si>
-  <si>
-    <t>1,04</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>LAMPUNG TIMUR</t>
-  </si>
-  <si>
-    <t>4,15</t>
-  </si>
-  <si>
-    <t>0,3</t>
-  </si>
-  <si>
-    <t>26,52</t>
-  </si>
-  <si>
-    <t>0,24</t>
-  </si>
-  <si>
-    <t>0,96</t>
-  </si>
-  <si>
-    <t>2,25</t>
-  </si>
-  <si>
-    <t>0,22</t>
-  </si>
-  <si>
-    <t>3,1</t>
+    <t>1,71</t>
+  </si>
+  <si>
+    <t>50,23</t>
+  </si>
+  <si>
+    <t>0,97</t>
+  </si>
+  <si>
+    <t>11,58</t>
+  </si>
+  <si>
+    <t>5,08</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG BARAT</t>
+  </si>
+  <si>
+    <t>22,56</t>
+  </si>
+  <si>
+    <t>0,16</t>
+  </si>
+  <si>
+    <t>0,42</t>
+  </si>
+  <si>
+    <t>1,62</t>
   </si>
   <si>
     <t>0,28</t>
   </si>
   <si>
-    <t>1,35</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>0,35</t>
-  </si>
-  <si>
-    <t>0,07</t>
-  </si>
-  <si>
-    <t>15,66</t>
-  </si>
-  <si>
-    <t>1,45</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>LAMPUNG TENGAH</t>
-  </si>
-  <si>
-    <t>4,18</t>
-  </si>
-  <si>
-    <t>0,09</t>
-  </si>
-  <si>
-    <t>22,38</t>
-  </si>
-  <si>
-    <t>0,23</t>
-  </si>
-  <si>
-    <t>5,96</t>
-  </si>
-  <si>
-    <t>0,45</t>
-  </si>
-  <si>
-    <t>0,14</t>
-  </si>
-  <si>
-    <t>45,05</t>
-  </si>
-  <si>
-    <t>1,14</t>
-  </si>
-  <si>
-    <t>14,99</t>
-  </si>
-  <si>
-    <t>0,61</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
-  </si>
-  <si>
-    <t>2,58</t>
-  </si>
-  <si>
-    <t>2,29</t>
-  </si>
-  <si>
-    <t>14,48</t>
-  </si>
-  <si>
-    <t>2,46</t>
-  </si>
-  <si>
-    <t>0,56</t>
-  </si>
-  <si>
-    <t>44,37</t>
-  </si>
-  <si>
-    <t>0,78</t>
-  </si>
-  <si>
-    <t>16,77</t>
-  </si>
-  <si>
-    <t>12,85</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>4,25</t>
-  </si>
-  <si>
-    <t>20,37</t>
-  </si>
-  <si>
-    <t>0,59</t>
-  </si>
-  <si>
-    <t>2,42</t>
-  </si>
-  <si>
-    <t>2,92</t>
+    <t>45,65</t>
+  </si>
+  <si>
+    <t>22,02</t>
+  </si>
+  <si>
+    <t>0,86</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>PESISIR BARAT</t>
+  </si>
+  <si>
+    <t>4,35</t>
+  </si>
+  <si>
+    <t>27,95</t>
+  </si>
+  <si>
+    <t>3,16</t>
+  </si>
+  <si>
+    <t>45,3</t>
+  </si>
+  <si>
+    <t>15,17</t>
+  </si>
+  <si>
+    <t>2,56</t>
+  </si>
+  <si>
+    <t>1871</t>
+  </si>
+  <si>
+    <t>BANDAR LAMPUNG</t>
+  </si>
+  <si>
+    <t>6,85</t>
+  </si>
+  <si>
+    <t>0,87</t>
+  </si>
+  <si>
+    <t>9,62</t>
+  </si>
+  <si>
+    <t>5,98</t>
+  </si>
+  <si>
+    <t>1,17</t>
+  </si>
+  <si>
+    <t>6,71</t>
+  </si>
+  <si>
+    <t>13,12</t>
+  </si>
+  <si>
+    <t>39,8</t>
+  </si>
+  <si>
+    <t>1,75</t>
+  </si>
+  <si>
+    <t>9,33</t>
+  </si>
+  <si>
+    <t>2,77</t>
+  </si>
+  <si>
+    <t>1872</t>
+  </si>
+  <si>
+    <t>METRO</t>
+  </si>
+  <si>
+    <t>2,67</t>
+  </si>
+  <si>
+    <t>0,4</t>
+  </si>
+  <si>
+    <t>11,6</t>
+  </si>
+  <si>
+    <t>2,33</t>
+  </si>
+  <si>
+    <t>2,8</t>
+  </si>
+  <si>
+    <t>2,6</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>40,8</t>
-  </si>
-  <si>
-    <t>25,45</t>
-  </si>
-  <si>
-    <t>1,15</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG</t>
-  </si>
-  <si>
-    <t>4,39</t>
-  </si>
-  <si>
-    <t>0,72</t>
-  </si>
-  <si>
-    <t>23,33</t>
-  </si>
-  <si>
-    <t>1,18</t>
-  </si>
-  <si>
-    <t>2,49</t>
-  </si>
-  <si>
-    <t>0,25</t>
-  </si>
-  <si>
-    <t>2,15</t>
-  </si>
-  <si>
-    <t>46,03</t>
-  </si>
-  <si>
-    <t>14,68</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>PESAWARAN</t>
-  </si>
-  <si>
-    <t>3,3</t>
-  </si>
-  <si>
-    <t>13,47</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>1,01</t>
-  </si>
-  <si>
-    <t>1,41</t>
-  </si>
-  <si>
-    <t>1,28</t>
-  </si>
-  <si>
-    <t>40,63</t>
-  </si>
-  <si>
-    <t>0,85</t>
-  </si>
-  <si>
-    <t>14,69</t>
-  </si>
-  <si>
-    <t>21,94</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>PRINGSEWU</t>
-  </si>
-  <si>
-    <t>4,96</t>
-  </si>
-  <si>
-    <t>0,27</t>
-  </si>
-  <si>
-    <t>16,73</t>
-  </si>
-  <si>
-    <t>1,33</t>
-  </si>
-  <si>
-    <t>4,03</t>
-  </si>
-  <si>
-    <t>43,45</t>
-  </si>
-  <si>
-    <t>1,55</t>
-  </si>
-  <si>
-    <t>18,98</t>
-  </si>
-  <si>
-    <t>2,52</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>0,02</t>
-  </si>
-  <si>
-    <t>4,63</t>
-  </si>
-  <si>
-    <t>23,26</t>
-  </si>
-  <si>
-    <t>0,51</t>
-  </si>
-  <si>
-    <t>0,68</t>
-  </si>
-  <si>
-    <t>0,7</t>
-  </si>
-  <si>
-    <t>0,21</t>
-  </si>
-  <si>
-    <t>1,73</t>
-  </si>
-  <si>
-    <t>49,7</t>
-  </si>
-  <si>
-    <t>0,98</t>
-  </si>
-  <si>
-    <t>11,62</t>
-  </si>
-  <si>
-    <t>5,14</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG BARAT</t>
-  </si>
-  <si>
-    <t>4,27</t>
-  </si>
-  <si>
-    <t>22,76</t>
-  </si>
-  <si>
-    <t>0,16</t>
-  </si>
-  <si>
-    <t>0,4</t>
-  </si>
-  <si>
-    <t>1,61</t>
-  </si>
-  <si>
-    <t>1,83</t>
-  </si>
-  <si>
-    <t>45,53</t>
-  </si>
-  <si>
-    <t>21,89</t>
-  </si>
-  <si>
-    <t>0,87</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>PESISIR BARAT</t>
-  </si>
-  <si>
-    <t>4,41</t>
-  </si>
-  <si>
-    <t>0,32</t>
-  </si>
-  <si>
-    <t>28,34</t>
-  </si>
-  <si>
-    <t>3,2</t>
-  </si>
-  <si>
-    <t>44,89</t>
-  </si>
-  <si>
-    <t>15,04</t>
-  </si>
-  <si>
-    <t>2,6</t>
-  </si>
-  <si>
-    <t>1871</t>
-  </si>
-  <si>
-    <t>BANDAR LAMPUNG</t>
-  </si>
-  <si>
-    <t>7,1</t>
-  </si>
-  <si>
-    <t>0,91</t>
-  </si>
-  <si>
-    <t>9,97</t>
-  </si>
-  <si>
-    <t>6,19</t>
-  </si>
-  <si>
-    <t>1,21</t>
-  </si>
-  <si>
-    <t>6,95</t>
-  </si>
-  <si>
-    <t>13,6</t>
-  </si>
-  <si>
-    <t>37,76</t>
-  </si>
-  <si>
-    <t>1,81</t>
-  </si>
-  <si>
-    <t>9,52</t>
-  </si>
-  <si>
-    <t>2,87</t>
-  </si>
-  <si>
-    <t>1872</t>
-  </si>
-  <si>
-    <t>METRO</t>
-  </si>
-  <si>
-    <t>2,67</t>
-  </si>
-  <si>
-    <t>11,61</t>
-  </si>
-  <si>
-    <t>2,33</t>
-  </si>
-  <si>
-    <t>2,8</t>
-  </si>
-  <si>
-    <t>42,09</t>
+    <t>42,13</t>
   </si>
   <si>
     <t>0,2</t>
   </si>
   <si>
-    <t>8,01</t>
-  </si>
-  <si>
-    <t>25,62</t>
+    <t>8</t>
+  </si>
+  <si>
+    <t>25,6</t>
   </si>
   <si>
     <t/>
@@ -1821,10 +1815,10 @@
         <v>93</v>
       </c>
       <c r="C6" s="6">
-        <v>66310</v>
+        <v>66820</v>
       </c>
       <c r="D6" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>94</v>
@@ -1866,13 +1860,13 @@
         <v>99</v>
       </c>
       <c r="R6" s="6">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="S6" s="7" t="s">
         <v>100</v>
       </c>
       <c r="T6" s="6">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="U6" s="7" t="s">
         <v>101</v>
@@ -1896,13 +1890,13 @@
         <v>104</v>
       </c>
       <c r="AB6" s="6">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="AC6" s="7" t="s">
         <v>105</v>
       </c>
       <c r="AD6" s="6">
-        <v>28917</v>
+        <v>29290</v>
       </c>
       <c r="AE6" s="7" t="s">
         <v>106</v>
@@ -1914,13 +1908,13 @@
         <v>107</v>
       </c>
       <c r="AH6" s="6">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI6" s="7" t="s">
         <v>108</v>
       </c>
       <c r="AJ6" s="6">
-        <v>10757</v>
+        <v>10867</v>
       </c>
       <c r="AK6" s="7" t="s">
         <v>109</v>
@@ -1932,7 +1926,7 @@
         <v>110</v>
       </c>
       <c r="AN6" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO6" s="7" t="s">
         <v>97</v>
@@ -2036,13 +2030,13 @@
         <v>5</v>
       </c>
       <c r="AC7" s="10" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="AD7" s="9">
         <v>1895</v>
       </c>
       <c r="AE7" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AF7" s="9">
         <v>21</v>
@@ -2054,19 +2048,19 @@
         <v>4</v>
       </c>
       <c r="AI7" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AJ7" s="9">
         <v>612</v>
       </c>
       <c r="AK7" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AL7" s="9">
         <v>381</v>
       </c>
       <c r="AM7" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AN7" s="9">
         <v>0</v>
@@ -2089,13 +2083,13 @@
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>127</v>
-      </c>
       <c r="C8" s="9">
-        <v>1699</v>
+        <v>1707</v>
       </c>
       <c r="D8" s="9">
         <v>0</v>
@@ -2107,7 +2101,7 @@
         <v>112</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
@@ -2125,7 +2119,7 @@
         <v>336</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N8" s="9">
         <v>0</v>
@@ -2137,19 +2131,19 @@
         <v>1</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="R8" s="9">
         <v>15</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="T8" s="9">
         <v>59</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="V8" s="9">
         <v>0</v>
@@ -2161,13 +2155,13 @@
         <v>55</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Z8" s="9">
         <v>5</v>
       </c>
       <c r="AA8" s="10" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="AB8" s="9">
         <v>3</v>
@@ -2176,7 +2170,7 @@
         <v>134</v>
       </c>
       <c r="AD8" s="9">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="AE8" s="10" t="s">
         <v>135</v>
@@ -2191,10 +2185,10 @@
         <v>1</v>
       </c>
       <c r="AI8" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AJ8" s="9">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AK8" s="10" t="s">
         <v>137</v>
@@ -2232,7 +2226,7 @@
         <v>140</v>
       </c>
       <c r="C9" s="9">
-        <v>6555</v>
+        <v>6616</v>
       </c>
       <c r="D9" s="9">
         <v>0</v>
@@ -2313,7 +2307,7 @@
         <v>97</v>
       </c>
       <c r="AD9" s="9">
-        <v>2894</v>
+        <v>2937</v>
       </c>
       <c r="AE9" s="10" t="s">
         <v>148</v>
@@ -2331,7 +2325,7 @@
         <v>97</v>
       </c>
       <c r="AJ9" s="9">
-        <v>1135</v>
+        <v>1153</v>
       </c>
       <c r="AK9" s="10" t="s">
         <v>150</v>
@@ -2358,7 +2352,7 @@
         <v>4</v>
       </c>
       <c r="AS9" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
@@ -2369,7 +2363,7 @@
         <v>153</v>
       </c>
       <c r="C10" s="9">
-        <v>8221</v>
+        <v>8397</v>
       </c>
       <c r="D10" s="9">
         <v>3</v>
@@ -2450,7 +2444,7 @@
         <v>163</v>
       </c>
       <c r="AD10" s="9">
-        <v>3535</v>
+        <v>3669</v>
       </c>
       <c r="AE10" s="10" t="s">
         <v>164</v>
@@ -2468,7 +2462,7 @@
         <v>166</v>
       </c>
       <c r="AJ10" s="9">
-        <v>1287</v>
+        <v>1329</v>
       </c>
       <c r="AK10" s="10" t="s">
         <v>167</v>
@@ -2506,7 +2500,7 @@
         <v>170</v>
       </c>
       <c r="C11" s="9">
-        <v>6390</v>
+        <v>6400</v>
       </c>
       <c r="D11" s="9">
         <v>2</v>
@@ -2572,31 +2566,31 @@
         <v>270</v>
       </c>
       <c r="Y11" s="10" t="s">
-        <v>114</v>
+        <v>176</v>
       </c>
       <c r="Z11" s="9">
         <v>29</v>
       </c>
       <c r="AA11" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AB11" s="9">
         <v>9</v>
       </c>
       <c r="AC11" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AD11" s="9">
-        <v>2879</v>
+        <v>2888</v>
       </c>
       <c r="AE11" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AF11" s="9">
         <v>73</v>
       </c>
       <c r="AG11" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AH11" s="9">
         <v>0</v>
@@ -2605,16 +2599,16 @@
         <v>97</v>
       </c>
       <c r="AJ11" s="9">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="AK11" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AL11" s="9">
         <v>39</v>
       </c>
       <c r="AM11" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AN11" s="9">
         <v>0</v>
@@ -2637,13 +2631,13 @@
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C12" s="9">
-        <v>5891</v>
+        <v>5899</v>
       </c>
       <c r="D12" s="9">
         <v>0</v>
@@ -2655,13 +2649,13 @@
         <v>152</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H12" s="9">
         <v>135</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J12" s="9">
         <v>0</v>
@@ -2673,7 +2667,7 @@
         <v>853</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N12" s="9">
         <v>0</v>
@@ -2697,7 +2691,7 @@
         <v>135</v>
       </c>
       <c r="U12" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="V12" s="9">
         <v>0</v>
@@ -2709,13 +2703,13 @@
         <v>145</v>
       </c>
       <c r="Y12" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Z12" s="9">
         <v>33</v>
       </c>
       <c r="AA12" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AB12" s="9">
         <v>0</v>
@@ -2724,16 +2718,16 @@
         <v>97</v>
       </c>
       <c r="AD12" s="9">
-        <v>2614</v>
+        <v>2622</v>
       </c>
       <c r="AE12" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AF12" s="9">
         <v>46</v>
       </c>
       <c r="AG12" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AH12" s="9">
         <v>0</v>
@@ -2745,13 +2739,13 @@
         <v>988</v>
       </c>
       <c r="AK12" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AL12" s="9">
         <v>757</v>
       </c>
       <c r="AM12" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AN12" s="9">
         <v>0</v>
@@ -2774,13 +2768,13 @@
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C13" s="9">
-        <v>3387</v>
+        <v>3429</v>
       </c>
       <c r="D13" s="9">
         <v>0</v>
@@ -2792,13 +2786,13 @@
         <v>144</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H13" s="9">
         <v>2</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J13" s="9">
         <v>0</v>
@@ -2810,7 +2804,7 @@
         <v>690</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N13" s="9">
         <v>1</v>
@@ -2822,19 +2816,19 @@
         <v>2</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="R13" s="9">
         <v>20</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="T13" s="9">
         <v>82</v>
       </c>
       <c r="U13" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="V13" s="9">
         <v>1</v>
@@ -2846,7 +2840,7 @@
         <v>99</v>
       </c>
       <c r="Y13" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Z13" s="9">
         <v>14</v>
@@ -2855,16 +2849,16 @@
         <v>138</v>
       </c>
       <c r="AB13" s="9">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="AC13" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AD13" s="9">
-        <v>1382</v>
+        <v>1390</v>
       </c>
       <c r="AE13" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF13" s="9">
         <v>12</v>
@@ -2879,22 +2873,22 @@
         <v>172</v>
       </c>
       <c r="AJ13" s="9">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="AK13" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AL13" s="9">
         <v>39</v>
       </c>
       <c r="AM13" s="10" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="AN13" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO13" s="10" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="AP13" s="9">
         <v>0</v>
@@ -2917,7 +2911,7 @@
         <v>205</v>
       </c>
       <c r="C14" s="9">
-        <v>2370</v>
+        <v>2376</v>
       </c>
       <c r="D14" s="9">
         <v>0</v>
@@ -2959,7 +2953,7 @@
         <v>7</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="R14" s="9">
         <v>28</v>
@@ -2989,7 +2983,7 @@
         <v>2</v>
       </c>
       <c r="AA14" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AB14" s="9">
         <v>0</v>
@@ -2998,7 +2992,7 @@
         <v>97</v>
       </c>
       <c r="AD14" s="9">
-        <v>1091</v>
+        <v>1096</v>
       </c>
       <c r="AE14" s="10" t="s">
         <v>213</v>
@@ -3007,7 +3001,7 @@
         <v>2</v>
       </c>
       <c r="AG14" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AH14" s="9">
         <v>0</v>
@@ -3016,7 +3010,7 @@
         <v>97</v>
       </c>
       <c r="AJ14" s="9">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AK14" s="10" t="s">
         <v>214</v>
@@ -3043,7 +3037,7 @@
         <v>2</v>
       </c>
       <c r="AS14" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
@@ -3054,13 +3048,13 @@
         <v>216</v>
       </c>
       <c r="C15" s="9">
-        <v>7731</v>
+        <v>7728</v>
       </c>
       <c r="D15" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F15" s="9">
         <v>255</v>
@@ -3072,7 +3066,7 @@
         <v>88</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J15" s="9">
         <v>0</v>
@@ -3135,7 +3129,7 @@
         <v>97</v>
       </c>
       <c r="AD15" s="9">
-        <v>3141</v>
+        <v>3142</v>
       </c>
       <c r="AE15" s="10" t="s">
         <v>223</v>
@@ -3147,10 +3141,10 @@
         <v>224</v>
       </c>
       <c r="AH15" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="10" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="AJ15" s="9">
         <v>1136</v>
@@ -3209,7 +3203,7 @@
         <v>6</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>230</v>
+        <v>162</v>
       </c>
       <c r="J16" s="9">
         <v>0</v>
@@ -3221,7 +3215,7 @@
         <v>378</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="N16" s="9">
         <v>0</v>
@@ -3239,7 +3233,7 @@
         <v>30</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="T16" s="9">
         <v>112</v>
@@ -3257,13 +3251,13 @@
         <v>91</v>
       </c>
       <c r="Y16" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Z16" s="9">
         <v>20</v>
       </c>
       <c r="AA16" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AB16" s="9">
         <v>4</v>
@@ -3275,13 +3269,13 @@
         <v>982</v>
       </c>
       <c r="AE16" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AF16" s="9">
         <v>35</v>
       </c>
       <c r="AG16" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AH16" s="9">
         <v>1</v>
@@ -3293,13 +3287,13 @@
         <v>429</v>
       </c>
       <c r="AK16" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AL16" s="9">
         <v>57</v>
       </c>
       <c r="AM16" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AN16" s="9">
         <v>0</v>
@@ -3322,31 +3316,31 @@
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>239</v>
-      </c>
       <c r="C17" s="9">
-        <v>4278</v>
+        <v>4334</v>
       </c>
       <c r="D17" s="9">
         <v>1</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F17" s="9">
         <v>198</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H17" s="9">
         <v>26</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>181</v>
+        <v>241</v>
       </c>
       <c r="J17" s="9">
         <v>0</v>
@@ -3370,31 +3364,31 @@
         <v>22</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>243</v>
+        <v>144</v>
       </c>
       <c r="R17" s="9">
         <v>29</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>244</v>
+        <v>115</v>
       </c>
       <c r="T17" s="9">
         <v>30</v>
       </c>
       <c r="U17" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="V17" s="9">
         <v>9</v>
       </c>
       <c r="W17" s="10" t="s">
-        <v>246</v>
+        <v>160</v>
       </c>
       <c r="X17" s="9">
         <v>74</v>
       </c>
       <c r="Y17" s="10" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Z17" s="9">
         <v>2</v>
@@ -3409,16 +3403,16 @@
         <v>172</v>
       </c>
       <c r="AD17" s="9">
-        <v>2126</v>
+        <v>2177</v>
       </c>
       <c r="AE17" s="10" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="AF17" s="9">
         <v>42</v>
       </c>
       <c r="AG17" s="10" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="AH17" s="9">
         <v>3</v>
@@ -3427,16 +3421,16 @@
         <v>166</v>
       </c>
       <c r="AJ17" s="9">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="AK17" s="10" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AL17" s="9">
         <v>220</v>
       </c>
       <c r="AM17" s="10" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AN17" s="9">
         <v>0</v>
@@ -3459,13 +3453,13 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C18" s="9">
-        <v>4970</v>
+        <v>5014</v>
       </c>
       <c r="D18" s="9">
         <v>0</v>
@@ -3477,7 +3471,7 @@
         <v>212</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>254</v>
+        <v>114</v>
       </c>
       <c r="H18" s="9">
         <v>6</v>
@@ -3495,7 +3489,7 @@
         <v>1131</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="N18" s="9">
         <v>0</v>
@@ -3507,19 +3501,19 @@
         <v>8</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="R18" s="9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="T18" s="9">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="U18" s="10" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="V18" s="9">
         <v>2</v>
@@ -3531,13 +3525,13 @@
         <v>91</v>
       </c>
       <c r="Y18" s="10" t="s">
-        <v>259</v>
+        <v>201</v>
       </c>
       <c r="Z18" s="9">
         <v>14</v>
       </c>
       <c r="AA18" s="10" t="s">
-        <v>162</v>
+        <v>255</v>
       </c>
       <c r="AB18" s="9">
         <v>0</v>
@@ -3546,10 +3540,10 @@
         <v>97</v>
       </c>
       <c r="AD18" s="9">
-        <v>2263</v>
+        <v>2289</v>
       </c>
       <c r="AE18" s="10" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="AF18" s="9">
         <v>12</v>
@@ -3564,16 +3558,16 @@
         <v>97</v>
       </c>
       <c r="AJ18" s="9">
-        <v>1088</v>
+        <v>1104</v>
       </c>
       <c r="AK18" s="10" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="AL18" s="9">
         <v>43</v>
       </c>
       <c r="AM18" s="10" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="AN18" s="9">
         <v>0</v>
@@ -3596,13 +3590,13 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C19" s="9">
-        <v>5618</v>
+        <v>5695</v>
       </c>
       <c r="D19" s="9">
         <v>0</v>
@@ -3614,13 +3608,13 @@
         <v>248</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="H19" s="9">
         <v>18</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>266</v>
+        <v>105</v>
       </c>
       <c r="J19" s="9">
         <v>0</v>
@@ -3632,7 +3626,7 @@
         <v>1592</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="N19" s="9">
         <v>0</v>
@@ -3650,7 +3644,7 @@
         <v>18</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>266</v>
+        <v>105</v>
       </c>
       <c r="T19" s="9">
         <v>17</v>
@@ -3668,7 +3662,7 @@
         <v>180</v>
       </c>
       <c r="Y19" s="10" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="Z19" s="9">
         <v>4</v>
@@ -3683,10 +3677,10 @@
         <v>97</v>
       </c>
       <c r="AD19" s="9">
-        <v>2522</v>
+        <v>2580</v>
       </c>
       <c r="AE19" s="10" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="AF19" s="9">
         <v>26</v>
@@ -3701,16 +3695,16 @@
         <v>97</v>
       </c>
       <c r="AJ19" s="9">
-        <v>845</v>
+        <v>864</v>
       </c>
       <c r="AK19" s="10" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="AL19" s="9">
         <v>146</v>
       </c>
       <c r="AM19" s="10" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AN19" s="9">
         <v>0</v>
@@ -3733,13 +3727,13 @@
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C20" s="9">
-        <v>662</v>
+        <v>686</v>
       </c>
       <c r="D20" s="9">
         <v>0</v>
@@ -3751,13 +3745,13 @@
         <v>47</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="H20" s="9">
         <v>6</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="J20" s="9">
         <v>0</v>
@@ -3769,7 +3763,7 @@
         <v>66</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="N20" s="9">
         <v>0</v>
@@ -3781,55 +3775,55 @@
         <v>4</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>96</v>
+        <v>198</v>
       </c>
       <c r="R20" s="9">
         <v>4</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>96</v>
+        <v>198</v>
       </c>
       <c r="T20" s="9">
         <v>41</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="V20" s="9">
         <v>8</v>
       </c>
       <c r="W20" s="10" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="X20" s="9">
         <v>46</v>
       </c>
       <c r="Y20" s="10" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="Z20" s="9">
         <v>90</v>
       </c>
       <c r="AA20" s="10" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="AB20" s="9">
         <v>4</v>
       </c>
       <c r="AC20" s="10" t="s">
-        <v>96</v>
+        <v>198</v>
       </c>
       <c r="AD20" s="9">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="AE20" s="10" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="AF20" s="9">
         <v>12</v>
       </c>
       <c r="AG20" s="10" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="AH20" s="9">
         <v>0</v>
@@ -3838,16 +3832,16 @@
         <v>97</v>
       </c>
       <c r="AJ20" s="9">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AK20" s="10" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="AL20" s="9">
         <v>19</v>
       </c>
       <c r="AM20" s="10" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="AN20" s="9">
         <v>0</v>
@@ -3865,18 +3859,18 @@
         <v>2</v>
       </c>
       <c r="AS20" s="10" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C21" s="9">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="D21" s="9">
         <v>0</v>
@@ -3888,13 +3882,13 @@
         <v>40</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="H21" s="9">
         <v>6</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="J21" s="9">
         <v>0</v>
@@ -3906,7 +3900,7 @@
         <v>174</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="N21" s="9">
         <v>0</v>
@@ -3924,13 +3918,13 @@
         <v>9</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>96</v>
+        <v>241</v>
       </c>
       <c r="T21" s="9">
         <v>35</v>
       </c>
       <c r="U21" s="10" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="V21" s="9">
         <v>1</v>
@@ -3942,31 +3936,31 @@
         <v>42</v>
       </c>
       <c r="Y21" s="10" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="Z21" s="9">
         <v>39</v>
       </c>
       <c r="AA21" s="10" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="AB21" s="9">
         <v>15</v>
       </c>
       <c r="AC21" s="10" t="s">
-        <v>200</v>
+        <v>288</v>
       </c>
       <c r="AD21" s="9">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AE21" s="10" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AF21" s="9">
         <v>3</v>
       </c>
       <c r="AG21" s="10" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AH21" s="9">
         <v>0</v>
@@ -3978,13 +3972,13 @@
         <v>120</v>
       </c>
       <c r="AK21" s="10" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AL21" s="9">
         <v>384</v>
       </c>
       <c r="AM21" s="10" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AN21" s="9">
         <v>0</v>
@@ -4007,16 +4001,16 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C22" s="12">
-        <v>66310</v>
+        <v>66820</v>
       </c>
       <c r="D22" s="12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>94</v>
@@ -4058,13 +4052,13 @@
         <v>99</v>
       </c>
       <c r="R22" s="12">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="S22" s="13" t="s">
         <v>100</v>
       </c>
       <c r="T22" s="12">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="U22" s="13" t="s">
         <v>101</v>
@@ -4088,13 +4082,13 @@
         <v>104</v>
       </c>
       <c r="AB22" s="12">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="AC22" s="13" t="s">
         <v>105</v>
       </c>
       <c r="AD22" s="12">
-        <v>28917</v>
+        <v>29290</v>
       </c>
       <c r="AE22" s="13" t="s">
         <v>106</v>
@@ -4106,13 +4100,13 @@
         <v>107</v>
       </c>
       <c r="AH22" s="12">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI22" s="13" t="s">
         <v>108</v>
       </c>
       <c r="AJ22" s="12">
-        <v>10757</v>
+        <v>10867</v>
       </c>
       <c r="AK22" s="13" t="s">
         <v>109</v>
@@ -4124,7 +4118,7 @@
         <v>110</v>
       </c>
       <c r="AN22" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO22" s="13" t="s">
         <v>97</v>
